--- a/Documentation/Planification_TPI_Ryan-Bersier.xlsx
+++ b/Documentation/Planification_TPI_Ryan-Bersier.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\4eme\T4\TPI\Documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc23owx\Documents\TPI_Horloge-Led-Capteurs\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A6E91AE-02FA-40A9-926D-D1D893AC13FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D09FC8A7-CFF6-4010-84C5-31985071EF70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-12825" windowWidth="16440" windowHeight="28320" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planification" sheetId="1" r:id="rId1"/>
@@ -907,10 +907,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -921,27 +942,6 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1218,3112 +1218,3112 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:676" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="49"/>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="50" t="s">
+      <c r="A1" s="56"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="57" t="s">
         <v>117</v>
       </c>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
-      <c r="T1" s="50"/>
-      <c r="U1" s="50"/>
-      <c r="V1" s="50"/>
-      <c r="W1" s="50"/>
-      <c r="X1" s="50"/>
-      <c r="Y1" s="50"/>
-      <c r="Z1" s="50"/>
-      <c r="AA1" s="50"/>
-      <c r="AB1" s="50"/>
-      <c r="AC1" s="50"/>
-      <c r="AD1" s="50"/>
-      <c r="AE1" s="50"/>
-      <c r="AF1" s="50"/>
-      <c r="AG1" s="50"/>
-      <c r="AH1" s="50"/>
-      <c r="AI1" s="50"/>
-      <c r="AJ1" s="50"/>
-      <c r="AK1" s="50"/>
-      <c r="AL1" s="50"/>
-      <c r="AM1" s="50"/>
-      <c r="AN1" s="50"/>
-      <c r="AO1" s="50"/>
-      <c r="AP1" s="50"/>
-      <c r="AQ1" s="50"/>
-      <c r="AR1" s="50"/>
-      <c r="AS1" s="50"/>
-      <c r="AT1" s="50"/>
-      <c r="AU1" s="50"/>
-      <c r="AV1" s="50"/>
-      <c r="AW1" s="50"/>
-      <c r="AX1" s="50"/>
-      <c r="AY1" s="50"/>
-      <c r="AZ1" s="50"/>
-      <c r="BA1" s="50"/>
-      <c r="BB1" s="50"/>
-      <c r="BC1" s="50"/>
-      <c r="BD1" s="50"/>
-      <c r="BE1" s="50"/>
-      <c r="BF1" s="50"/>
-      <c r="BG1" s="50"/>
-      <c r="BH1" s="50"/>
-      <c r="BI1" s="50"/>
-      <c r="BJ1" s="50"/>
-      <c r="BK1" s="50"/>
-      <c r="BL1" s="50"/>
-      <c r="BM1" s="50"/>
-      <c r="BN1" s="50"/>
-      <c r="BO1" s="50"/>
-      <c r="BP1" s="50"/>
-      <c r="BQ1" s="50"/>
-      <c r="BR1" s="50"/>
-      <c r="BS1" s="50"/>
-      <c r="BT1" s="50"/>
-      <c r="BU1" s="50"/>
-      <c r="BV1" s="50"/>
-      <c r="BW1" s="50"/>
-      <c r="BX1" s="50"/>
-      <c r="BY1" s="50"/>
-      <c r="BZ1" s="50"/>
-      <c r="CA1" s="50"/>
-      <c r="CB1" s="50"/>
-      <c r="CC1" s="50"/>
-      <c r="CD1" s="50"/>
-      <c r="CE1" s="50"/>
-      <c r="CF1" s="50"/>
-      <c r="CG1" s="50"/>
-      <c r="CH1" s="50"/>
-      <c r="CI1" s="50"/>
-      <c r="CJ1" s="50"/>
-      <c r="CK1" s="50"/>
-      <c r="CL1" s="50"/>
-      <c r="CM1" s="50"/>
-      <c r="CN1" s="50"/>
-      <c r="CO1" s="50"/>
-      <c r="CP1" s="50"/>
-      <c r="CQ1" s="50"/>
-      <c r="CR1" s="50"/>
-      <c r="CS1" s="50"/>
-      <c r="CT1" s="50"/>
-      <c r="CU1" s="50"/>
-      <c r="CV1" s="50"/>
-      <c r="CW1" s="50"/>
-      <c r="CX1" s="50"/>
-      <c r="CY1" s="50"/>
-      <c r="CZ1" s="50"/>
-      <c r="DA1" s="50"/>
-      <c r="DB1" s="50"/>
-      <c r="DC1" s="50"/>
-      <c r="DD1" s="50"/>
-      <c r="DE1" s="50"/>
-      <c r="DF1" s="50"/>
-      <c r="DG1" s="50"/>
-      <c r="DH1" s="50"/>
-      <c r="DI1" s="50"/>
-      <c r="DJ1" s="50"/>
-      <c r="DK1" s="50"/>
-      <c r="DL1" s="50"/>
-      <c r="DM1" s="50"/>
-      <c r="DN1" s="50"/>
-      <c r="DO1" s="50"/>
-      <c r="DP1" s="50"/>
-      <c r="DQ1" s="50"/>
-      <c r="DR1" s="50"/>
-      <c r="DS1" s="50"/>
-      <c r="DT1" s="50"/>
-      <c r="DU1" s="50"/>
-      <c r="DV1" s="50"/>
-      <c r="DW1" s="50"/>
-      <c r="DX1" s="50"/>
-      <c r="DY1" s="50"/>
-      <c r="DZ1" s="50"/>
-      <c r="EA1" s="50"/>
-      <c r="EB1" s="50"/>
-      <c r="EC1" s="50"/>
-      <c r="ED1" s="50"/>
-      <c r="EE1" s="50"/>
-      <c r="EF1" s="50"/>
-      <c r="EG1" s="50"/>
-      <c r="EH1" s="50"/>
-      <c r="EI1" s="50"/>
-      <c r="EJ1" s="50"/>
-      <c r="EK1" s="50"/>
-      <c r="EL1" s="50"/>
-      <c r="EM1" s="50"/>
-      <c r="EN1" s="50"/>
-      <c r="EO1" s="50"/>
-      <c r="EP1" s="50"/>
-      <c r="EQ1" s="50"/>
-      <c r="ER1" s="50"/>
-      <c r="ES1" s="50"/>
-      <c r="ET1" s="50"/>
-      <c r="EU1" s="50"/>
-      <c r="EV1" s="50"/>
-      <c r="EW1" s="50"/>
-      <c r="EX1" s="50"/>
-      <c r="EY1" s="50"/>
-      <c r="EZ1" s="50"/>
-      <c r="FA1" s="50"/>
-      <c r="FB1" s="50"/>
-      <c r="FC1" s="50"/>
-      <c r="FD1" s="50"/>
-      <c r="FE1" s="50"/>
-      <c r="FF1" s="50"/>
-      <c r="FG1" s="50"/>
-      <c r="FH1" s="50"/>
-      <c r="FI1" s="50"/>
-      <c r="FJ1" s="50"/>
-      <c r="FK1" s="50"/>
-      <c r="FL1" s="50"/>
-      <c r="FM1" s="50"/>
-      <c r="FN1" s="50"/>
-      <c r="FO1" s="50"/>
-      <c r="FP1" s="50"/>
-      <c r="FQ1" s="50"/>
-      <c r="FR1" s="50"/>
-      <c r="FS1" s="50"/>
-      <c r="FT1" s="50"/>
-      <c r="FU1" s="50"/>
-      <c r="FV1" s="50"/>
-      <c r="FW1" s="50"/>
-      <c r="FX1" s="50"/>
-      <c r="FY1" s="50"/>
-      <c r="FZ1" s="50"/>
-      <c r="GA1" s="50"/>
-      <c r="GB1" s="50"/>
-      <c r="GC1" s="50"/>
-      <c r="GD1" s="50"/>
-      <c r="GE1" s="50"/>
-      <c r="GF1" s="50"/>
-      <c r="GG1" s="50"/>
-      <c r="GH1" s="50"/>
-      <c r="GI1" s="50"/>
-      <c r="GJ1" s="50"/>
-      <c r="GK1" s="50"/>
-      <c r="GL1" s="50"/>
-      <c r="GM1" s="50"/>
-      <c r="GN1" s="50"/>
-      <c r="GO1" s="50"/>
-      <c r="GP1" s="50"/>
-      <c r="GQ1" s="50"/>
-      <c r="GR1" s="50"/>
-      <c r="GS1" s="50"/>
-      <c r="GT1" s="50"/>
-      <c r="GU1" s="50"/>
-      <c r="GV1" s="50"/>
-      <c r="GW1" s="50"/>
-      <c r="GX1" s="50"/>
-      <c r="GY1" s="50"/>
-      <c r="GZ1" s="50"/>
-      <c r="HA1" s="50"/>
-      <c r="HB1" s="50"/>
-      <c r="HC1" s="50"/>
-      <c r="HD1" s="50"/>
-      <c r="HE1" s="50"/>
-      <c r="HF1" s="50"/>
-      <c r="HG1" s="50"/>
-      <c r="HH1" s="50"/>
-      <c r="HI1" s="50"/>
-      <c r="HJ1" s="50"/>
-      <c r="HK1" s="50"/>
-      <c r="HL1" s="50"/>
-      <c r="HM1" s="50"/>
-      <c r="HN1" s="50"/>
-      <c r="HO1" s="50"/>
-      <c r="HP1" s="50"/>
-      <c r="HQ1" s="50"/>
-      <c r="HR1" s="50"/>
-      <c r="HS1" s="50"/>
-      <c r="HT1" s="50"/>
-      <c r="HU1" s="50"/>
-      <c r="HV1" s="50"/>
-      <c r="HW1" s="50"/>
-      <c r="HX1" s="50"/>
-      <c r="HY1" s="50"/>
-      <c r="HZ1" s="50"/>
-      <c r="IA1" s="50"/>
-      <c r="IB1" s="50"/>
-      <c r="IC1" s="50"/>
-      <c r="ID1" s="50"/>
-      <c r="IE1" s="50"/>
-      <c r="IF1" s="50"/>
-      <c r="IG1" s="50"/>
-      <c r="IH1" s="50"/>
-      <c r="II1" s="50"/>
-      <c r="IJ1" s="50"/>
-      <c r="IK1" s="50"/>
-      <c r="IL1" s="50"/>
-      <c r="IM1" s="50"/>
-      <c r="IN1" s="50"/>
-      <c r="IO1" s="50"/>
-      <c r="IP1" s="50"/>
-      <c r="IQ1" s="50"/>
-      <c r="IR1" s="50"/>
-      <c r="IS1" s="50"/>
-      <c r="IT1" s="50"/>
-      <c r="IU1" s="50"/>
-      <c r="IV1" s="50"/>
-      <c r="IW1" s="50"/>
-      <c r="IX1" s="50"/>
-      <c r="IY1" s="50"/>
-      <c r="IZ1" s="50"/>
-      <c r="JA1" s="50"/>
-      <c r="JB1" s="50"/>
-      <c r="JC1" s="50"/>
-      <c r="JD1" s="50"/>
-      <c r="JE1" s="50"/>
-      <c r="JF1" s="50"/>
-      <c r="JG1" s="50"/>
-      <c r="JH1" s="50"/>
-      <c r="JI1" s="50"/>
-      <c r="JJ1" s="50"/>
-      <c r="JK1" s="50"/>
-      <c r="JL1" s="50"/>
-      <c r="JM1" s="50"/>
-      <c r="JN1" s="50"/>
-      <c r="JO1" s="50"/>
-      <c r="JP1" s="50"/>
-      <c r="JQ1" s="50"/>
-      <c r="JR1" s="50"/>
-      <c r="JS1" s="50"/>
-      <c r="JT1" s="50"/>
-      <c r="JU1" s="50"/>
-      <c r="JV1" s="50"/>
-      <c r="JW1" s="50"/>
-      <c r="JX1" s="50"/>
-      <c r="JY1" s="50"/>
-      <c r="JZ1" s="50"/>
-      <c r="KA1" s="50"/>
-      <c r="KB1" s="50"/>
-      <c r="KC1" s="50"/>
-      <c r="KD1" s="50"/>
-      <c r="KE1" s="50"/>
-      <c r="KF1" s="50"/>
-      <c r="KG1" s="50"/>
-      <c r="KH1" s="50"/>
-      <c r="KI1" s="50"/>
-      <c r="KJ1" s="50"/>
-      <c r="KK1" s="50"/>
-      <c r="KL1" s="50"/>
-      <c r="KM1" s="50"/>
-      <c r="KN1" s="50"/>
-      <c r="KO1" s="50"/>
-      <c r="KP1" s="50"/>
-      <c r="KQ1" s="50"/>
-      <c r="KR1" s="50"/>
-      <c r="KS1" s="50"/>
-      <c r="KT1" s="50"/>
-      <c r="KU1" s="50"/>
-      <c r="KV1" s="50"/>
-      <c r="KW1" s="50"/>
-      <c r="KX1" s="50"/>
-      <c r="KY1" s="50"/>
-      <c r="KZ1" s="50"/>
-      <c r="LA1" s="50"/>
-      <c r="LB1" s="50"/>
-      <c r="LC1" s="50"/>
-      <c r="LD1" s="50"/>
-      <c r="LE1" s="50"/>
-      <c r="LF1" s="50"/>
-      <c r="LG1" s="50"/>
-      <c r="LH1" s="50"/>
-      <c r="LI1" s="50"/>
-      <c r="LJ1" s="50"/>
-      <c r="LK1" s="50"/>
-      <c r="LL1" s="50"/>
-      <c r="LM1" s="50"/>
-      <c r="LN1" s="50"/>
-      <c r="LO1" s="50"/>
-      <c r="LP1" s="50"/>
-      <c r="LQ1" s="50"/>
-      <c r="LR1" s="50"/>
-      <c r="LS1" s="50"/>
-      <c r="LT1" s="50"/>
-      <c r="LU1" s="50"/>
-      <c r="LV1" s="50"/>
-      <c r="LW1" s="50"/>
-      <c r="LX1" s="50"/>
-      <c r="LY1" s="50"/>
-      <c r="LZ1" s="50"/>
-      <c r="MA1" s="50"/>
-      <c r="MB1" s="50"/>
-      <c r="MC1" s="50"/>
-      <c r="MD1" s="50"/>
-      <c r="ME1" s="50"/>
-      <c r="MF1" s="50"/>
-      <c r="MG1" s="50"/>
-      <c r="MH1" s="50"/>
-      <c r="MI1" s="50"/>
-      <c r="MJ1" s="50"/>
-      <c r="MK1" s="50"/>
-      <c r="ML1" s="50"/>
-      <c r="MM1" s="50"/>
-      <c r="MN1" s="50"/>
-      <c r="MO1" s="50"/>
-      <c r="MP1" s="50"/>
-      <c r="MQ1" s="50"/>
-      <c r="MR1" s="50"/>
-      <c r="MS1" s="50"/>
-      <c r="MT1" s="50"/>
-      <c r="MU1" s="50"/>
-      <c r="MV1" s="50"/>
-      <c r="MW1" s="50"/>
-      <c r="MX1" s="50"/>
-      <c r="MY1" s="50"/>
-      <c r="MZ1" s="50"/>
-      <c r="NA1" s="50"/>
-      <c r="NB1" s="50"/>
-      <c r="NC1" s="50"/>
-      <c r="ND1" s="50"/>
-      <c r="NE1" s="50"/>
-      <c r="NF1" s="50"/>
-      <c r="NG1" s="50"/>
-      <c r="NH1" s="50"/>
-      <c r="NI1" s="50"/>
-      <c r="NJ1" s="50"/>
-      <c r="NK1" s="50"/>
-      <c r="NL1" s="50"/>
-      <c r="NM1" s="50"/>
-      <c r="NN1" s="50"/>
-      <c r="NO1" s="50"/>
-      <c r="NP1" s="50"/>
-      <c r="NQ1" s="50"/>
-      <c r="NR1" s="50"/>
-      <c r="NS1" s="50"/>
-      <c r="NT1" s="50"/>
-      <c r="NU1" s="50"/>
-      <c r="NV1" s="50"/>
-      <c r="NW1" s="50"/>
-      <c r="NX1" s="50"/>
-      <c r="NY1" s="50"/>
-      <c r="NZ1" s="50"/>
-      <c r="OA1" s="50"/>
-      <c r="OB1" s="50"/>
-      <c r="OC1" s="50"/>
-      <c r="OD1" s="50"/>
-      <c r="OE1" s="50"/>
-      <c r="OF1" s="50"/>
-      <c r="OG1" s="50"/>
-      <c r="OH1" s="50"/>
-      <c r="OI1" s="50"/>
-      <c r="OJ1" s="50"/>
-      <c r="OK1" s="50"/>
-      <c r="OL1" s="50"/>
-      <c r="OM1" s="50"/>
-      <c r="ON1" s="50"/>
-      <c r="OO1" s="50"/>
-      <c r="OP1" s="50"/>
-      <c r="OQ1" s="50"/>
-      <c r="OR1" s="50"/>
-      <c r="OS1" s="50"/>
-      <c r="OT1" s="50"/>
-      <c r="OU1" s="50"/>
-      <c r="OV1" s="50"/>
-      <c r="OW1" s="50"/>
-      <c r="OX1" s="50"/>
-      <c r="OY1" s="50"/>
-      <c r="OZ1" s="50"/>
-      <c r="PA1" s="50"/>
-      <c r="PB1" s="50"/>
-      <c r="PC1" s="50"/>
-      <c r="PD1" s="50"/>
-      <c r="PE1" s="50"/>
-      <c r="PF1" s="50"/>
-      <c r="PG1" s="50"/>
-      <c r="PH1" s="50"/>
-      <c r="PI1" s="50"/>
-      <c r="PJ1" s="50"/>
-      <c r="PK1" s="50"/>
-      <c r="PL1" s="50"/>
-      <c r="PM1" s="50"/>
-      <c r="PN1" s="50"/>
-      <c r="PO1" s="50"/>
-      <c r="PP1" s="50"/>
-      <c r="PQ1" s="50"/>
-      <c r="PR1" s="50"/>
-      <c r="PS1" s="50"/>
-      <c r="PT1" s="50"/>
-      <c r="PU1" s="50"/>
-      <c r="PV1" s="50"/>
-      <c r="PW1" s="50"/>
-      <c r="PX1" s="50"/>
-      <c r="PY1" s="50"/>
-      <c r="PZ1" s="50"/>
-      <c r="QA1" s="50"/>
-      <c r="QB1" s="50"/>
-      <c r="QC1" s="50"/>
-      <c r="QD1" s="50"/>
-      <c r="QE1" s="50"/>
-      <c r="QF1" s="50"/>
-      <c r="QG1" s="50"/>
-      <c r="QH1" s="50"/>
-      <c r="QI1" s="50"/>
-      <c r="QJ1" s="50"/>
-      <c r="QK1" s="50"/>
-      <c r="QL1" s="50"/>
-      <c r="QM1" s="50"/>
-      <c r="QN1" s="50"/>
-      <c r="QO1" s="50"/>
-      <c r="QP1" s="50"/>
-      <c r="QQ1" s="50"/>
-      <c r="QR1" s="50"/>
-      <c r="QS1" s="50"/>
-      <c r="QT1" s="50"/>
-      <c r="QU1" s="50"/>
-      <c r="QV1" s="50"/>
-      <c r="QW1" s="50"/>
-      <c r="QX1" s="50"/>
-      <c r="QY1" s="50"/>
-      <c r="QZ1" s="50"/>
-      <c r="RA1" s="50"/>
-      <c r="RB1" s="50"/>
-      <c r="RC1" s="50"/>
-      <c r="RD1" s="50"/>
-      <c r="RE1" s="50"/>
-      <c r="RF1" s="50"/>
-      <c r="RG1" s="50"/>
-      <c r="RH1" s="50"/>
-      <c r="RI1" s="50"/>
-      <c r="RJ1" s="50"/>
-      <c r="RK1" s="50"/>
-      <c r="RL1" s="50"/>
-      <c r="RM1" s="50"/>
-      <c r="RN1" s="50"/>
-      <c r="RO1" s="50"/>
-      <c r="RP1" s="50"/>
-      <c r="RQ1" s="50"/>
-      <c r="RR1" s="50"/>
-      <c r="RS1" s="50"/>
-      <c r="RT1" s="50"/>
-      <c r="RU1" s="50"/>
-      <c r="RV1" s="50"/>
-      <c r="RW1" s="50"/>
-      <c r="RX1" s="50"/>
-      <c r="RY1" s="50"/>
-      <c r="RZ1" s="50"/>
-      <c r="SA1" s="50"/>
-      <c r="SB1" s="50"/>
-      <c r="SC1" s="50"/>
-      <c r="SD1" s="50"/>
-      <c r="SE1" s="50"/>
-      <c r="SF1" s="50"/>
-      <c r="SG1" s="50"/>
-      <c r="SH1" s="50"/>
-      <c r="SI1" s="50"/>
-      <c r="SJ1" s="50"/>
-      <c r="SK1" s="50"/>
-      <c r="SL1" s="50"/>
-      <c r="SM1" s="50"/>
-      <c r="SN1" s="50"/>
-      <c r="SO1" s="50"/>
-      <c r="SP1" s="50"/>
-      <c r="SQ1" s="50"/>
-      <c r="SR1" s="50"/>
-      <c r="SS1" s="50"/>
-      <c r="ST1" s="50"/>
-      <c r="SU1" s="50"/>
-      <c r="SV1" s="50"/>
-      <c r="SW1" s="50"/>
-      <c r="SX1" s="50"/>
-      <c r="SY1" s="50"/>
-      <c r="SZ1" s="50"/>
-      <c r="TA1" s="50"/>
-      <c r="TB1" s="50"/>
-      <c r="TC1" s="50"/>
-      <c r="TD1" s="50"/>
-      <c r="TE1" s="50"/>
-      <c r="TF1" s="50"/>
-      <c r="TG1" s="50"/>
-      <c r="TH1" s="50"/>
-      <c r="TI1" s="50"/>
-      <c r="TJ1" s="50"/>
-      <c r="TK1" s="50"/>
-      <c r="TL1" s="50"/>
-      <c r="TM1" s="50"/>
-      <c r="TN1" s="50"/>
-      <c r="TO1" s="50"/>
-      <c r="TP1" s="50"/>
-      <c r="TQ1" s="50"/>
-      <c r="TR1" s="50"/>
-      <c r="TS1" s="50"/>
-      <c r="TT1" s="50"/>
-      <c r="TU1" s="50"/>
-      <c r="TV1" s="50"/>
-      <c r="TW1" s="50"/>
-      <c r="TX1" s="50"/>
-      <c r="TY1" s="50"/>
-      <c r="TZ1" s="50"/>
-      <c r="UA1" s="50"/>
-      <c r="UB1" s="50"/>
-      <c r="UC1" s="50"/>
-      <c r="UD1" s="50"/>
-      <c r="UE1" s="50"/>
-      <c r="UF1" s="50"/>
-      <c r="UG1" s="50"/>
-      <c r="UH1" s="50"/>
-      <c r="UI1" s="50"/>
-      <c r="UJ1" s="50"/>
-      <c r="UK1" s="50"/>
-      <c r="UL1" s="50"/>
-      <c r="UM1" s="50"/>
-      <c r="UN1" s="50"/>
-      <c r="UO1" s="50"/>
-      <c r="UP1" s="50"/>
-      <c r="UQ1" s="50"/>
-      <c r="UR1" s="50"/>
-      <c r="US1" s="50"/>
-      <c r="UT1" s="50"/>
-      <c r="UU1" s="50"/>
-      <c r="UV1" s="50"/>
-      <c r="UW1" s="50"/>
-      <c r="UX1" s="50"/>
-      <c r="UY1" s="50"/>
-      <c r="UZ1" s="50"/>
-      <c r="VA1" s="50"/>
-      <c r="VB1" s="50"/>
-      <c r="VC1" s="50"/>
-      <c r="VD1" s="50"/>
-      <c r="VE1" s="50"/>
-      <c r="VF1" s="50"/>
-      <c r="VG1" s="50"/>
-      <c r="VH1" s="50"/>
-      <c r="VI1" s="50"/>
-      <c r="VJ1" s="50"/>
-      <c r="VK1" s="50"/>
-      <c r="VL1" s="50"/>
-      <c r="VM1" s="50"/>
-      <c r="VN1" s="50"/>
-      <c r="VO1" s="50"/>
-      <c r="VP1" s="50"/>
-      <c r="VQ1" s="50"/>
-      <c r="VR1" s="50"/>
-      <c r="VS1" s="50"/>
-      <c r="VT1" s="50"/>
-      <c r="VU1" s="50"/>
-      <c r="VV1" s="50"/>
-      <c r="VW1" s="50"/>
-      <c r="VX1" s="50"/>
-      <c r="VY1" s="50"/>
-      <c r="VZ1" s="50"/>
-      <c r="WA1" s="50"/>
-      <c r="WB1" s="50"/>
-      <c r="WC1" s="50"/>
-      <c r="WD1" s="50"/>
-      <c r="WE1" s="50"/>
-      <c r="WF1" s="50"/>
-      <c r="WG1" s="50"/>
-      <c r="WH1" s="50"/>
-      <c r="WI1" s="50"/>
-      <c r="WJ1" s="50"/>
-      <c r="WK1" s="50"/>
-      <c r="WL1" s="50"/>
-      <c r="WM1" s="50"/>
-      <c r="WN1" s="50"/>
-      <c r="WO1" s="50"/>
-      <c r="WP1" s="50"/>
-      <c r="WQ1" s="50"/>
-      <c r="WR1" s="50"/>
-      <c r="WS1" s="50"/>
-      <c r="WT1" s="50"/>
-      <c r="WU1" s="50"/>
-      <c r="WV1" s="50"/>
-      <c r="WW1" s="50"/>
-      <c r="WX1" s="50"/>
-      <c r="WY1" s="50"/>
-      <c r="WZ1" s="50"/>
-      <c r="XA1" s="50"/>
-      <c r="XB1" s="50"/>
-      <c r="XC1" s="50"/>
-      <c r="XD1" s="50"/>
-      <c r="XE1" s="50"/>
-      <c r="XF1" s="50"/>
-      <c r="XG1" s="50"/>
-      <c r="XH1" s="50"/>
-      <c r="XI1" s="50"/>
-      <c r="XJ1" s="50"/>
-      <c r="XK1" s="50"/>
-      <c r="XL1" s="50"/>
-      <c r="XM1" s="50"/>
-      <c r="XN1" s="50"/>
-      <c r="XO1" s="50"/>
-      <c r="XP1" s="50"/>
-      <c r="XQ1" s="50"/>
-      <c r="XR1" s="50"/>
-      <c r="XS1" s="50"/>
-      <c r="XT1" s="50"/>
-      <c r="XU1" s="50"/>
-      <c r="XV1" s="50"/>
-      <c r="XW1" s="50"/>
-      <c r="XX1" s="50"/>
-      <c r="XY1" s="50"/>
-      <c r="XZ1" s="50"/>
-      <c r="YA1" s="50"/>
-      <c r="YB1" s="50"/>
-      <c r="YC1" s="50"/>
-      <c r="YD1" s="50"/>
-      <c r="YE1" s="50"/>
-      <c r="YF1" s="50"/>
-      <c r="YG1" s="50"/>
-      <c r="YH1" s="50"/>
-      <c r="YI1" s="50"/>
-      <c r="YJ1" s="50"/>
-      <c r="YK1" s="50"/>
-      <c r="YL1" s="50"/>
-      <c r="YM1" s="50"/>
-      <c r="YN1" s="50"/>
-      <c r="YO1" s="50"/>
-      <c r="YP1" s="50"/>
-      <c r="YQ1" s="50"/>
-      <c r="YR1" s="50"/>
-      <c r="YS1" s="50"/>
-      <c r="YT1" s="50"/>
-      <c r="YU1" s="50"/>
-      <c r="YV1" s="50"/>
-      <c r="YW1" s="50"/>
-      <c r="YX1" s="50"/>
-      <c r="YY1" s="50"/>
-      <c r="YZ1" s="50"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="57"/>
+      <c r="N1" s="57"/>
+      <c r="O1" s="57"/>
+      <c r="P1" s="57"/>
+      <c r="Q1" s="57"/>
+      <c r="R1" s="57"/>
+      <c r="S1" s="57"/>
+      <c r="T1" s="57"/>
+      <c r="U1" s="57"/>
+      <c r="V1" s="57"/>
+      <c r="W1" s="57"/>
+      <c r="X1" s="57"/>
+      <c r="Y1" s="57"/>
+      <c r="Z1" s="57"/>
+      <c r="AA1" s="57"/>
+      <c r="AB1" s="57"/>
+      <c r="AC1" s="57"/>
+      <c r="AD1" s="57"/>
+      <c r="AE1" s="57"/>
+      <c r="AF1" s="57"/>
+      <c r="AG1" s="57"/>
+      <c r="AH1" s="57"/>
+      <c r="AI1" s="57"/>
+      <c r="AJ1" s="57"/>
+      <c r="AK1" s="57"/>
+      <c r="AL1" s="57"/>
+      <c r="AM1" s="57"/>
+      <c r="AN1" s="57"/>
+      <c r="AO1" s="57"/>
+      <c r="AP1" s="57"/>
+      <c r="AQ1" s="57"/>
+      <c r="AR1" s="57"/>
+      <c r="AS1" s="57"/>
+      <c r="AT1" s="57"/>
+      <c r="AU1" s="57"/>
+      <c r="AV1" s="57"/>
+      <c r="AW1" s="57"/>
+      <c r="AX1" s="57"/>
+      <c r="AY1" s="57"/>
+      <c r="AZ1" s="57"/>
+      <c r="BA1" s="57"/>
+      <c r="BB1" s="57"/>
+      <c r="BC1" s="57"/>
+      <c r="BD1" s="57"/>
+      <c r="BE1" s="57"/>
+      <c r="BF1" s="57"/>
+      <c r="BG1" s="57"/>
+      <c r="BH1" s="57"/>
+      <c r="BI1" s="57"/>
+      <c r="BJ1" s="57"/>
+      <c r="BK1" s="57"/>
+      <c r="BL1" s="57"/>
+      <c r="BM1" s="57"/>
+      <c r="BN1" s="57"/>
+      <c r="BO1" s="57"/>
+      <c r="BP1" s="57"/>
+      <c r="BQ1" s="57"/>
+      <c r="BR1" s="57"/>
+      <c r="BS1" s="57"/>
+      <c r="BT1" s="57"/>
+      <c r="BU1" s="57"/>
+      <c r="BV1" s="57"/>
+      <c r="BW1" s="57"/>
+      <c r="BX1" s="57"/>
+      <c r="BY1" s="57"/>
+      <c r="BZ1" s="57"/>
+      <c r="CA1" s="57"/>
+      <c r="CB1" s="57"/>
+      <c r="CC1" s="57"/>
+      <c r="CD1" s="57"/>
+      <c r="CE1" s="57"/>
+      <c r="CF1" s="57"/>
+      <c r="CG1" s="57"/>
+      <c r="CH1" s="57"/>
+      <c r="CI1" s="57"/>
+      <c r="CJ1" s="57"/>
+      <c r="CK1" s="57"/>
+      <c r="CL1" s="57"/>
+      <c r="CM1" s="57"/>
+      <c r="CN1" s="57"/>
+      <c r="CO1" s="57"/>
+      <c r="CP1" s="57"/>
+      <c r="CQ1" s="57"/>
+      <c r="CR1" s="57"/>
+      <c r="CS1" s="57"/>
+      <c r="CT1" s="57"/>
+      <c r="CU1" s="57"/>
+      <c r="CV1" s="57"/>
+      <c r="CW1" s="57"/>
+      <c r="CX1" s="57"/>
+      <c r="CY1" s="57"/>
+      <c r="CZ1" s="57"/>
+      <c r="DA1" s="57"/>
+      <c r="DB1" s="57"/>
+      <c r="DC1" s="57"/>
+      <c r="DD1" s="57"/>
+      <c r="DE1" s="57"/>
+      <c r="DF1" s="57"/>
+      <c r="DG1" s="57"/>
+      <c r="DH1" s="57"/>
+      <c r="DI1" s="57"/>
+      <c r="DJ1" s="57"/>
+      <c r="DK1" s="57"/>
+      <c r="DL1" s="57"/>
+      <c r="DM1" s="57"/>
+      <c r="DN1" s="57"/>
+      <c r="DO1" s="57"/>
+      <c r="DP1" s="57"/>
+      <c r="DQ1" s="57"/>
+      <c r="DR1" s="57"/>
+      <c r="DS1" s="57"/>
+      <c r="DT1" s="57"/>
+      <c r="DU1" s="57"/>
+      <c r="DV1" s="57"/>
+      <c r="DW1" s="57"/>
+      <c r="DX1" s="57"/>
+      <c r="DY1" s="57"/>
+      <c r="DZ1" s="57"/>
+      <c r="EA1" s="57"/>
+      <c r="EB1" s="57"/>
+      <c r="EC1" s="57"/>
+      <c r="ED1" s="57"/>
+      <c r="EE1" s="57"/>
+      <c r="EF1" s="57"/>
+      <c r="EG1" s="57"/>
+      <c r="EH1" s="57"/>
+      <c r="EI1" s="57"/>
+      <c r="EJ1" s="57"/>
+      <c r="EK1" s="57"/>
+      <c r="EL1" s="57"/>
+      <c r="EM1" s="57"/>
+      <c r="EN1" s="57"/>
+      <c r="EO1" s="57"/>
+      <c r="EP1" s="57"/>
+      <c r="EQ1" s="57"/>
+      <c r="ER1" s="57"/>
+      <c r="ES1" s="57"/>
+      <c r="ET1" s="57"/>
+      <c r="EU1" s="57"/>
+      <c r="EV1" s="57"/>
+      <c r="EW1" s="57"/>
+      <c r="EX1" s="57"/>
+      <c r="EY1" s="57"/>
+      <c r="EZ1" s="57"/>
+      <c r="FA1" s="57"/>
+      <c r="FB1" s="57"/>
+      <c r="FC1" s="57"/>
+      <c r="FD1" s="57"/>
+      <c r="FE1" s="57"/>
+      <c r="FF1" s="57"/>
+      <c r="FG1" s="57"/>
+      <c r="FH1" s="57"/>
+      <c r="FI1" s="57"/>
+      <c r="FJ1" s="57"/>
+      <c r="FK1" s="57"/>
+      <c r="FL1" s="57"/>
+      <c r="FM1" s="57"/>
+      <c r="FN1" s="57"/>
+      <c r="FO1" s="57"/>
+      <c r="FP1" s="57"/>
+      <c r="FQ1" s="57"/>
+      <c r="FR1" s="57"/>
+      <c r="FS1" s="57"/>
+      <c r="FT1" s="57"/>
+      <c r="FU1" s="57"/>
+      <c r="FV1" s="57"/>
+      <c r="FW1" s="57"/>
+      <c r="FX1" s="57"/>
+      <c r="FY1" s="57"/>
+      <c r="FZ1" s="57"/>
+      <c r="GA1" s="57"/>
+      <c r="GB1" s="57"/>
+      <c r="GC1" s="57"/>
+      <c r="GD1" s="57"/>
+      <c r="GE1" s="57"/>
+      <c r="GF1" s="57"/>
+      <c r="GG1" s="57"/>
+      <c r="GH1" s="57"/>
+      <c r="GI1" s="57"/>
+      <c r="GJ1" s="57"/>
+      <c r="GK1" s="57"/>
+      <c r="GL1" s="57"/>
+      <c r="GM1" s="57"/>
+      <c r="GN1" s="57"/>
+      <c r="GO1" s="57"/>
+      <c r="GP1" s="57"/>
+      <c r="GQ1" s="57"/>
+      <c r="GR1" s="57"/>
+      <c r="GS1" s="57"/>
+      <c r="GT1" s="57"/>
+      <c r="GU1" s="57"/>
+      <c r="GV1" s="57"/>
+      <c r="GW1" s="57"/>
+      <c r="GX1" s="57"/>
+      <c r="GY1" s="57"/>
+      <c r="GZ1" s="57"/>
+      <c r="HA1" s="57"/>
+      <c r="HB1" s="57"/>
+      <c r="HC1" s="57"/>
+      <c r="HD1" s="57"/>
+      <c r="HE1" s="57"/>
+      <c r="HF1" s="57"/>
+      <c r="HG1" s="57"/>
+      <c r="HH1" s="57"/>
+      <c r="HI1" s="57"/>
+      <c r="HJ1" s="57"/>
+      <c r="HK1" s="57"/>
+      <c r="HL1" s="57"/>
+      <c r="HM1" s="57"/>
+      <c r="HN1" s="57"/>
+      <c r="HO1" s="57"/>
+      <c r="HP1" s="57"/>
+      <c r="HQ1" s="57"/>
+      <c r="HR1" s="57"/>
+      <c r="HS1" s="57"/>
+      <c r="HT1" s="57"/>
+      <c r="HU1" s="57"/>
+      <c r="HV1" s="57"/>
+      <c r="HW1" s="57"/>
+      <c r="HX1" s="57"/>
+      <c r="HY1" s="57"/>
+      <c r="HZ1" s="57"/>
+      <c r="IA1" s="57"/>
+      <c r="IB1" s="57"/>
+      <c r="IC1" s="57"/>
+      <c r="ID1" s="57"/>
+      <c r="IE1" s="57"/>
+      <c r="IF1" s="57"/>
+      <c r="IG1" s="57"/>
+      <c r="IH1" s="57"/>
+      <c r="II1" s="57"/>
+      <c r="IJ1" s="57"/>
+      <c r="IK1" s="57"/>
+      <c r="IL1" s="57"/>
+      <c r="IM1" s="57"/>
+      <c r="IN1" s="57"/>
+      <c r="IO1" s="57"/>
+      <c r="IP1" s="57"/>
+      <c r="IQ1" s="57"/>
+      <c r="IR1" s="57"/>
+      <c r="IS1" s="57"/>
+      <c r="IT1" s="57"/>
+      <c r="IU1" s="57"/>
+      <c r="IV1" s="57"/>
+      <c r="IW1" s="57"/>
+      <c r="IX1" s="57"/>
+      <c r="IY1" s="57"/>
+      <c r="IZ1" s="57"/>
+      <c r="JA1" s="57"/>
+      <c r="JB1" s="57"/>
+      <c r="JC1" s="57"/>
+      <c r="JD1" s="57"/>
+      <c r="JE1" s="57"/>
+      <c r="JF1" s="57"/>
+      <c r="JG1" s="57"/>
+      <c r="JH1" s="57"/>
+      <c r="JI1" s="57"/>
+      <c r="JJ1" s="57"/>
+      <c r="JK1" s="57"/>
+      <c r="JL1" s="57"/>
+      <c r="JM1" s="57"/>
+      <c r="JN1" s="57"/>
+      <c r="JO1" s="57"/>
+      <c r="JP1" s="57"/>
+      <c r="JQ1" s="57"/>
+      <c r="JR1" s="57"/>
+      <c r="JS1" s="57"/>
+      <c r="JT1" s="57"/>
+      <c r="JU1" s="57"/>
+      <c r="JV1" s="57"/>
+      <c r="JW1" s="57"/>
+      <c r="JX1" s="57"/>
+      <c r="JY1" s="57"/>
+      <c r="JZ1" s="57"/>
+      <c r="KA1" s="57"/>
+      <c r="KB1" s="57"/>
+      <c r="KC1" s="57"/>
+      <c r="KD1" s="57"/>
+      <c r="KE1" s="57"/>
+      <c r="KF1" s="57"/>
+      <c r="KG1" s="57"/>
+      <c r="KH1" s="57"/>
+      <c r="KI1" s="57"/>
+      <c r="KJ1" s="57"/>
+      <c r="KK1" s="57"/>
+      <c r="KL1" s="57"/>
+      <c r="KM1" s="57"/>
+      <c r="KN1" s="57"/>
+      <c r="KO1" s="57"/>
+      <c r="KP1" s="57"/>
+      <c r="KQ1" s="57"/>
+      <c r="KR1" s="57"/>
+      <c r="KS1" s="57"/>
+      <c r="KT1" s="57"/>
+      <c r="KU1" s="57"/>
+      <c r="KV1" s="57"/>
+      <c r="KW1" s="57"/>
+      <c r="KX1" s="57"/>
+      <c r="KY1" s="57"/>
+      <c r="KZ1" s="57"/>
+      <c r="LA1" s="57"/>
+      <c r="LB1" s="57"/>
+      <c r="LC1" s="57"/>
+      <c r="LD1" s="57"/>
+      <c r="LE1" s="57"/>
+      <c r="LF1" s="57"/>
+      <c r="LG1" s="57"/>
+      <c r="LH1" s="57"/>
+      <c r="LI1" s="57"/>
+      <c r="LJ1" s="57"/>
+      <c r="LK1" s="57"/>
+      <c r="LL1" s="57"/>
+      <c r="LM1" s="57"/>
+      <c r="LN1" s="57"/>
+      <c r="LO1" s="57"/>
+      <c r="LP1" s="57"/>
+      <c r="LQ1" s="57"/>
+      <c r="LR1" s="57"/>
+      <c r="LS1" s="57"/>
+      <c r="LT1" s="57"/>
+      <c r="LU1" s="57"/>
+      <c r="LV1" s="57"/>
+      <c r="LW1" s="57"/>
+      <c r="LX1" s="57"/>
+      <c r="LY1" s="57"/>
+      <c r="LZ1" s="57"/>
+      <c r="MA1" s="57"/>
+      <c r="MB1" s="57"/>
+      <c r="MC1" s="57"/>
+      <c r="MD1" s="57"/>
+      <c r="ME1" s="57"/>
+      <c r="MF1" s="57"/>
+      <c r="MG1" s="57"/>
+      <c r="MH1" s="57"/>
+      <c r="MI1" s="57"/>
+      <c r="MJ1" s="57"/>
+      <c r="MK1" s="57"/>
+      <c r="ML1" s="57"/>
+      <c r="MM1" s="57"/>
+      <c r="MN1" s="57"/>
+      <c r="MO1" s="57"/>
+      <c r="MP1" s="57"/>
+      <c r="MQ1" s="57"/>
+      <c r="MR1" s="57"/>
+      <c r="MS1" s="57"/>
+      <c r="MT1" s="57"/>
+      <c r="MU1" s="57"/>
+      <c r="MV1" s="57"/>
+      <c r="MW1" s="57"/>
+      <c r="MX1" s="57"/>
+      <c r="MY1" s="57"/>
+      <c r="MZ1" s="57"/>
+      <c r="NA1" s="57"/>
+      <c r="NB1" s="57"/>
+      <c r="NC1" s="57"/>
+      <c r="ND1" s="57"/>
+      <c r="NE1" s="57"/>
+      <c r="NF1" s="57"/>
+      <c r="NG1" s="57"/>
+      <c r="NH1" s="57"/>
+      <c r="NI1" s="57"/>
+      <c r="NJ1" s="57"/>
+      <c r="NK1" s="57"/>
+      <c r="NL1" s="57"/>
+      <c r="NM1" s="57"/>
+      <c r="NN1" s="57"/>
+      <c r="NO1" s="57"/>
+      <c r="NP1" s="57"/>
+      <c r="NQ1" s="57"/>
+      <c r="NR1" s="57"/>
+      <c r="NS1" s="57"/>
+      <c r="NT1" s="57"/>
+      <c r="NU1" s="57"/>
+      <c r="NV1" s="57"/>
+      <c r="NW1" s="57"/>
+      <c r="NX1" s="57"/>
+      <c r="NY1" s="57"/>
+      <c r="NZ1" s="57"/>
+      <c r="OA1" s="57"/>
+      <c r="OB1" s="57"/>
+      <c r="OC1" s="57"/>
+      <c r="OD1" s="57"/>
+      <c r="OE1" s="57"/>
+      <c r="OF1" s="57"/>
+      <c r="OG1" s="57"/>
+      <c r="OH1" s="57"/>
+      <c r="OI1" s="57"/>
+      <c r="OJ1" s="57"/>
+      <c r="OK1" s="57"/>
+      <c r="OL1" s="57"/>
+      <c r="OM1" s="57"/>
+      <c r="ON1" s="57"/>
+      <c r="OO1" s="57"/>
+      <c r="OP1" s="57"/>
+      <c r="OQ1" s="57"/>
+      <c r="OR1" s="57"/>
+      <c r="OS1" s="57"/>
+      <c r="OT1" s="57"/>
+      <c r="OU1" s="57"/>
+      <c r="OV1" s="57"/>
+      <c r="OW1" s="57"/>
+      <c r="OX1" s="57"/>
+      <c r="OY1" s="57"/>
+      <c r="OZ1" s="57"/>
+      <c r="PA1" s="57"/>
+      <c r="PB1" s="57"/>
+      <c r="PC1" s="57"/>
+      <c r="PD1" s="57"/>
+      <c r="PE1" s="57"/>
+      <c r="PF1" s="57"/>
+      <c r="PG1" s="57"/>
+      <c r="PH1" s="57"/>
+      <c r="PI1" s="57"/>
+      <c r="PJ1" s="57"/>
+      <c r="PK1" s="57"/>
+      <c r="PL1" s="57"/>
+      <c r="PM1" s="57"/>
+      <c r="PN1" s="57"/>
+      <c r="PO1" s="57"/>
+      <c r="PP1" s="57"/>
+      <c r="PQ1" s="57"/>
+      <c r="PR1" s="57"/>
+      <c r="PS1" s="57"/>
+      <c r="PT1" s="57"/>
+      <c r="PU1" s="57"/>
+      <c r="PV1" s="57"/>
+      <c r="PW1" s="57"/>
+      <c r="PX1" s="57"/>
+      <c r="PY1" s="57"/>
+      <c r="PZ1" s="57"/>
+      <c r="QA1" s="57"/>
+      <c r="QB1" s="57"/>
+      <c r="QC1" s="57"/>
+      <c r="QD1" s="57"/>
+      <c r="QE1" s="57"/>
+      <c r="QF1" s="57"/>
+      <c r="QG1" s="57"/>
+      <c r="QH1" s="57"/>
+      <c r="QI1" s="57"/>
+      <c r="QJ1" s="57"/>
+      <c r="QK1" s="57"/>
+      <c r="QL1" s="57"/>
+      <c r="QM1" s="57"/>
+      <c r="QN1" s="57"/>
+      <c r="QO1" s="57"/>
+      <c r="QP1" s="57"/>
+      <c r="QQ1" s="57"/>
+      <c r="QR1" s="57"/>
+      <c r="QS1" s="57"/>
+      <c r="QT1" s="57"/>
+      <c r="QU1" s="57"/>
+      <c r="QV1" s="57"/>
+      <c r="QW1" s="57"/>
+      <c r="QX1" s="57"/>
+      <c r="QY1" s="57"/>
+      <c r="QZ1" s="57"/>
+      <c r="RA1" s="57"/>
+      <c r="RB1" s="57"/>
+      <c r="RC1" s="57"/>
+      <c r="RD1" s="57"/>
+      <c r="RE1" s="57"/>
+      <c r="RF1" s="57"/>
+      <c r="RG1" s="57"/>
+      <c r="RH1" s="57"/>
+      <c r="RI1" s="57"/>
+      <c r="RJ1" s="57"/>
+      <c r="RK1" s="57"/>
+      <c r="RL1" s="57"/>
+      <c r="RM1" s="57"/>
+      <c r="RN1" s="57"/>
+      <c r="RO1" s="57"/>
+      <c r="RP1" s="57"/>
+      <c r="RQ1" s="57"/>
+      <c r="RR1" s="57"/>
+      <c r="RS1" s="57"/>
+      <c r="RT1" s="57"/>
+      <c r="RU1" s="57"/>
+      <c r="RV1" s="57"/>
+      <c r="RW1" s="57"/>
+      <c r="RX1" s="57"/>
+      <c r="RY1" s="57"/>
+      <c r="RZ1" s="57"/>
+      <c r="SA1" s="57"/>
+      <c r="SB1" s="57"/>
+      <c r="SC1" s="57"/>
+      <c r="SD1" s="57"/>
+      <c r="SE1" s="57"/>
+      <c r="SF1" s="57"/>
+      <c r="SG1" s="57"/>
+      <c r="SH1" s="57"/>
+      <c r="SI1" s="57"/>
+      <c r="SJ1" s="57"/>
+      <c r="SK1" s="57"/>
+      <c r="SL1" s="57"/>
+      <c r="SM1" s="57"/>
+      <c r="SN1" s="57"/>
+      <c r="SO1" s="57"/>
+      <c r="SP1" s="57"/>
+      <c r="SQ1" s="57"/>
+      <c r="SR1" s="57"/>
+      <c r="SS1" s="57"/>
+      <c r="ST1" s="57"/>
+      <c r="SU1" s="57"/>
+      <c r="SV1" s="57"/>
+      <c r="SW1" s="57"/>
+      <c r="SX1" s="57"/>
+      <c r="SY1" s="57"/>
+      <c r="SZ1" s="57"/>
+      <c r="TA1" s="57"/>
+      <c r="TB1" s="57"/>
+      <c r="TC1" s="57"/>
+      <c r="TD1" s="57"/>
+      <c r="TE1" s="57"/>
+      <c r="TF1" s="57"/>
+      <c r="TG1" s="57"/>
+      <c r="TH1" s="57"/>
+      <c r="TI1" s="57"/>
+      <c r="TJ1" s="57"/>
+      <c r="TK1" s="57"/>
+      <c r="TL1" s="57"/>
+      <c r="TM1" s="57"/>
+      <c r="TN1" s="57"/>
+      <c r="TO1" s="57"/>
+      <c r="TP1" s="57"/>
+      <c r="TQ1" s="57"/>
+      <c r="TR1" s="57"/>
+      <c r="TS1" s="57"/>
+      <c r="TT1" s="57"/>
+      <c r="TU1" s="57"/>
+      <c r="TV1" s="57"/>
+      <c r="TW1" s="57"/>
+      <c r="TX1" s="57"/>
+      <c r="TY1" s="57"/>
+      <c r="TZ1" s="57"/>
+      <c r="UA1" s="57"/>
+      <c r="UB1" s="57"/>
+      <c r="UC1" s="57"/>
+      <c r="UD1" s="57"/>
+      <c r="UE1" s="57"/>
+      <c r="UF1" s="57"/>
+      <c r="UG1" s="57"/>
+      <c r="UH1" s="57"/>
+      <c r="UI1" s="57"/>
+      <c r="UJ1" s="57"/>
+      <c r="UK1" s="57"/>
+      <c r="UL1" s="57"/>
+      <c r="UM1" s="57"/>
+      <c r="UN1" s="57"/>
+      <c r="UO1" s="57"/>
+      <c r="UP1" s="57"/>
+      <c r="UQ1" s="57"/>
+      <c r="UR1" s="57"/>
+      <c r="US1" s="57"/>
+      <c r="UT1" s="57"/>
+      <c r="UU1" s="57"/>
+      <c r="UV1" s="57"/>
+      <c r="UW1" s="57"/>
+      <c r="UX1" s="57"/>
+      <c r="UY1" s="57"/>
+      <c r="UZ1" s="57"/>
+      <c r="VA1" s="57"/>
+      <c r="VB1" s="57"/>
+      <c r="VC1" s="57"/>
+      <c r="VD1" s="57"/>
+      <c r="VE1" s="57"/>
+      <c r="VF1" s="57"/>
+      <c r="VG1" s="57"/>
+      <c r="VH1" s="57"/>
+      <c r="VI1" s="57"/>
+      <c r="VJ1" s="57"/>
+      <c r="VK1" s="57"/>
+      <c r="VL1" s="57"/>
+      <c r="VM1" s="57"/>
+      <c r="VN1" s="57"/>
+      <c r="VO1" s="57"/>
+      <c r="VP1" s="57"/>
+      <c r="VQ1" s="57"/>
+      <c r="VR1" s="57"/>
+      <c r="VS1" s="57"/>
+      <c r="VT1" s="57"/>
+      <c r="VU1" s="57"/>
+      <c r="VV1" s="57"/>
+      <c r="VW1" s="57"/>
+      <c r="VX1" s="57"/>
+      <c r="VY1" s="57"/>
+      <c r="VZ1" s="57"/>
+      <c r="WA1" s="57"/>
+      <c r="WB1" s="57"/>
+      <c r="WC1" s="57"/>
+      <c r="WD1" s="57"/>
+      <c r="WE1" s="57"/>
+      <c r="WF1" s="57"/>
+      <c r="WG1" s="57"/>
+      <c r="WH1" s="57"/>
+      <c r="WI1" s="57"/>
+      <c r="WJ1" s="57"/>
+      <c r="WK1" s="57"/>
+      <c r="WL1" s="57"/>
+      <c r="WM1" s="57"/>
+      <c r="WN1" s="57"/>
+      <c r="WO1" s="57"/>
+      <c r="WP1" s="57"/>
+      <c r="WQ1" s="57"/>
+      <c r="WR1" s="57"/>
+      <c r="WS1" s="57"/>
+      <c r="WT1" s="57"/>
+      <c r="WU1" s="57"/>
+      <c r="WV1" s="57"/>
+      <c r="WW1" s="57"/>
+      <c r="WX1" s="57"/>
+      <c r="WY1" s="57"/>
+      <c r="WZ1" s="57"/>
+      <c r="XA1" s="57"/>
+      <c r="XB1" s="57"/>
+      <c r="XC1" s="57"/>
+      <c r="XD1" s="57"/>
+      <c r="XE1" s="57"/>
+      <c r="XF1" s="57"/>
+      <c r="XG1" s="57"/>
+      <c r="XH1" s="57"/>
+      <c r="XI1" s="57"/>
+      <c r="XJ1" s="57"/>
+      <c r="XK1" s="57"/>
+      <c r="XL1" s="57"/>
+      <c r="XM1" s="57"/>
+      <c r="XN1" s="57"/>
+      <c r="XO1" s="57"/>
+      <c r="XP1" s="57"/>
+      <c r="XQ1" s="57"/>
+      <c r="XR1" s="57"/>
+      <c r="XS1" s="57"/>
+      <c r="XT1" s="57"/>
+      <c r="XU1" s="57"/>
+      <c r="XV1" s="57"/>
+      <c r="XW1" s="57"/>
+      <c r="XX1" s="57"/>
+      <c r="XY1" s="57"/>
+      <c r="XZ1" s="57"/>
+      <c r="YA1" s="57"/>
+      <c r="YB1" s="57"/>
+      <c r="YC1" s="57"/>
+      <c r="YD1" s="57"/>
+      <c r="YE1" s="57"/>
+      <c r="YF1" s="57"/>
+      <c r="YG1" s="57"/>
+      <c r="YH1" s="57"/>
+      <c r="YI1" s="57"/>
+      <c r="YJ1" s="57"/>
+      <c r="YK1" s="57"/>
+      <c r="YL1" s="57"/>
+      <c r="YM1" s="57"/>
+      <c r="YN1" s="57"/>
+      <c r="YO1" s="57"/>
+      <c r="YP1" s="57"/>
+      <c r="YQ1" s="57"/>
+      <c r="YR1" s="57"/>
+      <c r="YS1" s="57"/>
+      <c r="YT1" s="57"/>
+      <c r="YU1" s="57"/>
+      <c r="YV1" s="57"/>
+      <c r="YW1" s="57"/>
+      <c r="YX1" s="57"/>
+      <c r="YY1" s="57"/>
+      <c r="YZ1" s="57"/>
     </row>
     <row r="2" spans="1:676" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
-      <c r="W2" s="48"/>
-      <c r="X2" s="48"/>
-      <c r="Y2" s="48"/>
-      <c r="Z2" s="48"/>
-      <c r="AA2" s="48"/>
-      <c r="AB2" s="48"/>
-      <c r="AC2" s="48"/>
-      <c r="AD2" s="48"/>
-      <c r="AE2" s="48"/>
-      <c r="AF2" s="48"/>
-      <c r="AG2" s="48"/>
-      <c r="AH2" s="48"/>
-      <c r="AI2" s="48"/>
-      <c r="AJ2" s="48"/>
-      <c r="AK2" s="48"/>
-      <c r="AL2" s="48"/>
-      <c r="AM2" s="48"/>
-      <c r="AN2" s="48"/>
-      <c r="AO2" s="48"/>
-      <c r="AP2" s="48"/>
-      <c r="AQ2" s="48"/>
-      <c r="AR2" s="48"/>
-      <c r="AS2" s="48"/>
-      <c r="AT2" s="48"/>
-      <c r="AU2" s="48"/>
-      <c r="AV2" s="48"/>
-      <c r="AW2" s="48"/>
-      <c r="AX2" s="48"/>
-      <c r="AY2" s="48"/>
-      <c r="AZ2" s="48"/>
-      <c r="BA2" s="48"/>
-      <c r="BB2" s="48"/>
-      <c r="BC2" s="48"/>
-      <c r="BD2" s="48"/>
-      <c r="BE2" s="48"/>
-      <c r="BF2" s="48"/>
-      <c r="BG2" s="48"/>
-      <c r="BH2" s="48"/>
-      <c r="BI2" s="48"/>
-      <c r="BJ2" s="48"/>
-      <c r="BK2" s="48"/>
-      <c r="BL2" s="48"/>
-      <c r="BM2" s="48"/>
-      <c r="BN2" s="48"/>
-      <c r="BO2" s="48"/>
-      <c r="BP2" s="48"/>
-      <c r="BQ2" s="48"/>
-      <c r="BR2" s="48"/>
-      <c r="BS2" s="48"/>
-      <c r="BT2" s="48"/>
-      <c r="BU2" s="48"/>
-      <c r="BV2" s="48"/>
-      <c r="BW2" s="48"/>
-      <c r="BX2" s="48"/>
-      <c r="BY2" s="48"/>
-      <c r="BZ2" s="48"/>
-      <c r="CA2" s="48"/>
-      <c r="CB2" s="48"/>
-      <c r="CC2" s="48"/>
-      <c r="CD2" s="48"/>
-      <c r="CE2" s="48"/>
-      <c r="CF2" s="48"/>
-      <c r="CG2" s="48"/>
-      <c r="CH2" s="48"/>
-      <c r="CI2" s="48"/>
-      <c r="CJ2" s="48"/>
-      <c r="CK2" s="48"/>
-      <c r="CL2" s="48"/>
-      <c r="CM2" s="48"/>
-      <c r="CN2" s="48"/>
-      <c r="CO2" s="48"/>
-      <c r="CP2" s="48"/>
-      <c r="CQ2" s="48"/>
-      <c r="CR2" s="48"/>
-      <c r="CS2" s="48"/>
-      <c r="CT2" s="48"/>
-      <c r="CU2" s="48"/>
-      <c r="CV2" s="48"/>
-      <c r="CW2" s="48"/>
-      <c r="CX2" s="48"/>
-      <c r="CY2" s="48"/>
-      <c r="CZ2" s="48"/>
-      <c r="DA2" s="48"/>
-      <c r="DB2" s="48"/>
-      <c r="DC2" s="48"/>
-      <c r="DD2" s="48"/>
-      <c r="DE2" s="48"/>
-      <c r="DF2" s="48"/>
-      <c r="DG2" s="48"/>
-      <c r="DH2" s="48"/>
-      <c r="DI2" s="48"/>
-      <c r="DJ2" s="48"/>
-      <c r="DK2" s="48"/>
-      <c r="DL2" s="48"/>
-      <c r="DM2" s="48"/>
-      <c r="DN2" s="48"/>
-      <c r="DO2" s="48"/>
-      <c r="DP2" s="48"/>
-      <c r="DQ2" s="48"/>
-      <c r="DR2" s="48"/>
-      <c r="DS2" s="48"/>
-      <c r="DT2" s="48"/>
-      <c r="DU2" s="48"/>
-      <c r="DV2" s="48"/>
-      <c r="DW2" s="48"/>
-      <c r="DX2" s="48"/>
-      <c r="DY2" s="48"/>
-      <c r="DZ2" s="48"/>
-      <c r="EA2" s="48"/>
-      <c r="EB2" s="48"/>
-      <c r="EC2" s="48"/>
-      <c r="ED2" s="48"/>
-      <c r="EE2" s="48"/>
-      <c r="EF2" s="48"/>
-      <c r="EG2" s="48"/>
-      <c r="EH2" s="48"/>
-      <c r="EI2" s="48"/>
-      <c r="EJ2" s="48"/>
-      <c r="EK2" s="48"/>
-      <c r="EL2" s="48"/>
-      <c r="EM2" s="48"/>
-      <c r="EN2" s="48"/>
-      <c r="EO2" s="48"/>
-      <c r="EP2" s="48"/>
-      <c r="EQ2" s="48"/>
-      <c r="ER2" s="48"/>
-      <c r="ES2" s="48"/>
-      <c r="ET2" s="48"/>
-      <c r="EU2" s="48"/>
-      <c r="EV2" s="48"/>
-      <c r="EW2" s="48"/>
-      <c r="EX2" s="48"/>
-      <c r="EY2" s="48"/>
-      <c r="EZ2" s="48"/>
-      <c r="FA2" s="48"/>
-      <c r="FB2" s="48"/>
-      <c r="FC2" s="48"/>
-      <c r="FD2" s="48"/>
-      <c r="FE2" s="48"/>
-      <c r="FF2" s="48"/>
-      <c r="FG2" s="48"/>
-      <c r="FH2" s="48"/>
-      <c r="FI2" s="48"/>
-      <c r="FJ2" s="48"/>
-      <c r="FK2" s="48"/>
-      <c r="FL2" s="48"/>
-      <c r="FM2" s="48"/>
-      <c r="FN2" s="48"/>
-      <c r="FO2" s="48"/>
-      <c r="FP2" s="48"/>
-      <c r="FQ2" s="48"/>
-      <c r="FR2" s="48"/>
-      <c r="FS2" s="48"/>
-      <c r="FT2" s="48"/>
-      <c r="FU2" s="48"/>
-      <c r="FV2" s="48"/>
-      <c r="FW2" s="48"/>
-      <c r="FX2" s="48"/>
-      <c r="FY2" s="48"/>
-      <c r="FZ2" s="48"/>
-      <c r="GA2" s="48"/>
-      <c r="GB2" s="48"/>
-      <c r="GC2" s="48"/>
-      <c r="GD2" s="48"/>
-      <c r="GE2" s="48"/>
-      <c r="GF2" s="48"/>
-      <c r="GG2" s="48"/>
-      <c r="GH2" s="48"/>
-      <c r="GI2" s="48"/>
-      <c r="GJ2" s="48"/>
-      <c r="GK2" s="48"/>
-      <c r="GL2" s="48"/>
-      <c r="GM2" s="48"/>
-      <c r="GN2" s="48"/>
-      <c r="GO2" s="48"/>
-      <c r="GP2" s="48"/>
-      <c r="GQ2" s="48"/>
-      <c r="GR2" s="48"/>
-      <c r="GS2" s="48"/>
-      <c r="GT2" s="48"/>
-      <c r="GU2" s="48"/>
-      <c r="GV2" s="48"/>
-      <c r="GW2" s="48"/>
-      <c r="GX2" s="48"/>
-      <c r="GY2" s="48"/>
-      <c r="GZ2" s="48"/>
-      <c r="HA2" s="48"/>
-      <c r="HB2" s="48"/>
-      <c r="HC2" s="48"/>
-      <c r="HD2" s="48"/>
-      <c r="HE2" s="48"/>
-      <c r="HF2" s="48"/>
-      <c r="HG2" s="48"/>
-      <c r="HH2" s="48"/>
-      <c r="HI2" s="48"/>
-      <c r="HJ2" s="48"/>
-      <c r="HK2" s="48"/>
-      <c r="HL2" s="48"/>
-      <c r="HM2" s="48"/>
-      <c r="HN2" s="48"/>
-      <c r="HO2" s="48"/>
-      <c r="HP2" s="48"/>
-      <c r="HQ2" s="48"/>
-      <c r="HR2" s="48"/>
-      <c r="HS2" s="48"/>
-      <c r="HT2" s="48"/>
-      <c r="HU2" s="48"/>
-      <c r="HV2" s="48"/>
-      <c r="HW2" s="48"/>
-      <c r="HX2" s="48"/>
-      <c r="HY2" s="48"/>
-      <c r="HZ2" s="48"/>
-      <c r="IA2" s="48"/>
-      <c r="IB2" s="48"/>
-      <c r="IC2" s="48"/>
-      <c r="ID2" s="48"/>
-      <c r="IE2" s="48"/>
-      <c r="IF2" s="48"/>
-      <c r="IG2" s="48"/>
-      <c r="IH2" s="48"/>
-      <c r="II2" s="48"/>
-      <c r="IJ2" s="48"/>
-      <c r="IK2" s="48"/>
-      <c r="IL2" s="48"/>
-      <c r="IM2" s="48"/>
-      <c r="IN2" s="48"/>
-      <c r="IO2" s="48"/>
-      <c r="IP2" s="48"/>
-      <c r="IQ2" s="48"/>
-      <c r="IR2" s="48"/>
-      <c r="IS2" s="48"/>
-      <c r="IT2" s="48"/>
-      <c r="IU2" s="48"/>
-      <c r="IV2" s="48"/>
-      <c r="IW2" s="48"/>
-      <c r="IX2" s="48"/>
-      <c r="IY2" s="48"/>
-      <c r="IZ2" s="48"/>
-      <c r="JA2" s="48"/>
-      <c r="JB2" s="48"/>
-      <c r="JC2" s="48"/>
-      <c r="JD2" s="48"/>
-      <c r="JE2" s="48"/>
-      <c r="JF2" s="48"/>
-      <c r="JG2" s="48"/>
-      <c r="JH2" s="48"/>
-      <c r="JI2" s="48"/>
-      <c r="JJ2" s="48"/>
-      <c r="JK2" s="48"/>
-      <c r="JL2" s="48"/>
-      <c r="JM2" s="48"/>
-      <c r="JN2" s="48"/>
-      <c r="JO2" s="48"/>
-      <c r="JP2" s="48"/>
-      <c r="JQ2" s="48"/>
-      <c r="JR2" s="48"/>
-      <c r="JS2" s="48"/>
-      <c r="JT2" s="48"/>
-      <c r="JU2" s="48"/>
-      <c r="JV2" s="48"/>
-      <c r="JW2" s="48"/>
-      <c r="JX2" s="48"/>
-      <c r="JY2" s="48"/>
-      <c r="JZ2" s="48"/>
-      <c r="KA2" s="48"/>
-      <c r="KB2" s="48"/>
-      <c r="KC2" s="48"/>
-      <c r="KD2" s="48"/>
-      <c r="KE2" s="48"/>
-      <c r="KF2" s="48"/>
-      <c r="KG2" s="48"/>
-      <c r="KH2" s="48"/>
-      <c r="KI2" s="48"/>
-      <c r="KJ2" s="48"/>
-      <c r="KK2" s="48"/>
-      <c r="KL2" s="48"/>
-      <c r="KM2" s="48"/>
-      <c r="KN2" s="48"/>
-      <c r="KO2" s="48"/>
-      <c r="KP2" s="48"/>
-      <c r="KQ2" s="48"/>
-      <c r="KR2" s="48"/>
-      <c r="KS2" s="48"/>
-      <c r="KT2" s="48"/>
-      <c r="KU2" s="48"/>
-      <c r="KV2" s="48"/>
-      <c r="KW2" s="48"/>
-      <c r="KX2" s="48"/>
-      <c r="KY2" s="48"/>
-      <c r="KZ2" s="48"/>
-      <c r="LA2" s="48"/>
-      <c r="LB2" s="48"/>
-      <c r="LC2" s="48"/>
-      <c r="LD2" s="48"/>
-      <c r="LE2" s="48"/>
-      <c r="LF2" s="48"/>
-      <c r="LG2" s="48"/>
-      <c r="LH2" s="48"/>
-      <c r="LI2" s="48"/>
-      <c r="LJ2" s="48"/>
-      <c r="LK2" s="48"/>
-      <c r="LL2" s="48"/>
-      <c r="LM2" s="48"/>
-      <c r="LN2" s="48"/>
-      <c r="LO2" s="48"/>
-      <c r="LP2" s="48"/>
-      <c r="LQ2" s="48"/>
-      <c r="LR2" s="48"/>
-      <c r="LS2" s="48"/>
-      <c r="LT2" s="48"/>
-      <c r="LU2" s="48"/>
-      <c r="LV2" s="48"/>
-      <c r="LW2" s="48"/>
-      <c r="LX2" s="48"/>
-      <c r="LY2" s="48"/>
-      <c r="LZ2" s="48"/>
-      <c r="MA2" s="48"/>
-      <c r="MB2" s="48"/>
-      <c r="MC2" s="48"/>
-      <c r="MD2" s="48"/>
-      <c r="ME2" s="48"/>
-      <c r="MF2" s="48"/>
-      <c r="MG2" s="48"/>
-      <c r="MH2" s="48"/>
-      <c r="MI2" s="48"/>
-      <c r="MJ2" s="48"/>
-      <c r="MK2" s="48"/>
-      <c r="ML2" s="48"/>
-      <c r="MM2" s="48"/>
-      <c r="MN2" s="48"/>
-      <c r="MO2" s="48"/>
-      <c r="MP2" s="48"/>
-      <c r="MQ2" s="48"/>
-      <c r="MR2" s="48"/>
-      <c r="MS2" s="48"/>
-      <c r="MT2" s="48"/>
-      <c r="MU2" s="48"/>
-      <c r="MV2" s="48"/>
-      <c r="MW2" s="48"/>
-      <c r="MX2" s="48"/>
-      <c r="MY2" s="48"/>
-      <c r="MZ2" s="48"/>
-      <c r="NA2" s="48"/>
-      <c r="NB2" s="48"/>
-      <c r="NC2" s="48"/>
-      <c r="ND2" s="48"/>
-      <c r="NE2" s="48"/>
-      <c r="NF2" s="48"/>
-      <c r="NG2" s="48"/>
-      <c r="NH2" s="48"/>
-      <c r="NI2" s="48"/>
-      <c r="NJ2" s="48"/>
-      <c r="NK2" s="48"/>
-      <c r="NL2" s="48"/>
-      <c r="NM2" s="48"/>
-      <c r="NN2" s="48"/>
-      <c r="NO2" s="48"/>
-      <c r="NP2" s="48"/>
-      <c r="NQ2" s="48"/>
-      <c r="NR2" s="48"/>
-      <c r="NS2" s="48"/>
-      <c r="NT2" s="48"/>
-      <c r="NU2" s="48"/>
-      <c r="NV2" s="48"/>
-      <c r="NW2" s="48"/>
-      <c r="NX2" s="48"/>
-      <c r="NY2" s="48"/>
-      <c r="NZ2" s="48"/>
-      <c r="OA2" s="48"/>
-      <c r="OB2" s="48"/>
-      <c r="OC2" s="48"/>
-      <c r="OD2" s="48"/>
-      <c r="OE2" s="48"/>
-      <c r="OF2" s="48"/>
-      <c r="OG2" s="48"/>
-      <c r="OH2" s="48"/>
-      <c r="OI2" s="48"/>
-      <c r="OJ2" s="48"/>
-      <c r="OK2" s="48"/>
-      <c r="OL2" s="48"/>
-      <c r="OM2" s="48"/>
-      <c r="ON2" s="48"/>
-      <c r="OO2" s="48"/>
-      <c r="OP2" s="48"/>
-      <c r="OQ2" s="48"/>
-      <c r="OR2" s="48"/>
-      <c r="OS2" s="48"/>
-      <c r="OT2" s="48"/>
-      <c r="OU2" s="48"/>
-      <c r="OV2" s="48"/>
-      <c r="OW2" s="48"/>
-      <c r="OX2" s="48"/>
-      <c r="OY2" s="48"/>
-      <c r="OZ2" s="48"/>
-      <c r="PA2" s="48"/>
-      <c r="PB2" s="48"/>
-      <c r="PC2" s="48"/>
-      <c r="PD2" s="48"/>
-      <c r="PE2" s="48"/>
-      <c r="PF2" s="48"/>
-      <c r="PG2" s="48"/>
-      <c r="PH2" s="48"/>
-      <c r="PI2" s="48"/>
-      <c r="PJ2" s="48"/>
-      <c r="PK2" s="48"/>
-      <c r="PL2" s="48"/>
-      <c r="PM2" s="48"/>
-      <c r="PN2" s="48"/>
-      <c r="PO2" s="48"/>
-      <c r="PP2" s="48"/>
-      <c r="PQ2" s="48"/>
-      <c r="PR2" s="48"/>
-      <c r="PS2" s="48"/>
-      <c r="PT2" s="48"/>
-      <c r="PU2" s="48"/>
-      <c r="PV2" s="48"/>
-      <c r="PW2" s="48"/>
-      <c r="PX2" s="48"/>
-      <c r="PY2" s="48"/>
-      <c r="PZ2" s="48"/>
-      <c r="QA2" s="48"/>
-      <c r="QB2" s="48"/>
-      <c r="QC2" s="48"/>
-      <c r="QD2" s="48"/>
-      <c r="QE2" s="48"/>
-      <c r="QF2" s="48"/>
-      <c r="QG2" s="48"/>
-      <c r="QH2" s="48"/>
-      <c r="QI2" s="48"/>
-      <c r="QJ2" s="48"/>
-      <c r="QK2" s="48"/>
-      <c r="QL2" s="48"/>
-      <c r="QM2" s="48"/>
-      <c r="QN2" s="48"/>
-      <c r="QO2" s="48"/>
-      <c r="QP2" s="48"/>
-      <c r="QQ2" s="48"/>
-      <c r="QR2" s="48"/>
-      <c r="QS2" s="48"/>
-      <c r="QT2" s="48"/>
-      <c r="QU2" s="48"/>
-      <c r="QV2" s="48"/>
-      <c r="QW2" s="48"/>
-      <c r="QX2" s="48"/>
-      <c r="QY2" s="48"/>
-      <c r="QZ2" s="48"/>
-      <c r="RA2" s="48"/>
-      <c r="RB2" s="48"/>
-      <c r="RC2" s="48"/>
-      <c r="RD2" s="48"/>
-      <c r="RE2" s="48"/>
-      <c r="RF2" s="48"/>
-      <c r="RG2" s="48"/>
-      <c r="RH2" s="48"/>
-      <c r="RI2" s="48"/>
-      <c r="RJ2" s="48"/>
-      <c r="RK2" s="48"/>
-      <c r="RL2" s="48"/>
-      <c r="RM2" s="48"/>
-      <c r="RN2" s="48"/>
-      <c r="RO2" s="48"/>
-      <c r="RP2" s="48"/>
-      <c r="RQ2" s="48"/>
-      <c r="RR2" s="48"/>
-      <c r="RS2" s="48"/>
-      <c r="RT2" s="48"/>
-      <c r="RU2" s="48"/>
-      <c r="RV2" s="48"/>
-      <c r="RW2" s="48"/>
-      <c r="RX2" s="48"/>
-      <c r="RY2" s="48"/>
-      <c r="RZ2" s="48"/>
-      <c r="SA2" s="48"/>
-      <c r="SB2" s="48"/>
-      <c r="SC2" s="48"/>
-      <c r="SD2" s="48"/>
-      <c r="SE2" s="48"/>
-      <c r="SF2" s="48"/>
-      <c r="SG2" s="48"/>
-      <c r="SH2" s="48"/>
-      <c r="SI2" s="48"/>
-      <c r="SJ2" s="48"/>
-      <c r="SK2" s="48"/>
-      <c r="SL2" s="48"/>
-      <c r="SM2" s="48"/>
-      <c r="SN2" s="48"/>
-      <c r="SO2" s="48"/>
-      <c r="SP2" s="48"/>
-      <c r="SQ2" s="48"/>
-      <c r="SR2" s="48"/>
-      <c r="SS2" s="48"/>
-      <c r="ST2" s="48"/>
-      <c r="SU2" s="48"/>
-      <c r="SV2" s="48"/>
-      <c r="SW2" s="48"/>
-      <c r="SX2" s="48"/>
-      <c r="SY2" s="48"/>
-      <c r="SZ2" s="48"/>
-      <c r="TA2" s="48"/>
-      <c r="TB2" s="48"/>
-      <c r="TC2" s="48"/>
-      <c r="TD2" s="48"/>
-      <c r="TE2" s="48"/>
-      <c r="TF2" s="48"/>
-      <c r="TG2" s="48"/>
-      <c r="TH2" s="48"/>
-      <c r="TI2" s="48"/>
-      <c r="TJ2" s="48"/>
-      <c r="TK2" s="48"/>
-      <c r="TL2" s="48"/>
-      <c r="TM2" s="48"/>
-      <c r="TN2" s="48"/>
-      <c r="TO2" s="48"/>
-      <c r="TP2" s="48"/>
-      <c r="TQ2" s="48"/>
-      <c r="TR2" s="48"/>
-      <c r="TS2" s="48"/>
-      <c r="TT2" s="48"/>
-      <c r="TU2" s="48"/>
-      <c r="TV2" s="48"/>
-      <c r="TW2" s="48"/>
-      <c r="TX2" s="48"/>
-      <c r="TY2" s="48"/>
-      <c r="TZ2" s="48"/>
-      <c r="UA2" s="48"/>
-      <c r="UB2" s="48"/>
-      <c r="UC2" s="48"/>
-      <c r="UD2" s="48"/>
-      <c r="UE2" s="48"/>
-      <c r="UF2" s="48"/>
-      <c r="UG2" s="48"/>
-      <c r="UH2" s="48"/>
-      <c r="UI2" s="48"/>
-      <c r="UJ2" s="48"/>
-      <c r="UK2" s="48"/>
-      <c r="UL2" s="48"/>
-      <c r="UM2" s="48"/>
-      <c r="UN2" s="48"/>
-      <c r="UO2" s="48"/>
-      <c r="UP2" s="48"/>
-      <c r="UQ2" s="48"/>
-      <c r="UR2" s="48"/>
-      <c r="US2" s="48"/>
-      <c r="UT2" s="48"/>
-      <c r="UU2" s="48"/>
-      <c r="UV2" s="48"/>
-      <c r="UW2" s="48"/>
-      <c r="UX2" s="48"/>
-      <c r="UY2" s="48"/>
-      <c r="UZ2" s="48"/>
-      <c r="VA2" s="48"/>
-      <c r="VB2" s="48"/>
-      <c r="VC2" s="48"/>
-      <c r="VD2" s="48"/>
-      <c r="VE2" s="48"/>
-      <c r="VF2" s="48"/>
-      <c r="VG2" s="48"/>
-      <c r="VH2" s="48"/>
-      <c r="VI2" s="48"/>
-      <c r="VJ2" s="48"/>
-      <c r="VK2" s="48"/>
-      <c r="VL2" s="48"/>
-      <c r="VM2" s="48"/>
-      <c r="VN2" s="48"/>
-      <c r="VO2" s="48"/>
-      <c r="VP2" s="48"/>
-      <c r="VQ2" s="48"/>
-      <c r="VR2" s="48"/>
-      <c r="VS2" s="48"/>
-      <c r="VT2" s="48"/>
-      <c r="VU2" s="48"/>
-      <c r="VV2" s="48"/>
-      <c r="VW2" s="48"/>
-      <c r="VX2" s="48"/>
-      <c r="VY2" s="48"/>
-      <c r="VZ2" s="48"/>
-      <c r="WA2" s="48"/>
-      <c r="WB2" s="48"/>
-      <c r="WC2" s="48"/>
-      <c r="WD2" s="48"/>
-      <c r="WE2" s="48"/>
-      <c r="WF2" s="48"/>
-      <c r="WG2" s="48"/>
-      <c r="WH2" s="48"/>
-      <c r="WI2" s="48"/>
-      <c r="WJ2" s="48"/>
-      <c r="WK2" s="48"/>
-      <c r="WL2" s="48"/>
-      <c r="WM2" s="48"/>
-      <c r="WN2" s="48"/>
-      <c r="WO2" s="48"/>
-      <c r="WP2" s="48"/>
-      <c r="WQ2" s="48"/>
-      <c r="WR2" s="48"/>
-      <c r="WS2" s="48"/>
-      <c r="WT2" s="48"/>
-      <c r="WU2" s="48"/>
-      <c r="WV2" s="48"/>
-      <c r="WW2" s="48"/>
-      <c r="WX2" s="48"/>
-      <c r="WY2" s="48"/>
-      <c r="WZ2" s="48"/>
-      <c r="XA2" s="48"/>
-      <c r="XB2" s="48"/>
-      <c r="XC2" s="48"/>
-      <c r="XD2" s="48"/>
-      <c r="XE2" s="48"/>
-      <c r="XF2" s="48"/>
-      <c r="XG2" s="48"/>
-      <c r="XH2" s="48"/>
-      <c r="XI2" s="48"/>
-      <c r="XJ2" s="48"/>
-      <c r="XK2" s="48"/>
-      <c r="XL2" s="48"/>
-      <c r="XM2" s="48"/>
-      <c r="XN2" s="48"/>
-      <c r="XO2" s="48"/>
-      <c r="XP2" s="48"/>
-      <c r="XQ2" s="48"/>
-      <c r="XR2" s="48"/>
-      <c r="XS2" s="48"/>
-      <c r="XT2" s="48"/>
-      <c r="XU2" s="48"/>
-      <c r="XV2" s="48"/>
-      <c r="XW2" s="48"/>
-      <c r="XX2" s="48"/>
-      <c r="XY2" s="48"/>
-      <c r="XZ2" s="48"/>
-      <c r="YA2" s="48"/>
-      <c r="YB2" s="48"/>
-      <c r="YC2" s="48"/>
-      <c r="YD2" s="48"/>
-      <c r="YE2" s="48"/>
-      <c r="YF2" s="48"/>
-      <c r="YG2" s="48"/>
-      <c r="YH2" s="48"/>
-      <c r="YI2" s="48"/>
-      <c r="YJ2" s="48"/>
-      <c r="YK2" s="48"/>
-      <c r="YL2" s="48"/>
-      <c r="YM2" s="48"/>
-      <c r="YN2" s="48"/>
-      <c r="YO2" s="48"/>
-      <c r="YP2" s="48"/>
-      <c r="YQ2" s="48"/>
-      <c r="YR2" s="48"/>
-      <c r="YS2" s="48"/>
-      <c r="YT2" s="48"/>
-      <c r="YU2" s="48"/>
-      <c r="YV2" s="48"/>
-      <c r="YW2" s="48"/>
-      <c r="YX2" s="48"/>
-      <c r="YY2" s="48"/>
-      <c r="YZ2" s="48"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="55"/>
+      <c r="R2" s="55"/>
+      <c r="S2" s="55"/>
+      <c r="T2" s="55"/>
+      <c r="U2" s="55"/>
+      <c r="V2" s="55"/>
+      <c r="W2" s="55"/>
+      <c r="X2" s="55"/>
+      <c r="Y2" s="55"/>
+      <c r="Z2" s="55"/>
+      <c r="AA2" s="55"/>
+      <c r="AB2" s="55"/>
+      <c r="AC2" s="55"/>
+      <c r="AD2" s="55"/>
+      <c r="AE2" s="55"/>
+      <c r="AF2" s="55"/>
+      <c r="AG2" s="55"/>
+      <c r="AH2" s="55"/>
+      <c r="AI2" s="55"/>
+      <c r="AJ2" s="55"/>
+      <c r="AK2" s="55"/>
+      <c r="AL2" s="55"/>
+      <c r="AM2" s="55"/>
+      <c r="AN2" s="55"/>
+      <c r="AO2" s="55"/>
+      <c r="AP2" s="55"/>
+      <c r="AQ2" s="55"/>
+      <c r="AR2" s="55"/>
+      <c r="AS2" s="55"/>
+      <c r="AT2" s="55"/>
+      <c r="AU2" s="55"/>
+      <c r="AV2" s="55"/>
+      <c r="AW2" s="55"/>
+      <c r="AX2" s="55"/>
+      <c r="AY2" s="55"/>
+      <c r="AZ2" s="55"/>
+      <c r="BA2" s="55"/>
+      <c r="BB2" s="55"/>
+      <c r="BC2" s="55"/>
+      <c r="BD2" s="55"/>
+      <c r="BE2" s="55"/>
+      <c r="BF2" s="55"/>
+      <c r="BG2" s="55"/>
+      <c r="BH2" s="55"/>
+      <c r="BI2" s="55"/>
+      <c r="BJ2" s="55"/>
+      <c r="BK2" s="55"/>
+      <c r="BL2" s="55"/>
+      <c r="BM2" s="55"/>
+      <c r="BN2" s="55"/>
+      <c r="BO2" s="55"/>
+      <c r="BP2" s="55"/>
+      <c r="BQ2" s="55"/>
+      <c r="BR2" s="55"/>
+      <c r="BS2" s="55"/>
+      <c r="BT2" s="55"/>
+      <c r="BU2" s="55"/>
+      <c r="BV2" s="55"/>
+      <c r="BW2" s="55"/>
+      <c r="BX2" s="55"/>
+      <c r="BY2" s="55"/>
+      <c r="BZ2" s="55"/>
+      <c r="CA2" s="55"/>
+      <c r="CB2" s="55"/>
+      <c r="CC2" s="55"/>
+      <c r="CD2" s="55"/>
+      <c r="CE2" s="55"/>
+      <c r="CF2" s="55"/>
+      <c r="CG2" s="55"/>
+      <c r="CH2" s="55"/>
+      <c r="CI2" s="55"/>
+      <c r="CJ2" s="55"/>
+      <c r="CK2" s="55"/>
+      <c r="CL2" s="55"/>
+      <c r="CM2" s="55"/>
+      <c r="CN2" s="55"/>
+      <c r="CO2" s="55"/>
+      <c r="CP2" s="55"/>
+      <c r="CQ2" s="55"/>
+      <c r="CR2" s="55"/>
+      <c r="CS2" s="55"/>
+      <c r="CT2" s="55"/>
+      <c r="CU2" s="55"/>
+      <c r="CV2" s="55"/>
+      <c r="CW2" s="55"/>
+      <c r="CX2" s="55"/>
+      <c r="CY2" s="55"/>
+      <c r="CZ2" s="55"/>
+      <c r="DA2" s="55"/>
+      <c r="DB2" s="55"/>
+      <c r="DC2" s="55"/>
+      <c r="DD2" s="55"/>
+      <c r="DE2" s="55"/>
+      <c r="DF2" s="55"/>
+      <c r="DG2" s="55"/>
+      <c r="DH2" s="55"/>
+      <c r="DI2" s="55"/>
+      <c r="DJ2" s="55"/>
+      <c r="DK2" s="55"/>
+      <c r="DL2" s="55"/>
+      <c r="DM2" s="55"/>
+      <c r="DN2" s="55"/>
+      <c r="DO2" s="55"/>
+      <c r="DP2" s="55"/>
+      <c r="DQ2" s="55"/>
+      <c r="DR2" s="55"/>
+      <c r="DS2" s="55"/>
+      <c r="DT2" s="55"/>
+      <c r="DU2" s="55"/>
+      <c r="DV2" s="55"/>
+      <c r="DW2" s="55"/>
+      <c r="DX2" s="55"/>
+      <c r="DY2" s="55"/>
+      <c r="DZ2" s="55"/>
+      <c r="EA2" s="55"/>
+      <c r="EB2" s="55"/>
+      <c r="EC2" s="55"/>
+      <c r="ED2" s="55"/>
+      <c r="EE2" s="55"/>
+      <c r="EF2" s="55"/>
+      <c r="EG2" s="55"/>
+      <c r="EH2" s="55"/>
+      <c r="EI2" s="55"/>
+      <c r="EJ2" s="55"/>
+      <c r="EK2" s="55"/>
+      <c r="EL2" s="55"/>
+      <c r="EM2" s="55"/>
+      <c r="EN2" s="55"/>
+      <c r="EO2" s="55"/>
+      <c r="EP2" s="55"/>
+      <c r="EQ2" s="55"/>
+      <c r="ER2" s="55"/>
+      <c r="ES2" s="55"/>
+      <c r="ET2" s="55"/>
+      <c r="EU2" s="55"/>
+      <c r="EV2" s="55"/>
+      <c r="EW2" s="55"/>
+      <c r="EX2" s="55"/>
+      <c r="EY2" s="55"/>
+      <c r="EZ2" s="55"/>
+      <c r="FA2" s="55"/>
+      <c r="FB2" s="55"/>
+      <c r="FC2" s="55"/>
+      <c r="FD2" s="55"/>
+      <c r="FE2" s="55"/>
+      <c r="FF2" s="55"/>
+      <c r="FG2" s="55"/>
+      <c r="FH2" s="55"/>
+      <c r="FI2" s="55"/>
+      <c r="FJ2" s="55"/>
+      <c r="FK2" s="55"/>
+      <c r="FL2" s="55"/>
+      <c r="FM2" s="55"/>
+      <c r="FN2" s="55"/>
+      <c r="FO2" s="55"/>
+      <c r="FP2" s="55"/>
+      <c r="FQ2" s="55"/>
+      <c r="FR2" s="55"/>
+      <c r="FS2" s="55"/>
+      <c r="FT2" s="55"/>
+      <c r="FU2" s="55"/>
+      <c r="FV2" s="55"/>
+      <c r="FW2" s="55"/>
+      <c r="FX2" s="55"/>
+      <c r="FY2" s="55"/>
+      <c r="FZ2" s="55"/>
+      <c r="GA2" s="55"/>
+      <c r="GB2" s="55"/>
+      <c r="GC2" s="55"/>
+      <c r="GD2" s="55"/>
+      <c r="GE2" s="55"/>
+      <c r="GF2" s="55"/>
+      <c r="GG2" s="55"/>
+      <c r="GH2" s="55"/>
+      <c r="GI2" s="55"/>
+      <c r="GJ2" s="55"/>
+      <c r="GK2" s="55"/>
+      <c r="GL2" s="55"/>
+      <c r="GM2" s="55"/>
+      <c r="GN2" s="55"/>
+      <c r="GO2" s="55"/>
+      <c r="GP2" s="55"/>
+      <c r="GQ2" s="55"/>
+      <c r="GR2" s="55"/>
+      <c r="GS2" s="55"/>
+      <c r="GT2" s="55"/>
+      <c r="GU2" s="55"/>
+      <c r="GV2" s="55"/>
+      <c r="GW2" s="55"/>
+      <c r="GX2" s="55"/>
+      <c r="GY2" s="55"/>
+      <c r="GZ2" s="55"/>
+      <c r="HA2" s="55"/>
+      <c r="HB2" s="55"/>
+      <c r="HC2" s="55"/>
+      <c r="HD2" s="55"/>
+      <c r="HE2" s="55"/>
+      <c r="HF2" s="55"/>
+      <c r="HG2" s="55"/>
+      <c r="HH2" s="55"/>
+      <c r="HI2" s="55"/>
+      <c r="HJ2" s="55"/>
+      <c r="HK2" s="55"/>
+      <c r="HL2" s="55"/>
+      <c r="HM2" s="55"/>
+      <c r="HN2" s="55"/>
+      <c r="HO2" s="55"/>
+      <c r="HP2" s="55"/>
+      <c r="HQ2" s="55"/>
+      <c r="HR2" s="55"/>
+      <c r="HS2" s="55"/>
+      <c r="HT2" s="55"/>
+      <c r="HU2" s="55"/>
+      <c r="HV2" s="55"/>
+      <c r="HW2" s="55"/>
+      <c r="HX2" s="55"/>
+      <c r="HY2" s="55"/>
+      <c r="HZ2" s="55"/>
+      <c r="IA2" s="55"/>
+      <c r="IB2" s="55"/>
+      <c r="IC2" s="55"/>
+      <c r="ID2" s="55"/>
+      <c r="IE2" s="55"/>
+      <c r="IF2" s="55"/>
+      <c r="IG2" s="55"/>
+      <c r="IH2" s="55"/>
+      <c r="II2" s="55"/>
+      <c r="IJ2" s="55"/>
+      <c r="IK2" s="55"/>
+      <c r="IL2" s="55"/>
+      <c r="IM2" s="55"/>
+      <c r="IN2" s="55"/>
+      <c r="IO2" s="55"/>
+      <c r="IP2" s="55"/>
+      <c r="IQ2" s="55"/>
+      <c r="IR2" s="55"/>
+      <c r="IS2" s="55"/>
+      <c r="IT2" s="55"/>
+      <c r="IU2" s="55"/>
+      <c r="IV2" s="55"/>
+      <c r="IW2" s="55"/>
+      <c r="IX2" s="55"/>
+      <c r="IY2" s="55"/>
+      <c r="IZ2" s="55"/>
+      <c r="JA2" s="55"/>
+      <c r="JB2" s="55"/>
+      <c r="JC2" s="55"/>
+      <c r="JD2" s="55"/>
+      <c r="JE2" s="55"/>
+      <c r="JF2" s="55"/>
+      <c r="JG2" s="55"/>
+      <c r="JH2" s="55"/>
+      <c r="JI2" s="55"/>
+      <c r="JJ2" s="55"/>
+      <c r="JK2" s="55"/>
+      <c r="JL2" s="55"/>
+      <c r="JM2" s="55"/>
+      <c r="JN2" s="55"/>
+      <c r="JO2" s="55"/>
+      <c r="JP2" s="55"/>
+      <c r="JQ2" s="55"/>
+      <c r="JR2" s="55"/>
+      <c r="JS2" s="55"/>
+      <c r="JT2" s="55"/>
+      <c r="JU2" s="55"/>
+      <c r="JV2" s="55"/>
+      <c r="JW2" s="55"/>
+      <c r="JX2" s="55"/>
+      <c r="JY2" s="55"/>
+      <c r="JZ2" s="55"/>
+      <c r="KA2" s="55"/>
+      <c r="KB2" s="55"/>
+      <c r="KC2" s="55"/>
+      <c r="KD2" s="55"/>
+      <c r="KE2" s="55"/>
+      <c r="KF2" s="55"/>
+      <c r="KG2" s="55"/>
+      <c r="KH2" s="55"/>
+      <c r="KI2" s="55"/>
+      <c r="KJ2" s="55"/>
+      <c r="KK2" s="55"/>
+      <c r="KL2" s="55"/>
+      <c r="KM2" s="55"/>
+      <c r="KN2" s="55"/>
+      <c r="KO2" s="55"/>
+      <c r="KP2" s="55"/>
+      <c r="KQ2" s="55"/>
+      <c r="KR2" s="55"/>
+      <c r="KS2" s="55"/>
+      <c r="KT2" s="55"/>
+      <c r="KU2" s="55"/>
+      <c r="KV2" s="55"/>
+      <c r="KW2" s="55"/>
+      <c r="KX2" s="55"/>
+      <c r="KY2" s="55"/>
+      <c r="KZ2" s="55"/>
+      <c r="LA2" s="55"/>
+      <c r="LB2" s="55"/>
+      <c r="LC2" s="55"/>
+      <c r="LD2" s="55"/>
+      <c r="LE2" s="55"/>
+      <c r="LF2" s="55"/>
+      <c r="LG2" s="55"/>
+      <c r="LH2" s="55"/>
+      <c r="LI2" s="55"/>
+      <c r="LJ2" s="55"/>
+      <c r="LK2" s="55"/>
+      <c r="LL2" s="55"/>
+      <c r="LM2" s="55"/>
+      <c r="LN2" s="55"/>
+      <c r="LO2" s="55"/>
+      <c r="LP2" s="55"/>
+      <c r="LQ2" s="55"/>
+      <c r="LR2" s="55"/>
+      <c r="LS2" s="55"/>
+      <c r="LT2" s="55"/>
+      <c r="LU2" s="55"/>
+      <c r="LV2" s="55"/>
+      <c r="LW2" s="55"/>
+      <c r="LX2" s="55"/>
+      <c r="LY2" s="55"/>
+      <c r="LZ2" s="55"/>
+      <c r="MA2" s="55"/>
+      <c r="MB2" s="55"/>
+      <c r="MC2" s="55"/>
+      <c r="MD2" s="55"/>
+      <c r="ME2" s="55"/>
+      <c r="MF2" s="55"/>
+      <c r="MG2" s="55"/>
+      <c r="MH2" s="55"/>
+      <c r="MI2" s="55"/>
+      <c r="MJ2" s="55"/>
+      <c r="MK2" s="55"/>
+      <c r="ML2" s="55"/>
+      <c r="MM2" s="55"/>
+      <c r="MN2" s="55"/>
+      <c r="MO2" s="55"/>
+      <c r="MP2" s="55"/>
+      <c r="MQ2" s="55"/>
+      <c r="MR2" s="55"/>
+      <c r="MS2" s="55"/>
+      <c r="MT2" s="55"/>
+      <c r="MU2" s="55"/>
+      <c r="MV2" s="55"/>
+      <c r="MW2" s="55"/>
+      <c r="MX2" s="55"/>
+      <c r="MY2" s="55"/>
+      <c r="MZ2" s="55"/>
+      <c r="NA2" s="55"/>
+      <c r="NB2" s="55"/>
+      <c r="NC2" s="55"/>
+      <c r="ND2" s="55"/>
+      <c r="NE2" s="55"/>
+      <c r="NF2" s="55"/>
+      <c r="NG2" s="55"/>
+      <c r="NH2" s="55"/>
+      <c r="NI2" s="55"/>
+      <c r="NJ2" s="55"/>
+      <c r="NK2" s="55"/>
+      <c r="NL2" s="55"/>
+      <c r="NM2" s="55"/>
+      <c r="NN2" s="55"/>
+      <c r="NO2" s="55"/>
+      <c r="NP2" s="55"/>
+      <c r="NQ2" s="55"/>
+      <c r="NR2" s="55"/>
+      <c r="NS2" s="55"/>
+      <c r="NT2" s="55"/>
+      <c r="NU2" s="55"/>
+      <c r="NV2" s="55"/>
+      <c r="NW2" s="55"/>
+      <c r="NX2" s="55"/>
+      <c r="NY2" s="55"/>
+      <c r="NZ2" s="55"/>
+      <c r="OA2" s="55"/>
+      <c r="OB2" s="55"/>
+      <c r="OC2" s="55"/>
+      <c r="OD2" s="55"/>
+      <c r="OE2" s="55"/>
+      <c r="OF2" s="55"/>
+      <c r="OG2" s="55"/>
+      <c r="OH2" s="55"/>
+      <c r="OI2" s="55"/>
+      <c r="OJ2" s="55"/>
+      <c r="OK2" s="55"/>
+      <c r="OL2" s="55"/>
+      <c r="OM2" s="55"/>
+      <c r="ON2" s="55"/>
+      <c r="OO2" s="55"/>
+      <c r="OP2" s="55"/>
+      <c r="OQ2" s="55"/>
+      <c r="OR2" s="55"/>
+      <c r="OS2" s="55"/>
+      <c r="OT2" s="55"/>
+      <c r="OU2" s="55"/>
+      <c r="OV2" s="55"/>
+      <c r="OW2" s="55"/>
+      <c r="OX2" s="55"/>
+      <c r="OY2" s="55"/>
+      <c r="OZ2" s="55"/>
+      <c r="PA2" s="55"/>
+      <c r="PB2" s="55"/>
+      <c r="PC2" s="55"/>
+      <c r="PD2" s="55"/>
+      <c r="PE2" s="55"/>
+      <c r="PF2" s="55"/>
+      <c r="PG2" s="55"/>
+      <c r="PH2" s="55"/>
+      <c r="PI2" s="55"/>
+      <c r="PJ2" s="55"/>
+      <c r="PK2" s="55"/>
+      <c r="PL2" s="55"/>
+      <c r="PM2" s="55"/>
+      <c r="PN2" s="55"/>
+      <c r="PO2" s="55"/>
+      <c r="PP2" s="55"/>
+      <c r="PQ2" s="55"/>
+      <c r="PR2" s="55"/>
+      <c r="PS2" s="55"/>
+      <c r="PT2" s="55"/>
+      <c r="PU2" s="55"/>
+      <c r="PV2" s="55"/>
+      <c r="PW2" s="55"/>
+      <c r="PX2" s="55"/>
+      <c r="PY2" s="55"/>
+      <c r="PZ2" s="55"/>
+      <c r="QA2" s="55"/>
+      <c r="QB2" s="55"/>
+      <c r="QC2" s="55"/>
+      <c r="QD2" s="55"/>
+      <c r="QE2" s="55"/>
+      <c r="QF2" s="55"/>
+      <c r="QG2" s="55"/>
+      <c r="QH2" s="55"/>
+      <c r="QI2" s="55"/>
+      <c r="QJ2" s="55"/>
+      <c r="QK2" s="55"/>
+      <c r="QL2" s="55"/>
+      <c r="QM2" s="55"/>
+      <c r="QN2" s="55"/>
+      <c r="QO2" s="55"/>
+      <c r="QP2" s="55"/>
+      <c r="QQ2" s="55"/>
+      <c r="QR2" s="55"/>
+      <c r="QS2" s="55"/>
+      <c r="QT2" s="55"/>
+      <c r="QU2" s="55"/>
+      <c r="QV2" s="55"/>
+      <c r="QW2" s="55"/>
+      <c r="QX2" s="55"/>
+      <c r="QY2" s="55"/>
+      <c r="QZ2" s="55"/>
+      <c r="RA2" s="55"/>
+      <c r="RB2" s="55"/>
+      <c r="RC2" s="55"/>
+      <c r="RD2" s="55"/>
+      <c r="RE2" s="55"/>
+      <c r="RF2" s="55"/>
+      <c r="RG2" s="55"/>
+      <c r="RH2" s="55"/>
+      <c r="RI2" s="55"/>
+      <c r="RJ2" s="55"/>
+      <c r="RK2" s="55"/>
+      <c r="RL2" s="55"/>
+      <c r="RM2" s="55"/>
+      <c r="RN2" s="55"/>
+      <c r="RO2" s="55"/>
+      <c r="RP2" s="55"/>
+      <c r="RQ2" s="55"/>
+      <c r="RR2" s="55"/>
+      <c r="RS2" s="55"/>
+      <c r="RT2" s="55"/>
+      <c r="RU2" s="55"/>
+      <c r="RV2" s="55"/>
+      <c r="RW2" s="55"/>
+      <c r="RX2" s="55"/>
+      <c r="RY2" s="55"/>
+      <c r="RZ2" s="55"/>
+      <c r="SA2" s="55"/>
+      <c r="SB2" s="55"/>
+      <c r="SC2" s="55"/>
+      <c r="SD2" s="55"/>
+      <c r="SE2" s="55"/>
+      <c r="SF2" s="55"/>
+      <c r="SG2" s="55"/>
+      <c r="SH2" s="55"/>
+      <c r="SI2" s="55"/>
+      <c r="SJ2" s="55"/>
+      <c r="SK2" s="55"/>
+      <c r="SL2" s="55"/>
+      <c r="SM2" s="55"/>
+      <c r="SN2" s="55"/>
+      <c r="SO2" s="55"/>
+      <c r="SP2" s="55"/>
+      <c r="SQ2" s="55"/>
+      <c r="SR2" s="55"/>
+      <c r="SS2" s="55"/>
+      <c r="ST2" s="55"/>
+      <c r="SU2" s="55"/>
+      <c r="SV2" s="55"/>
+      <c r="SW2" s="55"/>
+      <c r="SX2" s="55"/>
+      <c r="SY2" s="55"/>
+      <c r="SZ2" s="55"/>
+      <c r="TA2" s="55"/>
+      <c r="TB2" s="55"/>
+      <c r="TC2" s="55"/>
+      <c r="TD2" s="55"/>
+      <c r="TE2" s="55"/>
+      <c r="TF2" s="55"/>
+      <c r="TG2" s="55"/>
+      <c r="TH2" s="55"/>
+      <c r="TI2" s="55"/>
+      <c r="TJ2" s="55"/>
+      <c r="TK2" s="55"/>
+      <c r="TL2" s="55"/>
+      <c r="TM2" s="55"/>
+      <c r="TN2" s="55"/>
+      <c r="TO2" s="55"/>
+      <c r="TP2" s="55"/>
+      <c r="TQ2" s="55"/>
+      <c r="TR2" s="55"/>
+      <c r="TS2" s="55"/>
+      <c r="TT2" s="55"/>
+      <c r="TU2" s="55"/>
+      <c r="TV2" s="55"/>
+      <c r="TW2" s="55"/>
+      <c r="TX2" s="55"/>
+      <c r="TY2" s="55"/>
+      <c r="TZ2" s="55"/>
+      <c r="UA2" s="55"/>
+      <c r="UB2" s="55"/>
+      <c r="UC2" s="55"/>
+      <c r="UD2" s="55"/>
+      <c r="UE2" s="55"/>
+      <c r="UF2" s="55"/>
+      <c r="UG2" s="55"/>
+      <c r="UH2" s="55"/>
+      <c r="UI2" s="55"/>
+      <c r="UJ2" s="55"/>
+      <c r="UK2" s="55"/>
+      <c r="UL2" s="55"/>
+      <c r="UM2" s="55"/>
+      <c r="UN2" s="55"/>
+      <c r="UO2" s="55"/>
+      <c r="UP2" s="55"/>
+      <c r="UQ2" s="55"/>
+      <c r="UR2" s="55"/>
+      <c r="US2" s="55"/>
+      <c r="UT2" s="55"/>
+      <c r="UU2" s="55"/>
+      <c r="UV2" s="55"/>
+      <c r="UW2" s="55"/>
+      <c r="UX2" s="55"/>
+      <c r="UY2" s="55"/>
+      <c r="UZ2" s="55"/>
+      <c r="VA2" s="55"/>
+      <c r="VB2" s="55"/>
+      <c r="VC2" s="55"/>
+      <c r="VD2" s="55"/>
+      <c r="VE2" s="55"/>
+      <c r="VF2" s="55"/>
+      <c r="VG2" s="55"/>
+      <c r="VH2" s="55"/>
+      <c r="VI2" s="55"/>
+      <c r="VJ2" s="55"/>
+      <c r="VK2" s="55"/>
+      <c r="VL2" s="55"/>
+      <c r="VM2" s="55"/>
+      <c r="VN2" s="55"/>
+      <c r="VO2" s="55"/>
+      <c r="VP2" s="55"/>
+      <c r="VQ2" s="55"/>
+      <c r="VR2" s="55"/>
+      <c r="VS2" s="55"/>
+      <c r="VT2" s="55"/>
+      <c r="VU2" s="55"/>
+      <c r="VV2" s="55"/>
+      <c r="VW2" s="55"/>
+      <c r="VX2" s="55"/>
+      <c r="VY2" s="55"/>
+      <c r="VZ2" s="55"/>
+      <c r="WA2" s="55"/>
+      <c r="WB2" s="55"/>
+      <c r="WC2" s="55"/>
+      <c r="WD2" s="55"/>
+      <c r="WE2" s="55"/>
+      <c r="WF2" s="55"/>
+      <c r="WG2" s="55"/>
+      <c r="WH2" s="55"/>
+      <c r="WI2" s="55"/>
+      <c r="WJ2" s="55"/>
+      <c r="WK2" s="55"/>
+      <c r="WL2" s="55"/>
+      <c r="WM2" s="55"/>
+      <c r="WN2" s="55"/>
+      <c r="WO2" s="55"/>
+      <c r="WP2" s="55"/>
+      <c r="WQ2" s="55"/>
+      <c r="WR2" s="55"/>
+      <c r="WS2" s="55"/>
+      <c r="WT2" s="55"/>
+      <c r="WU2" s="55"/>
+      <c r="WV2" s="55"/>
+      <c r="WW2" s="55"/>
+      <c r="WX2" s="55"/>
+      <c r="WY2" s="55"/>
+      <c r="WZ2" s="55"/>
+      <c r="XA2" s="55"/>
+      <c r="XB2" s="55"/>
+      <c r="XC2" s="55"/>
+      <c r="XD2" s="55"/>
+      <c r="XE2" s="55"/>
+      <c r="XF2" s="55"/>
+      <c r="XG2" s="55"/>
+      <c r="XH2" s="55"/>
+      <c r="XI2" s="55"/>
+      <c r="XJ2" s="55"/>
+      <c r="XK2" s="55"/>
+      <c r="XL2" s="55"/>
+      <c r="XM2" s="55"/>
+      <c r="XN2" s="55"/>
+      <c r="XO2" s="55"/>
+      <c r="XP2" s="55"/>
+      <c r="XQ2" s="55"/>
+      <c r="XR2" s="55"/>
+      <c r="XS2" s="55"/>
+      <c r="XT2" s="55"/>
+      <c r="XU2" s="55"/>
+      <c r="XV2" s="55"/>
+      <c r="XW2" s="55"/>
+      <c r="XX2" s="55"/>
+      <c r="XY2" s="55"/>
+      <c r="XZ2" s="55"/>
+      <c r="YA2" s="55"/>
+      <c r="YB2" s="55"/>
+      <c r="YC2" s="55"/>
+      <c r="YD2" s="55"/>
+      <c r="YE2" s="55"/>
+      <c r="YF2" s="55"/>
+      <c r="YG2" s="55"/>
+      <c r="YH2" s="55"/>
+      <c r="YI2" s="55"/>
+      <c r="YJ2" s="55"/>
+      <c r="YK2" s="55"/>
+      <c r="YL2" s="55"/>
+      <c r="YM2" s="55"/>
+      <c r="YN2" s="55"/>
+      <c r="YO2" s="55"/>
+      <c r="YP2" s="55"/>
+      <c r="YQ2" s="55"/>
+      <c r="YR2" s="55"/>
+      <c r="YS2" s="55"/>
+      <c r="YT2" s="55"/>
+      <c r="YU2" s="55"/>
+      <c r="YV2" s="55"/>
+      <c r="YW2" s="55"/>
+      <c r="YX2" s="55"/>
+      <c r="YY2" s="55"/>
+      <c r="YZ2" s="55"/>
     </row>
     <row r="3" spans="1:676" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="57" t="s">
+      <c r="C3" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="57" t="s">
+      <c r="D3" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="53" t="s">
+      <c r="E3" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="53"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="53"/>
-      <c r="N3" s="53"/>
-      <c r="O3" s="53"/>
-      <c r="P3" s="53"/>
-      <c r="Q3" s="53"/>
-      <c r="R3" s="53"/>
-      <c r="S3" s="53"/>
-      <c r="T3" s="53"/>
-      <c r="U3" s="53"/>
-      <c r="V3" s="53"/>
-      <c r="W3" s="53"/>
-      <c r="X3" s="53"/>
-      <c r="Y3" s="53"/>
-      <c r="Z3" s="53"/>
-      <c r="AA3" s="53"/>
-      <c r="AB3" s="53"/>
-      <c r="AC3" s="53"/>
-      <c r="AD3" s="53"/>
-      <c r="AE3" s="53"/>
-      <c r="AF3" s="53"/>
-      <c r="AG3" s="53"/>
-      <c r="AH3" s="53"/>
-      <c r="AI3" s="53"/>
-      <c r="AJ3" s="53"/>
-      <c r="AK3" s="53" t="s">
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="49"/>
+      <c r="N3" s="49"/>
+      <c r="O3" s="49"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="49"/>
+      <c r="S3" s="49"/>
+      <c r="T3" s="49"/>
+      <c r="U3" s="49"/>
+      <c r="V3" s="49"/>
+      <c r="W3" s="49"/>
+      <c r="X3" s="49"/>
+      <c r="Y3" s="49"/>
+      <c r="Z3" s="49"/>
+      <c r="AA3" s="49"/>
+      <c r="AB3" s="49"/>
+      <c r="AC3" s="49"/>
+      <c r="AD3" s="49"/>
+      <c r="AE3" s="49"/>
+      <c r="AF3" s="49"/>
+      <c r="AG3" s="49"/>
+      <c r="AH3" s="49"/>
+      <c r="AI3" s="49"/>
+      <c r="AJ3" s="49"/>
+      <c r="AK3" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="AL3" s="53"/>
-      <c r="AM3" s="53"/>
-      <c r="AN3" s="53"/>
-      <c r="AO3" s="53"/>
-      <c r="AP3" s="53"/>
-      <c r="AQ3" s="53"/>
-      <c r="AR3" s="53"/>
-      <c r="AS3" s="53"/>
-      <c r="AT3" s="53"/>
-      <c r="AU3" s="53"/>
-      <c r="AV3" s="53"/>
-      <c r="AW3" s="53"/>
-      <c r="AX3" s="53"/>
-      <c r="AY3" s="53"/>
-      <c r="AZ3" s="53"/>
-      <c r="BA3" s="53"/>
-      <c r="BB3" s="53"/>
-      <c r="BC3" s="53"/>
-      <c r="BD3" s="53"/>
-      <c r="BE3" s="53"/>
-      <c r="BF3" s="53"/>
-      <c r="BG3" s="53"/>
-      <c r="BH3" s="53"/>
-      <c r="BI3" s="53"/>
-      <c r="BJ3" s="53"/>
-      <c r="BK3" s="53"/>
-      <c r="BL3" s="53"/>
-      <c r="BM3" s="53"/>
-      <c r="BN3" s="53"/>
-      <c r="BO3" s="53"/>
-      <c r="BP3" s="53"/>
-      <c r="BQ3" s="53" t="s">
+      <c r="AL3" s="49"/>
+      <c r="AM3" s="49"/>
+      <c r="AN3" s="49"/>
+      <c r="AO3" s="49"/>
+      <c r="AP3" s="49"/>
+      <c r="AQ3" s="49"/>
+      <c r="AR3" s="49"/>
+      <c r="AS3" s="49"/>
+      <c r="AT3" s="49"/>
+      <c r="AU3" s="49"/>
+      <c r="AV3" s="49"/>
+      <c r="AW3" s="49"/>
+      <c r="AX3" s="49"/>
+      <c r="AY3" s="49"/>
+      <c r="AZ3" s="49"/>
+      <c r="BA3" s="49"/>
+      <c r="BB3" s="49"/>
+      <c r="BC3" s="49"/>
+      <c r="BD3" s="49"/>
+      <c r="BE3" s="49"/>
+      <c r="BF3" s="49"/>
+      <c r="BG3" s="49"/>
+      <c r="BH3" s="49"/>
+      <c r="BI3" s="49"/>
+      <c r="BJ3" s="49"/>
+      <c r="BK3" s="49"/>
+      <c r="BL3" s="49"/>
+      <c r="BM3" s="49"/>
+      <c r="BN3" s="49"/>
+      <c r="BO3" s="49"/>
+      <c r="BP3" s="49"/>
+      <c r="BQ3" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="BR3" s="53"/>
-      <c r="BS3" s="53"/>
-      <c r="BT3" s="53"/>
-      <c r="BU3" s="53"/>
-      <c r="BV3" s="53"/>
-      <c r="BW3" s="53"/>
-      <c r="BX3" s="53"/>
-      <c r="BY3" s="53"/>
-      <c r="BZ3" s="53"/>
-      <c r="CA3" s="53"/>
-      <c r="CB3" s="53"/>
-      <c r="CC3" s="53"/>
-      <c r="CD3" s="53"/>
-      <c r="CE3" s="53"/>
-      <c r="CF3" s="53"/>
-      <c r="CG3" s="53"/>
-      <c r="CH3" s="53"/>
-      <c r="CI3" s="53"/>
-      <c r="CJ3" s="53"/>
-      <c r="CK3" s="53"/>
-      <c r="CL3" s="53"/>
-      <c r="CM3" s="53"/>
-      <c r="CN3" s="53"/>
-      <c r="CO3" s="53"/>
-      <c r="CP3" s="53"/>
-      <c r="CQ3" s="53"/>
-      <c r="CR3" s="53"/>
-      <c r="CS3" s="53"/>
-      <c r="CT3" s="53"/>
-      <c r="CU3" s="53"/>
-      <c r="CV3" s="53"/>
-      <c r="CW3" s="53" t="s">
+      <c r="BR3" s="49"/>
+      <c r="BS3" s="49"/>
+      <c r="BT3" s="49"/>
+      <c r="BU3" s="49"/>
+      <c r="BV3" s="49"/>
+      <c r="BW3" s="49"/>
+      <c r="BX3" s="49"/>
+      <c r="BY3" s="49"/>
+      <c r="BZ3" s="49"/>
+      <c r="CA3" s="49"/>
+      <c r="CB3" s="49"/>
+      <c r="CC3" s="49"/>
+      <c r="CD3" s="49"/>
+      <c r="CE3" s="49"/>
+      <c r="CF3" s="49"/>
+      <c r="CG3" s="49"/>
+      <c r="CH3" s="49"/>
+      <c r="CI3" s="49"/>
+      <c r="CJ3" s="49"/>
+      <c r="CK3" s="49"/>
+      <c r="CL3" s="49"/>
+      <c r="CM3" s="49"/>
+      <c r="CN3" s="49"/>
+      <c r="CO3" s="49"/>
+      <c r="CP3" s="49"/>
+      <c r="CQ3" s="49"/>
+      <c r="CR3" s="49"/>
+      <c r="CS3" s="49"/>
+      <c r="CT3" s="49"/>
+      <c r="CU3" s="49"/>
+      <c r="CV3" s="49"/>
+      <c r="CW3" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="CX3" s="53"/>
-      <c r="CY3" s="53"/>
-      <c r="CZ3" s="53"/>
-      <c r="DA3" s="53"/>
-      <c r="DB3" s="53"/>
-      <c r="DC3" s="53"/>
-      <c r="DD3" s="53"/>
-      <c r="DE3" s="53"/>
-      <c r="DF3" s="53"/>
-      <c r="DG3" s="53"/>
-      <c r="DH3" s="53"/>
-      <c r="DI3" s="53"/>
-      <c r="DJ3" s="53"/>
-      <c r="DK3" s="53"/>
-      <c r="DL3" s="53"/>
-      <c r="DM3" s="53"/>
-      <c r="DN3" s="53"/>
-      <c r="DO3" s="53"/>
-      <c r="DP3" s="53"/>
-      <c r="DQ3" s="53"/>
-      <c r="DR3" s="53"/>
-      <c r="DS3" s="53"/>
-      <c r="DT3" s="53"/>
-      <c r="DU3" s="53"/>
-      <c r="DV3" s="53"/>
-      <c r="DW3" s="53"/>
-      <c r="DX3" s="53"/>
-      <c r="DY3" s="53"/>
-      <c r="DZ3" s="53"/>
-      <c r="EA3" s="53"/>
-      <c r="EB3" s="53"/>
-      <c r="EC3" s="54" t="s">
+      <c r="CX3" s="49"/>
+      <c r="CY3" s="49"/>
+      <c r="CZ3" s="49"/>
+      <c r="DA3" s="49"/>
+      <c r="DB3" s="49"/>
+      <c r="DC3" s="49"/>
+      <c r="DD3" s="49"/>
+      <c r="DE3" s="49"/>
+      <c r="DF3" s="49"/>
+      <c r="DG3" s="49"/>
+      <c r="DH3" s="49"/>
+      <c r="DI3" s="49"/>
+      <c r="DJ3" s="49"/>
+      <c r="DK3" s="49"/>
+      <c r="DL3" s="49"/>
+      <c r="DM3" s="49"/>
+      <c r="DN3" s="49"/>
+      <c r="DO3" s="49"/>
+      <c r="DP3" s="49"/>
+      <c r="DQ3" s="49"/>
+      <c r="DR3" s="49"/>
+      <c r="DS3" s="49"/>
+      <c r="DT3" s="49"/>
+      <c r="DU3" s="49"/>
+      <c r="DV3" s="49"/>
+      <c r="DW3" s="49"/>
+      <c r="DX3" s="49"/>
+      <c r="DY3" s="49"/>
+      <c r="DZ3" s="49"/>
+      <c r="EA3" s="49"/>
+      <c r="EB3" s="49"/>
+      <c r="EC3" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="ED3" s="54"/>
-      <c r="EE3" s="54"/>
-      <c r="EF3" s="54"/>
-      <c r="EG3" s="54"/>
-      <c r="EH3" s="54"/>
-      <c r="EI3" s="54"/>
-      <c r="EJ3" s="54"/>
-      <c r="EK3" s="54"/>
-      <c r="EL3" s="54"/>
-      <c r="EM3" s="54"/>
-      <c r="EN3" s="54"/>
-      <c r="EO3" s="54"/>
-      <c r="EP3" s="54"/>
-      <c r="EQ3" s="54"/>
-      <c r="ER3" s="54"/>
-      <c r="ES3" s="54"/>
-      <c r="ET3" s="54"/>
-      <c r="EU3" s="54"/>
-      <c r="EV3" s="54"/>
-      <c r="EW3" s="54"/>
-      <c r="EX3" s="54"/>
-      <c r="EY3" s="54"/>
-      <c r="EZ3" s="54"/>
-      <c r="FA3" s="54"/>
-      <c r="FB3" s="54"/>
-      <c r="FC3" s="54"/>
-      <c r="FD3" s="54"/>
-      <c r="FE3" s="54"/>
-      <c r="FF3" s="54"/>
-      <c r="FG3" s="54"/>
-      <c r="FH3" s="54"/>
-      <c r="FI3" s="53" t="s">
+      <c r="ED3" s="46"/>
+      <c r="EE3" s="46"/>
+      <c r="EF3" s="46"/>
+      <c r="EG3" s="46"/>
+      <c r="EH3" s="46"/>
+      <c r="EI3" s="46"/>
+      <c r="EJ3" s="46"/>
+      <c r="EK3" s="46"/>
+      <c r="EL3" s="46"/>
+      <c r="EM3" s="46"/>
+      <c r="EN3" s="46"/>
+      <c r="EO3" s="46"/>
+      <c r="EP3" s="46"/>
+      <c r="EQ3" s="46"/>
+      <c r="ER3" s="46"/>
+      <c r="ES3" s="46"/>
+      <c r="ET3" s="46"/>
+      <c r="EU3" s="46"/>
+      <c r="EV3" s="46"/>
+      <c r="EW3" s="46"/>
+      <c r="EX3" s="46"/>
+      <c r="EY3" s="46"/>
+      <c r="EZ3" s="46"/>
+      <c r="FA3" s="46"/>
+      <c r="FB3" s="46"/>
+      <c r="FC3" s="46"/>
+      <c r="FD3" s="46"/>
+      <c r="FE3" s="46"/>
+      <c r="FF3" s="46"/>
+      <c r="FG3" s="46"/>
+      <c r="FH3" s="46"/>
+      <c r="FI3" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="FJ3" s="53"/>
-      <c r="FK3" s="53"/>
-      <c r="FL3" s="53"/>
-      <c r="FM3" s="53"/>
-      <c r="FN3" s="53"/>
-      <c r="FO3" s="53"/>
-      <c r="FP3" s="53"/>
-      <c r="FQ3" s="53"/>
-      <c r="FR3" s="53"/>
-      <c r="FS3" s="53"/>
-      <c r="FT3" s="53"/>
-      <c r="FU3" s="53"/>
-      <c r="FV3" s="53"/>
-      <c r="FW3" s="53"/>
-      <c r="FX3" s="53"/>
-      <c r="FY3" s="53"/>
-      <c r="FZ3" s="53"/>
-      <c r="GA3" s="53"/>
-      <c r="GB3" s="53"/>
-      <c r="GC3" s="53"/>
-      <c r="GD3" s="53"/>
-      <c r="GE3" s="53"/>
-      <c r="GF3" s="53"/>
-      <c r="GG3" s="53"/>
-      <c r="GH3" s="53"/>
-      <c r="GI3" s="53"/>
-      <c r="GJ3" s="53"/>
-      <c r="GK3" s="53"/>
-      <c r="GL3" s="53"/>
-      <c r="GM3" s="53"/>
-      <c r="GN3" s="53"/>
-      <c r="GO3" s="53" t="s">
+      <c r="FJ3" s="49"/>
+      <c r="FK3" s="49"/>
+      <c r="FL3" s="49"/>
+      <c r="FM3" s="49"/>
+      <c r="FN3" s="49"/>
+      <c r="FO3" s="49"/>
+      <c r="FP3" s="49"/>
+      <c r="FQ3" s="49"/>
+      <c r="FR3" s="49"/>
+      <c r="FS3" s="49"/>
+      <c r="FT3" s="49"/>
+      <c r="FU3" s="49"/>
+      <c r="FV3" s="49"/>
+      <c r="FW3" s="49"/>
+      <c r="FX3" s="49"/>
+      <c r="FY3" s="49"/>
+      <c r="FZ3" s="49"/>
+      <c r="GA3" s="49"/>
+      <c r="GB3" s="49"/>
+      <c r="GC3" s="49"/>
+      <c r="GD3" s="49"/>
+      <c r="GE3" s="49"/>
+      <c r="GF3" s="49"/>
+      <c r="GG3" s="49"/>
+      <c r="GH3" s="49"/>
+      <c r="GI3" s="49"/>
+      <c r="GJ3" s="49"/>
+      <c r="GK3" s="49"/>
+      <c r="GL3" s="49"/>
+      <c r="GM3" s="49"/>
+      <c r="GN3" s="49"/>
+      <c r="GO3" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="GP3" s="53"/>
-      <c r="GQ3" s="53"/>
-      <c r="GR3" s="53"/>
-      <c r="GS3" s="53"/>
-      <c r="GT3" s="53"/>
-      <c r="GU3" s="53"/>
-      <c r="GV3" s="53"/>
-      <c r="GW3" s="53"/>
-      <c r="GX3" s="53"/>
-      <c r="GY3" s="53"/>
-      <c r="GZ3" s="53"/>
-      <c r="HA3" s="53"/>
-      <c r="HB3" s="53"/>
-      <c r="HC3" s="53"/>
-      <c r="HD3" s="53"/>
-      <c r="HE3" s="53"/>
-      <c r="HF3" s="53"/>
-      <c r="HG3" s="53"/>
-      <c r="HH3" s="53"/>
-      <c r="HI3" s="53"/>
-      <c r="HJ3" s="53"/>
-      <c r="HK3" s="53"/>
-      <c r="HL3" s="53"/>
-      <c r="HM3" s="53"/>
-      <c r="HN3" s="53"/>
-      <c r="HO3" s="53"/>
-      <c r="HP3" s="53"/>
-      <c r="HQ3" s="53"/>
-      <c r="HR3" s="53"/>
-      <c r="HS3" s="53"/>
-      <c r="HT3" s="53"/>
-      <c r="HU3" s="53" t="s">
+      <c r="GP3" s="49"/>
+      <c r="GQ3" s="49"/>
+      <c r="GR3" s="49"/>
+      <c r="GS3" s="49"/>
+      <c r="GT3" s="49"/>
+      <c r="GU3" s="49"/>
+      <c r="GV3" s="49"/>
+      <c r="GW3" s="49"/>
+      <c r="GX3" s="49"/>
+      <c r="GY3" s="49"/>
+      <c r="GZ3" s="49"/>
+      <c r="HA3" s="49"/>
+      <c r="HB3" s="49"/>
+      <c r="HC3" s="49"/>
+      <c r="HD3" s="49"/>
+      <c r="HE3" s="49"/>
+      <c r="HF3" s="49"/>
+      <c r="HG3" s="49"/>
+      <c r="HH3" s="49"/>
+      <c r="HI3" s="49"/>
+      <c r="HJ3" s="49"/>
+      <c r="HK3" s="49"/>
+      <c r="HL3" s="49"/>
+      <c r="HM3" s="49"/>
+      <c r="HN3" s="49"/>
+      <c r="HO3" s="49"/>
+      <c r="HP3" s="49"/>
+      <c r="HQ3" s="49"/>
+      <c r="HR3" s="49"/>
+      <c r="HS3" s="49"/>
+      <c r="HT3" s="49"/>
+      <c r="HU3" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="HV3" s="53"/>
-      <c r="HW3" s="53"/>
-      <c r="HX3" s="53"/>
-      <c r="HY3" s="53"/>
-      <c r="HZ3" s="53"/>
-      <c r="IA3" s="53"/>
-      <c r="IB3" s="53"/>
-      <c r="IC3" s="53"/>
-      <c r="ID3" s="53"/>
-      <c r="IE3" s="53"/>
-      <c r="IF3" s="53"/>
-      <c r="IG3" s="53"/>
-      <c r="IH3" s="53"/>
-      <c r="II3" s="53"/>
-      <c r="IJ3" s="53"/>
-      <c r="IK3" s="53"/>
-      <c r="IL3" s="53"/>
-      <c r="IM3" s="53"/>
-      <c r="IN3" s="53"/>
-      <c r="IO3" s="53"/>
-      <c r="IP3" s="53"/>
-      <c r="IQ3" s="53"/>
-      <c r="IR3" s="53"/>
-      <c r="IS3" s="53"/>
-      <c r="IT3" s="53"/>
-      <c r="IU3" s="53"/>
-      <c r="IV3" s="53"/>
-      <c r="IW3" s="53"/>
-      <c r="IX3" s="53"/>
-      <c r="IY3" s="53"/>
-      <c r="IZ3" s="53"/>
-      <c r="JA3" s="53" t="s">
+      <c r="HV3" s="49"/>
+      <c r="HW3" s="49"/>
+      <c r="HX3" s="49"/>
+      <c r="HY3" s="49"/>
+      <c r="HZ3" s="49"/>
+      <c r="IA3" s="49"/>
+      <c r="IB3" s="49"/>
+      <c r="IC3" s="49"/>
+      <c r="ID3" s="49"/>
+      <c r="IE3" s="49"/>
+      <c r="IF3" s="49"/>
+      <c r="IG3" s="49"/>
+      <c r="IH3" s="49"/>
+      <c r="II3" s="49"/>
+      <c r="IJ3" s="49"/>
+      <c r="IK3" s="49"/>
+      <c r="IL3" s="49"/>
+      <c r="IM3" s="49"/>
+      <c r="IN3" s="49"/>
+      <c r="IO3" s="49"/>
+      <c r="IP3" s="49"/>
+      <c r="IQ3" s="49"/>
+      <c r="IR3" s="49"/>
+      <c r="IS3" s="49"/>
+      <c r="IT3" s="49"/>
+      <c r="IU3" s="49"/>
+      <c r="IV3" s="49"/>
+      <c r="IW3" s="49"/>
+      <c r="IX3" s="49"/>
+      <c r="IY3" s="49"/>
+      <c r="IZ3" s="49"/>
+      <c r="JA3" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="JB3" s="53"/>
-      <c r="JC3" s="53"/>
-      <c r="JD3" s="53"/>
-      <c r="JE3" s="53"/>
-      <c r="JF3" s="53"/>
-      <c r="JG3" s="53"/>
-      <c r="JH3" s="53"/>
-      <c r="JI3" s="53"/>
-      <c r="JJ3" s="53"/>
-      <c r="JK3" s="53"/>
-      <c r="JL3" s="53"/>
-      <c r="JM3" s="53"/>
-      <c r="JN3" s="53"/>
-      <c r="JO3" s="53"/>
-      <c r="JP3" s="53"/>
-      <c r="JQ3" s="53"/>
-      <c r="JR3" s="53"/>
-      <c r="JS3" s="53"/>
-      <c r="JT3" s="53"/>
-      <c r="JU3" s="53"/>
-      <c r="JV3" s="53"/>
-      <c r="JW3" s="53"/>
-      <c r="JX3" s="53"/>
-      <c r="JY3" s="53"/>
-      <c r="JZ3" s="53"/>
-      <c r="KA3" s="53"/>
-      <c r="KB3" s="53"/>
-      <c r="KC3" s="53"/>
-      <c r="KD3" s="53"/>
-      <c r="KE3" s="53"/>
-      <c r="KF3" s="53"/>
-      <c r="KG3" s="54" t="s">
+      <c r="JB3" s="49"/>
+      <c r="JC3" s="49"/>
+      <c r="JD3" s="49"/>
+      <c r="JE3" s="49"/>
+      <c r="JF3" s="49"/>
+      <c r="JG3" s="49"/>
+      <c r="JH3" s="49"/>
+      <c r="JI3" s="49"/>
+      <c r="JJ3" s="49"/>
+      <c r="JK3" s="49"/>
+      <c r="JL3" s="49"/>
+      <c r="JM3" s="49"/>
+      <c r="JN3" s="49"/>
+      <c r="JO3" s="49"/>
+      <c r="JP3" s="49"/>
+      <c r="JQ3" s="49"/>
+      <c r="JR3" s="49"/>
+      <c r="JS3" s="49"/>
+      <c r="JT3" s="49"/>
+      <c r="JU3" s="49"/>
+      <c r="JV3" s="49"/>
+      <c r="JW3" s="49"/>
+      <c r="JX3" s="49"/>
+      <c r="JY3" s="49"/>
+      <c r="JZ3" s="49"/>
+      <c r="KA3" s="49"/>
+      <c r="KB3" s="49"/>
+      <c r="KC3" s="49"/>
+      <c r="KD3" s="49"/>
+      <c r="KE3" s="49"/>
+      <c r="KF3" s="49"/>
+      <c r="KG3" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="KH3" s="54"/>
-      <c r="KI3" s="54"/>
-      <c r="KJ3" s="54"/>
-      <c r="KK3" s="54"/>
-      <c r="KL3" s="54"/>
-      <c r="KM3" s="54"/>
-      <c r="KN3" s="54"/>
-      <c r="KO3" s="54"/>
-      <c r="KP3" s="54"/>
-      <c r="KQ3" s="54"/>
-      <c r="KR3" s="54"/>
-      <c r="KS3" s="54"/>
-      <c r="KT3" s="54"/>
-      <c r="KU3" s="54"/>
-      <c r="KV3" s="54"/>
-      <c r="KW3" s="54"/>
-      <c r="KX3" s="54"/>
-      <c r="KY3" s="54"/>
-      <c r="KZ3" s="54"/>
-      <c r="LA3" s="54"/>
-      <c r="LB3" s="54"/>
-      <c r="LC3" s="54"/>
-      <c r="LD3" s="54"/>
-      <c r="LE3" s="54"/>
-      <c r="LF3" s="54"/>
-      <c r="LG3" s="54"/>
-      <c r="LH3" s="54"/>
-      <c r="LI3" s="54"/>
-      <c r="LJ3" s="54"/>
-      <c r="LK3" s="54"/>
-      <c r="LL3" s="54"/>
-      <c r="LM3" s="53" t="s">
+      <c r="KH3" s="46"/>
+      <c r="KI3" s="46"/>
+      <c r="KJ3" s="46"/>
+      <c r="KK3" s="46"/>
+      <c r="KL3" s="46"/>
+      <c r="KM3" s="46"/>
+      <c r="KN3" s="46"/>
+      <c r="KO3" s="46"/>
+      <c r="KP3" s="46"/>
+      <c r="KQ3" s="46"/>
+      <c r="KR3" s="46"/>
+      <c r="KS3" s="46"/>
+      <c r="KT3" s="46"/>
+      <c r="KU3" s="46"/>
+      <c r="KV3" s="46"/>
+      <c r="KW3" s="46"/>
+      <c r="KX3" s="46"/>
+      <c r="KY3" s="46"/>
+      <c r="KZ3" s="46"/>
+      <c r="LA3" s="46"/>
+      <c r="LB3" s="46"/>
+      <c r="LC3" s="46"/>
+      <c r="LD3" s="46"/>
+      <c r="LE3" s="46"/>
+      <c r="LF3" s="46"/>
+      <c r="LG3" s="46"/>
+      <c r="LH3" s="46"/>
+      <c r="LI3" s="46"/>
+      <c r="LJ3" s="46"/>
+      <c r="LK3" s="46"/>
+      <c r="LL3" s="46"/>
+      <c r="LM3" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="LN3" s="53"/>
-      <c r="LO3" s="53"/>
-      <c r="LP3" s="53"/>
-      <c r="LQ3" s="53"/>
-      <c r="LR3" s="53"/>
-      <c r="LS3" s="53"/>
-      <c r="LT3" s="53"/>
-      <c r="LU3" s="53"/>
-      <c r="LV3" s="53"/>
-      <c r="LW3" s="53"/>
-      <c r="LX3" s="53"/>
-      <c r="LY3" s="53"/>
-      <c r="LZ3" s="53"/>
-      <c r="MA3" s="53"/>
-      <c r="MB3" s="53"/>
-      <c r="MC3" s="53"/>
-      <c r="MD3" s="53"/>
-      <c r="ME3" s="53"/>
-      <c r="MF3" s="53"/>
-      <c r="MG3" s="53"/>
-      <c r="MH3" s="53"/>
-      <c r="MI3" s="53"/>
-      <c r="MJ3" s="53"/>
-      <c r="MK3" s="53"/>
-      <c r="ML3" s="53"/>
-      <c r="MM3" s="53"/>
-      <c r="MN3" s="53"/>
-      <c r="MO3" s="53"/>
-      <c r="MP3" s="53"/>
-      <c r="MQ3" s="53"/>
-      <c r="MR3" s="53"/>
-      <c r="MS3" s="53" t="s">
+      <c r="LN3" s="49"/>
+      <c r="LO3" s="49"/>
+      <c r="LP3" s="49"/>
+      <c r="LQ3" s="49"/>
+      <c r="LR3" s="49"/>
+      <c r="LS3" s="49"/>
+      <c r="LT3" s="49"/>
+      <c r="LU3" s="49"/>
+      <c r="LV3" s="49"/>
+      <c r="LW3" s="49"/>
+      <c r="LX3" s="49"/>
+      <c r="LY3" s="49"/>
+      <c r="LZ3" s="49"/>
+      <c r="MA3" s="49"/>
+      <c r="MB3" s="49"/>
+      <c r="MC3" s="49"/>
+      <c r="MD3" s="49"/>
+      <c r="ME3" s="49"/>
+      <c r="MF3" s="49"/>
+      <c r="MG3" s="49"/>
+      <c r="MH3" s="49"/>
+      <c r="MI3" s="49"/>
+      <c r="MJ3" s="49"/>
+      <c r="MK3" s="49"/>
+      <c r="ML3" s="49"/>
+      <c r="MM3" s="49"/>
+      <c r="MN3" s="49"/>
+      <c r="MO3" s="49"/>
+      <c r="MP3" s="49"/>
+      <c r="MQ3" s="49"/>
+      <c r="MR3" s="49"/>
+      <c r="MS3" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="MT3" s="53"/>
-      <c r="MU3" s="53"/>
-      <c r="MV3" s="53"/>
-      <c r="MW3" s="53"/>
-      <c r="MX3" s="53"/>
-      <c r="MY3" s="53"/>
-      <c r="MZ3" s="53"/>
-      <c r="NA3" s="53"/>
-      <c r="NB3" s="53"/>
-      <c r="NC3" s="53"/>
-      <c r="ND3" s="53"/>
-      <c r="NE3" s="53"/>
-      <c r="NF3" s="53"/>
-      <c r="NG3" s="53"/>
-      <c r="NH3" s="53"/>
-      <c r="NI3" s="53"/>
-      <c r="NJ3" s="53"/>
-      <c r="NK3" s="53"/>
-      <c r="NL3" s="53"/>
-      <c r="NM3" s="53"/>
-      <c r="NN3" s="53"/>
-      <c r="NO3" s="53"/>
-      <c r="NP3" s="53"/>
-      <c r="NQ3" s="53"/>
-      <c r="NR3" s="53"/>
-      <c r="NS3" s="53"/>
-      <c r="NT3" s="53"/>
-      <c r="NU3" s="53"/>
-      <c r="NV3" s="53"/>
-      <c r="NW3" s="53"/>
-      <c r="NX3" s="53"/>
-      <c r="NY3" s="53" t="s">
+      <c r="MT3" s="49"/>
+      <c r="MU3" s="49"/>
+      <c r="MV3" s="49"/>
+      <c r="MW3" s="49"/>
+      <c r="MX3" s="49"/>
+      <c r="MY3" s="49"/>
+      <c r="MZ3" s="49"/>
+      <c r="NA3" s="49"/>
+      <c r="NB3" s="49"/>
+      <c r="NC3" s="49"/>
+      <c r="ND3" s="49"/>
+      <c r="NE3" s="49"/>
+      <c r="NF3" s="49"/>
+      <c r="NG3" s="49"/>
+      <c r="NH3" s="49"/>
+      <c r="NI3" s="49"/>
+      <c r="NJ3" s="49"/>
+      <c r="NK3" s="49"/>
+      <c r="NL3" s="49"/>
+      <c r="NM3" s="49"/>
+      <c r="NN3" s="49"/>
+      <c r="NO3" s="49"/>
+      <c r="NP3" s="49"/>
+      <c r="NQ3" s="49"/>
+      <c r="NR3" s="49"/>
+      <c r="NS3" s="49"/>
+      <c r="NT3" s="49"/>
+      <c r="NU3" s="49"/>
+      <c r="NV3" s="49"/>
+      <c r="NW3" s="49"/>
+      <c r="NX3" s="49"/>
+      <c r="NY3" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="NZ3" s="53"/>
-      <c r="OA3" s="53"/>
-      <c r="OB3" s="53"/>
-      <c r="OC3" s="53"/>
-      <c r="OD3" s="53"/>
-      <c r="OE3" s="53"/>
-      <c r="OF3" s="53"/>
-      <c r="OG3" s="53"/>
-      <c r="OH3" s="53"/>
-      <c r="OI3" s="53"/>
-      <c r="OJ3" s="53"/>
-      <c r="OK3" s="53"/>
-      <c r="OL3" s="53"/>
-      <c r="OM3" s="53"/>
-      <c r="ON3" s="53"/>
-      <c r="OO3" s="53"/>
-      <c r="OP3" s="53"/>
-      <c r="OQ3" s="53"/>
-      <c r="OR3" s="53"/>
-      <c r="OS3" s="53"/>
-      <c r="OT3" s="53"/>
-      <c r="OU3" s="53"/>
-      <c r="OV3" s="53"/>
-      <c r="OW3" s="53"/>
-      <c r="OX3" s="53"/>
-      <c r="OY3" s="53"/>
-      <c r="OZ3" s="53"/>
-      <c r="PA3" s="53"/>
-      <c r="PB3" s="53"/>
-      <c r="PC3" s="53"/>
-      <c r="PD3" s="53"/>
-      <c r="PE3" s="53" t="s">
+      <c r="NZ3" s="49"/>
+      <c r="OA3" s="49"/>
+      <c r="OB3" s="49"/>
+      <c r="OC3" s="49"/>
+      <c r="OD3" s="49"/>
+      <c r="OE3" s="49"/>
+      <c r="OF3" s="49"/>
+      <c r="OG3" s="49"/>
+      <c r="OH3" s="49"/>
+      <c r="OI3" s="49"/>
+      <c r="OJ3" s="49"/>
+      <c r="OK3" s="49"/>
+      <c r="OL3" s="49"/>
+      <c r="OM3" s="49"/>
+      <c r="ON3" s="49"/>
+      <c r="OO3" s="49"/>
+      <c r="OP3" s="49"/>
+      <c r="OQ3" s="49"/>
+      <c r="OR3" s="49"/>
+      <c r="OS3" s="49"/>
+      <c r="OT3" s="49"/>
+      <c r="OU3" s="49"/>
+      <c r="OV3" s="49"/>
+      <c r="OW3" s="49"/>
+      <c r="OX3" s="49"/>
+      <c r="OY3" s="49"/>
+      <c r="OZ3" s="49"/>
+      <c r="PA3" s="49"/>
+      <c r="PB3" s="49"/>
+      <c r="PC3" s="49"/>
+      <c r="PD3" s="49"/>
+      <c r="PE3" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="PF3" s="53"/>
-      <c r="PG3" s="53"/>
-      <c r="PH3" s="53"/>
-      <c r="PI3" s="53"/>
-      <c r="PJ3" s="53"/>
-      <c r="PK3" s="53"/>
-      <c r="PL3" s="53"/>
-      <c r="PM3" s="53"/>
-      <c r="PN3" s="53"/>
-      <c r="PO3" s="53"/>
-      <c r="PP3" s="53"/>
-      <c r="PQ3" s="53"/>
-      <c r="PR3" s="53"/>
-      <c r="PS3" s="53"/>
-      <c r="PT3" s="53"/>
-      <c r="PU3" s="53"/>
-      <c r="PV3" s="53"/>
-      <c r="PW3" s="53"/>
-      <c r="PX3" s="53"/>
-      <c r="PY3" s="53"/>
-      <c r="PZ3" s="53"/>
-      <c r="QA3" s="53"/>
-      <c r="QB3" s="53"/>
-      <c r="QC3" s="53"/>
-      <c r="QD3" s="53"/>
-      <c r="QE3" s="53"/>
-      <c r="QF3" s="53"/>
-      <c r="QG3" s="53"/>
-      <c r="QH3" s="53"/>
-      <c r="QI3" s="53"/>
-      <c r="QJ3" s="53"/>
-      <c r="QK3" s="54" t="s">
+      <c r="PF3" s="49"/>
+      <c r="PG3" s="49"/>
+      <c r="PH3" s="49"/>
+      <c r="PI3" s="49"/>
+      <c r="PJ3" s="49"/>
+      <c r="PK3" s="49"/>
+      <c r="PL3" s="49"/>
+      <c r="PM3" s="49"/>
+      <c r="PN3" s="49"/>
+      <c r="PO3" s="49"/>
+      <c r="PP3" s="49"/>
+      <c r="PQ3" s="49"/>
+      <c r="PR3" s="49"/>
+      <c r="PS3" s="49"/>
+      <c r="PT3" s="49"/>
+      <c r="PU3" s="49"/>
+      <c r="PV3" s="49"/>
+      <c r="PW3" s="49"/>
+      <c r="PX3" s="49"/>
+      <c r="PY3" s="49"/>
+      <c r="PZ3" s="49"/>
+      <c r="QA3" s="49"/>
+      <c r="QB3" s="49"/>
+      <c r="QC3" s="49"/>
+      <c r="QD3" s="49"/>
+      <c r="QE3" s="49"/>
+      <c r="QF3" s="49"/>
+      <c r="QG3" s="49"/>
+      <c r="QH3" s="49"/>
+      <c r="QI3" s="49"/>
+      <c r="QJ3" s="49"/>
+      <c r="QK3" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="QL3" s="54"/>
-      <c r="QM3" s="54"/>
-      <c r="QN3" s="54"/>
-      <c r="QO3" s="54"/>
-      <c r="QP3" s="54"/>
-      <c r="QQ3" s="54"/>
-      <c r="QR3" s="54"/>
-      <c r="QS3" s="54"/>
-      <c r="QT3" s="54"/>
-      <c r="QU3" s="54"/>
-      <c r="QV3" s="54"/>
-      <c r="QW3" s="54"/>
-      <c r="QX3" s="54"/>
-      <c r="QY3" s="54"/>
-      <c r="QZ3" s="54"/>
-      <c r="RA3" s="54"/>
-      <c r="RB3" s="54"/>
-      <c r="RC3" s="54"/>
-      <c r="RD3" s="54"/>
-      <c r="RE3" s="54"/>
-      <c r="RF3" s="54"/>
-      <c r="RG3" s="54"/>
-      <c r="RH3" s="54"/>
-      <c r="RI3" s="54"/>
-      <c r="RJ3" s="54"/>
-      <c r="RK3" s="54"/>
-      <c r="RL3" s="54"/>
-      <c r="RM3" s="54"/>
-      <c r="RN3" s="54"/>
-      <c r="RO3" s="54"/>
-      <c r="RP3" s="54"/>
-      <c r="RQ3" s="52" t="s">
+      <c r="QL3" s="46"/>
+      <c r="QM3" s="46"/>
+      <c r="QN3" s="46"/>
+      <c r="QO3" s="46"/>
+      <c r="QP3" s="46"/>
+      <c r="QQ3" s="46"/>
+      <c r="QR3" s="46"/>
+      <c r="QS3" s="46"/>
+      <c r="QT3" s="46"/>
+      <c r="QU3" s="46"/>
+      <c r="QV3" s="46"/>
+      <c r="QW3" s="46"/>
+      <c r="QX3" s="46"/>
+      <c r="QY3" s="46"/>
+      <c r="QZ3" s="46"/>
+      <c r="RA3" s="46"/>
+      <c r="RB3" s="46"/>
+      <c r="RC3" s="46"/>
+      <c r="RD3" s="46"/>
+      <c r="RE3" s="46"/>
+      <c r="RF3" s="46"/>
+      <c r="RG3" s="46"/>
+      <c r="RH3" s="46"/>
+      <c r="RI3" s="46"/>
+      <c r="RJ3" s="46"/>
+      <c r="RK3" s="46"/>
+      <c r="RL3" s="46"/>
+      <c r="RM3" s="46"/>
+      <c r="RN3" s="46"/>
+      <c r="RO3" s="46"/>
+      <c r="RP3" s="46"/>
+      <c r="RQ3" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="RR3" s="52"/>
-      <c r="RS3" s="52"/>
-      <c r="RT3" s="52"/>
-      <c r="RU3" s="52"/>
-      <c r="RV3" s="52"/>
-      <c r="RW3" s="52"/>
-      <c r="RX3" s="52"/>
-      <c r="RY3" s="52"/>
-      <c r="RZ3" s="52"/>
-      <c r="SA3" s="52"/>
-      <c r="SB3" s="52"/>
-      <c r="SC3" s="52"/>
-      <c r="SD3" s="52"/>
-      <c r="SE3" s="52"/>
-      <c r="SF3" s="52"/>
-      <c r="SG3" s="52"/>
-      <c r="SH3" s="52"/>
-      <c r="SI3" s="52"/>
-      <c r="SJ3" s="52"/>
-      <c r="SK3" s="52"/>
-      <c r="SL3" s="52"/>
-      <c r="SM3" s="52"/>
-      <c r="SN3" s="52"/>
-      <c r="SO3" s="52"/>
-      <c r="SP3" s="52"/>
-      <c r="SQ3" s="52"/>
-      <c r="SR3" s="52"/>
-      <c r="SS3" s="52"/>
-      <c r="ST3" s="52"/>
-      <c r="SU3" s="52"/>
-      <c r="SV3" s="52"/>
-      <c r="SW3" s="52" t="s">
+      <c r="RR3" s="47"/>
+      <c r="RS3" s="47"/>
+      <c r="RT3" s="47"/>
+      <c r="RU3" s="47"/>
+      <c r="RV3" s="47"/>
+      <c r="RW3" s="47"/>
+      <c r="RX3" s="47"/>
+      <c r="RY3" s="47"/>
+      <c r="RZ3" s="47"/>
+      <c r="SA3" s="47"/>
+      <c r="SB3" s="47"/>
+      <c r="SC3" s="47"/>
+      <c r="SD3" s="47"/>
+      <c r="SE3" s="47"/>
+      <c r="SF3" s="47"/>
+      <c r="SG3" s="47"/>
+      <c r="SH3" s="47"/>
+      <c r="SI3" s="47"/>
+      <c r="SJ3" s="47"/>
+      <c r="SK3" s="47"/>
+      <c r="SL3" s="47"/>
+      <c r="SM3" s="47"/>
+      <c r="SN3" s="47"/>
+      <c r="SO3" s="47"/>
+      <c r="SP3" s="47"/>
+      <c r="SQ3" s="47"/>
+      <c r="SR3" s="47"/>
+      <c r="SS3" s="47"/>
+      <c r="ST3" s="47"/>
+      <c r="SU3" s="47"/>
+      <c r="SV3" s="47"/>
+      <c r="SW3" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="SX3" s="52"/>
-      <c r="SY3" s="52"/>
-      <c r="SZ3" s="52"/>
-      <c r="TA3" s="52"/>
-      <c r="TB3" s="52"/>
-      <c r="TC3" s="52"/>
-      <c r="TD3" s="52"/>
-      <c r="TE3" s="52"/>
-      <c r="TF3" s="52"/>
-      <c r="TG3" s="52"/>
-      <c r="TH3" s="52"/>
-      <c r="TI3" s="52"/>
-      <c r="TJ3" s="52"/>
-      <c r="TK3" s="52"/>
-      <c r="TL3" s="52"/>
-      <c r="TM3" s="52"/>
-      <c r="TN3" s="52"/>
-      <c r="TO3" s="52"/>
-      <c r="TP3" s="52"/>
-      <c r="TQ3" s="52"/>
-      <c r="TR3" s="52"/>
-      <c r="TS3" s="52"/>
-      <c r="TT3" s="52"/>
-      <c r="TU3" s="52"/>
-      <c r="TV3" s="52"/>
-      <c r="TW3" s="52"/>
-      <c r="TX3" s="52"/>
-      <c r="TY3" s="52"/>
-      <c r="TZ3" s="52"/>
-      <c r="UA3" s="52"/>
-      <c r="UB3" s="52"/>
-      <c r="UC3" s="53" t="s">
+      <c r="SX3" s="47"/>
+      <c r="SY3" s="47"/>
+      <c r="SZ3" s="47"/>
+      <c r="TA3" s="47"/>
+      <c r="TB3" s="47"/>
+      <c r="TC3" s="47"/>
+      <c r="TD3" s="47"/>
+      <c r="TE3" s="47"/>
+      <c r="TF3" s="47"/>
+      <c r="TG3" s="47"/>
+      <c r="TH3" s="47"/>
+      <c r="TI3" s="47"/>
+      <c r="TJ3" s="47"/>
+      <c r="TK3" s="47"/>
+      <c r="TL3" s="47"/>
+      <c r="TM3" s="47"/>
+      <c r="TN3" s="47"/>
+      <c r="TO3" s="47"/>
+      <c r="TP3" s="47"/>
+      <c r="TQ3" s="47"/>
+      <c r="TR3" s="47"/>
+      <c r="TS3" s="47"/>
+      <c r="TT3" s="47"/>
+      <c r="TU3" s="47"/>
+      <c r="TV3" s="47"/>
+      <c r="TW3" s="47"/>
+      <c r="TX3" s="47"/>
+      <c r="TY3" s="47"/>
+      <c r="TZ3" s="47"/>
+      <c r="UA3" s="47"/>
+      <c r="UB3" s="47"/>
+      <c r="UC3" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="UD3" s="53"/>
-      <c r="UE3" s="53"/>
-      <c r="UF3" s="53"/>
-      <c r="UG3" s="53"/>
-      <c r="UH3" s="53"/>
-      <c r="UI3" s="53"/>
-      <c r="UJ3" s="53"/>
-      <c r="UK3" s="53"/>
-      <c r="UL3" s="53"/>
-      <c r="UM3" s="53"/>
-      <c r="UN3" s="53"/>
-      <c r="UO3" s="53"/>
-      <c r="UP3" s="53"/>
-      <c r="UQ3" s="53"/>
-      <c r="UR3" s="53"/>
-      <c r="US3" s="53"/>
-      <c r="UT3" s="53"/>
-      <c r="UU3" s="53"/>
-      <c r="UV3" s="53"/>
-      <c r="UW3" s="53"/>
-      <c r="UX3" s="53"/>
-      <c r="UY3" s="53"/>
-      <c r="UZ3" s="53"/>
-      <c r="VA3" s="53"/>
-      <c r="VB3" s="53"/>
-      <c r="VC3" s="53"/>
-      <c r="VD3" s="53"/>
-      <c r="VE3" s="53"/>
-      <c r="VF3" s="53"/>
-      <c r="VG3" s="53"/>
-      <c r="VH3" s="53"/>
-      <c r="VI3" s="53" t="s">
+      <c r="UD3" s="49"/>
+      <c r="UE3" s="49"/>
+      <c r="UF3" s="49"/>
+      <c r="UG3" s="49"/>
+      <c r="UH3" s="49"/>
+      <c r="UI3" s="49"/>
+      <c r="UJ3" s="49"/>
+      <c r="UK3" s="49"/>
+      <c r="UL3" s="49"/>
+      <c r="UM3" s="49"/>
+      <c r="UN3" s="49"/>
+      <c r="UO3" s="49"/>
+      <c r="UP3" s="49"/>
+      <c r="UQ3" s="49"/>
+      <c r="UR3" s="49"/>
+      <c r="US3" s="49"/>
+      <c r="UT3" s="49"/>
+      <c r="UU3" s="49"/>
+      <c r="UV3" s="49"/>
+      <c r="UW3" s="49"/>
+      <c r="UX3" s="49"/>
+      <c r="UY3" s="49"/>
+      <c r="UZ3" s="49"/>
+      <c r="VA3" s="49"/>
+      <c r="VB3" s="49"/>
+      <c r="VC3" s="49"/>
+      <c r="VD3" s="49"/>
+      <c r="VE3" s="49"/>
+      <c r="VF3" s="49"/>
+      <c r="VG3" s="49"/>
+      <c r="VH3" s="49"/>
+      <c r="VI3" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="VJ3" s="53"/>
-      <c r="VK3" s="53"/>
-      <c r="VL3" s="53"/>
-      <c r="VM3" s="53"/>
-      <c r="VN3" s="53"/>
-      <c r="VO3" s="53"/>
-      <c r="VP3" s="53"/>
-      <c r="VQ3" s="53"/>
-      <c r="VR3" s="53"/>
-      <c r="VS3" s="53"/>
-      <c r="VT3" s="53"/>
-      <c r="VU3" s="53"/>
-      <c r="VV3" s="53"/>
-      <c r="VW3" s="53"/>
-      <c r="VX3" s="53"/>
-      <c r="VY3" s="53"/>
-      <c r="VZ3" s="53"/>
-      <c r="WA3" s="53"/>
-      <c r="WB3" s="53"/>
-      <c r="WC3" s="53"/>
-      <c r="WD3" s="53"/>
-      <c r="WE3" s="53"/>
-      <c r="WF3" s="53"/>
-      <c r="WG3" s="53"/>
-      <c r="WH3" s="53"/>
-      <c r="WI3" s="53"/>
-      <c r="WJ3" s="53"/>
-      <c r="WK3" s="53"/>
-      <c r="WL3" s="53"/>
-      <c r="WM3" s="53"/>
-      <c r="WN3" s="53"/>
-      <c r="WO3" s="54" t="s">
+      <c r="VJ3" s="49"/>
+      <c r="VK3" s="49"/>
+      <c r="VL3" s="49"/>
+      <c r="VM3" s="49"/>
+      <c r="VN3" s="49"/>
+      <c r="VO3" s="49"/>
+      <c r="VP3" s="49"/>
+      <c r="VQ3" s="49"/>
+      <c r="VR3" s="49"/>
+      <c r="VS3" s="49"/>
+      <c r="VT3" s="49"/>
+      <c r="VU3" s="49"/>
+      <c r="VV3" s="49"/>
+      <c r="VW3" s="49"/>
+      <c r="VX3" s="49"/>
+      <c r="VY3" s="49"/>
+      <c r="VZ3" s="49"/>
+      <c r="WA3" s="49"/>
+      <c r="WB3" s="49"/>
+      <c r="WC3" s="49"/>
+      <c r="WD3" s="49"/>
+      <c r="WE3" s="49"/>
+      <c r="WF3" s="49"/>
+      <c r="WG3" s="49"/>
+      <c r="WH3" s="49"/>
+      <c r="WI3" s="49"/>
+      <c r="WJ3" s="49"/>
+      <c r="WK3" s="49"/>
+      <c r="WL3" s="49"/>
+      <c r="WM3" s="49"/>
+      <c r="WN3" s="49"/>
+      <c r="WO3" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="WP3" s="54"/>
-      <c r="WQ3" s="54"/>
-      <c r="WR3" s="54"/>
-      <c r="WS3" s="54"/>
-      <c r="WT3" s="54"/>
-      <c r="WU3" s="54"/>
-      <c r="WV3" s="54"/>
-      <c r="WW3" s="54"/>
-      <c r="WX3" s="54"/>
-      <c r="WY3" s="54"/>
-      <c r="WZ3" s="54"/>
-      <c r="XA3" s="54"/>
-      <c r="XB3" s="54"/>
-      <c r="XC3" s="54"/>
-      <c r="XD3" s="54"/>
-      <c r="XE3" s="54"/>
-      <c r="XF3" s="54"/>
-      <c r="XG3" s="54"/>
-      <c r="XH3" s="54"/>
-      <c r="XI3" s="54"/>
-      <c r="XJ3" s="54"/>
-      <c r="XK3" s="54"/>
-      <c r="XL3" s="54"/>
-      <c r="XM3" s="54"/>
-      <c r="XN3" s="54"/>
-      <c r="XO3" s="54"/>
-      <c r="XP3" s="54"/>
-      <c r="XQ3" s="54"/>
-      <c r="XR3" s="54"/>
-      <c r="XS3" s="54"/>
-      <c r="XT3" s="54"/>
-      <c r="XU3" s="53" t="s">
+      <c r="WP3" s="46"/>
+      <c r="WQ3" s="46"/>
+      <c r="WR3" s="46"/>
+      <c r="WS3" s="46"/>
+      <c r="WT3" s="46"/>
+      <c r="WU3" s="46"/>
+      <c r="WV3" s="46"/>
+      <c r="WW3" s="46"/>
+      <c r="WX3" s="46"/>
+      <c r="WY3" s="46"/>
+      <c r="WZ3" s="46"/>
+      <c r="XA3" s="46"/>
+      <c r="XB3" s="46"/>
+      <c r="XC3" s="46"/>
+      <c r="XD3" s="46"/>
+      <c r="XE3" s="46"/>
+      <c r="XF3" s="46"/>
+      <c r="XG3" s="46"/>
+      <c r="XH3" s="46"/>
+      <c r="XI3" s="46"/>
+      <c r="XJ3" s="46"/>
+      <c r="XK3" s="46"/>
+      <c r="XL3" s="46"/>
+      <c r="XM3" s="46"/>
+      <c r="XN3" s="46"/>
+      <c r="XO3" s="46"/>
+      <c r="XP3" s="46"/>
+      <c r="XQ3" s="46"/>
+      <c r="XR3" s="46"/>
+      <c r="XS3" s="46"/>
+      <c r="XT3" s="46"/>
+      <c r="XU3" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="XV3" s="53"/>
-      <c r="XW3" s="53"/>
-      <c r="XX3" s="53"/>
-      <c r="XY3" s="53"/>
-      <c r="XZ3" s="53"/>
-      <c r="YA3" s="53"/>
-      <c r="YB3" s="53"/>
-      <c r="YC3" s="53"/>
-      <c r="YD3" s="53"/>
-      <c r="YE3" s="53"/>
-      <c r="YF3" s="53"/>
-      <c r="YG3" s="53"/>
-      <c r="YH3" s="53"/>
-      <c r="YI3" s="53"/>
-      <c r="YJ3" s="53"/>
-      <c r="YK3" s="53"/>
-      <c r="YL3" s="53"/>
-      <c r="YM3" s="53"/>
-      <c r="YN3" s="53"/>
-      <c r="YO3" s="53"/>
-      <c r="YP3" s="53"/>
-      <c r="YQ3" s="53"/>
-      <c r="YR3" s="53"/>
-      <c r="YS3" s="53"/>
-      <c r="YT3" s="53"/>
-      <c r="YU3" s="53"/>
-      <c r="YV3" s="53"/>
-      <c r="YW3" s="53"/>
-      <c r="YX3" s="53"/>
-      <c r="YY3" s="53"/>
-      <c r="YZ3" s="53"/>
+      <c r="XV3" s="49"/>
+      <c r="XW3" s="49"/>
+      <c r="XX3" s="49"/>
+      <c r="XY3" s="49"/>
+      <c r="XZ3" s="49"/>
+      <c r="YA3" s="49"/>
+      <c r="YB3" s="49"/>
+      <c r="YC3" s="49"/>
+      <c r="YD3" s="49"/>
+      <c r="YE3" s="49"/>
+      <c r="YF3" s="49"/>
+      <c r="YG3" s="49"/>
+      <c r="YH3" s="49"/>
+      <c r="YI3" s="49"/>
+      <c r="YJ3" s="49"/>
+      <c r="YK3" s="49"/>
+      <c r="YL3" s="49"/>
+      <c r="YM3" s="49"/>
+      <c r="YN3" s="49"/>
+      <c r="YO3" s="49"/>
+      <c r="YP3" s="49"/>
+      <c r="YQ3" s="49"/>
+      <c r="YR3" s="49"/>
+      <c r="YS3" s="49"/>
+      <c r="YT3" s="49"/>
+      <c r="YU3" s="49"/>
+      <c r="YV3" s="49"/>
+      <c r="YW3" s="49"/>
+      <c r="YX3" s="49"/>
+      <c r="YY3" s="49"/>
+      <c r="YZ3" s="49"/>
     </row>
     <row r="4" spans="1:676" x14ac:dyDescent="0.25">
-      <c r="A4" s="57"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="47">
+      <c r="A4" s="51"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="48">
         <v>1</v>
       </c>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47">
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48">
         <v>2</v>
       </c>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
-      <c r="M4" s="47">
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
+      <c r="L4" s="48"/>
+      <c r="M4" s="48">
         <v>3</v>
       </c>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47">
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48">
         <v>4</v>
       </c>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47">
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48">
         <v>5</v>
       </c>
-      <c r="V4" s="47"/>
-      <c r="W4" s="47"/>
-      <c r="X4" s="47"/>
-      <c r="Y4" s="47">
+      <c r="V4" s="48"/>
+      <c r="W4" s="48"/>
+      <c r="X4" s="48"/>
+      <c r="Y4" s="48">
         <v>6</v>
       </c>
-      <c r="Z4" s="47"/>
-      <c r="AA4" s="47"/>
-      <c r="AB4" s="47"/>
-      <c r="AC4" s="47">
+      <c r="Z4" s="48"/>
+      <c r="AA4" s="48"/>
+      <c r="AB4" s="48"/>
+      <c r="AC4" s="48">
         <v>7</v>
       </c>
-      <c r="AD4" s="47"/>
-      <c r="AE4" s="47"/>
-      <c r="AF4" s="47"/>
-      <c r="AG4" s="47">
+      <c r="AD4" s="48"/>
+      <c r="AE4" s="48"/>
+      <c r="AF4" s="48"/>
+      <c r="AG4" s="48">
         <v>8</v>
       </c>
-      <c r="AH4" s="55"/>
-      <c r="AI4" s="55"/>
-      <c r="AJ4" s="56"/>
-      <c r="AK4" s="47">
+      <c r="AH4" s="52"/>
+      <c r="AI4" s="52"/>
+      <c r="AJ4" s="53"/>
+      <c r="AK4" s="48">
         <v>1</v>
       </c>
-      <c r="AL4" s="47"/>
-      <c r="AM4" s="47"/>
-      <c r="AN4" s="47"/>
-      <c r="AO4" s="47">
+      <c r="AL4" s="48"/>
+      <c r="AM4" s="48"/>
+      <c r="AN4" s="48"/>
+      <c r="AO4" s="48">
         <v>2</v>
       </c>
-      <c r="AP4" s="47"/>
-      <c r="AQ4" s="47"/>
-      <c r="AR4" s="47"/>
-      <c r="AS4" s="47">
+      <c r="AP4" s="48"/>
+      <c r="AQ4" s="48"/>
+      <c r="AR4" s="48"/>
+      <c r="AS4" s="48">
         <v>3</v>
       </c>
-      <c r="AT4" s="47"/>
-      <c r="AU4" s="47"/>
-      <c r="AV4" s="47"/>
-      <c r="AW4" s="47">
+      <c r="AT4" s="48"/>
+      <c r="AU4" s="48"/>
+      <c r="AV4" s="48"/>
+      <c r="AW4" s="48">
         <v>4</v>
       </c>
-      <c r="AX4" s="47"/>
-      <c r="AY4" s="47"/>
-      <c r="AZ4" s="47"/>
-      <c r="BA4" s="46">
+      <c r="AX4" s="48"/>
+      <c r="AY4" s="48"/>
+      <c r="AZ4" s="48"/>
+      <c r="BA4" s="50">
         <v>5</v>
       </c>
-      <c r="BB4" s="46"/>
-      <c r="BC4" s="46"/>
-      <c r="BD4" s="46"/>
-      <c r="BE4" s="46">
+      <c r="BB4" s="50"/>
+      <c r="BC4" s="50"/>
+      <c r="BD4" s="50"/>
+      <c r="BE4" s="50">
         <v>6</v>
       </c>
-      <c r="BF4" s="46"/>
-      <c r="BG4" s="46"/>
-      <c r="BH4" s="46"/>
-      <c r="BI4" s="46">
+      <c r="BF4" s="50"/>
+      <c r="BG4" s="50"/>
+      <c r="BH4" s="50"/>
+      <c r="BI4" s="50">
         <v>7</v>
       </c>
-      <c r="BJ4" s="46"/>
-      <c r="BK4" s="46"/>
-      <c r="BL4" s="46"/>
-      <c r="BM4" s="46">
+      <c r="BJ4" s="50"/>
+      <c r="BK4" s="50"/>
+      <c r="BL4" s="50"/>
+      <c r="BM4" s="50">
         <v>8</v>
       </c>
-      <c r="BN4" s="46"/>
-      <c r="BO4" s="46"/>
-      <c r="BP4" s="46"/>
-      <c r="BQ4" s="47">
+      <c r="BN4" s="50"/>
+      <c r="BO4" s="50"/>
+      <c r="BP4" s="50"/>
+      <c r="BQ4" s="48">
         <v>1</v>
       </c>
-      <c r="BR4" s="47"/>
-      <c r="BS4" s="47"/>
-      <c r="BT4" s="47"/>
-      <c r="BU4" s="47">
+      <c r="BR4" s="48"/>
+      <c r="BS4" s="48"/>
+      <c r="BT4" s="48"/>
+      <c r="BU4" s="48">
         <v>2</v>
       </c>
-      <c r="BV4" s="47"/>
-      <c r="BW4" s="47"/>
-      <c r="BX4" s="47"/>
-      <c r="BY4" s="47">
+      <c r="BV4" s="48"/>
+      <c r="BW4" s="48"/>
+      <c r="BX4" s="48"/>
+      <c r="BY4" s="48">
         <v>3</v>
       </c>
-      <c r="BZ4" s="47"/>
-      <c r="CA4" s="47"/>
-      <c r="CB4" s="47"/>
-      <c r="CC4" s="47">
+      <c r="BZ4" s="48"/>
+      <c r="CA4" s="48"/>
+      <c r="CB4" s="48"/>
+      <c r="CC4" s="48">
         <v>4</v>
       </c>
-      <c r="CD4" s="47"/>
-      <c r="CE4" s="47"/>
-      <c r="CF4" s="47"/>
-      <c r="CG4" s="47">
+      <c r="CD4" s="48"/>
+      <c r="CE4" s="48"/>
+      <c r="CF4" s="48"/>
+      <c r="CG4" s="48">
         <v>5</v>
       </c>
-      <c r="CH4" s="47"/>
-      <c r="CI4" s="47"/>
-      <c r="CJ4" s="47"/>
-      <c r="CK4" s="47">
+      <c r="CH4" s="48"/>
+      <c r="CI4" s="48"/>
+      <c r="CJ4" s="48"/>
+      <c r="CK4" s="48">
         <v>6</v>
       </c>
-      <c r="CL4" s="47"/>
-      <c r="CM4" s="47"/>
-      <c r="CN4" s="47"/>
-      <c r="CO4" s="46">
+      <c r="CL4" s="48"/>
+      <c r="CM4" s="48"/>
+      <c r="CN4" s="48"/>
+      <c r="CO4" s="50">
         <v>7</v>
       </c>
-      <c r="CP4" s="46"/>
-      <c r="CQ4" s="46"/>
-      <c r="CR4" s="46"/>
-      <c r="CS4" s="46">
+      <c r="CP4" s="50"/>
+      <c r="CQ4" s="50"/>
+      <c r="CR4" s="50"/>
+      <c r="CS4" s="50">
         <v>8</v>
       </c>
-      <c r="CT4" s="46"/>
-      <c r="CU4" s="46"/>
-      <c r="CV4" s="46"/>
-      <c r="CW4" s="47">
+      <c r="CT4" s="50"/>
+      <c r="CU4" s="50"/>
+      <c r="CV4" s="50"/>
+      <c r="CW4" s="48">
         <v>1</v>
       </c>
-      <c r="CX4" s="47"/>
-      <c r="CY4" s="47"/>
-      <c r="CZ4" s="47"/>
-      <c r="DA4" s="47">
+      <c r="CX4" s="48"/>
+      <c r="CY4" s="48"/>
+      <c r="CZ4" s="48"/>
+      <c r="DA4" s="48">
         <v>2</v>
       </c>
-      <c r="DB4" s="47"/>
-      <c r="DC4" s="47"/>
-      <c r="DD4" s="47"/>
-      <c r="DE4" s="47">
+      <c r="DB4" s="48"/>
+      <c r="DC4" s="48"/>
+      <c r="DD4" s="48"/>
+      <c r="DE4" s="48">
         <v>3</v>
       </c>
-      <c r="DF4" s="47"/>
-      <c r="DG4" s="47"/>
-      <c r="DH4" s="47"/>
-      <c r="DI4" s="47">
+      <c r="DF4" s="48"/>
+      <c r="DG4" s="48"/>
+      <c r="DH4" s="48"/>
+      <c r="DI4" s="48">
         <v>4</v>
       </c>
-      <c r="DJ4" s="47"/>
-      <c r="DK4" s="47"/>
-      <c r="DL4" s="47"/>
-      <c r="DM4" s="47">
+      <c r="DJ4" s="48"/>
+      <c r="DK4" s="48"/>
+      <c r="DL4" s="48"/>
+      <c r="DM4" s="48">
         <v>5</v>
       </c>
-      <c r="DN4" s="47"/>
-      <c r="DO4" s="47"/>
-      <c r="DP4" s="47"/>
-      <c r="DQ4" s="47">
+      <c r="DN4" s="48"/>
+      <c r="DO4" s="48"/>
+      <c r="DP4" s="48"/>
+      <c r="DQ4" s="48">
         <v>6</v>
       </c>
-      <c r="DR4" s="47"/>
-      <c r="DS4" s="47"/>
-      <c r="DT4" s="47"/>
-      <c r="DU4" s="47">
+      <c r="DR4" s="48"/>
+      <c r="DS4" s="48"/>
+      <c r="DT4" s="48"/>
+      <c r="DU4" s="48">
         <v>7</v>
       </c>
-      <c r="DV4" s="47"/>
-      <c r="DW4" s="47"/>
-      <c r="DX4" s="47"/>
-      <c r="DY4" s="47">
+      <c r="DV4" s="48"/>
+      <c r="DW4" s="48"/>
+      <c r="DX4" s="48"/>
+      <c r="DY4" s="48">
         <v>8</v>
       </c>
-      <c r="DZ4" s="47"/>
-      <c r="EA4" s="47"/>
-      <c r="EB4" s="47"/>
-      <c r="EC4" s="46">
+      <c r="DZ4" s="48"/>
+      <c r="EA4" s="48"/>
+      <c r="EB4" s="48"/>
+      <c r="EC4" s="50">
         <v>1</v>
       </c>
-      <c r="ED4" s="46"/>
-      <c r="EE4" s="46"/>
-      <c r="EF4" s="46"/>
-      <c r="EG4" s="46">
+      <c r="ED4" s="50"/>
+      <c r="EE4" s="50"/>
+      <c r="EF4" s="50"/>
+      <c r="EG4" s="50">
         <v>2</v>
       </c>
-      <c r="EH4" s="46"/>
-      <c r="EI4" s="46"/>
-      <c r="EJ4" s="46"/>
-      <c r="EK4" s="46">
+      <c r="EH4" s="50"/>
+      <c r="EI4" s="50"/>
+      <c r="EJ4" s="50"/>
+      <c r="EK4" s="50">
         <v>3</v>
       </c>
-      <c r="EL4" s="46"/>
-      <c r="EM4" s="46"/>
-      <c r="EN4" s="46"/>
-      <c r="EO4" s="46">
+      <c r="EL4" s="50"/>
+      <c r="EM4" s="50"/>
+      <c r="EN4" s="50"/>
+      <c r="EO4" s="50">
         <v>4</v>
       </c>
-      <c r="EP4" s="46"/>
-      <c r="EQ4" s="46"/>
-      <c r="ER4" s="46"/>
-      <c r="ES4" s="46">
+      <c r="EP4" s="50"/>
+      <c r="EQ4" s="50"/>
+      <c r="ER4" s="50"/>
+      <c r="ES4" s="50">
         <v>5</v>
       </c>
-      <c r="ET4" s="46"/>
-      <c r="EU4" s="46"/>
-      <c r="EV4" s="46"/>
-      <c r="EW4" s="46">
+      <c r="ET4" s="50"/>
+      <c r="EU4" s="50"/>
+      <c r="EV4" s="50"/>
+      <c r="EW4" s="50">
         <v>6</v>
       </c>
-      <c r="EX4" s="46"/>
-      <c r="EY4" s="46"/>
-      <c r="EZ4" s="46"/>
-      <c r="FA4" s="46">
+      <c r="EX4" s="50"/>
+      <c r="EY4" s="50"/>
+      <c r="EZ4" s="50"/>
+      <c r="FA4" s="50">
         <v>7</v>
       </c>
-      <c r="FB4" s="46"/>
-      <c r="FC4" s="46"/>
-      <c r="FD4" s="46"/>
-      <c r="FE4" s="46">
+      <c r="FB4" s="50"/>
+      <c r="FC4" s="50"/>
+      <c r="FD4" s="50"/>
+      <c r="FE4" s="50">
         <v>8</v>
       </c>
-      <c r="FF4" s="46"/>
-      <c r="FG4" s="46"/>
-      <c r="FH4" s="46"/>
-      <c r="FI4" s="47">
+      <c r="FF4" s="50"/>
+      <c r="FG4" s="50"/>
+      <c r="FH4" s="50"/>
+      <c r="FI4" s="48">
         <v>1</v>
       </c>
-      <c r="FJ4" s="47"/>
-      <c r="FK4" s="47"/>
-      <c r="FL4" s="47"/>
-      <c r="FM4" s="47">
+      <c r="FJ4" s="48"/>
+      <c r="FK4" s="48"/>
+      <c r="FL4" s="48"/>
+      <c r="FM4" s="48">
         <v>2</v>
       </c>
-      <c r="FN4" s="47"/>
-      <c r="FO4" s="47"/>
-      <c r="FP4" s="47"/>
-      <c r="FQ4" s="47">
+      <c r="FN4" s="48"/>
+      <c r="FO4" s="48"/>
+      <c r="FP4" s="48"/>
+      <c r="FQ4" s="48">
         <v>3</v>
       </c>
-      <c r="FR4" s="47"/>
-      <c r="FS4" s="47"/>
-      <c r="FT4" s="47"/>
-      <c r="FU4" s="47">
+      <c r="FR4" s="48"/>
+      <c r="FS4" s="48"/>
+      <c r="FT4" s="48"/>
+      <c r="FU4" s="48">
         <v>4</v>
       </c>
-      <c r="FV4" s="47"/>
-      <c r="FW4" s="47"/>
-      <c r="FX4" s="47"/>
-      <c r="FY4" s="47">
+      <c r="FV4" s="48"/>
+      <c r="FW4" s="48"/>
+      <c r="FX4" s="48"/>
+      <c r="FY4" s="48">
         <v>5</v>
       </c>
-      <c r="FZ4" s="47"/>
-      <c r="GA4" s="47"/>
-      <c r="GB4" s="47"/>
-      <c r="GC4" s="47">
+      <c r="FZ4" s="48"/>
+      <c r="GA4" s="48"/>
+      <c r="GB4" s="48"/>
+      <c r="GC4" s="48">
         <v>6</v>
       </c>
-      <c r="GD4" s="47"/>
-      <c r="GE4" s="47"/>
-      <c r="GF4" s="47"/>
-      <c r="GG4" s="47">
+      <c r="GD4" s="48"/>
+      <c r="GE4" s="48"/>
+      <c r="GF4" s="48"/>
+      <c r="GG4" s="48">
         <v>7</v>
       </c>
-      <c r="GH4" s="47"/>
-      <c r="GI4" s="47"/>
-      <c r="GJ4" s="47"/>
-      <c r="GK4" s="47">
+      <c r="GH4" s="48"/>
+      <c r="GI4" s="48"/>
+      <c r="GJ4" s="48"/>
+      <c r="GK4" s="48">
         <v>8</v>
       </c>
-      <c r="GL4" s="47"/>
-      <c r="GM4" s="47"/>
-      <c r="GN4" s="47"/>
-      <c r="GO4" s="47">
+      <c r="GL4" s="48"/>
+      <c r="GM4" s="48"/>
+      <c r="GN4" s="48"/>
+      <c r="GO4" s="48">
         <v>1</v>
       </c>
-      <c r="GP4" s="47"/>
-      <c r="GQ4" s="47"/>
-      <c r="GR4" s="47"/>
-      <c r="GS4" s="47">
+      <c r="GP4" s="48"/>
+      <c r="GQ4" s="48"/>
+      <c r="GR4" s="48"/>
+      <c r="GS4" s="48">
         <v>2</v>
       </c>
-      <c r="GT4" s="47"/>
-      <c r="GU4" s="47"/>
-      <c r="GV4" s="47"/>
-      <c r="GW4" s="47">
+      <c r="GT4" s="48"/>
+      <c r="GU4" s="48"/>
+      <c r="GV4" s="48"/>
+      <c r="GW4" s="48">
         <v>3</v>
       </c>
-      <c r="GX4" s="47"/>
-      <c r="GY4" s="47"/>
-      <c r="GZ4" s="47"/>
-      <c r="HA4" s="47">
+      <c r="GX4" s="48"/>
+      <c r="GY4" s="48"/>
+      <c r="GZ4" s="48"/>
+      <c r="HA4" s="48">
         <v>4</v>
       </c>
-      <c r="HB4" s="47"/>
-      <c r="HC4" s="47"/>
-      <c r="HD4" s="47"/>
-      <c r="HE4" s="46">
+      <c r="HB4" s="48"/>
+      <c r="HC4" s="48"/>
+      <c r="HD4" s="48"/>
+      <c r="HE4" s="50">
         <v>5</v>
       </c>
-      <c r="HF4" s="46"/>
-      <c r="HG4" s="46"/>
-      <c r="HH4" s="46"/>
-      <c r="HI4" s="46">
+      <c r="HF4" s="50"/>
+      <c r="HG4" s="50"/>
+      <c r="HH4" s="50"/>
+      <c r="HI4" s="50">
         <v>6</v>
       </c>
-      <c r="HJ4" s="46"/>
-      <c r="HK4" s="46"/>
-      <c r="HL4" s="46"/>
-      <c r="HM4" s="46">
+      <c r="HJ4" s="50"/>
+      <c r="HK4" s="50"/>
+      <c r="HL4" s="50"/>
+      <c r="HM4" s="50">
         <v>7</v>
       </c>
-      <c r="HN4" s="46"/>
-      <c r="HO4" s="46"/>
-      <c r="HP4" s="46"/>
-      <c r="HQ4" s="46">
+      <c r="HN4" s="50"/>
+      <c r="HO4" s="50"/>
+      <c r="HP4" s="50"/>
+      <c r="HQ4" s="50">
         <v>8</v>
       </c>
-      <c r="HR4" s="46"/>
-      <c r="HS4" s="46"/>
-      <c r="HT4" s="46"/>
-      <c r="HU4" s="47">
+      <c r="HR4" s="50"/>
+      <c r="HS4" s="50"/>
+      <c r="HT4" s="50"/>
+      <c r="HU4" s="48">
         <v>1</v>
       </c>
-      <c r="HV4" s="47"/>
-      <c r="HW4" s="47"/>
-      <c r="HX4" s="47"/>
-      <c r="HY4" s="47">
+      <c r="HV4" s="48"/>
+      <c r="HW4" s="48"/>
+      <c r="HX4" s="48"/>
+      <c r="HY4" s="48">
         <v>2</v>
       </c>
-      <c r="HZ4" s="47"/>
-      <c r="IA4" s="47"/>
-      <c r="IB4" s="47"/>
-      <c r="IC4" s="47">
+      <c r="HZ4" s="48"/>
+      <c r="IA4" s="48"/>
+      <c r="IB4" s="48"/>
+      <c r="IC4" s="48">
         <v>3</v>
       </c>
-      <c r="ID4" s="47"/>
-      <c r="IE4" s="47"/>
-      <c r="IF4" s="47"/>
-      <c r="IG4" s="47">
+      <c r="ID4" s="48"/>
+      <c r="IE4" s="48"/>
+      <c r="IF4" s="48"/>
+      <c r="IG4" s="48">
         <v>4</v>
       </c>
-      <c r="IH4" s="47"/>
-      <c r="II4" s="47"/>
-      <c r="IJ4" s="47"/>
-      <c r="IK4" s="47">
+      <c r="IH4" s="48"/>
+      <c r="II4" s="48"/>
+      <c r="IJ4" s="48"/>
+      <c r="IK4" s="48">
         <v>5</v>
       </c>
-      <c r="IL4" s="47"/>
-      <c r="IM4" s="47"/>
-      <c r="IN4" s="47"/>
-      <c r="IO4" s="47">
+      <c r="IL4" s="48"/>
+      <c r="IM4" s="48"/>
+      <c r="IN4" s="48"/>
+      <c r="IO4" s="48">
         <v>6</v>
       </c>
-      <c r="IP4" s="47"/>
-      <c r="IQ4" s="47"/>
-      <c r="IR4" s="47"/>
-      <c r="IS4" s="46">
+      <c r="IP4" s="48"/>
+      <c r="IQ4" s="48"/>
+      <c r="IR4" s="48"/>
+      <c r="IS4" s="50">
         <v>7</v>
       </c>
-      <c r="IT4" s="46"/>
-      <c r="IU4" s="46"/>
-      <c r="IV4" s="46"/>
-      <c r="IW4" s="46">
+      <c r="IT4" s="50"/>
+      <c r="IU4" s="50"/>
+      <c r="IV4" s="50"/>
+      <c r="IW4" s="50">
         <v>8</v>
       </c>
-      <c r="IX4" s="46"/>
-      <c r="IY4" s="46"/>
-      <c r="IZ4" s="46"/>
-      <c r="JA4" s="47">
+      <c r="IX4" s="50"/>
+      <c r="IY4" s="50"/>
+      <c r="IZ4" s="50"/>
+      <c r="JA4" s="48">
         <v>1</v>
       </c>
-      <c r="JB4" s="47"/>
-      <c r="JC4" s="47"/>
-      <c r="JD4" s="47"/>
-      <c r="JE4" s="47">
+      <c r="JB4" s="48"/>
+      <c r="JC4" s="48"/>
+      <c r="JD4" s="48"/>
+      <c r="JE4" s="48">
         <v>2</v>
       </c>
-      <c r="JF4" s="47"/>
-      <c r="JG4" s="47"/>
-      <c r="JH4" s="47"/>
-      <c r="JI4" s="47">
+      <c r="JF4" s="48"/>
+      <c r="JG4" s="48"/>
+      <c r="JH4" s="48"/>
+      <c r="JI4" s="48">
         <v>3</v>
       </c>
-      <c r="JJ4" s="47"/>
-      <c r="JK4" s="47"/>
-      <c r="JL4" s="47"/>
-      <c r="JM4" s="47">
+      <c r="JJ4" s="48"/>
+      <c r="JK4" s="48"/>
+      <c r="JL4" s="48"/>
+      <c r="JM4" s="48">
         <v>4</v>
       </c>
-      <c r="JN4" s="47"/>
-      <c r="JO4" s="47"/>
-      <c r="JP4" s="47"/>
-      <c r="JQ4" s="47">
+      <c r="JN4" s="48"/>
+      <c r="JO4" s="48"/>
+      <c r="JP4" s="48"/>
+      <c r="JQ4" s="48">
         <v>5</v>
       </c>
-      <c r="JR4" s="47"/>
-      <c r="JS4" s="47"/>
-      <c r="JT4" s="47"/>
-      <c r="JU4" s="47">
+      <c r="JR4" s="48"/>
+      <c r="JS4" s="48"/>
+      <c r="JT4" s="48"/>
+      <c r="JU4" s="48">
         <v>6</v>
       </c>
-      <c r="JV4" s="47"/>
-      <c r="JW4" s="47"/>
-      <c r="JX4" s="47"/>
-      <c r="JY4" s="47">
+      <c r="JV4" s="48"/>
+      <c r="JW4" s="48"/>
+      <c r="JX4" s="48"/>
+      <c r="JY4" s="48">
         <v>7</v>
       </c>
-      <c r="JZ4" s="47"/>
-      <c r="KA4" s="47"/>
-      <c r="KB4" s="47"/>
-      <c r="KC4" s="47">
+      <c r="JZ4" s="48"/>
+      <c r="KA4" s="48"/>
+      <c r="KB4" s="48"/>
+      <c r="KC4" s="48">
         <v>8</v>
       </c>
-      <c r="KD4" s="47"/>
-      <c r="KE4" s="47"/>
-      <c r="KF4" s="47"/>
-      <c r="KG4" s="46">
+      <c r="KD4" s="48"/>
+      <c r="KE4" s="48"/>
+      <c r="KF4" s="48"/>
+      <c r="KG4" s="50">
         <v>1</v>
       </c>
-      <c r="KH4" s="46"/>
-      <c r="KI4" s="46"/>
-      <c r="KJ4" s="46"/>
-      <c r="KK4" s="46">
+      <c r="KH4" s="50"/>
+      <c r="KI4" s="50"/>
+      <c r="KJ4" s="50"/>
+      <c r="KK4" s="50">
         <v>2</v>
       </c>
-      <c r="KL4" s="46"/>
-      <c r="KM4" s="46"/>
-      <c r="KN4" s="46"/>
-      <c r="KO4" s="46">
+      <c r="KL4" s="50"/>
+      <c r="KM4" s="50"/>
+      <c r="KN4" s="50"/>
+      <c r="KO4" s="50">
         <v>3</v>
       </c>
-      <c r="KP4" s="46"/>
-      <c r="KQ4" s="46"/>
-      <c r="KR4" s="46"/>
-      <c r="KS4" s="46">
+      <c r="KP4" s="50"/>
+      <c r="KQ4" s="50"/>
+      <c r="KR4" s="50"/>
+      <c r="KS4" s="50">
         <v>4</v>
       </c>
-      <c r="KT4" s="46"/>
-      <c r="KU4" s="46"/>
-      <c r="KV4" s="46"/>
-      <c r="KW4" s="46">
+      <c r="KT4" s="50"/>
+      <c r="KU4" s="50"/>
+      <c r="KV4" s="50"/>
+      <c r="KW4" s="50">
         <v>5</v>
       </c>
-      <c r="KX4" s="46"/>
-      <c r="KY4" s="46"/>
-      <c r="KZ4" s="46"/>
-      <c r="LA4" s="46">
+      <c r="KX4" s="50"/>
+      <c r="KY4" s="50"/>
+      <c r="KZ4" s="50"/>
+      <c r="LA4" s="50">
         <v>6</v>
       </c>
-      <c r="LB4" s="46"/>
-      <c r="LC4" s="46"/>
-      <c r="LD4" s="46"/>
-      <c r="LE4" s="46">
+      <c r="LB4" s="50"/>
+      <c r="LC4" s="50"/>
+      <c r="LD4" s="50"/>
+      <c r="LE4" s="50">
         <v>7</v>
       </c>
-      <c r="LF4" s="46"/>
-      <c r="LG4" s="46"/>
-      <c r="LH4" s="46"/>
-      <c r="LI4" s="46">
+      <c r="LF4" s="50"/>
+      <c r="LG4" s="50"/>
+      <c r="LH4" s="50"/>
+      <c r="LI4" s="50">
         <v>8</v>
       </c>
-      <c r="LJ4" s="46"/>
-      <c r="LK4" s="46"/>
-      <c r="LL4" s="46"/>
-      <c r="LM4" s="47">
+      <c r="LJ4" s="50"/>
+      <c r="LK4" s="50"/>
+      <c r="LL4" s="50"/>
+      <c r="LM4" s="48">
         <v>1</v>
       </c>
-      <c r="LN4" s="47"/>
-      <c r="LO4" s="47"/>
-      <c r="LP4" s="47"/>
-      <c r="LQ4" s="47">
+      <c r="LN4" s="48"/>
+      <c r="LO4" s="48"/>
+      <c r="LP4" s="48"/>
+      <c r="LQ4" s="48">
         <v>2</v>
       </c>
-      <c r="LR4" s="47"/>
-      <c r="LS4" s="47"/>
-      <c r="LT4" s="47"/>
-      <c r="LU4" s="47">
+      <c r="LR4" s="48"/>
+      <c r="LS4" s="48"/>
+      <c r="LT4" s="48"/>
+      <c r="LU4" s="48">
         <v>3</v>
       </c>
-      <c r="LV4" s="47"/>
-      <c r="LW4" s="47"/>
-      <c r="LX4" s="47"/>
-      <c r="LY4" s="47">
+      <c r="LV4" s="48"/>
+      <c r="LW4" s="48"/>
+      <c r="LX4" s="48"/>
+      <c r="LY4" s="48">
         <v>4</v>
       </c>
-      <c r="LZ4" s="47"/>
-      <c r="MA4" s="47"/>
-      <c r="MB4" s="47"/>
-      <c r="MC4" s="47">
+      <c r="LZ4" s="48"/>
+      <c r="MA4" s="48"/>
+      <c r="MB4" s="48"/>
+      <c r="MC4" s="48">
         <v>5</v>
       </c>
-      <c r="MD4" s="47"/>
-      <c r="ME4" s="47"/>
-      <c r="MF4" s="47"/>
-      <c r="MG4" s="47">
+      <c r="MD4" s="48"/>
+      <c r="ME4" s="48"/>
+      <c r="MF4" s="48"/>
+      <c r="MG4" s="48">
         <v>6</v>
       </c>
-      <c r="MH4" s="47"/>
-      <c r="MI4" s="47"/>
-      <c r="MJ4" s="47"/>
-      <c r="MK4" s="47">
+      <c r="MH4" s="48"/>
+      <c r="MI4" s="48"/>
+      <c r="MJ4" s="48"/>
+      <c r="MK4" s="48">
         <v>7</v>
       </c>
-      <c r="ML4" s="47"/>
-      <c r="MM4" s="47"/>
-      <c r="MN4" s="47"/>
-      <c r="MO4" s="47">
+      <c r="ML4" s="48"/>
+      <c r="MM4" s="48"/>
+      <c r="MN4" s="48"/>
+      <c r="MO4" s="48">
         <v>8</v>
       </c>
-      <c r="MP4" s="47"/>
-      <c r="MQ4" s="47"/>
-      <c r="MR4" s="47"/>
-      <c r="MS4" s="47">
+      <c r="MP4" s="48"/>
+      <c r="MQ4" s="48"/>
+      <c r="MR4" s="48"/>
+      <c r="MS4" s="48">
         <v>1</v>
       </c>
-      <c r="MT4" s="47"/>
-      <c r="MU4" s="47"/>
-      <c r="MV4" s="47"/>
-      <c r="MW4" s="47">
+      <c r="MT4" s="48"/>
+      <c r="MU4" s="48"/>
+      <c r="MV4" s="48"/>
+      <c r="MW4" s="48">
         <v>2</v>
       </c>
-      <c r="MX4" s="47"/>
-      <c r="MY4" s="47"/>
-      <c r="MZ4" s="47"/>
-      <c r="NA4" s="47">
+      <c r="MX4" s="48"/>
+      <c r="MY4" s="48"/>
+      <c r="MZ4" s="48"/>
+      <c r="NA4" s="48">
         <v>3</v>
       </c>
-      <c r="NB4" s="47"/>
-      <c r="NC4" s="47"/>
-      <c r="ND4" s="47"/>
-      <c r="NE4" s="47">
+      <c r="NB4" s="48"/>
+      <c r="NC4" s="48"/>
+      <c r="ND4" s="48"/>
+      <c r="NE4" s="48">
         <v>4</v>
       </c>
-      <c r="NF4" s="47"/>
-      <c r="NG4" s="47"/>
-      <c r="NH4" s="47"/>
-      <c r="NI4" s="46">
+      <c r="NF4" s="48"/>
+      <c r="NG4" s="48"/>
+      <c r="NH4" s="48"/>
+      <c r="NI4" s="50">
         <v>5</v>
       </c>
-      <c r="NJ4" s="46"/>
-      <c r="NK4" s="46"/>
-      <c r="NL4" s="46"/>
-      <c r="NM4" s="46">
+      <c r="NJ4" s="50"/>
+      <c r="NK4" s="50"/>
+      <c r="NL4" s="50"/>
+      <c r="NM4" s="50">
         <v>6</v>
       </c>
-      <c r="NN4" s="46"/>
-      <c r="NO4" s="46"/>
-      <c r="NP4" s="46"/>
-      <c r="NQ4" s="46">
+      <c r="NN4" s="50"/>
+      <c r="NO4" s="50"/>
+      <c r="NP4" s="50"/>
+      <c r="NQ4" s="50">
         <v>7</v>
       </c>
-      <c r="NR4" s="46"/>
-      <c r="NS4" s="46"/>
-      <c r="NT4" s="46"/>
-      <c r="NU4" s="46">
+      <c r="NR4" s="50"/>
+      <c r="NS4" s="50"/>
+      <c r="NT4" s="50"/>
+      <c r="NU4" s="50">
         <v>8</v>
       </c>
-      <c r="NV4" s="46"/>
-      <c r="NW4" s="46"/>
-      <c r="NX4" s="46"/>
-      <c r="NY4" s="47">
+      <c r="NV4" s="50"/>
+      <c r="NW4" s="50"/>
+      <c r="NX4" s="50"/>
+      <c r="NY4" s="48">
         <v>1</v>
       </c>
-      <c r="NZ4" s="47"/>
-      <c r="OA4" s="47"/>
-      <c r="OB4" s="47"/>
-      <c r="OC4" s="47">
+      <c r="NZ4" s="48"/>
+      <c r="OA4" s="48"/>
+      <c r="OB4" s="48"/>
+      <c r="OC4" s="48">
         <v>2</v>
       </c>
-      <c r="OD4" s="47"/>
-      <c r="OE4" s="47"/>
-      <c r="OF4" s="47"/>
-      <c r="OG4" s="47">
+      <c r="OD4" s="48"/>
+      <c r="OE4" s="48"/>
+      <c r="OF4" s="48"/>
+      <c r="OG4" s="48">
         <v>3</v>
       </c>
-      <c r="OH4" s="47"/>
-      <c r="OI4" s="47"/>
-      <c r="OJ4" s="47"/>
-      <c r="OK4" s="47">
+      <c r="OH4" s="48"/>
+      <c r="OI4" s="48"/>
+      <c r="OJ4" s="48"/>
+      <c r="OK4" s="48">
         <v>4</v>
       </c>
-      <c r="OL4" s="47"/>
-      <c r="OM4" s="47"/>
-      <c r="ON4" s="47"/>
-      <c r="OO4" s="47">
+      <c r="OL4" s="48"/>
+      <c r="OM4" s="48"/>
+      <c r="ON4" s="48"/>
+      <c r="OO4" s="48">
         <v>5</v>
       </c>
-      <c r="OP4" s="47"/>
-      <c r="OQ4" s="47"/>
-      <c r="OR4" s="47"/>
-      <c r="OS4" s="47">
+      <c r="OP4" s="48"/>
+      <c r="OQ4" s="48"/>
+      <c r="OR4" s="48"/>
+      <c r="OS4" s="48">
         <v>6</v>
       </c>
-      <c r="OT4" s="47"/>
-      <c r="OU4" s="47"/>
-      <c r="OV4" s="47"/>
-      <c r="OW4" s="46">
+      <c r="OT4" s="48"/>
+      <c r="OU4" s="48"/>
+      <c r="OV4" s="48"/>
+      <c r="OW4" s="50">
         <v>7</v>
       </c>
-      <c r="OX4" s="46"/>
-      <c r="OY4" s="46"/>
-      <c r="OZ4" s="46"/>
-      <c r="PA4" s="46">
+      <c r="OX4" s="50"/>
+      <c r="OY4" s="50"/>
+      <c r="OZ4" s="50"/>
+      <c r="PA4" s="50">
         <v>8</v>
       </c>
-      <c r="PB4" s="46"/>
-      <c r="PC4" s="46"/>
-      <c r="PD4" s="46"/>
-      <c r="PE4" s="47">
+      <c r="PB4" s="50"/>
+      <c r="PC4" s="50"/>
+      <c r="PD4" s="50"/>
+      <c r="PE4" s="48">
         <v>1</v>
       </c>
-      <c r="PF4" s="47"/>
-      <c r="PG4" s="47"/>
-      <c r="PH4" s="47"/>
-      <c r="PI4" s="47">
+      <c r="PF4" s="48"/>
+      <c r="PG4" s="48"/>
+      <c r="PH4" s="48"/>
+      <c r="PI4" s="48">
         <v>2</v>
       </c>
-      <c r="PJ4" s="47"/>
-      <c r="PK4" s="47"/>
-      <c r="PL4" s="47"/>
-      <c r="PM4" s="47">
+      <c r="PJ4" s="48"/>
+      <c r="PK4" s="48"/>
+      <c r="PL4" s="48"/>
+      <c r="PM4" s="48">
         <v>3</v>
       </c>
-      <c r="PN4" s="47"/>
-      <c r="PO4" s="47"/>
-      <c r="PP4" s="47"/>
-      <c r="PQ4" s="47">
+      <c r="PN4" s="48"/>
+      <c r="PO4" s="48"/>
+      <c r="PP4" s="48"/>
+      <c r="PQ4" s="48">
         <v>4</v>
       </c>
-      <c r="PR4" s="47"/>
-      <c r="PS4" s="47"/>
-      <c r="PT4" s="47"/>
-      <c r="PU4" s="47">
+      <c r="PR4" s="48"/>
+      <c r="PS4" s="48"/>
+      <c r="PT4" s="48"/>
+      <c r="PU4" s="48">
         <v>5</v>
       </c>
-      <c r="PV4" s="47"/>
-      <c r="PW4" s="47"/>
-      <c r="PX4" s="47"/>
-      <c r="PY4" s="47">
+      <c r="PV4" s="48"/>
+      <c r="PW4" s="48"/>
+      <c r="PX4" s="48"/>
+      <c r="PY4" s="48">
         <v>6</v>
       </c>
-      <c r="PZ4" s="47"/>
-      <c r="QA4" s="47"/>
-      <c r="QB4" s="47"/>
-      <c r="QC4" s="47">
+      <c r="PZ4" s="48"/>
+      <c r="QA4" s="48"/>
+      <c r="QB4" s="48"/>
+      <c r="QC4" s="48">
         <v>7</v>
       </c>
-      <c r="QD4" s="47"/>
-      <c r="QE4" s="47"/>
-      <c r="QF4" s="47"/>
-      <c r="QG4" s="47">
+      <c r="QD4" s="48"/>
+      <c r="QE4" s="48"/>
+      <c r="QF4" s="48"/>
+      <c r="QG4" s="48">
         <v>8</v>
       </c>
-      <c r="QH4" s="47"/>
-      <c r="QI4" s="47"/>
-      <c r="QJ4" s="47"/>
-      <c r="QK4" s="46">
+      <c r="QH4" s="48"/>
+      <c r="QI4" s="48"/>
+      <c r="QJ4" s="48"/>
+      <c r="QK4" s="50">
         <v>1</v>
       </c>
-      <c r="QL4" s="46"/>
-      <c r="QM4" s="46"/>
-      <c r="QN4" s="46"/>
-      <c r="QO4" s="46">
+      <c r="QL4" s="50"/>
+      <c r="QM4" s="50"/>
+      <c r="QN4" s="50"/>
+      <c r="QO4" s="50">
         <v>2</v>
       </c>
-      <c r="QP4" s="46"/>
-      <c r="QQ4" s="46"/>
-      <c r="QR4" s="46"/>
-      <c r="QS4" s="46">
+      <c r="QP4" s="50"/>
+      <c r="QQ4" s="50"/>
+      <c r="QR4" s="50"/>
+      <c r="QS4" s="50">
         <v>3</v>
       </c>
-      <c r="QT4" s="46"/>
-      <c r="QU4" s="46"/>
-      <c r="QV4" s="46"/>
-      <c r="QW4" s="46">
+      <c r="QT4" s="50"/>
+      <c r="QU4" s="50"/>
+      <c r="QV4" s="50"/>
+      <c r="QW4" s="50">
         <v>4</v>
       </c>
-      <c r="QX4" s="46"/>
-      <c r="QY4" s="46"/>
-      <c r="QZ4" s="46"/>
-      <c r="RA4" s="46">
+      <c r="QX4" s="50"/>
+      <c r="QY4" s="50"/>
+      <c r="QZ4" s="50"/>
+      <c r="RA4" s="50">
         <v>5</v>
       </c>
-      <c r="RB4" s="46"/>
-      <c r="RC4" s="46"/>
-      <c r="RD4" s="46"/>
-      <c r="RE4" s="46">
+      <c r="RB4" s="50"/>
+      <c r="RC4" s="50"/>
+      <c r="RD4" s="50"/>
+      <c r="RE4" s="50">
         <v>6</v>
       </c>
-      <c r="RF4" s="46"/>
-      <c r="RG4" s="46"/>
-      <c r="RH4" s="46"/>
-      <c r="RI4" s="46">
+      <c r="RF4" s="50"/>
+      <c r="RG4" s="50"/>
+      <c r="RH4" s="50"/>
+      <c r="RI4" s="50">
         <v>7</v>
       </c>
-      <c r="RJ4" s="46"/>
-      <c r="RK4" s="46"/>
-      <c r="RL4" s="46"/>
-      <c r="RM4" s="46">
+      <c r="RJ4" s="50"/>
+      <c r="RK4" s="50"/>
+      <c r="RL4" s="50"/>
+      <c r="RM4" s="50">
         <v>8</v>
       </c>
-      <c r="RN4" s="46"/>
-      <c r="RO4" s="46"/>
-      <c r="RP4" s="46"/>
-      <c r="RQ4" s="51">
+      <c r="RN4" s="50"/>
+      <c r="RO4" s="50"/>
+      <c r="RP4" s="50"/>
+      <c r="RQ4" s="54">
         <v>1</v>
       </c>
-      <c r="RR4" s="51"/>
-      <c r="RS4" s="51"/>
-      <c r="RT4" s="51"/>
-      <c r="RU4" s="51">
+      <c r="RR4" s="54"/>
+      <c r="RS4" s="54"/>
+      <c r="RT4" s="54"/>
+      <c r="RU4" s="54">
         <v>2</v>
       </c>
-      <c r="RV4" s="51"/>
-      <c r="RW4" s="51"/>
-      <c r="RX4" s="51"/>
-      <c r="RY4" s="51">
+      <c r="RV4" s="54"/>
+      <c r="RW4" s="54"/>
+      <c r="RX4" s="54"/>
+      <c r="RY4" s="54">
         <v>3</v>
       </c>
-      <c r="RZ4" s="51"/>
-      <c r="SA4" s="51"/>
-      <c r="SB4" s="51"/>
-      <c r="SC4" s="51">
+      <c r="RZ4" s="54"/>
+      <c r="SA4" s="54"/>
+      <c r="SB4" s="54"/>
+      <c r="SC4" s="54">
         <v>4</v>
       </c>
-      <c r="SD4" s="51"/>
-      <c r="SE4" s="51"/>
-      <c r="SF4" s="51"/>
-      <c r="SG4" s="51">
+      <c r="SD4" s="54"/>
+      <c r="SE4" s="54"/>
+      <c r="SF4" s="54"/>
+      <c r="SG4" s="54">
         <v>5</v>
       </c>
-      <c r="SH4" s="51"/>
-      <c r="SI4" s="51"/>
-      <c r="SJ4" s="51"/>
-      <c r="SK4" s="51">
+      <c r="SH4" s="54"/>
+      <c r="SI4" s="54"/>
+      <c r="SJ4" s="54"/>
+      <c r="SK4" s="54">
         <v>6</v>
       </c>
-      <c r="SL4" s="51"/>
-      <c r="SM4" s="51"/>
-      <c r="SN4" s="51"/>
-      <c r="SO4" s="51">
+      <c r="SL4" s="54"/>
+      <c r="SM4" s="54"/>
+      <c r="SN4" s="54"/>
+      <c r="SO4" s="54">
         <v>7</v>
       </c>
-      <c r="SP4" s="51"/>
-      <c r="SQ4" s="51"/>
-      <c r="SR4" s="51"/>
-      <c r="SS4" s="51">
+      <c r="SP4" s="54"/>
+      <c r="SQ4" s="54"/>
+      <c r="SR4" s="54"/>
+      <c r="SS4" s="54">
         <v>8</v>
       </c>
-      <c r="ST4" s="51"/>
-      <c r="SU4" s="51"/>
-      <c r="SV4" s="51"/>
-      <c r="SW4" s="51">
+      <c r="ST4" s="54"/>
+      <c r="SU4" s="54"/>
+      <c r="SV4" s="54"/>
+      <c r="SW4" s="54">
         <v>1</v>
       </c>
-      <c r="SX4" s="51"/>
-      <c r="SY4" s="51"/>
-      <c r="SZ4" s="51"/>
-      <c r="TA4" s="51">
+      <c r="SX4" s="54"/>
+      <c r="SY4" s="54"/>
+      <c r="SZ4" s="54"/>
+      <c r="TA4" s="54">
         <v>2</v>
       </c>
-      <c r="TB4" s="51"/>
-      <c r="TC4" s="51"/>
-      <c r="TD4" s="51"/>
-      <c r="TE4" s="51">
+      <c r="TB4" s="54"/>
+      <c r="TC4" s="54"/>
+      <c r="TD4" s="54"/>
+      <c r="TE4" s="54">
         <v>3</v>
       </c>
-      <c r="TF4" s="51"/>
-      <c r="TG4" s="51"/>
-      <c r="TH4" s="51"/>
-      <c r="TI4" s="51">
+      <c r="TF4" s="54"/>
+      <c r="TG4" s="54"/>
+      <c r="TH4" s="54"/>
+      <c r="TI4" s="54">
         <v>4</v>
       </c>
-      <c r="TJ4" s="51"/>
-      <c r="TK4" s="51"/>
-      <c r="TL4" s="51"/>
-      <c r="TM4" s="51">
+      <c r="TJ4" s="54"/>
+      <c r="TK4" s="54"/>
+      <c r="TL4" s="54"/>
+      <c r="TM4" s="54">
         <v>5</v>
       </c>
-      <c r="TN4" s="51"/>
-      <c r="TO4" s="51"/>
-      <c r="TP4" s="51"/>
-      <c r="TQ4" s="51">
+      <c r="TN4" s="54"/>
+      <c r="TO4" s="54"/>
+      <c r="TP4" s="54"/>
+      <c r="TQ4" s="54">
         <v>6</v>
       </c>
-      <c r="TR4" s="51"/>
-      <c r="TS4" s="51"/>
-      <c r="TT4" s="51"/>
-      <c r="TU4" s="51">
+      <c r="TR4" s="54"/>
+      <c r="TS4" s="54"/>
+      <c r="TT4" s="54"/>
+      <c r="TU4" s="54">
         <v>7</v>
       </c>
-      <c r="TV4" s="51"/>
-      <c r="TW4" s="51"/>
-      <c r="TX4" s="51"/>
-      <c r="TY4" s="51">
+      <c r="TV4" s="54"/>
+      <c r="TW4" s="54"/>
+      <c r="TX4" s="54"/>
+      <c r="TY4" s="54">
         <v>8</v>
       </c>
-      <c r="TZ4" s="51"/>
-      <c r="UA4" s="51"/>
-      <c r="UB4" s="51"/>
-      <c r="UC4" s="47">
+      <c r="TZ4" s="54"/>
+      <c r="UA4" s="54"/>
+      <c r="UB4" s="54"/>
+      <c r="UC4" s="48">
         <v>1</v>
       </c>
-      <c r="UD4" s="47"/>
-      <c r="UE4" s="47"/>
-      <c r="UF4" s="47"/>
-      <c r="UG4" s="47">
+      <c r="UD4" s="48"/>
+      <c r="UE4" s="48"/>
+      <c r="UF4" s="48"/>
+      <c r="UG4" s="48">
         <v>2</v>
       </c>
-      <c r="UH4" s="47"/>
-      <c r="UI4" s="47"/>
-      <c r="UJ4" s="47"/>
-      <c r="UK4" s="47">
+      <c r="UH4" s="48"/>
+      <c r="UI4" s="48"/>
+      <c r="UJ4" s="48"/>
+      <c r="UK4" s="48">
         <v>3</v>
       </c>
-      <c r="UL4" s="47"/>
-      <c r="UM4" s="47"/>
-      <c r="UN4" s="47"/>
-      <c r="UO4" s="47">
+      <c r="UL4" s="48"/>
+      <c r="UM4" s="48"/>
+      <c r="UN4" s="48"/>
+      <c r="UO4" s="48">
         <v>4</v>
       </c>
-      <c r="UP4" s="47"/>
-      <c r="UQ4" s="47"/>
-      <c r="UR4" s="47"/>
-      <c r="US4" s="47">
+      <c r="UP4" s="48"/>
+      <c r="UQ4" s="48"/>
+      <c r="UR4" s="48"/>
+      <c r="US4" s="48">
         <v>5</v>
       </c>
-      <c r="UT4" s="47"/>
-      <c r="UU4" s="47"/>
-      <c r="UV4" s="47"/>
-      <c r="UW4" s="47">
+      <c r="UT4" s="48"/>
+      <c r="UU4" s="48"/>
+      <c r="UV4" s="48"/>
+      <c r="UW4" s="48">
         <v>6</v>
       </c>
-      <c r="UX4" s="47"/>
-      <c r="UY4" s="47"/>
-      <c r="UZ4" s="47"/>
-      <c r="VA4" s="46">
+      <c r="UX4" s="48"/>
+      <c r="UY4" s="48"/>
+      <c r="UZ4" s="48"/>
+      <c r="VA4" s="50">
         <v>7</v>
       </c>
-      <c r="VB4" s="46"/>
-      <c r="VC4" s="46"/>
-      <c r="VD4" s="46"/>
-      <c r="VE4" s="46">
+      <c r="VB4" s="50"/>
+      <c r="VC4" s="50"/>
+      <c r="VD4" s="50"/>
+      <c r="VE4" s="50">
         <v>8</v>
       </c>
-      <c r="VF4" s="46"/>
-      <c r="VG4" s="46"/>
-      <c r="VH4" s="46"/>
-      <c r="VI4" s="47">
+      <c r="VF4" s="50"/>
+      <c r="VG4" s="50"/>
+      <c r="VH4" s="50"/>
+      <c r="VI4" s="48">
         <v>1</v>
       </c>
-      <c r="VJ4" s="47"/>
-      <c r="VK4" s="47"/>
-      <c r="VL4" s="47"/>
-      <c r="VM4" s="47">
+      <c r="VJ4" s="48"/>
+      <c r="VK4" s="48"/>
+      <c r="VL4" s="48"/>
+      <c r="VM4" s="48">
         <v>2</v>
       </c>
-      <c r="VN4" s="47"/>
-      <c r="VO4" s="47"/>
-      <c r="VP4" s="47"/>
-      <c r="VQ4" s="47">
+      <c r="VN4" s="48"/>
+      <c r="VO4" s="48"/>
+      <c r="VP4" s="48"/>
+      <c r="VQ4" s="48">
         <v>3</v>
       </c>
-      <c r="VR4" s="47"/>
-      <c r="VS4" s="47"/>
-      <c r="VT4" s="47"/>
-      <c r="VU4" s="47">
+      <c r="VR4" s="48"/>
+      <c r="VS4" s="48"/>
+      <c r="VT4" s="48"/>
+      <c r="VU4" s="48">
         <v>4</v>
       </c>
-      <c r="VV4" s="47"/>
-      <c r="VW4" s="47"/>
-      <c r="VX4" s="47"/>
-      <c r="VY4" s="47">
+      <c r="VV4" s="48"/>
+      <c r="VW4" s="48"/>
+      <c r="VX4" s="48"/>
+      <c r="VY4" s="48">
         <v>5</v>
       </c>
-      <c r="VZ4" s="47"/>
-      <c r="WA4" s="47"/>
-      <c r="WB4" s="47"/>
-      <c r="WC4" s="47">
+      <c r="VZ4" s="48"/>
+      <c r="WA4" s="48"/>
+      <c r="WB4" s="48"/>
+      <c r="WC4" s="48">
         <v>6</v>
       </c>
-      <c r="WD4" s="47"/>
-      <c r="WE4" s="47"/>
-      <c r="WF4" s="47"/>
-      <c r="WG4" s="47">
+      <c r="WD4" s="48"/>
+      <c r="WE4" s="48"/>
+      <c r="WF4" s="48"/>
+      <c r="WG4" s="48">
         <v>7</v>
       </c>
-      <c r="WH4" s="47"/>
-      <c r="WI4" s="47"/>
-      <c r="WJ4" s="47"/>
-      <c r="WK4" s="47">
+      <c r="WH4" s="48"/>
+      <c r="WI4" s="48"/>
+      <c r="WJ4" s="48"/>
+      <c r="WK4" s="48">
         <v>8</v>
       </c>
-      <c r="WL4" s="47"/>
-      <c r="WM4" s="47"/>
-      <c r="WN4" s="47"/>
-      <c r="WO4" s="46">
+      <c r="WL4" s="48"/>
+      <c r="WM4" s="48"/>
+      <c r="WN4" s="48"/>
+      <c r="WO4" s="50">
         <v>1</v>
       </c>
-      <c r="WP4" s="46"/>
-      <c r="WQ4" s="46"/>
-      <c r="WR4" s="46"/>
-      <c r="WS4" s="46">
+      <c r="WP4" s="50"/>
+      <c r="WQ4" s="50"/>
+      <c r="WR4" s="50"/>
+      <c r="WS4" s="50">
         <v>2</v>
       </c>
-      <c r="WT4" s="46"/>
-      <c r="WU4" s="46"/>
-      <c r="WV4" s="46"/>
-      <c r="WW4" s="46">
+      <c r="WT4" s="50"/>
+      <c r="WU4" s="50"/>
+      <c r="WV4" s="50"/>
+      <c r="WW4" s="50">
         <v>3</v>
       </c>
-      <c r="WX4" s="46"/>
-      <c r="WY4" s="46"/>
-      <c r="WZ4" s="46"/>
-      <c r="XA4" s="46">
+      <c r="WX4" s="50"/>
+      <c r="WY4" s="50"/>
+      <c r="WZ4" s="50"/>
+      <c r="XA4" s="50">
         <v>4</v>
       </c>
-      <c r="XB4" s="46"/>
-      <c r="XC4" s="46"/>
-      <c r="XD4" s="46"/>
-      <c r="XE4" s="46">
+      <c r="XB4" s="50"/>
+      <c r="XC4" s="50"/>
+      <c r="XD4" s="50"/>
+      <c r="XE4" s="50">
         <v>5</v>
       </c>
-      <c r="XF4" s="46"/>
-      <c r="XG4" s="46"/>
-      <c r="XH4" s="46"/>
-      <c r="XI4" s="46">
+      <c r="XF4" s="50"/>
+      <c r="XG4" s="50"/>
+      <c r="XH4" s="50"/>
+      <c r="XI4" s="50">
         <v>6</v>
       </c>
-      <c r="XJ4" s="46"/>
-      <c r="XK4" s="46"/>
-      <c r="XL4" s="46"/>
-      <c r="XM4" s="46">
+      <c r="XJ4" s="50"/>
+      <c r="XK4" s="50"/>
+      <c r="XL4" s="50"/>
+      <c r="XM4" s="50">
         <v>7</v>
       </c>
-      <c r="XN4" s="46"/>
-      <c r="XO4" s="46"/>
-      <c r="XP4" s="46"/>
-      <c r="XQ4" s="46">
+      <c r="XN4" s="50"/>
+      <c r="XO4" s="50"/>
+      <c r="XP4" s="50"/>
+      <c r="XQ4" s="50">
         <v>8</v>
       </c>
-      <c r="XR4" s="46"/>
-      <c r="XS4" s="46"/>
-      <c r="XT4" s="46"/>
-      <c r="XU4" s="47">
+      <c r="XR4" s="50"/>
+      <c r="XS4" s="50"/>
+      <c r="XT4" s="50"/>
+      <c r="XU4" s="48">
         <v>1</v>
       </c>
-      <c r="XV4" s="47"/>
-      <c r="XW4" s="47"/>
-      <c r="XX4" s="47"/>
-      <c r="XY4" s="47">
+      <c r="XV4" s="48"/>
+      <c r="XW4" s="48"/>
+      <c r="XX4" s="48"/>
+      <c r="XY4" s="48">
         <v>2</v>
       </c>
-      <c r="XZ4" s="47"/>
-      <c r="YA4" s="47"/>
-      <c r="YB4" s="47"/>
-      <c r="YC4" s="47">
+      <c r="XZ4" s="48"/>
+      <c r="YA4" s="48"/>
+      <c r="YB4" s="48"/>
+      <c r="YC4" s="48">
         <v>3</v>
       </c>
-      <c r="YD4" s="47"/>
-      <c r="YE4" s="47"/>
-      <c r="YF4" s="47"/>
-      <c r="YG4" s="47">
+      <c r="YD4" s="48"/>
+      <c r="YE4" s="48"/>
+      <c r="YF4" s="48"/>
+      <c r="YG4" s="48">
         <v>4</v>
       </c>
-      <c r="YH4" s="47"/>
-      <c r="YI4" s="47"/>
-      <c r="YJ4" s="47"/>
-      <c r="YK4" s="47">
+      <c r="YH4" s="48"/>
+      <c r="YI4" s="48"/>
+      <c r="YJ4" s="48"/>
+      <c r="YK4" s="48">
         <v>5</v>
       </c>
-      <c r="YL4" s="47"/>
-      <c r="YM4" s="47"/>
-      <c r="YN4" s="47"/>
-      <c r="YO4" s="47">
+      <c r="YL4" s="48"/>
+      <c r="YM4" s="48"/>
+      <c r="YN4" s="48"/>
+      <c r="YO4" s="48">
         <v>6</v>
       </c>
-      <c r="YP4" s="47"/>
-      <c r="YQ4" s="47"/>
-      <c r="YR4" s="47"/>
-      <c r="YS4" s="47">
+      <c r="YP4" s="48"/>
+      <c r="YQ4" s="48"/>
+      <c r="YR4" s="48"/>
+      <c r="YS4" s="48">
         <v>7</v>
       </c>
-      <c r="YT4" s="47"/>
-      <c r="YU4" s="47"/>
-      <c r="YV4" s="47"/>
-      <c r="YW4" s="46">
+      <c r="YT4" s="48"/>
+      <c r="YU4" s="48"/>
+      <c r="YV4" s="48"/>
+      <c r="YW4" s="50">
         <v>8</v>
       </c>
-      <c r="YX4" s="46"/>
-      <c r="YY4" s="46"/>
-      <c r="YZ4" s="46"/>
+      <c r="YX4" s="50"/>
+      <c r="YY4" s="50"/>
+      <c r="YZ4" s="50"/>
     </row>
     <row r="5" spans="1:676" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="57"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
+      <c r="A5" s="51"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
       <c r="E5" s="1" t="s">
         <v>26</v>
       </c>
@@ -26220,7 +26220,9 @@
       <c r="C35" s="41">
         <v>0.5</v>
       </c>
-      <c r="D35" s="11"/>
+      <c r="D35" s="41">
+        <v>1</v>
+      </c>
       <c r="E35" s="14"/>
       <c r="F35" s="15"/>
       <c r="G35" s="15"/>
@@ -26902,7 +26904,9 @@
       <c r="C36" s="41">
         <v>1.5</v>
       </c>
-      <c r="D36" s="11"/>
+      <c r="D36" s="41">
+        <v>1</v>
+      </c>
       <c r="E36" s="14"/>
       <c r="F36" s="15"/>
       <c r="G36" s="15"/>
@@ -27586,7 +27590,9 @@
       <c r="C37" s="41">
         <v>2</v>
       </c>
-      <c r="D37" s="11"/>
+      <c r="D37" s="41">
+        <v>2</v>
+      </c>
       <c r="E37" s="14"/>
       <c r="F37" s="15"/>
       <c r="G37" s="15"/>
@@ -53555,6 +53561,178 @@
     </row>
   </sheetData>
   <mergeCells count="196">
+    <mergeCell ref="XA4:XD4"/>
+    <mergeCell ref="VQ4:VT4"/>
+    <mergeCell ref="YO4:YR4"/>
+    <mergeCell ref="YS4:YV4"/>
+    <mergeCell ref="YW4:YZ4"/>
+    <mergeCell ref="A2:YZ2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:YZ1"/>
+    <mergeCell ref="XE4:XH4"/>
+    <mergeCell ref="XI4:XL4"/>
+    <mergeCell ref="XM4:XP4"/>
+    <mergeCell ref="XQ4:XT4"/>
+    <mergeCell ref="XU4:XX4"/>
+    <mergeCell ref="XY4:YB4"/>
+    <mergeCell ref="YC4:YF4"/>
+    <mergeCell ref="YG4:YJ4"/>
+    <mergeCell ref="YK4:YN4"/>
+    <mergeCell ref="VU4:VX4"/>
+    <mergeCell ref="VY4:WB4"/>
+    <mergeCell ref="WC4:WF4"/>
+    <mergeCell ref="WG4:WJ4"/>
+    <mergeCell ref="WK4:WN4"/>
+    <mergeCell ref="WO4:WR4"/>
+    <mergeCell ref="WS4:WV4"/>
+    <mergeCell ref="WW4:WZ4"/>
+    <mergeCell ref="UG4:UJ4"/>
+    <mergeCell ref="UK4:UN4"/>
+    <mergeCell ref="UO4:UR4"/>
+    <mergeCell ref="US4:UV4"/>
+    <mergeCell ref="UW4:UZ4"/>
+    <mergeCell ref="VA4:VD4"/>
+    <mergeCell ref="VE4:VH4"/>
+    <mergeCell ref="VI4:VL4"/>
+    <mergeCell ref="VM4:VP4"/>
+    <mergeCell ref="SW4:SZ4"/>
+    <mergeCell ref="TA4:TD4"/>
+    <mergeCell ref="TE4:TH4"/>
+    <mergeCell ref="TI4:TL4"/>
+    <mergeCell ref="TM4:TP4"/>
+    <mergeCell ref="TQ4:TT4"/>
+    <mergeCell ref="TU4:TX4"/>
+    <mergeCell ref="TY4:UB4"/>
+    <mergeCell ref="UC4:UF4"/>
+    <mergeCell ref="RM4:RP4"/>
+    <mergeCell ref="RQ4:RT4"/>
+    <mergeCell ref="RU4:RX4"/>
+    <mergeCell ref="RY4:SB4"/>
+    <mergeCell ref="SC4:SF4"/>
+    <mergeCell ref="SG4:SJ4"/>
+    <mergeCell ref="SK4:SN4"/>
+    <mergeCell ref="SO4:SR4"/>
+    <mergeCell ref="SS4:SV4"/>
+    <mergeCell ref="QC4:QF4"/>
+    <mergeCell ref="QG4:QJ4"/>
+    <mergeCell ref="QK4:QN4"/>
+    <mergeCell ref="QO4:QR4"/>
+    <mergeCell ref="QS4:QV4"/>
+    <mergeCell ref="QW4:QZ4"/>
+    <mergeCell ref="RA4:RD4"/>
+    <mergeCell ref="RE4:RH4"/>
+    <mergeCell ref="RI4:RL4"/>
+    <mergeCell ref="OS4:OV4"/>
+    <mergeCell ref="OW4:OZ4"/>
+    <mergeCell ref="PA4:PD4"/>
+    <mergeCell ref="PE4:PH4"/>
+    <mergeCell ref="PI4:PL4"/>
+    <mergeCell ref="PM4:PP4"/>
+    <mergeCell ref="PQ4:PT4"/>
+    <mergeCell ref="PU4:PX4"/>
+    <mergeCell ref="PY4:QB4"/>
+    <mergeCell ref="NI4:NL4"/>
+    <mergeCell ref="NM4:NP4"/>
+    <mergeCell ref="NQ4:NT4"/>
+    <mergeCell ref="NU4:NX4"/>
+    <mergeCell ref="NY4:OB4"/>
+    <mergeCell ref="OC4:OF4"/>
+    <mergeCell ref="OG4:OJ4"/>
+    <mergeCell ref="OK4:ON4"/>
+    <mergeCell ref="OO4:OR4"/>
+    <mergeCell ref="LY4:MB4"/>
+    <mergeCell ref="MC4:MF4"/>
+    <mergeCell ref="MG4:MJ4"/>
+    <mergeCell ref="MK4:MN4"/>
+    <mergeCell ref="MO4:MR4"/>
+    <mergeCell ref="MS4:MV4"/>
+    <mergeCell ref="MW4:MZ4"/>
+    <mergeCell ref="NA4:ND4"/>
+    <mergeCell ref="NE4:NH4"/>
+    <mergeCell ref="KO4:KR4"/>
+    <mergeCell ref="KS4:KV4"/>
+    <mergeCell ref="KW4:KZ4"/>
+    <mergeCell ref="LA4:LD4"/>
+    <mergeCell ref="LE4:LH4"/>
+    <mergeCell ref="LI4:LL4"/>
+    <mergeCell ref="LM4:LP4"/>
+    <mergeCell ref="LQ4:LT4"/>
+    <mergeCell ref="LU4:LX4"/>
+    <mergeCell ref="JE4:JH4"/>
+    <mergeCell ref="JI4:JL4"/>
+    <mergeCell ref="JM4:JP4"/>
+    <mergeCell ref="JQ4:JT4"/>
+    <mergeCell ref="JU4:JX4"/>
+    <mergeCell ref="JY4:KB4"/>
+    <mergeCell ref="KC4:KF4"/>
+    <mergeCell ref="KG4:KJ4"/>
+    <mergeCell ref="KK4:KN4"/>
+    <mergeCell ref="HU4:HX4"/>
+    <mergeCell ref="HY4:IB4"/>
+    <mergeCell ref="IC4:IF4"/>
+    <mergeCell ref="IG4:IJ4"/>
+    <mergeCell ref="IK4:IN4"/>
+    <mergeCell ref="IO4:IR4"/>
+    <mergeCell ref="IS4:IV4"/>
+    <mergeCell ref="IW4:IZ4"/>
+    <mergeCell ref="JA4:JD4"/>
+    <mergeCell ref="GK4:GN4"/>
+    <mergeCell ref="GO4:GR4"/>
+    <mergeCell ref="GS4:GV4"/>
+    <mergeCell ref="GW4:GZ4"/>
+    <mergeCell ref="HA4:HD4"/>
+    <mergeCell ref="HE4:HH4"/>
+    <mergeCell ref="HI4:HL4"/>
+    <mergeCell ref="HM4:HP4"/>
+    <mergeCell ref="HQ4:HT4"/>
+    <mergeCell ref="SW3:UB3"/>
+    <mergeCell ref="UC3:VH3"/>
+    <mergeCell ref="VI3:WN3"/>
+    <mergeCell ref="WO3:XT3"/>
+    <mergeCell ref="XU3:YZ3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:L4"/>
+    <mergeCell ref="M4:P4"/>
+    <mergeCell ref="Q4:T4"/>
+    <mergeCell ref="U4:X4"/>
+    <mergeCell ref="Y4:AB4"/>
+    <mergeCell ref="AC4:AF4"/>
+    <mergeCell ref="AG4:AJ4"/>
+    <mergeCell ref="AK4:AN4"/>
+    <mergeCell ref="AO4:AR4"/>
+    <mergeCell ref="AS4:AV4"/>
+    <mergeCell ref="AW4:AZ4"/>
+    <mergeCell ref="BA4:BD4"/>
+    <mergeCell ref="BE4:BH4"/>
+    <mergeCell ref="BI4:BL4"/>
+    <mergeCell ref="BM4:BP4"/>
+    <mergeCell ref="BQ4:BT4"/>
+    <mergeCell ref="BU4:BX4"/>
+    <mergeCell ref="BY4:CB4"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:AJ3"/>
+    <mergeCell ref="AK3:BP3"/>
+    <mergeCell ref="BQ3:CV3"/>
+    <mergeCell ref="CW3:EB3"/>
+    <mergeCell ref="EC3:FH3"/>
+    <mergeCell ref="CK4:CN4"/>
+    <mergeCell ref="CO4:CR4"/>
+    <mergeCell ref="CS4:CV4"/>
+    <mergeCell ref="CW4:CZ4"/>
+    <mergeCell ref="DA4:DD4"/>
+    <mergeCell ref="DE4:DH4"/>
+    <mergeCell ref="DI4:DL4"/>
+    <mergeCell ref="DM4:DP4"/>
+    <mergeCell ref="DQ4:DT4"/>
+    <mergeCell ref="DU4:DX4"/>
+    <mergeCell ref="DY4:EB4"/>
+    <mergeCell ref="EC4:EF4"/>
+    <mergeCell ref="EG4:EJ4"/>
+    <mergeCell ref="EK4:EN4"/>
+    <mergeCell ref="EO4:ER4"/>
     <mergeCell ref="QK3:RP3"/>
     <mergeCell ref="RQ3:SV3"/>
     <mergeCell ref="CC4:CF4"/>
@@ -53579,178 +53757,6 @@
     <mergeCell ref="FY4:GB4"/>
     <mergeCell ref="GC4:GF4"/>
     <mergeCell ref="GG4:GJ4"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:AJ3"/>
-    <mergeCell ref="AK3:BP3"/>
-    <mergeCell ref="BQ3:CV3"/>
-    <mergeCell ref="CW3:EB3"/>
-    <mergeCell ref="EC3:FH3"/>
-    <mergeCell ref="CK4:CN4"/>
-    <mergeCell ref="CO4:CR4"/>
-    <mergeCell ref="CS4:CV4"/>
-    <mergeCell ref="CW4:CZ4"/>
-    <mergeCell ref="DA4:DD4"/>
-    <mergeCell ref="DE4:DH4"/>
-    <mergeCell ref="DI4:DL4"/>
-    <mergeCell ref="DM4:DP4"/>
-    <mergeCell ref="DQ4:DT4"/>
-    <mergeCell ref="DU4:DX4"/>
-    <mergeCell ref="DY4:EB4"/>
-    <mergeCell ref="EC4:EF4"/>
-    <mergeCell ref="EG4:EJ4"/>
-    <mergeCell ref="EK4:EN4"/>
-    <mergeCell ref="EO4:ER4"/>
-    <mergeCell ref="SW3:UB3"/>
-    <mergeCell ref="UC3:VH3"/>
-    <mergeCell ref="VI3:WN3"/>
-    <mergeCell ref="WO3:XT3"/>
-    <mergeCell ref="XU3:YZ3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:L4"/>
-    <mergeCell ref="M4:P4"/>
-    <mergeCell ref="Q4:T4"/>
-    <mergeCell ref="U4:X4"/>
-    <mergeCell ref="Y4:AB4"/>
-    <mergeCell ref="AC4:AF4"/>
-    <mergeCell ref="AG4:AJ4"/>
-    <mergeCell ref="AK4:AN4"/>
-    <mergeCell ref="AO4:AR4"/>
-    <mergeCell ref="AS4:AV4"/>
-    <mergeCell ref="AW4:AZ4"/>
-    <mergeCell ref="BA4:BD4"/>
-    <mergeCell ref="BE4:BH4"/>
-    <mergeCell ref="BI4:BL4"/>
-    <mergeCell ref="BM4:BP4"/>
-    <mergeCell ref="BQ4:BT4"/>
-    <mergeCell ref="BU4:BX4"/>
-    <mergeCell ref="BY4:CB4"/>
-    <mergeCell ref="GK4:GN4"/>
-    <mergeCell ref="GO4:GR4"/>
-    <mergeCell ref="GS4:GV4"/>
-    <mergeCell ref="GW4:GZ4"/>
-    <mergeCell ref="HA4:HD4"/>
-    <mergeCell ref="HE4:HH4"/>
-    <mergeCell ref="HI4:HL4"/>
-    <mergeCell ref="HM4:HP4"/>
-    <mergeCell ref="HQ4:HT4"/>
-    <mergeCell ref="HU4:HX4"/>
-    <mergeCell ref="HY4:IB4"/>
-    <mergeCell ref="IC4:IF4"/>
-    <mergeCell ref="IG4:IJ4"/>
-    <mergeCell ref="IK4:IN4"/>
-    <mergeCell ref="IO4:IR4"/>
-    <mergeCell ref="IS4:IV4"/>
-    <mergeCell ref="IW4:IZ4"/>
-    <mergeCell ref="JA4:JD4"/>
-    <mergeCell ref="JE4:JH4"/>
-    <mergeCell ref="JI4:JL4"/>
-    <mergeCell ref="JM4:JP4"/>
-    <mergeCell ref="JQ4:JT4"/>
-    <mergeCell ref="JU4:JX4"/>
-    <mergeCell ref="JY4:KB4"/>
-    <mergeCell ref="KC4:KF4"/>
-    <mergeCell ref="KG4:KJ4"/>
-    <mergeCell ref="KK4:KN4"/>
-    <mergeCell ref="KO4:KR4"/>
-    <mergeCell ref="KS4:KV4"/>
-    <mergeCell ref="KW4:KZ4"/>
-    <mergeCell ref="LA4:LD4"/>
-    <mergeCell ref="LE4:LH4"/>
-    <mergeCell ref="LI4:LL4"/>
-    <mergeCell ref="LM4:LP4"/>
-    <mergeCell ref="LQ4:LT4"/>
-    <mergeCell ref="LU4:LX4"/>
-    <mergeCell ref="LY4:MB4"/>
-    <mergeCell ref="MC4:MF4"/>
-    <mergeCell ref="MG4:MJ4"/>
-    <mergeCell ref="MK4:MN4"/>
-    <mergeCell ref="MO4:MR4"/>
-    <mergeCell ref="MS4:MV4"/>
-    <mergeCell ref="MW4:MZ4"/>
-    <mergeCell ref="NA4:ND4"/>
-    <mergeCell ref="NE4:NH4"/>
-    <mergeCell ref="NI4:NL4"/>
-    <mergeCell ref="NM4:NP4"/>
-    <mergeCell ref="NQ4:NT4"/>
-    <mergeCell ref="NU4:NX4"/>
-    <mergeCell ref="NY4:OB4"/>
-    <mergeCell ref="OC4:OF4"/>
-    <mergeCell ref="OG4:OJ4"/>
-    <mergeCell ref="OK4:ON4"/>
-    <mergeCell ref="OO4:OR4"/>
-    <mergeCell ref="OS4:OV4"/>
-    <mergeCell ref="OW4:OZ4"/>
-    <mergeCell ref="PA4:PD4"/>
-    <mergeCell ref="PE4:PH4"/>
-    <mergeCell ref="PI4:PL4"/>
-    <mergeCell ref="PM4:PP4"/>
-    <mergeCell ref="PQ4:PT4"/>
-    <mergeCell ref="PU4:PX4"/>
-    <mergeCell ref="PY4:QB4"/>
-    <mergeCell ref="QC4:QF4"/>
-    <mergeCell ref="QG4:QJ4"/>
-    <mergeCell ref="QK4:QN4"/>
-    <mergeCell ref="QO4:QR4"/>
-    <mergeCell ref="QS4:QV4"/>
-    <mergeCell ref="QW4:QZ4"/>
-    <mergeCell ref="RA4:RD4"/>
-    <mergeCell ref="RE4:RH4"/>
-    <mergeCell ref="RI4:RL4"/>
-    <mergeCell ref="RM4:RP4"/>
-    <mergeCell ref="RQ4:RT4"/>
-    <mergeCell ref="RU4:RX4"/>
-    <mergeCell ref="RY4:SB4"/>
-    <mergeCell ref="SC4:SF4"/>
-    <mergeCell ref="SG4:SJ4"/>
-    <mergeCell ref="SK4:SN4"/>
-    <mergeCell ref="SO4:SR4"/>
-    <mergeCell ref="SS4:SV4"/>
-    <mergeCell ref="SW4:SZ4"/>
-    <mergeCell ref="TA4:TD4"/>
-    <mergeCell ref="TE4:TH4"/>
-    <mergeCell ref="TI4:TL4"/>
-    <mergeCell ref="TM4:TP4"/>
-    <mergeCell ref="TQ4:TT4"/>
-    <mergeCell ref="TU4:TX4"/>
-    <mergeCell ref="TY4:UB4"/>
-    <mergeCell ref="UC4:UF4"/>
-    <mergeCell ref="WW4:WZ4"/>
-    <mergeCell ref="UG4:UJ4"/>
-    <mergeCell ref="UK4:UN4"/>
-    <mergeCell ref="UO4:UR4"/>
-    <mergeCell ref="US4:UV4"/>
-    <mergeCell ref="UW4:UZ4"/>
-    <mergeCell ref="VA4:VD4"/>
-    <mergeCell ref="VE4:VH4"/>
-    <mergeCell ref="VI4:VL4"/>
-    <mergeCell ref="VM4:VP4"/>
-    <mergeCell ref="XA4:XD4"/>
-    <mergeCell ref="VQ4:VT4"/>
-    <mergeCell ref="YO4:YR4"/>
-    <mergeCell ref="YS4:YV4"/>
-    <mergeCell ref="YW4:YZ4"/>
-    <mergeCell ref="A2:YZ2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:YZ1"/>
-    <mergeCell ref="XE4:XH4"/>
-    <mergeCell ref="XI4:XL4"/>
-    <mergeCell ref="XM4:XP4"/>
-    <mergeCell ref="XQ4:XT4"/>
-    <mergeCell ref="XU4:XX4"/>
-    <mergeCell ref="XY4:YB4"/>
-    <mergeCell ref="YC4:YF4"/>
-    <mergeCell ref="YG4:YJ4"/>
-    <mergeCell ref="YK4:YN4"/>
-    <mergeCell ref="VU4:VX4"/>
-    <mergeCell ref="VY4:WB4"/>
-    <mergeCell ref="WC4:WF4"/>
-    <mergeCell ref="WG4:WJ4"/>
-    <mergeCell ref="WK4:WN4"/>
-    <mergeCell ref="WO4:WR4"/>
-    <mergeCell ref="WS4:WV4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="41" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/Documentation/Planification_TPI_Ryan-Bersier.xlsx
+++ b/Documentation/Planification_TPI_Ryan-Bersier.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc23owx\Documents\TPI_Horloge-Led-Capteurs\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D09FC8A7-CFF6-4010-84C5-31985071EF70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA511AE2-E64F-4FA3-96A1-6CAE80B88719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -907,31 +907,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -942,6 +921,27 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1218,3112 +1218,3112 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:676" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="56"/>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="57" t="s">
+      <c r="A1" s="49"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="50" t="s">
         <v>117</v>
       </c>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="57"/>
-      <c r="R1" s="57"/>
-      <c r="S1" s="57"/>
-      <c r="T1" s="57"/>
-      <c r="U1" s="57"/>
-      <c r="V1" s="57"/>
-      <c r="W1" s="57"/>
-      <c r="X1" s="57"/>
-      <c r="Y1" s="57"/>
-      <c r="Z1" s="57"/>
-      <c r="AA1" s="57"/>
-      <c r="AB1" s="57"/>
-      <c r="AC1" s="57"/>
-      <c r="AD1" s="57"/>
-      <c r="AE1" s="57"/>
-      <c r="AF1" s="57"/>
-      <c r="AG1" s="57"/>
-      <c r="AH1" s="57"/>
-      <c r="AI1" s="57"/>
-      <c r="AJ1" s="57"/>
-      <c r="AK1" s="57"/>
-      <c r="AL1" s="57"/>
-      <c r="AM1" s="57"/>
-      <c r="AN1" s="57"/>
-      <c r="AO1" s="57"/>
-      <c r="AP1" s="57"/>
-      <c r="AQ1" s="57"/>
-      <c r="AR1" s="57"/>
-      <c r="AS1" s="57"/>
-      <c r="AT1" s="57"/>
-      <c r="AU1" s="57"/>
-      <c r="AV1" s="57"/>
-      <c r="AW1" s="57"/>
-      <c r="AX1" s="57"/>
-      <c r="AY1" s="57"/>
-      <c r="AZ1" s="57"/>
-      <c r="BA1" s="57"/>
-      <c r="BB1" s="57"/>
-      <c r="BC1" s="57"/>
-      <c r="BD1" s="57"/>
-      <c r="BE1" s="57"/>
-      <c r="BF1" s="57"/>
-      <c r="BG1" s="57"/>
-      <c r="BH1" s="57"/>
-      <c r="BI1" s="57"/>
-      <c r="BJ1" s="57"/>
-      <c r="BK1" s="57"/>
-      <c r="BL1" s="57"/>
-      <c r="BM1" s="57"/>
-      <c r="BN1" s="57"/>
-      <c r="BO1" s="57"/>
-      <c r="BP1" s="57"/>
-      <c r="BQ1" s="57"/>
-      <c r="BR1" s="57"/>
-      <c r="BS1" s="57"/>
-      <c r="BT1" s="57"/>
-      <c r="BU1" s="57"/>
-      <c r="BV1" s="57"/>
-      <c r="BW1" s="57"/>
-      <c r="BX1" s="57"/>
-      <c r="BY1" s="57"/>
-      <c r="BZ1" s="57"/>
-      <c r="CA1" s="57"/>
-      <c r="CB1" s="57"/>
-      <c r="CC1" s="57"/>
-      <c r="CD1" s="57"/>
-      <c r="CE1" s="57"/>
-      <c r="CF1" s="57"/>
-      <c r="CG1" s="57"/>
-      <c r="CH1" s="57"/>
-      <c r="CI1" s="57"/>
-      <c r="CJ1" s="57"/>
-      <c r="CK1" s="57"/>
-      <c r="CL1" s="57"/>
-      <c r="CM1" s="57"/>
-      <c r="CN1" s="57"/>
-      <c r="CO1" s="57"/>
-      <c r="CP1" s="57"/>
-      <c r="CQ1" s="57"/>
-      <c r="CR1" s="57"/>
-      <c r="CS1" s="57"/>
-      <c r="CT1" s="57"/>
-      <c r="CU1" s="57"/>
-      <c r="CV1" s="57"/>
-      <c r="CW1" s="57"/>
-      <c r="CX1" s="57"/>
-      <c r="CY1" s="57"/>
-      <c r="CZ1" s="57"/>
-      <c r="DA1" s="57"/>
-      <c r="DB1" s="57"/>
-      <c r="DC1" s="57"/>
-      <c r="DD1" s="57"/>
-      <c r="DE1" s="57"/>
-      <c r="DF1" s="57"/>
-      <c r="DG1" s="57"/>
-      <c r="DH1" s="57"/>
-      <c r="DI1" s="57"/>
-      <c r="DJ1" s="57"/>
-      <c r="DK1" s="57"/>
-      <c r="DL1" s="57"/>
-      <c r="DM1" s="57"/>
-      <c r="DN1" s="57"/>
-      <c r="DO1" s="57"/>
-      <c r="DP1" s="57"/>
-      <c r="DQ1" s="57"/>
-      <c r="DR1" s="57"/>
-      <c r="DS1" s="57"/>
-      <c r="DT1" s="57"/>
-      <c r="DU1" s="57"/>
-      <c r="DV1" s="57"/>
-      <c r="DW1" s="57"/>
-      <c r="DX1" s="57"/>
-      <c r="DY1" s="57"/>
-      <c r="DZ1" s="57"/>
-      <c r="EA1" s="57"/>
-      <c r="EB1" s="57"/>
-      <c r="EC1" s="57"/>
-      <c r="ED1" s="57"/>
-      <c r="EE1" s="57"/>
-      <c r="EF1" s="57"/>
-      <c r="EG1" s="57"/>
-      <c r="EH1" s="57"/>
-      <c r="EI1" s="57"/>
-      <c r="EJ1" s="57"/>
-      <c r="EK1" s="57"/>
-      <c r="EL1" s="57"/>
-      <c r="EM1" s="57"/>
-      <c r="EN1" s="57"/>
-      <c r="EO1" s="57"/>
-      <c r="EP1" s="57"/>
-      <c r="EQ1" s="57"/>
-      <c r="ER1" s="57"/>
-      <c r="ES1" s="57"/>
-      <c r="ET1" s="57"/>
-      <c r="EU1" s="57"/>
-      <c r="EV1" s="57"/>
-      <c r="EW1" s="57"/>
-      <c r="EX1" s="57"/>
-      <c r="EY1" s="57"/>
-      <c r="EZ1" s="57"/>
-      <c r="FA1" s="57"/>
-      <c r="FB1" s="57"/>
-      <c r="FC1" s="57"/>
-      <c r="FD1" s="57"/>
-      <c r="FE1" s="57"/>
-      <c r="FF1" s="57"/>
-      <c r="FG1" s="57"/>
-      <c r="FH1" s="57"/>
-      <c r="FI1" s="57"/>
-      <c r="FJ1" s="57"/>
-      <c r="FK1" s="57"/>
-      <c r="FL1" s="57"/>
-      <c r="FM1" s="57"/>
-      <c r="FN1" s="57"/>
-      <c r="FO1" s="57"/>
-      <c r="FP1" s="57"/>
-      <c r="FQ1" s="57"/>
-      <c r="FR1" s="57"/>
-      <c r="FS1" s="57"/>
-      <c r="FT1" s="57"/>
-      <c r="FU1" s="57"/>
-      <c r="FV1" s="57"/>
-      <c r="FW1" s="57"/>
-      <c r="FX1" s="57"/>
-      <c r="FY1" s="57"/>
-      <c r="FZ1" s="57"/>
-      <c r="GA1" s="57"/>
-      <c r="GB1" s="57"/>
-      <c r="GC1" s="57"/>
-      <c r="GD1" s="57"/>
-      <c r="GE1" s="57"/>
-      <c r="GF1" s="57"/>
-      <c r="GG1" s="57"/>
-      <c r="GH1" s="57"/>
-      <c r="GI1" s="57"/>
-      <c r="GJ1" s="57"/>
-      <c r="GK1" s="57"/>
-      <c r="GL1" s="57"/>
-      <c r="GM1" s="57"/>
-      <c r="GN1" s="57"/>
-      <c r="GO1" s="57"/>
-      <c r="GP1" s="57"/>
-      <c r="GQ1" s="57"/>
-      <c r="GR1" s="57"/>
-      <c r="GS1" s="57"/>
-      <c r="GT1" s="57"/>
-      <c r="GU1" s="57"/>
-      <c r="GV1" s="57"/>
-      <c r="GW1" s="57"/>
-      <c r="GX1" s="57"/>
-      <c r="GY1" s="57"/>
-      <c r="GZ1" s="57"/>
-      <c r="HA1" s="57"/>
-      <c r="HB1" s="57"/>
-      <c r="HC1" s="57"/>
-      <c r="HD1" s="57"/>
-      <c r="HE1" s="57"/>
-      <c r="HF1" s="57"/>
-      <c r="HG1" s="57"/>
-      <c r="HH1" s="57"/>
-      <c r="HI1" s="57"/>
-      <c r="HJ1" s="57"/>
-      <c r="HK1" s="57"/>
-      <c r="HL1" s="57"/>
-      <c r="HM1" s="57"/>
-      <c r="HN1" s="57"/>
-      <c r="HO1" s="57"/>
-      <c r="HP1" s="57"/>
-      <c r="HQ1" s="57"/>
-      <c r="HR1" s="57"/>
-      <c r="HS1" s="57"/>
-      <c r="HT1" s="57"/>
-      <c r="HU1" s="57"/>
-      <c r="HV1" s="57"/>
-      <c r="HW1" s="57"/>
-      <c r="HX1" s="57"/>
-      <c r="HY1" s="57"/>
-      <c r="HZ1" s="57"/>
-      <c r="IA1" s="57"/>
-      <c r="IB1" s="57"/>
-      <c r="IC1" s="57"/>
-      <c r="ID1" s="57"/>
-      <c r="IE1" s="57"/>
-      <c r="IF1" s="57"/>
-      <c r="IG1" s="57"/>
-      <c r="IH1" s="57"/>
-      <c r="II1" s="57"/>
-      <c r="IJ1" s="57"/>
-      <c r="IK1" s="57"/>
-      <c r="IL1" s="57"/>
-      <c r="IM1" s="57"/>
-      <c r="IN1" s="57"/>
-      <c r="IO1" s="57"/>
-      <c r="IP1" s="57"/>
-      <c r="IQ1" s="57"/>
-      <c r="IR1" s="57"/>
-      <c r="IS1" s="57"/>
-      <c r="IT1" s="57"/>
-      <c r="IU1" s="57"/>
-      <c r="IV1" s="57"/>
-      <c r="IW1" s="57"/>
-      <c r="IX1" s="57"/>
-      <c r="IY1" s="57"/>
-      <c r="IZ1" s="57"/>
-      <c r="JA1" s="57"/>
-      <c r="JB1" s="57"/>
-      <c r="JC1" s="57"/>
-      <c r="JD1" s="57"/>
-      <c r="JE1" s="57"/>
-      <c r="JF1" s="57"/>
-      <c r="JG1" s="57"/>
-      <c r="JH1" s="57"/>
-      <c r="JI1" s="57"/>
-      <c r="JJ1" s="57"/>
-      <c r="JK1" s="57"/>
-      <c r="JL1" s="57"/>
-      <c r="JM1" s="57"/>
-      <c r="JN1" s="57"/>
-      <c r="JO1" s="57"/>
-      <c r="JP1" s="57"/>
-      <c r="JQ1" s="57"/>
-      <c r="JR1" s="57"/>
-      <c r="JS1" s="57"/>
-      <c r="JT1" s="57"/>
-      <c r="JU1" s="57"/>
-      <c r="JV1" s="57"/>
-      <c r="JW1" s="57"/>
-      <c r="JX1" s="57"/>
-      <c r="JY1" s="57"/>
-      <c r="JZ1" s="57"/>
-      <c r="KA1" s="57"/>
-      <c r="KB1" s="57"/>
-      <c r="KC1" s="57"/>
-      <c r="KD1" s="57"/>
-      <c r="KE1" s="57"/>
-      <c r="KF1" s="57"/>
-      <c r="KG1" s="57"/>
-      <c r="KH1" s="57"/>
-      <c r="KI1" s="57"/>
-      <c r="KJ1" s="57"/>
-      <c r="KK1" s="57"/>
-      <c r="KL1" s="57"/>
-      <c r="KM1" s="57"/>
-      <c r="KN1" s="57"/>
-      <c r="KO1" s="57"/>
-      <c r="KP1" s="57"/>
-      <c r="KQ1" s="57"/>
-      <c r="KR1" s="57"/>
-      <c r="KS1" s="57"/>
-      <c r="KT1" s="57"/>
-      <c r="KU1" s="57"/>
-      <c r="KV1" s="57"/>
-      <c r="KW1" s="57"/>
-      <c r="KX1" s="57"/>
-      <c r="KY1" s="57"/>
-      <c r="KZ1" s="57"/>
-      <c r="LA1" s="57"/>
-      <c r="LB1" s="57"/>
-      <c r="LC1" s="57"/>
-      <c r="LD1" s="57"/>
-      <c r="LE1" s="57"/>
-      <c r="LF1" s="57"/>
-      <c r="LG1" s="57"/>
-      <c r="LH1" s="57"/>
-      <c r="LI1" s="57"/>
-      <c r="LJ1" s="57"/>
-      <c r="LK1" s="57"/>
-      <c r="LL1" s="57"/>
-      <c r="LM1" s="57"/>
-      <c r="LN1" s="57"/>
-      <c r="LO1" s="57"/>
-      <c r="LP1" s="57"/>
-      <c r="LQ1" s="57"/>
-      <c r="LR1" s="57"/>
-      <c r="LS1" s="57"/>
-      <c r="LT1" s="57"/>
-      <c r="LU1" s="57"/>
-      <c r="LV1" s="57"/>
-      <c r="LW1" s="57"/>
-      <c r="LX1" s="57"/>
-      <c r="LY1" s="57"/>
-      <c r="LZ1" s="57"/>
-      <c r="MA1" s="57"/>
-      <c r="MB1" s="57"/>
-      <c r="MC1" s="57"/>
-      <c r="MD1" s="57"/>
-      <c r="ME1" s="57"/>
-      <c r="MF1" s="57"/>
-      <c r="MG1" s="57"/>
-      <c r="MH1" s="57"/>
-      <c r="MI1" s="57"/>
-      <c r="MJ1" s="57"/>
-      <c r="MK1" s="57"/>
-      <c r="ML1" s="57"/>
-      <c r="MM1" s="57"/>
-      <c r="MN1" s="57"/>
-      <c r="MO1" s="57"/>
-      <c r="MP1" s="57"/>
-      <c r="MQ1" s="57"/>
-      <c r="MR1" s="57"/>
-      <c r="MS1" s="57"/>
-      <c r="MT1" s="57"/>
-      <c r="MU1" s="57"/>
-      <c r="MV1" s="57"/>
-      <c r="MW1" s="57"/>
-      <c r="MX1" s="57"/>
-      <c r="MY1" s="57"/>
-      <c r="MZ1" s="57"/>
-      <c r="NA1" s="57"/>
-      <c r="NB1" s="57"/>
-      <c r="NC1" s="57"/>
-      <c r="ND1" s="57"/>
-      <c r="NE1" s="57"/>
-      <c r="NF1" s="57"/>
-      <c r="NG1" s="57"/>
-      <c r="NH1" s="57"/>
-      <c r="NI1" s="57"/>
-      <c r="NJ1" s="57"/>
-      <c r="NK1" s="57"/>
-      <c r="NL1" s="57"/>
-      <c r="NM1" s="57"/>
-      <c r="NN1" s="57"/>
-      <c r="NO1" s="57"/>
-      <c r="NP1" s="57"/>
-      <c r="NQ1" s="57"/>
-      <c r="NR1" s="57"/>
-      <c r="NS1" s="57"/>
-      <c r="NT1" s="57"/>
-      <c r="NU1" s="57"/>
-      <c r="NV1" s="57"/>
-      <c r="NW1" s="57"/>
-      <c r="NX1" s="57"/>
-      <c r="NY1" s="57"/>
-      <c r="NZ1" s="57"/>
-      <c r="OA1" s="57"/>
-      <c r="OB1" s="57"/>
-      <c r="OC1" s="57"/>
-      <c r="OD1" s="57"/>
-      <c r="OE1" s="57"/>
-      <c r="OF1" s="57"/>
-      <c r="OG1" s="57"/>
-      <c r="OH1" s="57"/>
-      <c r="OI1" s="57"/>
-      <c r="OJ1" s="57"/>
-      <c r="OK1" s="57"/>
-      <c r="OL1" s="57"/>
-      <c r="OM1" s="57"/>
-      <c r="ON1" s="57"/>
-      <c r="OO1" s="57"/>
-      <c r="OP1" s="57"/>
-      <c r="OQ1" s="57"/>
-      <c r="OR1" s="57"/>
-      <c r="OS1" s="57"/>
-      <c r="OT1" s="57"/>
-      <c r="OU1" s="57"/>
-      <c r="OV1" s="57"/>
-      <c r="OW1" s="57"/>
-      <c r="OX1" s="57"/>
-      <c r="OY1" s="57"/>
-      <c r="OZ1" s="57"/>
-      <c r="PA1" s="57"/>
-      <c r="PB1" s="57"/>
-      <c r="PC1" s="57"/>
-      <c r="PD1" s="57"/>
-      <c r="PE1" s="57"/>
-      <c r="PF1" s="57"/>
-      <c r="PG1" s="57"/>
-      <c r="PH1" s="57"/>
-      <c r="PI1" s="57"/>
-      <c r="PJ1" s="57"/>
-      <c r="PK1" s="57"/>
-      <c r="PL1" s="57"/>
-      <c r="PM1" s="57"/>
-      <c r="PN1" s="57"/>
-      <c r="PO1" s="57"/>
-      <c r="PP1" s="57"/>
-      <c r="PQ1" s="57"/>
-      <c r="PR1" s="57"/>
-      <c r="PS1" s="57"/>
-      <c r="PT1" s="57"/>
-      <c r="PU1" s="57"/>
-      <c r="PV1" s="57"/>
-      <c r="PW1" s="57"/>
-      <c r="PX1" s="57"/>
-      <c r="PY1" s="57"/>
-      <c r="PZ1" s="57"/>
-      <c r="QA1" s="57"/>
-      <c r="QB1" s="57"/>
-      <c r="QC1" s="57"/>
-      <c r="QD1" s="57"/>
-      <c r="QE1" s="57"/>
-      <c r="QF1" s="57"/>
-      <c r="QG1" s="57"/>
-      <c r="QH1" s="57"/>
-      <c r="QI1" s="57"/>
-      <c r="QJ1" s="57"/>
-      <c r="QK1" s="57"/>
-      <c r="QL1" s="57"/>
-      <c r="QM1" s="57"/>
-      <c r="QN1" s="57"/>
-      <c r="QO1" s="57"/>
-      <c r="QP1" s="57"/>
-      <c r="QQ1" s="57"/>
-      <c r="QR1" s="57"/>
-      <c r="QS1" s="57"/>
-      <c r="QT1" s="57"/>
-      <c r="QU1" s="57"/>
-      <c r="QV1" s="57"/>
-      <c r="QW1" s="57"/>
-      <c r="QX1" s="57"/>
-      <c r="QY1" s="57"/>
-      <c r="QZ1" s="57"/>
-      <c r="RA1" s="57"/>
-      <c r="RB1" s="57"/>
-      <c r="RC1" s="57"/>
-      <c r="RD1" s="57"/>
-      <c r="RE1" s="57"/>
-      <c r="RF1" s="57"/>
-      <c r="RG1" s="57"/>
-      <c r="RH1" s="57"/>
-      <c r="RI1" s="57"/>
-      <c r="RJ1" s="57"/>
-      <c r="RK1" s="57"/>
-      <c r="RL1" s="57"/>
-      <c r="RM1" s="57"/>
-      <c r="RN1" s="57"/>
-      <c r="RO1" s="57"/>
-      <c r="RP1" s="57"/>
-      <c r="RQ1" s="57"/>
-      <c r="RR1" s="57"/>
-      <c r="RS1" s="57"/>
-      <c r="RT1" s="57"/>
-      <c r="RU1" s="57"/>
-      <c r="RV1" s="57"/>
-      <c r="RW1" s="57"/>
-      <c r="RX1" s="57"/>
-      <c r="RY1" s="57"/>
-      <c r="RZ1" s="57"/>
-      <c r="SA1" s="57"/>
-      <c r="SB1" s="57"/>
-      <c r="SC1" s="57"/>
-      <c r="SD1" s="57"/>
-      <c r="SE1" s="57"/>
-      <c r="SF1" s="57"/>
-      <c r="SG1" s="57"/>
-      <c r="SH1" s="57"/>
-      <c r="SI1" s="57"/>
-      <c r="SJ1" s="57"/>
-      <c r="SK1" s="57"/>
-      <c r="SL1" s="57"/>
-      <c r="SM1" s="57"/>
-      <c r="SN1" s="57"/>
-      <c r="SO1" s="57"/>
-      <c r="SP1" s="57"/>
-      <c r="SQ1" s="57"/>
-      <c r="SR1" s="57"/>
-      <c r="SS1" s="57"/>
-      <c r="ST1" s="57"/>
-      <c r="SU1" s="57"/>
-      <c r="SV1" s="57"/>
-      <c r="SW1" s="57"/>
-      <c r="SX1" s="57"/>
-      <c r="SY1" s="57"/>
-      <c r="SZ1" s="57"/>
-      <c r="TA1" s="57"/>
-      <c r="TB1" s="57"/>
-      <c r="TC1" s="57"/>
-      <c r="TD1" s="57"/>
-      <c r="TE1" s="57"/>
-      <c r="TF1" s="57"/>
-      <c r="TG1" s="57"/>
-      <c r="TH1" s="57"/>
-      <c r="TI1" s="57"/>
-      <c r="TJ1" s="57"/>
-      <c r="TK1" s="57"/>
-      <c r="TL1" s="57"/>
-      <c r="TM1" s="57"/>
-      <c r="TN1" s="57"/>
-      <c r="TO1" s="57"/>
-      <c r="TP1" s="57"/>
-      <c r="TQ1" s="57"/>
-      <c r="TR1" s="57"/>
-      <c r="TS1" s="57"/>
-      <c r="TT1" s="57"/>
-      <c r="TU1" s="57"/>
-      <c r="TV1" s="57"/>
-      <c r="TW1" s="57"/>
-      <c r="TX1" s="57"/>
-      <c r="TY1" s="57"/>
-      <c r="TZ1" s="57"/>
-      <c r="UA1" s="57"/>
-      <c r="UB1" s="57"/>
-      <c r="UC1" s="57"/>
-      <c r="UD1" s="57"/>
-      <c r="UE1" s="57"/>
-      <c r="UF1" s="57"/>
-      <c r="UG1" s="57"/>
-      <c r="UH1" s="57"/>
-      <c r="UI1" s="57"/>
-      <c r="UJ1" s="57"/>
-      <c r="UK1" s="57"/>
-      <c r="UL1" s="57"/>
-      <c r="UM1" s="57"/>
-      <c r="UN1" s="57"/>
-      <c r="UO1" s="57"/>
-      <c r="UP1" s="57"/>
-      <c r="UQ1" s="57"/>
-      <c r="UR1" s="57"/>
-      <c r="US1" s="57"/>
-      <c r="UT1" s="57"/>
-      <c r="UU1" s="57"/>
-      <c r="UV1" s="57"/>
-      <c r="UW1" s="57"/>
-      <c r="UX1" s="57"/>
-      <c r="UY1" s="57"/>
-      <c r="UZ1" s="57"/>
-      <c r="VA1" s="57"/>
-      <c r="VB1" s="57"/>
-      <c r="VC1" s="57"/>
-      <c r="VD1" s="57"/>
-      <c r="VE1" s="57"/>
-      <c r="VF1" s="57"/>
-      <c r="VG1" s="57"/>
-      <c r="VH1" s="57"/>
-      <c r="VI1" s="57"/>
-      <c r="VJ1" s="57"/>
-      <c r="VK1" s="57"/>
-      <c r="VL1" s="57"/>
-      <c r="VM1" s="57"/>
-      <c r="VN1" s="57"/>
-      <c r="VO1" s="57"/>
-      <c r="VP1" s="57"/>
-      <c r="VQ1" s="57"/>
-      <c r="VR1" s="57"/>
-      <c r="VS1" s="57"/>
-      <c r="VT1" s="57"/>
-      <c r="VU1" s="57"/>
-      <c r="VV1" s="57"/>
-      <c r="VW1" s="57"/>
-      <c r="VX1" s="57"/>
-      <c r="VY1" s="57"/>
-      <c r="VZ1" s="57"/>
-      <c r="WA1" s="57"/>
-      <c r="WB1" s="57"/>
-      <c r="WC1" s="57"/>
-      <c r="WD1" s="57"/>
-      <c r="WE1" s="57"/>
-      <c r="WF1" s="57"/>
-      <c r="WG1" s="57"/>
-      <c r="WH1" s="57"/>
-      <c r="WI1" s="57"/>
-      <c r="WJ1" s="57"/>
-      <c r="WK1" s="57"/>
-      <c r="WL1" s="57"/>
-      <c r="WM1" s="57"/>
-      <c r="WN1" s="57"/>
-      <c r="WO1" s="57"/>
-      <c r="WP1" s="57"/>
-      <c r="WQ1" s="57"/>
-      <c r="WR1" s="57"/>
-      <c r="WS1" s="57"/>
-      <c r="WT1" s="57"/>
-      <c r="WU1" s="57"/>
-      <c r="WV1" s="57"/>
-      <c r="WW1" s="57"/>
-      <c r="WX1" s="57"/>
-      <c r="WY1" s="57"/>
-      <c r="WZ1" s="57"/>
-      <c r="XA1" s="57"/>
-      <c r="XB1" s="57"/>
-      <c r="XC1" s="57"/>
-      <c r="XD1" s="57"/>
-      <c r="XE1" s="57"/>
-      <c r="XF1" s="57"/>
-      <c r="XG1" s="57"/>
-      <c r="XH1" s="57"/>
-      <c r="XI1" s="57"/>
-      <c r="XJ1" s="57"/>
-      <c r="XK1" s="57"/>
-      <c r="XL1" s="57"/>
-      <c r="XM1" s="57"/>
-      <c r="XN1" s="57"/>
-      <c r="XO1" s="57"/>
-      <c r="XP1" s="57"/>
-      <c r="XQ1" s="57"/>
-      <c r="XR1" s="57"/>
-      <c r="XS1" s="57"/>
-      <c r="XT1" s="57"/>
-      <c r="XU1" s="57"/>
-      <c r="XV1" s="57"/>
-      <c r="XW1" s="57"/>
-      <c r="XX1" s="57"/>
-      <c r="XY1" s="57"/>
-      <c r="XZ1" s="57"/>
-      <c r="YA1" s="57"/>
-      <c r="YB1" s="57"/>
-      <c r="YC1" s="57"/>
-      <c r="YD1" s="57"/>
-      <c r="YE1" s="57"/>
-      <c r="YF1" s="57"/>
-      <c r="YG1" s="57"/>
-      <c r="YH1" s="57"/>
-      <c r="YI1" s="57"/>
-      <c r="YJ1" s="57"/>
-      <c r="YK1" s="57"/>
-      <c r="YL1" s="57"/>
-      <c r="YM1" s="57"/>
-      <c r="YN1" s="57"/>
-      <c r="YO1" s="57"/>
-      <c r="YP1" s="57"/>
-      <c r="YQ1" s="57"/>
-      <c r="YR1" s="57"/>
-      <c r="YS1" s="57"/>
-      <c r="YT1" s="57"/>
-      <c r="YU1" s="57"/>
-      <c r="YV1" s="57"/>
-      <c r="YW1" s="57"/>
-      <c r="YX1" s="57"/>
-      <c r="YY1" s="57"/>
-      <c r="YZ1" s="57"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
+      <c r="AA1" s="50"/>
+      <c r="AB1" s="50"/>
+      <c r="AC1" s="50"/>
+      <c r="AD1" s="50"/>
+      <c r="AE1" s="50"/>
+      <c r="AF1" s="50"/>
+      <c r="AG1" s="50"/>
+      <c r="AH1" s="50"/>
+      <c r="AI1" s="50"/>
+      <c r="AJ1" s="50"/>
+      <c r="AK1" s="50"/>
+      <c r="AL1" s="50"/>
+      <c r="AM1" s="50"/>
+      <c r="AN1" s="50"/>
+      <c r="AO1" s="50"/>
+      <c r="AP1" s="50"/>
+      <c r="AQ1" s="50"/>
+      <c r="AR1" s="50"/>
+      <c r="AS1" s="50"/>
+      <c r="AT1" s="50"/>
+      <c r="AU1" s="50"/>
+      <c r="AV1" s="50"/>
+      <c r="AW1" s="50"/>
+      <c r="AX1" s="50"/>
+      <c r="AY1" s="50"/>
+      <c r="AZ1" s="50"/>
+      <c r="BA1" s="50"/>
+      <c r="BB1" s="50"/>
+      <c r="BC1" s="50"/>
+      <c r="BD1" s="50"/>
+      <c r="BE1" s="50"/>
+      <c r="BF1" s="50"/>
+      <c r="BG1" s="50"/>
+      <c r="BH1" s="50"/>
+      <c r="BI1" s="50"/>
+      <c r="BJ1" s="50"/>
+      <c r="BK1" s="50"/>
+      <c r="BL1" s="50"/>
+      <c r="BM1" s="50"/>
+      <c r="BN1" s="50"/>
+      <c r="BO1" s="50"/>
+      <c r="BP1" s="50"/>
+      <c r="BQ1" s="50"/>
+      <c r="BR1" s="50"/>
+      <c r="BS1" s="50"/>
+      <c r="BT1" s="50"/>
+      <c r="BU1" s="50"/>
+      <c r="BV1" s="50"/>
+      <c r="BW1" s="50"/>
+      <c r="BX1" s="50"/>
+      <c r="BY1" s="50"/>
+      <c r="BZ1" s="50"/>
+      <c r="CA1" s="50"/>
+      <c r="CB1" s="50"/>
+      <c r="CC1" s="50"/>
+      <c r="CD1" s="50"/>
+      <c r="CE1" s="50"/>
+      <c r="CF1" s="50"/>
+      <c r="CG1" s="50"/>
+      <c r="CH1" s="50"/>
+      <c r="CI1" s="50"/>
+      <c r="CJ1" s="50"/>
+      <c r="CK1" s="50"/>
+      <c r="CL1" s="50"/>
+      <c r="CM1" s="50"/>
+      <c r="CN1" s="50"/>
+      <c r="CO1" s="50"/>
+      <c r="CP1" s="50"/>
+      <c r="CQ1" s="50"/>
+      <c r="CR1" s="50"/>
+      <c r="CS1" s="50"/>
+      <c r="CT1" s="50"/>
+      <c r="CU1" s="50"/>
+      <c r="CV1" s="50"/>
+      <c r="CW1" s="50"/>
+      <c r="CX1" s="50"/>
+      <c r="CY1" s="50"/>
+      <c r="CZ1" s="50"/>
+      <c r="DA1" s="50"/>
+      <c r="DB1" s="50"/>
+      <c r="DC1" s="50"/>
+      <c r="DD1" s="50"/>
+      <c r="DE1" s="50"/>
+      <c r="DF1" s="50"/>
+      <c r="DG1" s="50"/>
+      <c r="DH1" s="50"/>
+      <c r="DI1" s="50"/>
+      <c r="DJ1" s="50"/>
+      <c r="DK1" s="50"/>
+      <c r="DL1" s="50"/>
+      <c r="DM1" s="50"/>
+      <c r="DN1" s="50"/>
+      <c r="DO1" s="50"/>
+      <c r="DP1" s="50"/>
+      <c r="DQ1" s="50"/>
+      <c r="DR1" s="50"/>
+      <c r="DS1" s="50"/>
+      <c r="DT1" s="50"/>
+      <c r="DU1" s="50"/>
+      <c r="DV1" s="50"/>
+      <c r="DW1" s="50"/>
+      <c r="DX1" s="50"/>
+      <c r="DY1" s="50"/>
+      <c r="DZ1" s="50"/>
+      <c r="EA1" s="50"/>
+      <c r="EB1" s="50"/>
+      <c r="EC1" s="50"/>
+      <c r="ED1" s="50"/>
+      <c r="EE1" s="50"/>
+      <c r="EF1" s="50"/>
+      <c r="EG1" s="50"/>
+      <c r="EH1" s="50"/>
+      <c r="EI1" s="50"/>
+      <c r="EJ1" s="50"/>
+      <c r="EK1" s="50"/>
+      <c r="EL1" s="50"/>
+      <c r="EM1" s="50"/>
+      <c r="EN1" s="50"/>
+      <c r="EO1" s="50"/>
+      <c r="EP1" s="50"/>
+      <c r="EQ1" s="50"/>
+      <c r="ER1" s="50"/>
+      <c r="ES1" s="50"/>
+      <c r="ET1" s="50"/>
+      <c r="EU1" s="50"/>
+      <c r="EV1" s="50"/>
+      <c r="EW1" s="50"/>
+      <c r="EX1" s="50"/>
+      <c r="EY1" s="50"/>
+      <c r="EZ1" s="50"/>
+      <c r="FA1" s="50"/>
+      <c r="FB1" s="50"/>
+      <c r="FC1" s="50"/>
+      <c r="FD1" s="50"/>
+      <c r="FE1" s="50"/>
+      <c r="FF1" s="50"/>
+      <c r="FG1" s="50"/>
+      <c r="FH1" s="50"/>
+      <c r="FI1" s="50"/>
+      <c r="FJ1" s="50"/>
+      <c r="FK1" s="50"/>
+      <c r="FL1" s="50"/>
+      <c r="FM1" s="50"/>
+      <c r="FN1" s="50"/>
+      <c r="FO1" s="50"/>
+      <c r="FP1" s="50"/>
+      <c r="FQ1" s="50"/>
+      <c r="FR1" s="50"/>
+      <c r="FS1" s="50"/>
+      <c r="FT1" s="50"/>
+      <c r="FU1" s="50"/>
+      <c r="FV1" s="50"/>
+      <c r="FW1" s="50"/>
+      <c r="FX1" s="50"/>
+      <c r="FY1" s="50"/>
+      <c r="FZ1" s="50"/>
+      <c r="GA1" s="50"/>
+      <c r="GB1" s="50"/>
+      <c r="GC1" s="50"/>
+      <c r="GD1" s="50"/>
+      <c r="GE1" s="50"/>
+      <c r="GF1" s="50"/>
+      <c r="GG1" s="50"/>
+      <c r="GH1" s="50"/>
+      <c r="GI1" s="50"/>
+      <c r="GJ1" s="50"/>
+      <c r="GK1" s="50"/>
+      <c r="GL1" s="50"/>
+      <c r="GM1" s="50"/>
+      <c r="GN1" s="50"/>
+      <c r="GO1" s="50"/>
+      <c r="GP1" s="50"/>
+      <c r="GQ1" s="50"/>
+      <c r="GR1" s="50"/>
+      <c r="GS1" s="50"/>
+      <c r="GT1" s="50"/>
+      <c r="GU1" s="50"/>
+      <c r="GV1" s="50"/>
+      <c r="GW1" s="50"/>
+      <c r="GX1" s="50"/>
+      <c r="GY1" s="50"/>
+      <c r="GZ1" s="50"/>
+      <c r="HA1" s="50"/>
+      <c r="HB1" s="50"/>
+      <c r="HC1" s="50"/>
+      <c r="HD1" s="50"/>
+      <c r="HE1" s="50"/>
+      <c r="HF1" s="50"/>
+      <c r="HG1" s="50"/>
+      <c r="HH1" s="50"/>
+      <c r="HI1" s="50"/>
+      <c r="HJ1" s="50"/>
+      <c r="HK1" s="50"/>
+      <c r="HL1" s="50"/>
+      <c r="HM1" s="50"/>
+      <c r="HN1" s="50"/>
+      <c r="HO1" s="50"/>
+      <c r="HP1" s="50"/>
+      <c r="HQ1" s="50"/>
+      <c r="HR1" s="50"/>
+      <c r="HS1" s="50"/>
+      <c r="HT1" s="50"/>
+      <c r="HU1" s="50"/>
+      <c r="HV1" s="50"/>
+      <c r="HW1" s="50"/>
+      <c r="HX1" s="50"/>
+      <c r="HY1" s="50"/>
+      <c r="HZ1" s="50"/>
+      <c r="IA1" s="50"/>
+      <c r="IB1" s="50"/>
+      <c r="IC1" s="50"/>
+      <c r="ID1" s="50"/>
+      <c r="IE1" s="50"/>
+      <c r="IF1" s="50"/>
+      <c r="IG1" s="50"/>
+      <c r="IH1" s="50"/>
+      <c r="II1" s="50"/>
+      <c r="IJ1" s="50"/>
+      <c r="IK1" s="50"/>
+      <c r="IL1" s="50"/>
+      <c r="IM1" s="50"/>
+      <c r="IN1" s="50"/>
+      <c r="IO1" s="50"/>
+      <c r="IP1" s="50"/>
+      <c r="IQ1" s="50"/>
+      <c r="IR1" s="50"/>
+      <c r="IS1" s="50"/>
+      <c r="IT1" s="50"/>
+      <c r="IU1" s="50"/>
+      <c r="IV1" s="50"/>
+      <c r="IW1" s="50"/>
+      <c r="IX1" s="50"/>
+      <c r="IY1" s="50"/>
+      <c r="IZ1" s="50"/>
+      <c r="JA1" s="50"/>
+      <c r="JB1" s="50"/>
+      <c r="JC1" s="50"/>
+      <c r="JD1" s="50"/>
+      <c r="JE1" s="50"/>
+      <c r="JF1" s="50"/>
+      <c r="JG1" s="50"/>
+      <c r="JH1" s="50"/>
+      <c r="JI1" s="50"/>
+      <c r="JJ1" s="50"/>
+      <c r="JK1" s="50"/>
+      <c r="JL1" s="50"/>
+      <c r="JM1" s="50"/>
+      <c r="JN1" s="50"/>
+      <c r="JO1" s="50"/>
+      <c r="JP1" s="50"/>
+      <c r="JQ1" s="50"/>
+      <c r="JR1" s="50"/>
+      <c r="JS1" s="50"/>
+      <c r="JT1" s="50"/>
+      <c r="JU1" s="50"/>
+      <c r="JV1" s="50"/>
+      <c r="JW1" s="50"/>
+      <c r="JX1" s="50"/>
+      <c r="JY1" s="50"/>
+      <c r="JZ1" s="50"/>
+      <c r="KA1" s="50"/>
+      <c r="KB1" s="50"/>
+      <c r="KC1" s="50"/>
+      <c r="KD1" s="50"/>
+      <c r="KE1" s="50"/>
+      <c r="KF1" s="50"/>
+      <c r="KG1" s="50"/>
+      <c r="KH1" s="50"/>
+      <c r="KI1" s="50"/>
+      <c r="KJ1" s="50"/>
+      <c r="KK1" s="50"/>
+      <c r="KL1" s="50"/>
+      <c r="KM1" s="50"/>
+      <c r="KN1" s="50"/>
+      <c r="KO1" s="50"/>
+      <c r="KP1" s="50"/>
+      <c r="KQ1" s="50"/>
+      <c r="KR1" s="50"/>
+      <c r="KS1" s="50"/>
+      <c r="KT1" s="50"/>
+      <c r="KU1" s="50"/>
+      <c r="KV1" s="50"/>
+      <c r="KW1" s="50"/>
+      <c r="KX1" s="50"/>
+      <c r="KY1" s="50"/>
+      <c r="KZ1" s="50"/>
+      <c r="LA1" s="50"/>
+      <c r="LB1" s="50"/>
+      <c r="LC1" s="50"/>
+      <c r="LD1" s="50"/>
+      <c r="LE1" s="50"/>
+      <c r="LF1" s="50"/>
+      <c r="LG1" s="50"/>
+      <c r="LH1" s="50"/>
+      <c r="LI1" s="50"/>
+      <c r="LJ1" s="50"/>
+      <c r="LK1" s="50"/>
+      <c r="LL1" s="50"/>
+      <c r="LM1" s="50"/>
+      <c r="LN1" s="50"/>
+      <c r="LO1" s="50"/>
+      <c r="LP1" s="50"/>
+      <c r="LQ1" s="50"/>
+      <c r="LR1" s="50"/>
+      <c r="LS1" s="50"/>
+      <c r="LT1" s="50"/>
+      <c r="LU1" s="50"/>
+      <c r="LV1" s="50"/>
+      <c r="LW1" s="50"/>
+      <c r="LX1" s="50"/>
+      <c r="LY1" s="50"/>
+      <c r="LZ1" s="50"/>
+      <c r="MA1" s="50"/>
+      <c r="MB1" s="50"/>
+      <c r="MC1" s="50"/>
+      <c r="MD1" s="50"/>
+      <c r="ME1" s="50"/>
+      <c r="MF1" s="50"/>
+      <c r="MG1" s="50"/>
+      <c r="MH1" s="50"/>
+      <c r="MI1" s="50"/>
+      <c r="MJ1" s="50"/>
+      <c r="MK1" s="50"/>
+      <c r="ML1" s="50"/>
+      <c r="MM1" s="50"/>
+      <c r="MN1" s="50"/>
+      <c r="MO1" s="50"/>
+      <c r="MP1" s="50"/>
+      <c r="MQ1" s="50"/>
+      <c r="MR1" s="50"/>
+      <c r="MS1" s="50"/>
+      <c r="MT1" s="50"/>
+      <c r="MU1" s="50"/>
+      <c r="MV1" s="50"/>
+      <c r="MW1" s="50"/>
+      <c r="MX1" s="50"/>
+      <c r="MY1" s="50"/>
+      <c r="MZ1" s="50"/>
+      <c r="NA1" s="50"/>
+      <c r="NB1" s="50"/>
+      <c r="NC1" s="50"/>
+      <c r="ND1" s="50"/>
+      <c r="NE1" s="50"/>
+      <c r="NF1" s="50"/>
+      <c r="NG1" s="50"/>
+      <c r="NH1" s="50"/>
+      <c r="NI1" s="50"/>
+      <c r="NJ1" s="50"/>
+      <c r="NK1" s="50"/>
+      <c r="NL1" s="50"/>
+      <c r="NM1" s="50"/>
+      <c r="NN1" s="50"/>
+      <c r="NO1" s="50"/>
+      <c r="NP1" s="50"/>
+      <c r="NQ1" s="50"/>
+      <c r="NR1" s="50"/>
+      <c r="NS1" s="50"/>
+      <c r="NT1" s="50"/>
+      <c r="NU1" s="50"/>
+      <c r="NV1" s="50"/>
+      <c r="NW1" s="50"/>
+      <c r="NX1" s="50"/>
+      <c r="NY1" s="50"/>
+      <c r="NZ1" s="50"/>
+      <c r="OA1" s="50"/>
+      <c r="OB1" s="50"/>
+      <c r="OC1" s="50"/>
+      <c r="OD1" s="50"/>
+      <c r="OE1" s="50"/>
+      <c r="OF1" s="50"/>
+      <c r="OG1" s="50"/>
+      <c r="OH1" s="50"/>
+      <c r="OI1" s="50"/>
+      <c r="OJ1" s="50"/>
+      <c r="OK1" s="50"/>
+      <c r="OL1" s="50"/>
+      <c r="OM1" s="50"/>
+      <c r="ON1" s="50"/>
+      <c r="OO1" s="50"/>
+      <c r="OP1" s="50"/>
+      <c r="OQ1" s="50"/>
+      <c r="OR1" s="50"/>
+      <c r="OS1" s="50"/>
+      <c r="OT1" s="50"/>
+      <c r="OU1" s="50"/>
+      <c r="OV1" s="50"/>
+      <c r="OW1" s="50"/>
+      <c r="OX1" s="50"/>
+      <c r="OY1" s="50"/>
+      <c r="OZ1" s="50"/>
+      <c r="PA1" s="50"/>
+      <c r="PB1" s="50"/>
+      <c r="PC1" s="50"/>
+      <c r="PD1" s="50"/>
+      <c r="PE1" s="50"/>
+      <c r="PF1" s="50"/>
+      <c r="PG1" s="50"/>
+      <c r="PH1" s="50"/>
+      <c r="PI1" s="50"/>
+      <c r="PJ1" s="50"/>
+      <c r="PK1" s="50"/>
+      <c r="PL1" s="50"/>
+      <c r="PM1" s="50"/>
+      <c r="PN1" s="50"/>
+      <c r="PO1" s="50"/>
+      <c r="PP1" s="50"/>
+      <c r="PQ1" s="50"/>
+      <c r="PR1" s="50"/>
+      <c r="PS1" s="50"/>
+      <c r="PT1" s="50"/>
+      <c r="PU1" s="50"/>
+      <c r="PV1" s="50"/>
+      <c r="PW1" s="50"/>
+      <c r="PX1" s="50"/>
+      <c r="PY1" s="50"/>
+      <c r="PZ1" s="50"/>
+      <c r="QA1" s="50"/>
+      <c r="QB1" s="50"/>
+      <c r="QC1" s="50"/>
+      <c r="QD1" s="50"/>
+      <c r="QE1" s="50"/>
+      <c r="QF1" s="50"/>
+      <c r="QG1" s="50"/>
+      <c r="QH1" s="50"/>
+      <c r="QI1" s="50"/>
+      <c r="QJ1" s="50"/>
+      <c r="QK1" s="50"/>
+      <c r="QL1" s="50"/>
+      <c r="QM1" s="50"/>
+      <c r="QN1" s="50"/>
+      <c r="QO1" s="50"/>
+      <c r="QP1" s="50"/>
+      <c r="QQ1" s="50"/>
+      <c r="QR1" s="50"/>
+      <c r="QS1" s="50"/>
+      <c r="QT1" s="50"/>
+      <c r="QU1" s="50"/>
+      <c r="QV1" s="50"/>
+      <c r="QW1" s="50"/>
+      <c r="QX1" s="50"/>
+      <c r="QY1" s="50"/>
+      <c r="QZ1" s="50"/>
+      <c r="RA1" s="50"/>
+      <c r="RB1" s="50"/>
+      <c r="RC1" s="50"/>
+      <c r="RD1" s="50"/>
+      <c r="RE1" s="50"/>
+      <c r="RF1" s="50"/>
+      <c r="RG1" s="50"/>
+      <c r="RH1" s="50"/>
+      <c r="RI1" s="50"/>
+      <c r="RJ1" s="50"/>
+      <c r="RK1" s="50"/>
+      <c r="RL1" s="50"/>
+      <c r="RM1" s="50"/>
+      <c r="RN1" s="50"/>
+      <c r="RO1" s="50"/>
+      <c r="RP1" s="50"/>
+      <c r="RQ1" s="50"/>
+      <c r="RR1" s="50"/>
+      <c r="RS1" s="50"/>
+      <c r="RT1" s="50"/>
+      <c r="RU1" s="50"/>
+      <c r="RV1" s="50"/>
+      <c r="RW1" s="50"/>
+      <c r="RX1" s="50"/>
+      <c r="RY1" s="50"/>
+      <c r="RZ1" s="50"/>
+      <c r="SA1" s="50"/>
+      <c r="SB1" s="50"/>
+      <c r="SC1" s="50"/>
+      <c r="SD1" s="50"/>
+      <c r="SE1" s="50"/>
+      <c r="SF1" s="50"/>
+      <c r="SG1" s="50"/>
+      <c r="SH1" s="50"/>
+      <c r="SI1" s="50"/>
+      <c r="SJ1" s="50"/>
+      <c r="SK1" s="50"/>
+      <c r="SL1" s="50"/>
+      <c r="SM1" s="50"/>
+      <c r="SN1" s="50"/>
+      <c r="SO1" s="50"/>
+      <c r="SP1" s="50"/>
+      <c r="SQ1" s="50"/>
+      <c r="SR1" s="50"/>
+      <c r="SS1" s="50"/>
+      <c r="ST1" s="50"/>
+      <c r="SU1" s="50"/>
+      <c r="SV1" s="50"/>
+      <c r="SW1" s="50"/>
+      <c r="SX1" s="50"/>
+      <c r="SY1" s="50"/>
+      <c r="SZ1" s="50"/>
+      <c r="TA1" s="50"/>
+      <c r="TB1" s="50"/>
+      <c r="TC1" s="50"/>
+      <c r="TD1" s="50"/>
+      <c r="TE1" s="50"/>
+      <c r="TF1" s="50"/>
+      <c r="TG1" s="50"/>
+      <c r="TH1" s="50"/>
+      <c r="TI1" s="50"/>
+      <c r="TJ1" s="50"/>
+      <c r="TK1" s="50"/>
+      <c r="TL1" s="50"/>
+      <c r="TM1" s="50"/>
+      <c r="TN1" s="50"/>
+      <c r="TO1" s="50"/>
+      <c r="TP1" s="50"/>
+      <c r="TQ1" s="50"/>
+      <c r="TR1" s="50"/>
+      <c r="TS1" s="50"/>
+      <c r="TT1" s="50"/>
+      <c r="TU1" s="50"/>
+      <c r="TV1" s="50"/>
+      <c r="TW1" s="50"/>
+      <c r="TX1" s="50"/>
+      <c r="TY1" s="50"/>
+      <c r="TZ1" s="50"/>
+      <c r="UA1" s="50"/>
+      <c r="UB1" s="50"/>
+      <c r="UC1" s="50"/>
+      <c r="UD1" s="50"/>
+      <c r="UE1" s="50"/>
+      <c r="UF1" s="50"/>
+      <c r="UG1" s="50"/>
+      <c r="UH1" s="50"/>
+      <c r="UI1" s="50"/>
+      <c r="UJ1" s="50"/>
+      <c r="UK1" s="50"/>
+      <c r="UL1" s="50"/>
+      <c r="UM1" s="50"/>
+      <c r="UN1" s="50"/>
+      <c r="UO1" s="50"/>
+      <c r="UP1" s="50"/>
+      <c r="UQ1" s="50"/>
+      <c r="UR1" s="50"/>
+      <c r="US1" s="50"/>
+      <c r="UT1" s="50"/>
+      <c r="UU1" s="50"/>
+      <c r="UV1" s="50"/>
+      <c r="UW1" s="50"/>
+      <c r="UX1" s="50"/>
+      <c r="UY1" s="50"/>
+      <c r="UZ1" s="50"/>
+      <c r="VA1" s="50"/>
+      <c r="VB1" s="50"/>
+      <c r="VC1" s="50"/>
+      <c r="VD1" s="50"/>
+      <c r="VE1" s="50"/>
+      <c r="VF1" s="50"/>
+      <c r="VG1" s="50"/>
+      <c r="VH1" s="50"/>
+      <c r="VI1" s="50"/>
+      <c r="VJ1" s="50"/>
+      <c r="VK1" s="50"/>
+      <c r="VL1" s="50"/>
+      <c r="VM1" s="50"/>
+      <c r="VN1" s="50"/>
+      <c r="VO1" s="50"/>
+      <c r="VP1" s="50"/>
+      <c r="VQ1" s="50"/>
+      <c r="VR1" s="50"/>
+      <c r="VS1" s="50"/>
+      <c r="VT1" s="50"/>
+      <c r="VU1" s="50"/>
+      <c r="VV1" s="50"/>
+      <c r="VW1" s="50"/>
+      <c r="VX1" s="50"/>
+      <c r="VY1" s="50"/>
+      <c r="VZ1" s="50"/>
+      <c r="WA1" s="50"/>
+      <c r="WB1" s="50"/>
+      <c r="WC1" s="50"/>
+      <c r="WD1" s="50"/>
+      <c r="WE1" s="50"/>
+      <c r="WF1" s="50"/>
+      <c r="WG1" s="50"/>
+      <c r="WH1" s="50"/>
+      <c r="WI1" s="50"/>
+      <c r="WJ1" s="50"/>
+      <c r="WK1" s="50"/>
+      <c r="WL1" s="50"/>
+      <c r="WM1" s="50"/>
+      <c r="WN1" s="50"/>
+      <c r="WO1" s="50"/>
+      <c r="WP1" s="50"/>
+      <c r="WQ1" s="50"/>
+      <c r="WR1" s="50"/>
+      <c r="WS1" s="50"/>
+      <c r="WT1" s="50"/>
+      <c r="WU1" s="50"/>
+      <c r="WV1" s="50"/>
+      <c r="WW1" s="50"/>
+      <c r="WX1" s="50"/>
+      <c r="WY1" s="50"/>
+      <c r="WZ1" s="50"/>
+      <c r="XA1" s="50"/>
+      <c r="XB1" s="50"/>
+      <c r="XC1" s="50"/>
+      <c r="XD1" s="50"/>
+      <c r="XE1" s="50"/>
+      <c r="XF1" s="50"/>
+      <c r="XG1" s="50"/>
+      <c r="XH1" s="50"/>
+      <c r="XI1" s="50"/>
+      <c r="XJ1" s="50"/>
+      <c r="XK1" s="50"/>
+      <c r="XL1" s="50"/>
+      <c r="XM1" s="50"/>
+      <c r="XN1" s="50"/>
+      <c r="XO1" s="50"/>
+      <c r="XP1" s="50"/>
+      <c r="XQ1" s="50"/>
+      <c r="XR1" s="50"/>
+      <c r="XS1" s="50"/>
+      <c r="XT1" s="50"/>
+      <c r="XU1" s="50"/>
+      <c r="XV1" s="50"/>
+      <c r="XW1" s="50"/>
+      <c r="XX1" s="50"/>
+      <c r="XY1" s="50"/>
+      <c r="XZ1" s="50"/>
+      <c r="YA1" s="50"/>
+      <c r="YB1" s="50"/>
+      <c r="YC1" s="50"/>
+      <c r="YD1" s="50"/>
+      <c r="YE1" s="50"/>
+      <c r="YF1" s="50"/>
+      <c r="YG1" s="50"/>
+      <c r="YH1" s="50"/>
+      <c r="YI1" s="50"/>
+      <c r="YJ1" s="50"/>
+      <c r="YK1" s="50"/>
+      <c r="YL1" s="50"/>
+      <c r="YM1" s="50"/>
+      <c r="YN1" s="50"/>
+      <c r="YO1" s="50"/>
+      <c r="YP1" s="50"/>
+      <c r="YQ1" s="50"/>
+      <c r="YR1" s="50"/>
+      <c r="YS1" s="50"/>
+      <c r="YT1" s="50"/>
+      <c r="YU1" s="50"/>
+      <c r="YV1" s="50"/>
+      <c r="YW1" s="50"/>
+      <c r="YX1" s="50"/>
+      <c r="YY1" s="50"/>
+      <c r="YZ1" s="50"/>
     </row>
     <row r="2" spans="1:676" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
-      <c r="Q2" s="55"/>
-      <c r="R2" s="55"/>
-      <c r="S2" s="55"/>
-      <c r="T2" s="55"/>
-      <c r="U2" s="55"/>
-      <c r="V2" s="55"/>
-      <c r="W2" s="55"/>
-      <c r="X2" s="55"/>
-      <c r="Y2" s="55"/>
-      <c r="Z2" s="55"/>
-      <c r="AA2" s="55"/>
-      <c r="AB2" s="55"/>
-      <c r="AC2" s="55"/>
-      <c r="AD2" s="55"/>
-      <c r="AE2" s="55"/>
-      <c r="AF2" s="55"/>
-      <c r="AG2" s="55"/>
-      <c r="AH2" s="55"/>
-      <c r="AI2" s="55"/>
-      <c r="AJ2" s="55"/>
-      <c r="AK2" s="55"/>
-      <c r="AL2" s="55"/>
-      <c r="AM2" s="55"/>
-      <c r="AN2" s="55"/>
-      <c r="AO2" s="55"/>
-      <c r="AP2" s="55"/>
-      <c r="AQ2" s="55"/>
-      <c r="AR2" s="55"/>
-      <c r="AS2" s="55"/>
-      <c r="AT2" s="55"/>
-      <c r="AU2" s="55"/>
-      <c r="AV2" s="55"/>
-      <c r="AW2" s="55"/>
-      <c r="AX2" s="55"/>
-      <c r="AY2" s="55"/>
-      <c r="AZ2" s="55"/>
-      <c r="BA2" s="55"/>
-      <c r="BB2" s="55"/>
-      <c r="BC2" s="55"/>
-      <c r="BD2" s="55"/>
-      <c r="BE2" s="55"/>
-      <c r="BF2" s="55"/>
-      <c r="BG2" s="55"/>
-      <c r="BH2" s="55"/>
-      <c r="BI2" s="55"/>
-      <c r="BJ2" s="55"/>
-      <c r="BK2" s="55"/>
-      <c r="BL2" s="55"/>
-      <c r="BM2" s="55"/>
-      <c r="BN2" s="55"/>
-      <c r="BO2" s="55"/>
-      <c r="BP2" s="55"/>
-      <c r="BQ2" s="55"/>
-      <c r="BR2" s="55"/>
-      <c r="BS2" s="55"/>
-      <c r="BT2" s="55"/>
-      <c r="BU2" s="55"/>
-      <c r="BV2" s="55"/>
-      <c r="BW2" s="55"/>
-      <c r="BX2" s="55"/>
-      <c r="BY2" s="55"/>
-      <c r="BZ2" s="55"/>
-      <c r="CA2" s="55"/>
-      <c r="CB2" s="55"/>
-      <c r="CC2" s="55"/>
-      <c r="CD2" s="55"/>
-      <c r="CE2" s="55"/>
-      <c r="CF2" s="55"/>
-      <c r="CG2" s="55"/>
-      <c r="CH2" s="55"/>
-      <c r="CI2" s="55"/>
-      <c r="CJ2" s="55"/>
-      <c r="CK2" s="55"/>
-      <c r="CL2" s="55"/>
-      <c r="CM2" s="55"/>
-      <c r="CN2" s="55"/>
-      <c r="CO2" s="55"/>
-      <c r="CP2" s="55"/>
-      <c r="CQ2" s="55"/>
-      <c r="CR2" s="55"/>
-      <c r="CS2" s="55"/>
-      <c r="CT2" s="55"/>
-      <c r="CU2" s="55"/>
-      <c r="CV2" s="55"/>
-      <c r="CW2" s="55"/>
-      <c r="CX2" s="55"/>
-      <c r="CY2" s="55"/>
-      <c r="CZ2" s="55"/>
-      <c r="DA2" s="55"/>
-      <c r="DB2" s="55"/>
-      <c r="DC2" s="55"/>
-      <c r="DD2" s="55"/>
-      <c r="DE2" s="55"/>
-      <c r="DF2" s="55"/>
-      <c r="DG2" s="55"/>
-      <c r="DH2" s="55"/>
-      <c r="DI2" s="55"/>
-      <c r="DJ2" s="55"/>
-      <c r="DK2" s="55"/>
-      <c r="DL2" s="55"/>
-      <c r="DM2" s="55"/>
-      <c r="DN2" s="55"/>
-      <c r="DO2" s="55"/>
-      <c r="DP2" s="55"/>
-      <c r="DQ2" s="55"/>
-      <c r="DR2" s="55"/>
-      <c r="DS2" s="55"/>
-      <c r="DT2" s="55"/>
-      <c r="DU2" s="55"/>
-      <c r="DV2" s="55"/>
-      <c r="DW2" s="55"/>
-      <c r="DX2" s="55"/>
-      <c r="DY2" s="55"/>
-      <c r="DZ2" s="55"/>
-      <c r="EA2" s="55"/>
-      <c r="EB2" s="55"/>
-      <c r="EC2" s="55"/>
-      <c r="ED2" s="55"/>
-      <c r="EE2" s="55"/>
-      <c r="EF2" s="55"/>
-      <c r="EG2" s="55"/>
-      <c r="EH2" s="55"/>
-      <c r="EI2" s="55"/>
-      <c r="EJ2" s="55"/>
-      <c r="EK2" s="55"/>
-      <c r="EL2" s="55"/>
-      <c r="EM2" s="55"/>
-      <c r="EN2" s="55"/>
-      <c r="EO2" s="55"/>
-      <c r="EP2" s="55"/>
-      <c r="EQ2" s="55"/>
-      <c r="ER2" s="55"/>
-      <c r="ES2" s="55"/>
-      <c r="ET2" s="55"/>
-      <c r="EU2" s="55"/>
-      <c r="EV2" s="55"/>
-      <c r="EW2" s="55"/>
-      <c r="EX2" s="55"/>
-      <c r="EY2" s="55"/>
-      <c r="EZ2" s="55"/>
-      <c r="FA2" s="55"/>
-      <c r="FB2" s="55"/>
-      <c r="FC2" s="55"/>
-      <c r="FD2" s="55"/>
-      <c r="FE2" s="55"/>
-      <c r="FF2" s="55"/>
-      <c r="FG2" s="55"/>
-      <c r="FH2" s="55"/>
-      <c r="FI2" s="55"/>
-      <c r="FJ2" s="55"/>
-      <c r="FK2" s="55"/>
-      <c r="FL2" s="55"/>
-      <c r="FM2" s="55"/>
-      <c r="FN2" s="55"/>
-      <c r="FO2" s="55"/>
-      <c r="FP2" s="55"/>
-      <c r="FQ2" s="55"/>
-      <c r="FR2" s="55"/>
-      <c r="FS2" s="55"/>
-      <c r="FT2" s="55"/>
-      <c r="FU2" s="55"/>
-      <c r="FV2" s="55"/>
-      <c r="FW2" s="55"/>
-      <c r="FX2" s="55"/>
-      <c r="FY2" s="55"/>
-      <c r="FZ2" s="55"/>
-      <c r="GA2" s="55"/>
-      <c r="GB2" s="55"/>
-      <c r="GC2" s="55"/>
-      <c r="GD2" s="55"/>
-      <c r="GE2" s="55"/>
-      <c r="GF2" s="55"/>
-      <c r="GG2" s="55"/>
-      <c r="GH2" s="55"/>
-      <c r="GI2" s="55"/>
-      <c r="GJ2" s="55"/>
-      <c r="GK2" s="55"/>
-      <c r="GL2" s="55"/>
-      <c r="GM2" s="55"/>
-      <c r="GN2" s="55"/>
-      <c r="GO2" s="55"/>
-      <c r="GP2" s="55"/>
-      <c r="GQ2" s="55"/>
-      <c r="GR2" s="55"/>
-      <c r="GS2" s="55"/>
-      <c r="GT2" s="55"/>
-      <c r="GU2" s="55"/>
-      <c r="GV2" s="55"/>
-      <c r="GW2" s="55"/>
-      <c r="GX2" s="55"/>
-      <c r="GY2" s="55"/>
-      <c r="GZ2" s="55"/>
-      <c r="HA2" s="55"/>
-      <c r="HB2" s="55"/>
-      <c r="HC2" s="55"/>
-      <c r="HD2" s="55"/>
-      <c r="HE2" s="55"/>
-      <c r="HF2" s="55"/>
-      <c r="HG2" s="55"/>
-      <c r="HH2" s="55"/>
-      <c r="HI2" s="55"/>
-      <c r="HJ2" s="55"/>
-      <c r="HK2" s="55"/>
-      <c r="HL2" s="55"/>
-      <c r="HM2" s="55"/>
-      <c r="HN2" s="55"/>
-      <c r="HO2" s="55"/>
-      <c r="HP2" s="55"/>
-      <c r="HQ2" s="55"/>
-      <c r="HR2" s="55"/>
-      <c r="HS2" s="55"/>
-      <c r="HT2" s="55"/>
-      <c r="HU2" s="55"/>
-      <c r="HV2" s="55"/>
-      <c r="HW2" s="55"/>
-      <c r="HX2" s="55"/>
-      <c r="HY2" s="55"/>
-      <c r="HZ2" s="55"/>
-      <c r="IA2" s="55"/>
-      <c r="IB2" s="55"/>
-      <c r="IC2" s="55"/>
-      <c r="ID2" s="55"/>
-      <c r="IE2" s="55"/>
-      <c r="IF2" s="55"/>
-      <c r="IG2" s="55"/>
-      <c r="IH2" s="55"/>
-      <c r="II2" s="55"/>
-      <c r="IJ2" s="55"/>
-      <c r="IK2" s="55"/>
-      <c r="IL2" s="55"/>
-      <c r="IM2" s="55"/>
-      <c r="IN2" s="55"/>
-      <c r="IO2" s="55"/>
-      <c r="IP2" s="55"/>
-      <c r="IQ2" s="55"/>
-      <c r="IR2" s="55"/>
-      <c r="IS2" s="55"/>
-      <c r="IT2" s="55"/>
-      <c r="IU2" s="55"/>
-      <c r="IV2" s="55"/>
-      <c r="IW2" s="55"/>
-      <c r="IX2" s="55"/>
-      <c r="IY2" s="55"/>
-      <c r="IZ2" s="55"/>
-      <c r="JA2" s="55"/>
-      <c r="JB2" s="55"/>
-      <c r="JC2" s="55"/>
-      <c r="JD2" s="55"/>
-      <c r="JE2" s="55"/>
-      <c r="JF2" s="55"/>
-      <c r="JG2" s="55"/>
-      <c r="JH2" s="55"/>
-      <c r="JI2" s="55"/>
-      <c r="JJ2" s="55"/>
-      <c r="JK2" s="55"/>
-      <c r="JL2" s="55"/>
-      <c r="JM2" s="55"/>
-      <c r="JN2" s="55"/>
-      <c r="JO2" s="55"/>
-      <c r="JP2" s="55"/>
-      <c r="JQ2" s="55"/>
-      <c r="JR2" s="55"/>
-      <c r="JS2" s="55"/>
-      <c r="JT2" s="55"/>
-      <c r="JU2" s="55"/>
-      <c r="JV2" s="55"/>
-      <c r="JW2" s="55"/>
-      <c r="JX2" s="55"/>
-      <c r="JY2" s="55"/>
-      <c r="JZ2" s="55"/>
-      <c r="KA2" s="55"/>
-      <c r="KB2" s="55"/>
-      <c r="KC2" s="55"/>
-      <c r="KD2" s="55"/>
-      <c r="KE2" s="55"/>
-      <c r="KF2" s="55"/>
-      <c r="KG2" s="55"/>
-      <c r="KH2" s="55"/>
-      <c r="KI2" s="55"/>
-      <c r="KJ2" s="55"/>
-      <c r="KK2" s="55"/>
-      <c r="KL2" s="55"/>
-      <c r="KM2" s="55"/>
-      <c r="KN2" s="55"/>
-      <c r="KO2" s="55"/>
-      <c r="KP2" s="55"/>
-      <c r="KQ2" s="55"/>
-      <c r="KR2" s="55"/>
-      <c r="KS2" s="55"/>
-      <c r="KT2" s="55"/>
-      <c r="KU2" s="55"/>
-      <c r="KV2" s="55"/>
-      <c r="KW2" s="55"/>
-      <c r="KX2" s="55"/>
-      <c r="KY2" s="55"/>
-      <c r="KZ2" s="55"/>
-      <c r="LA2" s="55"/>
-      <c r="LB2" s="55"/>
-      <c r="LC2" s="55"/>
-      <c r="LD2" s="55"/>
-      <c r="LE2" s="55"/>
-      <c r="LF2" s="55"/>
-      <c r="LG2" s="55"/>
-      <c r="LH2" s="55"/>
-      <c r="LI2" s="55"/>
-      <c r="LJ2" s="55"/>
-      <c r="LK2" s="55"/>
-      <c r="LL2" s="55"/>
-      <c r="LM2" s="55"/>
-      <c r="LN2" s="55"/>
-      <c r="LO2" s="55"/>
-      <c r="LP2" s="55"/>
-      <c r="LQ2" s="55"/>
-      <c r="LR2" s="55"/>
-      <c r="LS2" s="55"/>
-      <c r="LT2" s="55"/>
-      <c r="LU2" s="55"/>
-      <c r="LV2" s="55"/>
-      <c r="LW2" s="55"/>
-      <c r="LX2" s="55"/>
-      <c r="LY2" s="55"/>
-      <c r="LZ2" s="55"/>
-      <c r="MA2" s="55"/>
-      <c r="MB2" s="55"/>
-      <c r="MC2" s="55"/>
-      <c r="MD2" s="55"/>
-      <c r="ME2" s="55"/>
-      <c r="MF2" s="55"/>
-      <c r="MG2" s="55"/>
-      <c r="MH2" s="55"/>
-      <c r="MI2" s="55"/>
-      <c r="MJ2" s="55"/>
-      <c r="MK2" s="55"/>
-      <c r="ML2" s="55"/>
-      <c r="MM2" s="55"/>
-      <c r="MN2" s="55"/>
-      <c r="MO2" s="55"/>
-      <c r="MP2" s="55"/>
-      <c r="MQ2" s="55"/>
-      <c r="MR2" s="55"/>
-      <c r="MS2" s="55"/>
-      <c r="MT2" s="55"/>
-      <c r="MU2" s="55"/>
-      <c r="MV2" s="55"/>
-      <c r="MW2" s="55"/>
-      <c r="MX2" s="55"/>
-      <c r="MY2" s="55"/>
-      <c r="MZ2" s="55"/>
-      <c r="NA2" s="55"/>
-      <c r="NB2" s="55"/>
-      <c r="NC2" s="55"/>
-      <c r="ND2" s="55"/>
-      <c r="NE2" s="55"/>
-      <c r="NF2" s="55"/>
-      <c r="NG2" s="55"/>
-      <c r="NH2" s="55"/>
-      <c r="NI2" s="55"/>
-      <c r="NJ2" s="55"/>
-      <c r="NK2" s="55"/>
-      <c r="NL2" s="55"/>
-      <c r="NM2" s="55"/>
-      <c r="NN2" s="55"/>
-      <c r="NO2" s="55"/>
-      <c r="NP2" s="55"/>
-      <c r="NQ2" s="55"/>
-      <c r="NR2" s="55"/>
-      <c r="NS2" s="55"/>
-      <c r="NT2" s="55"/>
-      <c r="NU2" s="55"/>
-      <c r="NV2" s="55"/>
-      <c r="NW2" s="55"/>
-      <c r="NX2" s="55"/>
-      <c r="NY2" s="55"/>
-      <c r="NZ2" s="55"/>
-      <c r="OA2" s="55"/>
-      <c r="OB2" s="55"/>
-      <c r="OC2" s="55"/>
-      <c r="OD2" s="55"/>
-      <c r="OE2" s="55"/>
-      <c r="OF2" s="55"/>
-      <c r="OG2" s="55"/>
-      <c r="OH2" s="55"/>
-      <c r="OI2" s="55"/>
-      <c r="OJ2" s="55"/>
-      <c r="OK2" s="55"/>
-      <c r="OL2" s="55"/>
-      <c r="OM2" s="55"/>
-      <c r="ON2" s="55"/>
-      <c r="OO2" s="55"/>
-      <c r="OP2" s="55"/>
-      <c r="OQ2" s="55"/>
-      <c r="OR2" s="55"/>
-      <c r="OS2" s="55"/>
-      <c r="OT2" s="55"/>
-      <c r="OU2" s="55"/>
-      <c r="OV2" s="55"/>
-      <c r="OW2" s="55"/>
-      <c r="OX2" s="55"/>
-      <c r="OY2" s="55"/>
-      <c r="OZ2" s="55"/>
-      <c r="PA2" s="55"/>
-      <c r="PB2" s="55"/>
-      <c r="PC2" s="55"/>
-      <c r="PD2" s="55"/>
-      <c r="PE2" s="55"/>
-      <c r="PF2" s="55"/>
-      <c r="PG2" s="55"/>
-      <c r="PH2" s="55"/>
-      <c r="PI2" s="55"/>
-      <c r="PJ2" s="55"/>
-      <c r="PK2" s="55"/>
-      <c r="PL2" s="55"/>
-      <c r="PM2" s="55"/>
-      <c r="PN2" s="55"/>
-      <c r="PO2" s="55"/>
-      <c r="PP2" s="55"/>
-      <c r="PQ2" s="55"/>
-      <c r="PR2" s="55"/>
-      <c r="PS2" s="55"/>
-      <c r="PT2" s="55"/>
-      <c r="PU2" s="55"/>
-      <c r="PV2" s="55"/>
-      <c r="PW2" s="55"/>
-      <c r="PX2" s="55"/>
-      <c r="PY2" s="55"/>
-      <c r="PZ2" s="55"/>
-      <c r="QA2" s="55"/>
-      <c r="QB2" s="55"/>
-      <c r="QC2" s="55"/>
-      <c r="QD2" s="55"/>
-      <c r="QE2" s="55"/>
-      <c r="QF2" s="55"/>
-      <c r="QG2" s="55"/>
-      <c r="QH2" s="55"/>
-      <c r="QI2" s="55"/>
-      <c r="QJ2" s="55"/>
-      <c r="QK2" s="55"/>
-      <c r="QL2" s="55"/>
-      <c r="QM2" s="55"/>
-      <c r="QN2" s="55"/>
-      <c r="QO2" s="55"/>
-      <c r="QP2" s="55"/>
-      <c r="QQ2" s="55"/>
-      <c r="QR2" s="55"/>
-      <c r="QS2" s="55"/>
-      <c r="QT2" s="55"/>
-      <c r="QU2" s="55"/>
-      <c r="QV2" s="55"/>
-      <c r="QW2" s="55"/>
-      <c r="QX2" s="55"/>
-      <c r="QY2" s="55"/>
-      <c r="QZ2" s="55"/>
-      <c r="RA2" s="55"/>
-      <c r="RB2" s="55"/>
-      <c r="RC2" s="55"/>
-      <c r="RD2" s="55"/>
-      <c r="RE2" s="55"/>
-      <c r="RF2" s="55"/>
-      <c r="RG2" s="55"/>
-      <c r="RH2" s="55"/>
-      <c r="RI2" s="55"/>
-      <c r="RJ2" s="55"/>
-      <c r="RK2" s="55"/>
-      <c r="RL2" s="55"/>
-      <c r="RM2" s="55"/>
-      <c r="RN2" s="55"/>
-      <c r="RO2" s="55"/>
-      <c r="RP2" s="55"/>
-      <c r="RQ2" s="55"/>
-      <c r="RR2" s="55"/>
-      <c r="RS2" s="55"/>
-      <c r="RT2" s="55"/>
-      <c r="RU2" s="55"/>
-      <c r="RV2" s="55"/>
-      <c r="RW2" s="55"/>
-      <c r="RX2" s="55"/>
-      <c r="RY2" s="55"/>
-      <c r="RZ2" s="55"/>
-      <c r="SA2" s="55"/>
-      <c r="SB2" s="55"/>
-      <c r="SC2" s="55"/>
-      <c r="SD2" s="55"/>
-      <c r="SE2" s="55"/>
-      <c r="SF2" s="55"/>
-      <c r="SG2" s="55"/>
-      <c r="SH2" s="55"/>
-      <c r="SI2" s="55"/>
-      <c r="SJ2" s="55"/>
-      <c r="SK2" s="55"/>
-      <c r="SL2" s="55"/>
-      <c r="SM2" s="55"/>
-      <c r="SN2" s="55"/>
-      <c r="SO2" s="55"/>
-      <c r="SP2" s="55"/>
-      <c r="SQ2" s="55"/>
-      <c r="SR2" s="55"/>
-      <c r="SS2" s="55"/>
-      <c r="ST2" s="55"/>
-      <c r="SU2" s="55"/>
-      <c r="SV2" s="55"/>
-      <c r="SW2" s="55"/>
-      <c r="SX2" s="55"/>
-      <c r="SY2" s="55"/>
-      <c r="SZ2" s="55"/>
-      <c r="TA2" s="55"/>
-      <c r="TB2" s="55"/>
-      <c r="TC2" s="55"/>
-      <c r="TD2" s="55"/>
-      <c r="TE2" s="55"/>
-      <c r="TF2" s="55"/>
-      <c r="TG2" s="55"/>
-      <c r="TH2" s="55"/>
-      <c r="TI2" s="55"/>
-      <c r="TJ2" s="55"/>
-      <c r="TK2" s="55"/>
-      <c r="TL2" s="55"/>
-      <c r="TM2" s="55"/>
-      <c r="TN2" s="55"/>
-      <c r="TO2" s="55"/>
-      <c r="TP2" s="55"/>
-      <c r="TQ2" s="55"/>
-      <c r="TR2" s="55"/>
-      <c r="TS2" s="55"/>
-      <c r="TT2" s="55"/>
-      <c r="TU2" s="55"/>
-      <c r="TV2" s="55"/>
-      <c r="TW2" s="55"/>
-      <c r="TX2" s="55"/>
-      <c r="TY2" s="55"/>
-      <c r="TZ2" s="55"/>
-      <c r="UA2" s="55"/>
-      <c r="UB2" s="55"/>
-      <c r="UC2" s="55"/>
-      <c r="UD2" s="55"/>
-      <c r="UE2" s="55"/>
-      <c r="UF2" s="55"/>
-      <c r="UG2" s="55"/>
-      <c r="UH2" s="55"/>
-      <c r="UI2" s="55"/>
-      <c r="UJ2" s="55"/>
-      <c r="UK2" s="55"/>
-      <c r="UL2" s="55"/>
-      <c r="UM2" s="55"/>
-      <c r="UN2" s="55"/>
-      <c r="UO2" s="55"/>
-      <c r="UP2" s="55"/>
-      <c r="UQ2" s="55"/>
-      <c r="UR2" s="55"/>
-      <c r="US2" s="55"/>
-      <c r="UT2" s="55"/>
-      <c r="UU2" s="55"/>
-      <c r="UV2" s="55"/>
-      <c r="UW2" s="55"/>
-      <c r="UX2" s="55"/>
-      <c r="UY2" s="55"/>
-      <c r="UZ2" s="55"/>
-      <c r="VA2" s="55"/>
-      <c r="VB2" s="55"/>
-      <c r="VC2" s="55"/>
-      <c r="VD2" s="55"/>
-      <c r="VE2" s="55"/>
-      <c r="VF2" s="55"/>
-      <c r="VG2" s="55"/>
-      <c r="VH2" s="55"/>
-      <c r="VI2" s="55"/>
-      <c r="VJ2" s="55"/>
-      <c r="VK2" s="55"/>
-      <c r="VL2" s="55"/>
-      <c r="VM2" s="55"/>
-      <c r="VN2" s="55"/>
-      <c r="VO2" s="55"/>
-      <c r="VP2" s="55"/>
-      <c r="VQ2" s="55"/>
-      <c r="VR2" s="55"/>
-      <c r="VS2" s="55"/>
-      <c r="VT2" s="55"/>
-      <c r="VU2" s="55"/>
-      <c r="VV2" s="55"/>
-      <c r="VW2" s="55"/>
-      <c r="VX2" s="55"/>
-      <c r="VY2" s="55"/>
-      <c r="VZ2" s="55"/>
-      <c r="WA2" s="55"/>
-      <c r="WB2" s="55"/>
-      <c r="WC2" s="55"/>
-      <c r="WD2" s="55"/>
-      <c r="WE2" s="55"/>
-      <c r="WF2" s="55"/>
-      <c r="WG2" s="55"/>
-      <c r="WH2" s="55"/>
-      <c r="WI2" s="55"/>
-      <c r="WJ2" s="55"/>
-      <c r="WK2" s="55"/>
-      <c r="WL2" s="55"/>
-      <c r="WM2" s="55"/>
-      <c r="WN2" s="55"/>
-      <c r="WO2" s="55"/>
-      <c r="WP2" s="55"/>
-      <c r="WQ2" s="55"/>
-      <c r="WR2" s="55"/>
-      <c r="WS2" s="55"/>
-      <c r="WT2" s="55"/>
-      <c r="WU2" s="55"/>
-      <c r="WV2" s="55"/>
-      <c r="WW2" s="55"/>
-      <c r="WX2" s="55"/>
-      <c r="WY2" s="55"/>
-      <c r="WZ2" s="55"/>
-      <c r="XA2" s="55"/>
-      <c r="XB2" s="55"/>
-      <c r="XC2" s="55"/>
-      <c r="XD2" s="55"/>
-      <c r="XE2" s="55"/>
-      <c r="XF2" s="55"/>
-      <c r="XG2" s="55"/>
-      <c r="XH2" s="55"/>
-      <c r="XI2" s="55"/>
-      <c r="XJ2" s="55"/>
-      <c r="XK2" s="55"/>
-      <c r="XL2" s="55"/>
-      <c r="XM2" s="55"/>
-      <c r="XN2" s="55"/>
-      <c r="XO2" s="55"/>
-      <c r="XP2" s="55"/>
-      <c r="XQ2" s="55"/>
-      <c r="XR2" s="55"/>
-      <c r="XS2" s="55"/>
-      <c r="XT2" s="55"/>
-      <c r="XU2" s="55"/>
-      <c r="XV2" s="55"/>
-      <c r="XW2" s="55"/>
-      <c r="XX2" s="55"/>
-      <c r="XY2" s="55"/>
-      <c r="XZ2" s="55"/>
-      <c r="YA2" s="55"/>
-      <c r="YB2" s="55"/>
-      <c r="YC2" s="55"/>
-      <c r="YD2" s="55"/>
-      <c r="YE2" s="55"/>
-      <c r="YF2" s="55"/>
-      <c r="YG2" s="55"/>
-      <c r="YH2" s="55"/>
-      <c r="YI2" s="55"/>
-      <c r="YJ2" s="55"/>
-      <c r="YK2" s="55"/>
-      <c r="YL2" s="55"/>
-      <c r="YM2" s="55"/>
-      <c r="YN2" s="55"/>
-      <c r="YO2" s="55"/>
-      <c r="YP2" s="55"/>
-      <c r="YQ2" s="55"/>
-      <c r="YR2" s="55"/>
-      <c r="YS2" s="55"/>
-      <c r="YT2" s="55"/>
-      <c r="YU2" s="55"/>
-      <c r="YV2" s="55"/>
-      <c r="YW2" s="55"/>
-      <c r="YX2" s="55"/>
-      <c r="YY2" s="55"/>
-      <c r="YZ2" s="55"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
+      <c r="W2" s="48"/>
+      <c r="X2" s="48"/>
+      <c r="Y2" s="48"/>
+      <c r="Z2" s="48"/>
+      <c r="AA2" s="48"/>
+      <c r="AB2" s="48"/>
+      <c r="AC2" s="48"/>
+      <c r="AD2" s="48"/>
+      <c r="AE2" s="48"/>
+      <c r="AF2" s="48"/>
+      <c r="AG2" s="48"/>
+      <c r="AH2" s="48"/>
+      <c r="AI2" s="48"/>
+      <c r="AJ2" s="48"/>
+      <c r="AK2" s="48"/>
+      <c r="AL2" s="48"/>
+      <c r="AM2" s="48"/>
+      <c r="AN2" s="48"/>
+      <c r="AO2" s="48"/>
+      <c r="AP2" s="48"/>
+      <c r="AQ2" s="48"/>
+      <c r="AR2" s="48"/>
+      <c r="AS2" s="48"/>
+      <c r="AT2" s="48"/>
+      <c r="AU2" s="48"/>
+      <c r="AV2" s="48"/>
+      <c r="AW2" s="48"/>
+      <c r="AX2" s="48"/>
+      <c r="AY2" s="48"/>
+      <c r="AZ2" s="48"/>
+      <c r="BA2" s="48"/>
+      <c r="BB2" s="48"/>
+      <c r="BC2" s="48"/>
+      <c r="BD2" s="48"/>
+      <c r="BE2" s="48"/>
+      <c r="BF2" s="48"/>
+      <c r="BG2" s="48"/>
+      <c r="BH2" s="48"/>
+      <c r="BI2" s="48"/>
+      <c r="BJ2" s="48"/>
+      <c r="BK2" s="48"/>
+      <c r="BL2" s="48"/>
+      <c r="BM2" s="48"/>
+      <c r="BN2" s="48"/>
+      <c r="BO2" s="48"/>
+      <c r="BP2" s="48"/>
+      <c r="BQ2" s="48"/>
+      <c r="BR2" s="48"/>
+      <c r="BS2" s="48"/>
+      <c r="BT2" s="48"/>
+      <c r="BU2" s="48"/>
+      <c r="BV2" s="48"/>
+      <c r="BW2" s="48"/>
+      <c r="BX2" s="48"/>
+      <c r="BY2" s="48"/>
+      <c r="BZ2" s="48"/>
+      <c r="CA2" s="48"/>
+      <c r="CB2" s="48"/>
+      <c r="CC2" s="48"/>
+      <c r="CD2" s="48"/>
+      <c r="CE2" s="48"/>
+      <c r="CF2" s="48"/>
+      <c r="CG2" s="48"/>
+      <c r="CH2" s="48"/>
+      <c r="CI2" s="48"/>
+      <c r="CJ2" s="48"/>
+      <c r="CK2" s="48"/>
+      <c r="CL2" s="48"/>
+      <c r="CM2" s="48"/>
+      <c r="CN2" s="48"/>
+      <c r="CO2" s="48"/>
+      <c r="CP2" s="48"/>
+      <c r="CQ2" s="48"/>
+      <c r="CR2" s="48"/>
+      <c r="CS2" s="48"/>
+      <c r="CT2" s="48"/>
+      <c r="CU2" s="48"/>
+      <c r="CV2" s="48"/>
+      <c r="CW2" s="48"/>
+      <c r="CX2" s="48"/>
+      <c r="CY2" s="48"/>
+      <c r="CZ2" s="48"/>
+      <c r="DA2" s="48"/>
+      <c r="DB2" s="48"/>
+      <c r="DC2" s="48"/>
+      <c r="DD2" s="48"/>
+      <c r="DE2" s="48"/>
+      <c r="DF2" s="48"/>
+      <c r="DG2" s="48"/>
+      <c r="DH2" s="48"/>
+      <c r="DI2" s="48"/>
+      <c r="DJ2" s="48"/>
+      <c r="DK2" s="48"/>
+      <c r="DL2" s="48"/>
+      <c r="DM2" s="48"/>
+      <c r="DN2" s="48"/>
+      <c r="DO2" s="48"/>
+      <c r="DP2" s="48"/>
+      <c r="DQ2" s="48"/>
+      <c r="DR2" s="48"/>
+      <c r="DS2" s="48"/>
+      <c r="DT2" s="48"/>
+      <c r="DU2" s="48"/>
+      <c r="DV2" s="48"/>
+      <c r="DW2" s="48"/>
+      <c r="DX2" s="48"/>
+      <c r="DY2" s="48"/>
+      <c r="DZ2" s="48"/>
+      <c r="EA2" s="48"/>
+      <c r="EB2" s="48"/>
+      <c r="EC2" s="48"/>
+      <c r="ED2" s="48"/>
+      <c r="EE2" s="48"/>
+      <c r="EF2" s="48"/>
+      <c r="EG2" s="48"/>
+      <c r="EH2" s="48"/>
+      <c r="EI2" s="48"/>
+      <c r="EJ2" s="48"/>
+      <c r="EK2" s="48"/>
+      <c r="EL2" s="48"/>
+      <c r="EM2" s="48"/>
+      <c r="EN2" s="48"/>
+      <c r="EO2" s="48"/>
+      <c r="EP2" s="48"/>
+      <c r="EQ2" s="48"/>
+      <c r="ER2" s="48"/>
+      <c r="ES2" s="48"/>
+      <c r="ET2" s="48"/>
+      <c r="EU2" s="48"/>
+      <c r="EV2" s="48"/>
+      <c r="EW2" s="48"/>
+      <c r="EX2" s="48"/>
+      <c r="EY2" s="48"/>
+      <c r="EZ2" s="48"/>
+      <c r="FA2" s="48"/>
+      <c r="FB2" s="48"/>
+      <c r="FC2" s="48"/>
+      <c r="FD2" s="48"/>
+      <c r="FE2" s="48"/>
+      <c r="FF2" s="48"/>
+      <c r="FG2" s="48"/>
+      <c r="FH2" s="48"/>
+      <c r="FI2" s="48"/>
+      <c r="FJ2" s="48"/>
+      <c r="FK2" s="48"/>
+      <c r="FL2" s="48"/>
+      <c r="FM2" s="48"/>
+      <c r="FN2" s="48"/>
+      <c r="FO2" s="48"/>
+      <c r="FP2" s="48"/>
+      <c r="FQ2" s="48"/>
+      <c r="FR2" s="48"/>
+      <c r="FS2" s="48"/>
+      <c r="FT2" s="48"/>
+      <c r="FU2" s="48"/>
+      <c r="FV2" s="48"/>
+      <c r="FW2" s="48"/>
+      <c r="FX2" s="48"/>
+      <c r="FY2" s="48"/>
+      <c r="FZ2" s="48"/>
+      <c r="GA2" s="48"/>
+      <c r="GB2" s="48"/>
+      <c r="GC2" s="48"/>
+      <c r="GD2" s="48"/>
+      <c r="GE2" s="48"/>
+      <c r="GF2" s="48"/>
+      <c r="GG2" s="48"/>
+      <c r="GH2" s="48"/>
+      <c r="GI2" s="48"/>
+      <c r="GJ2" s="48"/>
+      <c r="GK2" s="48"/>
+      <c r="GL2" s="48"/>
+      <c r="GM2" s="48"/>
+      <c r="GN2" s="48"/>
+      <c r="GO2" s="48"/>
+      <c r="GP2" s="48"/>
+      <c r="GQ2" s="48"/>
+      <c r="GR2" s="48"/>
+      <c r="GS2" s="48"/>
+      <c r="GT2" s="48"/>
+      <c r="GU2" s="48"/>
+      <c r="GV2" s="48"/>
+      <c r="GW2" s="48"/>
+      <c r="GX2" s="48"/>
+      <c r="GY2" s="48"/>
+      <c r="GZ2" s="48"/>
+      <c r="HA2" s="48"/>
+      <c r="HB2" s="48"/>
+      <c r="HC2" s="48"/>
+      <c r="HD2" s="48"/>
+      <c r="HE2" s="48"/>
+      <c r="HF2" s="48"/>
+      <c r="HG2" s="48"/>
+      <c r="HH2" s="48"/>
+      <c r="HI2" s="48"/>
+      <c r="HJ2" s="48"/>
+      <c r="HK2" s="48"/>
+      <c r="HL2" s="48"/>
+      <c r="HM2" s="48"/>
+      <c r="HN2" s="48"/>
+      <c r="HO2" s="48"/>
+      <c r="HP2" s="48"/>
+      <c r="HQ2" s="48"/>
+      <c r="HR2" s="48"/>
+      <c r="HS2" s="48"/>
+      <c r="HT2" s="48"/>
+      <c r="HU2" s="48"/>
+      <c r="HV2" s="48"/>
+      <c r="HW2" s="48"/>
+      <c r="HX2" s="48"/>
+      <c r="HY2" s="48"/>
+      <c r="HZ2" s="48"/>
+      <c r="IA2" s="48"/>
+      <c r="IB2" s="48"/>
+      <c r="IC2" s="48"/>
+      <c r="ID2" s="48"/>
+      <c r="IE2" s="48"/>
+      <c r="IF2" s="48"/>
+      <c r="IG2" s="48"/>
+      <c r="IH2" s="48"/>
+      <c r="II2" s="48"/>
+      <c r="IJ2" s="48"/>
+      <c r="IK2" s="48"/>
+      <c r="IL2" s="48"/>
+      <c r="IM2" s="48"/>
+      <c r="IN2" s="48"/>
+      <c r="IO2" s="48"/>
+      <c r="IP2" s="48"/>
+      <c r="IQ2" s="48"/>
+      <c r="IR2" s="48"/>
+      <c r="IS2" s="48"/>
+      <c r="IT2" s="48"/>
+      <c r="IU2" s="48"/>
+      <c r="IV2" s="48"/>
+      <c r="IW2" s="48"/>
+      <c r="IX2" s="48"/>
+      <c r="IY2" s="48"/>
+      <c r="IZ2" s="48"/>
+      <c r="JA2" s="48"/>
+      <c r="JB2" s="48"/>
+      <c r="JC2" s="48"/>
+      <c r="JD2" s="48"/>
+      <c r="JE2" s="48"/>
+      <c r="JF2" s="48"/>
+      <c r="JG2" s="48"/>
+      <c r="JH2" s="48"/>
+      <c r="JI2" s="48"/>
+      <c r="JJ2" s="48"/>
+      <c r="JK2" s="48"/>
+      <c r="JL2" s="48"/>
+      <c r="JM2" s="48"/>
+      <c r="JN2" s="48"/>
+      <c r="JO2" s="48"/>
+      <c r="JP2" s="48"/>
+      <c r="JQ2" s="48"/>
+      <c r="JR2" s="48"/>
+      <c r="JS2" s="48"/>
+      <c r="JT2" s="48"/>
+      <c r="JU2" s="48"/>
+      <c r="JV2" s="48"/>
+      <c r="JW2" s="48"/>
+      <c r="JX2" s="48"/>
+      <c r="JY2" s="48"/>
+      <c r="JZ2" s="48"/>
+      <c r="KA2" s="48"/>
+      <c r="KB2" s="48"/>
+      <c r="KC2" s="48"/>
+      <c r="KD2" s="48"/>
+      <c r="KE2" s="48"/>
+      <c r="KF2" s="48"/>
+      <c r="KG2" s="48"/>
+      <c r="KH2" s="48"/>
+      <c r="KI2" s="48"/>
+      <c r="KJ2" s="48"/>
+      <c r="KK2" s="48"/>
+      <c r="KL2" s="48"/>
+      <c r="KM2" s="48"/>
+      <c r="KN2" s="48"/>
+      <c r="KO2" s="48"/>
+      <c r="KP2" s="48"/>
+      <c r="KQ2" s="48"/>
+      <c r="KR2" s="48"/>
+      <c r="KS2" s="48"/>
+      <c r="KT2" s="48"/>
+      <c r="KU2" s="48"/>
+      <c r="KV2" s="48"/>
+      <c r="KW2" s="48"/>
+      <c r="KX2" s="48"/>
+      <c r="KY2" s="48"/>
+      <c r="KZ2" s="48"/>
+      <c r="LA2" s="48"/>
+      <c r="LB2" s="48"/>
+      <c r="LC2" s="48"/>
+      <c r="LD2" s="48"/>
+      <c r="LE2" s="48"/>
+      <c r="LF2" s="48"/>
+      <c r="LG2" s="48"/>
+      <c r="LH2" s="48"/>
+      <c r="LI2" s="48"/>
+      <c r="LJ2" s="48"/>
+      <c r="LK2" s="48"/>
+      <c r="LL2" s="48"/>
+      <c r="LM2" s="48"/>
+      <c r="LN2" s="48"/>
+      <c r="LO2" s="48"/>
+      <c r="LP2" s="48"/>
+      <c r="LQ2" s="48"/>
+      <c r="LR2" s="48"/>
+      <c r="LS2" s="48"/>
+      <c r="LT2" s="48"/>
+      <c r="LU2" s="48"/>
+      <c r="LV2" s="48"/>
+      <c r="LW2" s="48"/>
+      <c r="LX2" s="48"/>
+      <c r="LY2" s="48"/>
+      <c r="LZ2" s="48"/>
+      <c r="MA2" s="48"/>
+      <c r="MB2" s="48"/>
+      <c r="MC2" s="48"/>
+      <c r="MD2" s="48"/>
+      <c r="ME2" s="48"/>
+      <c r="MF2" s="48"/>
+      <c r="MG2" s="48"/>
+      <c r="MH2" s="48"/>
+      <c r="MI2" s="48"/>
+      <c r="MJ2" s="48"/>
+      <c r="MK2" s="48"/>
+      <c r="ML2" s="48"/>
+      <c r="MM2" s="48"/>
+      <c r="MN2" s="48"/>
+      <c r="MO2" s="48"/>
+      <c r="MP2" s="48"/>
+      <c r="MQ2" s="48"/>
+      <c r="MR2" s="48"/>
+      <c r="MS2" s="48"/>
+      <c r="MT2" s="48"/>
+      <c r="MU2" s="48"/>
+      <c r="MV2" s="48"/>
+      <c r="MW2" s="48"/>
+      <c r="MX2" s="48"/>
+      <c r="MY2" s="48"/>
+      <c r="MZ2" s="48"/>
+      <c r="NA2" s="48"/>
+      <c r="NB2" s="48"/>
+      <c r="NC2" s="48"/>
+      <c r="ND2" s="48"/>
+      <c r="NE2" s="48"/>
+      <c r="NF2" s="48"/>
+      <c r="NG2" s="48"/>
+      <c r="NH2" s="48"/>
+      <c r="NI2" s="48"/>
+      <c r="NJ2" s="48"/>
+      <c r="NK2" s="48"/>
+      <c r="NL2" s="48"/>
+      <c r="NM2" s="48"/>
+      <c r="NN2" s="48"/>
+      <c r="NO2" s="48"/>
+      <c r="NP2" s="48"/>
+      <c r="NQ2" s="48"/>
+      <c r="NR2" s="48"/>
+      <c r="NS2" s="48"/>
+      <c r="NT2" s="48"/>
+      <c r="NU2" s="48"/>
+      <c r="NV2" s="48"/>
+      <c r="NW2" s="48"/>
+      <c r="NX2" s="48"/>
+      <c r="NY2" s="48"/>
+      <c r="NZ2" s="48"/>
+      <c r="OA2" s="48"/>
+      <c r="OB2" s="48"/>
+      <c r="OC2" s="48"/>
+      <c r="OD2" s="48"/>
+      <c r="OE2" s="48"/>
+      <c r="OF2" s="48"/>
+      <c r="OG2" s="48"/>
+      <c r="OH2" s="48"/>
+      <c r="OI2" s="48"/>
+      <c r="OJ2" s="48"/>
+      <c r="OK2" s="48"/>
+      <c r="OL2" s="48"/>
+      <c r="OM2" s="48"/>
+      <c r="ON2" s="48"/>
+      <c r="OO2" s="48"/>
+      <c r="OP2" s="48"/>
+      <c r="OQ2" s="48"/>
+      <c r="OR2" s="48"/>
+      <c r="OS2" s="48"/>
+      <c r="OT2" s="48"/>
+      <c r="OU2" s="48"/>
+      <c r="OV2" s="48"/>
+      <c r="OW2" s="48"/>
+      <c r="OX2" s="48"/>
+      <c r="OY2" s="48"/>
+      <c r="OZ2" s="48"/>
+      <c r="PA2" s="48"/>
+      <c r="PB2" s="48"/>
+      <c r="PC2" s="48"/>
+      <c r="PD2" s="48"/>
+      <c r="PE2" s="48"/>
+      <c r="PF2" s="48"/>
+      <c r="PG2" s="48"/>
+      <c r="PH2" s="48"/>
+      <c r="PI2" s="48"/>
+      <c r="PJ2" s="48"/>
+      <c r="PK2" s="48"/>
+      <c r="PL2" s="48"/>
+      <c r="PM2" s="48"/>
+      <c r="PN2" s="48"/>
+      <c r="PO2" s="48"/>
+      <c r="PP2" s="48"/>
+      <c r="PQ2" s="48"/>
+      <c r="PR2" s="48"/>
+      <c r="PS2" s="48"/>
+      <c r="PT2" s="48"/>
+      <c r="PU2" s="48"/>
+      <c r="PV2" s="48"/>
+      <c r="PW2" s="48"/>
+      <c r="PX2" s="48"/>
+      <c r="PY2" s="48"/>
+      <c r="PZ2" s="48"/>
+      <c r="QA2" s="48"/>
+      <c r="QB2" s="48"/>
+      <c r="QC2" s="48"/>
+      <c r="QD2" s="48"/>
+      <c r="QE2" s="48"/>
+      <c r="QF2" s="48"/>
+      <c r="QG2" s="48"/>
+      <c r="QH2" s="48"/>
+      <c r="QI2" s="48"/>
+      <c r="QJ2" s="48"/>
+      <c r="QK2" s="48"/>
+      <c r="QL2" s="48"/>
+      <c r="QM2" s="48"/>
+      <c r="QN2" s="48"/>
+      <c r="QO2" s="48"/>
+      <c r="QP2" s="48"/>
+      <c r="QQ2" s="48"/>
+      <c r="QR2" s="48"/>
+      <c r="QS2" s="48"/>
+      <c r="QT2" s="48"/>
+      <c r="QU2" s="48"/>
+      <c r="QV2" s="48"/>
+      <c r="QW2" s="48"/>
+      <c r="QX2" s="48"/>
+      <c r="QY2" s="48"/>
+      <c r="QZ2" s="48"/>
+      <c r="RA2" s="48"/>
+      <c r="RB2" s="48"/>
+      <c r="RC2" s="48"/>
+      <c r="RD2" s="48"/>
+      <c r="RE2" s="48"/>
+      <c r="RF2" s="48"/>
+      <c r="RG2" s="48"/>
+      <c r="RH2" s="48"/>
+      <c r="RI2" s="48"/>
+      <c r="RJ2" s="48"/>
+      <c r="RK2" s="48"/>
+      <c r="RL2" s="48"/>
+      <c r="RM2" s="48"/>
+      <c r="RN2" s="48"/>
+      <c r="RO2" s="48"/>
+      <c r="RP2" s="48"/>
+      <c r="RQ2" s="48"/>
+      <c r="RR2" s="48"/>
+      <c r="RS2" s="48"/>
+      <c r="RT2" s="48"/>
+      <c r="RU2" s="48"/>
+      <c r="RV2" s="48"/>
+      <c r="RW2" s="48"/>
+      <c r="RX2" s="48"/>
+      <c r="RY2" s="48"/>
+      <c r="RZ2" s="48"/>
+      <c r="SA2" s="48"/>
+      <c r="SB2" s="48"/>
+      <c r="SC2" s="48"/>
+      <c r="SD2" s="48"/>
+      <c r="SE2" s="48"/>
+      <c r="SF2" s="48"/>
+      <c r="SG2" s="48"/>
+      <c r="SH2" s="48"/>
+      <c r="SI2" s="48"/>
+      <c r="SJ2" s="48"/>
+      <c r="SK2" s="48"/>
+      <c r="SL2" s="48"/>
+      <c r="SM2" s="48"/>
+      <c r="SN2" s="48"/>
+      <c r="SO2" s="48"/>
+      <c r="SP2" s="48"/>
+      <c r="SQ2" s="48"/>
+      <c r="SR2" s="48"/>
+      <c r="SS2" s="48"/>
+      <c r="ST2" s="48"/>
+      <c r="SU2" s="48"/>
+      <c r="SV2" s="48"/>
+      <c r="SW2" s="48"/>
+      <c r="SX2" s="48"/>
+      <c r="SY2" s="48"/>
+      <c r="SZ2" s="48"/>
+      <c r="TA2" s="48"/>
+      <c r="TB2" s="48"/>
+      <c r="TC2" s="48"/>
+      <c r="TD2" s="48"/>
+      <c r="TE2" s="48"/>
+      <c r="TF2" s="48"/>
+      <c r="TG2" s="48"/>
+      <c r="TH2" s="48"/>
+      <c r="TI2" s="48"/>
+      <c r="TJ2" s="48"/>
+      <c r="TK2" s="48"/>
+      <c r="TL2" s="48"/>
+      <c r="TM2" s="48"/>
+      <c r="TN2" s="48"/>
+      <c r="TO2" s="48"/>
+      <c r="TP2" s="48"/>
+      <c r="TQ2" s="48"/>
+      <c r="TR2" s="48"/>
+      <c r="TS2" s="48"/>
+      <c r="TT2" s="48"/>
+      <c r="TU2" s="48"/>
+      <c r="TV2" s="48"/>
+      <c r="TW2" s="48"/>
+      <c r="TX2" s="48"/>
+      <c r="TY2" s="48"/>
+      <c r="TZ2" s="48"/>
+      <c r="UA2" s="48"/>
+      <c r="UB2" s="48"/>
+      <c r="UC2" s="48"/>
+      <c r="UD2" s="48"/>
+      <c r="UE2" s="48"/>
+      <c r="UF2" s="48"/>
+      <c r="UG2" s="48"/>
+      <c r="UH2" s="48"/>
+      <c r="UI2" s="48"/>
+      <c r="UJ2" s="48"/>
+      <c r="UK2" s="48"/>
+      <c r="UL2" s="48"/>
+      <c r="UM2" s="48"/>
+      <c r="UN2" s="48"/>
+      <c r="UO2" s="48"/>
+      <c r="UP2" s="48"/>
+      <c r="UQ2" s="48"/>
+      <c r="UR2" s="48"/>
+      <c r="US2" s="48"/>
+      <c r="UT2" s="48"/>
+      <c r="UU2" s="48"/>
+      <c r="UV2" s="48"/>
+      <c r="UW2" s="48"/>
+      <c r="UX2" s="48"/>
+      <c r="UY2" s="48"/>
+      <c r="UZ2" s="48"/>
+      <c r="VA2" s="48"/>
+      <c r="VB2" s="48"/>
+      <c r="VC2" s="48"/>
+      <c r="VD2" s="48"/>
+      <c r="VE2" s="48"/>
+      <c r="VF2" s="48"/>
+      <c r="VG2" s="48"/>
+      <c r="VH2" s="48"/>
+      <c r="VI2" s="48"/>
+      <c r="VJ2" s="48"/>
+      <c r="VK2" s="48"/>
+      <c r="VL2" s="48"/>
+      <c r="VM2" s="48"/>
+      <c r="VN2" s="48"/>
+      <c r="VO2" s="48"/>
+      <c r="VP2" s="48"/>
+      <c r="VQ2" s="48"/>
+      <c r="VR2" s="48"/>
+      <c r="VS2" s="48"/>
+      <c r="VT2" s="48"/>
+      <c r="VU2" s="48"/>
+      <c r="VV2" s="48"/>
+      <c r="VW2" s="48"/>
+      <c r="VX2" s="48"/>
+      <c r="VY2" s="48"/>
+      <c r="VZ2" s="48"/>
+      <c r="WA2" s="48"/>
+      <c r="WB2" s="48"/>
+      <c r="WC2" s="48"/>
+      <c r="WD2" s="48"/>
+      <c r="WE2" s="48"/>
+      <c r="WF2" s="48"/>
+      <c r="WG2" s="48"/>
+      <c r="WH2" s="48"/>
+      <c r="WI2" s="48"/>
+      <c r="WJ2" s="48"/>
+      <c r="WK2" s="48"/>
+      <c r="WL2" s="48"/>
+      <c r="WM2" s="48"/>
+      <c r="WN2" s="48"/>
+      <c r="WO2" s="48"/>
+      <c r="WP2" s="48"/>
+      <c r="WQ2" s="48"/>
+      <c r="WR2" s="48"/>
+      <c r="WS2" s="48"/>
+      <c r="WT2" s="48"/>
+      <c r="WU2" s="48"/>
+      <c r="WV2" s="48"/>
+      <c r="WW2" s="48"/>
+      <c r="WX2" s="48"/>
+      <c r="WY2" s="48"/>
+      <c r="WZ2" s="48"/>
+      <c r="XA2" s="48"/>
+      <c r="XB2" s="48"/>
+      <c r="XC2" s="48"/>
+      <c r="XD2" s="48"/>
+      <c r="XE2" s="48"/>
+      <c r="XF2" s="48"/>
+      <c r="XG2" s="48"/>
+      <c r="XH2" s="48"/>
+      <c r="XI2" s="48"/>
+      <c r="XJ2" s="48"/>
+      <c r="XK2" s="48"/>
+      <c r="XL2" s="48"/>
+      <c r="XM2" s="48"/>
+      <c r="XN2" s="48"/>
+      <c r="XO2" s="48"/>
+      <c r="XP2" s="48"/>
+      <c r="XQ2" s="48"/>
+      <c r="XR2" s="48"/>
+      <c r="XS2" s="48"/>
+      <c r="XT2" s="48"/>
+      <c r="XU2" s="48"/>
+      <c r="XV2" s="48"/>
+      <c r="XW2" s="48"/>
+      <c r="XX2" s="48"/>
+      <c r="XY2" s="48"/>
+      <c r="XZ2" s="48"/>
+      <c r="YA2" s="48"/>
+      <c r="YB2" s="48"/>
+      <c r="YC2" s="48"/>
+      <c r="YD2" s="48"/>
+      <c r="YE2" s="48"/>
+      <c r="YF2" s="48"/>
+      <c r="YG2" s="48"/>
+      <c r="YH2" s="48"/>
+      <c r="YI2" s="48"/>
+      <c r="YJ2" s="48"/>
+      <c r="YK2" s="48"/>
+      <c r="YL2" s="48"/>
+      <c r="YM2" s="48"/>
+      <c r="YN2" s="48"/>
+      <c r="YO2" s="48"/>
+      <c r="YP2" s="48"/>
+      <c r="YQ2" s="48"/>
+      <c r="YR2" s="48"/>
+      <c r="YS2" s="48"/>
+      <c r="YT2" s="48"/>
+      <c r="YU2" s="48"/>
+      <c r="YV2" s="48"/>
+      <c r="YW2" s="48"/>
+      <c r="YX2" s="48"/>
+      <c r="YY2" s="48"/>
+      <c r="YZ2" s="48"/>
     </row>
     <row r="3" spans="1:676" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="51" t="s">
+      <c r="D3" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="49" t="s">
+      <c r="E3" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="49"/>
-      <c r="L3" s="49"/>
-      <c r="M3" s="49"/>
-      <c r="N3" s="49"/>
-      <c r="O3" s="49"/>
-      <c r="P3" s="49"/>
-      <c r="Q3" s="49"/>
-      <c r="R3" s="49"/>
-      <c r="S3" s="49"/>
-      <c r="T3" s="49"/>
-      <c r="U3" s="49"/>
-      <c r="V3" s="49"/>
-      <c r="W3" s="49"/>
-      <c r="X3" s="49"/>
-      <c r="Y3" s="49"/>
-      <c r="Z3" s="49"/>
-      <c r="AA3" s="49"/>
-      <c r="AB3" s="49"/>
-      <c r="AC3" s="49"/>
-      <c r="AD3" s="49"/>
-      <c r="AE3" s="49"/>
-      <c r="AF3" s="49"/>
-      <c r="AG3" s="49"/>
-      <c r="AH3" s="49"/>
-      <c r="AI3" s="49"/>
-      <c r="AJ3" s="49"/>
-      <c r="AK3" s="49" t="s">
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="53"/>
+      <c r="N3" s="53"/>
+      <c r="O3" s="53"/>
+      <c r="P3" s="53"/>
+      <c r="Q3" s="53"/>
+      <c r="R3" s="53"/>
+      <c r="S3" s="53"/>
+      <c r="T3" s="53"/>
+      <c r="U3" s="53"/>
+      <c r="V3" s="53"/>
+      <c r="W3" s="53"/>
+      <c r="X3" s="53"/>
+      <c r="Y3" s="53"/>
+      <c r="Z3" s="53"/>
+      <c r="AA3" s="53"/>
+      <c r="AB3" s="53"/>
+      <c r="AC3" s="53"/>
+      <c r="AD3" s="53"/>
+      <c r="AE3" s="53"/>
+      <c r="AF3" s="53"/>
+      <c r="AG3" s="53"/>
+      <c r="AH3" s="53"/>
+      <c r="AI3" s="53"/>
+      <c r="AJ3" s="53"/>
+      <c r="AK3" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="AL3" s="49"/>
-      <c r="AM3" s="49"/>
-      <c r="AN3" s="49"/>
-      <c r="AO3" s="49"/>
-      <c r="AP3" s="49"/>
-      <c r="AQ3" s="49"/>
-      <c r="AR3" s="49"/>
-      <c r="AS3" s="49"/>
-      <c r="AT3" s="49"/>
-      <c r="AU3" s="49"/>
-      <c r="AV3" s="49"/>
-      <c r="AW3" s="49"/>
-      <c r="AX3" s="49"/>
-      <c r="AY3" s="49"/>
-      <c r="AZ3" s="49"/>
-      <c r="BA3" s="49"/>
-      <c r="BB3" s="49"/>
-      <c r="BC3" s="49"/>
-      <c r="BD3" s="49"/>
-      <c r="BE3" s="49"/>
-      <c r="BF3" s="49"/>
-      <c r="BG3" s="49"/>
-      <c r="BH3" s="49"/>
-      <c r="BI3" s="49"/>
-      <c r="BJ3" s="49"/>
-      <c r="BK3" s="49"/>
-      <c r="BL3" s="49"/>
-      <c r="BM3" s="49"/>
-      <c r="BN3" s="49"/>
-      <c r="BO3" s="49"/>
-      <c r="BP3" s="49"/>
-      <c r="BQ3" s="49" t="s">
+      <c r="AL3" s="53"/>
+      <c r="AM3" s="53"/>
+      <c r="AN3" s="53"/>
+      <c r="AO3" s="53"/>
+      <c r="AP3" s="53"/>
+      <c r="AQ3" s="53"/>
+      <c r="AR3" s="53"/>
+      <c r="AS3" s="53"/>
+      <c r="AT3" s="53"/>
+      <c r="AU3" s="53"/>
+      <c r="AV3" s="53"/>
+      <c r="AW3" s="53"/>
+      <c r="AX3" s="53"/>
+      <c r="AY3" s="53"/>
+      <c r="AZ3" s="53"/>
+      <c r="BA3" s="53"/>
+      <c r="BB3" s="53"/>
+      <c r="BC3" s="53"/>
+      <c r="BD3" s="53"/>
+      <c r="BE3" s="53"/>
+      <c r="BF3" s="53"/>
+      <c r="BG3" s="53"/>
+      <c r="BH3" s="53"/>
+      <c r="BI3" s="53"/>
+      <c r="BJ3" s="53"/>
+      <c r="BK3" s="53"/>
+      <c r="BL3" s="53"/>
+      <c r="BM3" s="53"/>
+      <c r="BN3" s="53"/>
+      <c r="BO3" s="53"/>
+      <c r="BP3" s="53"/>
+      <c r="BQ3" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="BR3" s="49"/>
-      <c r="BS3" s="49"/>
-      <c r="BT3" s="49"/>
-      <c r="BU3" s="49"/>
-      <c r="BV3" s="49"/>
-      <c r="BW3" s="49"/>
-      <c r="BX3" s="49"/>
-      <c r="BY3" s="49"/>
-      <c r="BZ3" s="49"/>
-      <c r="CA3" s="49"/>
-      <c r="CB3" s="49"/>
-      <c r="CC3" s="49"/>
-      <c r="CD3" s="49"/>
-      <c r="CE3" s="49"/>
-      <c r="CF3" s="49"/>
-      <c r="CG3" s="49"/>
-      <c r="CH3" s="49"/>
-      <c r="CI3" s="49"/>
-      <c r="CJ3" s="49"/>
-      <c r="CK3" s="49"/>
-      <c r="CL3" s="49"/>
-      <c r="CM3" s="49"/>
-      <c r="CN3" s="49"/>
-      <c r="CO3" s="49"/>
-      <c r="CP3" s="49"/>
-      <c r="CQ3" s="49"/>
-      <c r="CR3" s="49"/>
-      <c r="CS3" s="49"/>
-      <c r="CT3" s="49"/>
-      <c r="CU3" s="49"/>
-      <c r="CV3" s="49"/>
-      <c r="CW3" s="49" t="s">
+      <c r="BR3" s="53"/>
+      <c r="BS3" s="53"/>
+      <c r="BT3" s="53"/>
+      <c r="BU3" s="53"/>
+      <c r="BV3" s="53"/>
+      <c r="BW3" s="53"/>
+      <c r="BX3" s="53"/>
+      <c r="BY3" s="53"/>
+      <c r="BZ3" s="53"/>
+      <c r="CA3" s="53"/>
+      <c r="CB3" s="53"/>
+      <c r="CC3" s="53"/>
+      <c r="CD3" s="53"/>
+      <c r="CE3" s="53"/>
+      <c r="CF3" s="53"/>
+      <c r="CG3" s="53"/>
+      <c r="CH3" s="53"/>
+      <c r="CI3" s="53"/>
+      <c r="CJ3" s="53"/>
+      <c r="CK3" s="53"/>
+      <c r="CL3" s="53"/>
+      <c r="CM3" s="53"/>
+      <c r="CN3" s="53"/>
+      <c r="CO3" s="53"/>
+      <c r="CP3" s="53"/>
+      <c r="CQ3" s="53"/>
+      <c r="CR3" s="53"/>
+      <c r="CS3" s="53"/>
+      <c r="CT3" s="53"/>
+      <c r="CU3" s="53"/>
+      <c r="CV3" s="53"/>
+      <c r="CW3" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="CX3" s="49"/>
-      <c r="CY3" s="49"/>
-      <c r="CZ3" s="49"/>
-      <c r="DA3" s="49"/>
-      <c r="DB3" s="49"/>
-      <c r="DC3" s="49"/>
-      <c r="DD3" s="49"/>
-      <c r="DE3" s="49"/>
-      <c r="DF3" s="49"/>
-      <c r="DG3" s="49"/>
-      <c r="DH3" s="49"/>
-      <c r="DI3" s="49"/>
-      <c r="DJ3" s="49"/>
-      <c r="DK3" s="49"/>
-      <c r="DL3" s="49"/>
-      <c r="DM3" s="49"/>
-      <c r="DN3" s="49"/>
-      <c r="DO3" s="49"/>
-      <c r="DP3" s="49"/>
-      <c r="DQ3" s="49"/>
-      <c r="DR3" s="49"/>
-      <c r="DS3" s="49"/>
-      <c r="DT3" s="49"/>
-      <c r="DU3" s="49"/>
-      <c r="DV3" s="49"/>
-      <c r="DW3" s="49"/>
-      <c r="DX3" s="49"/>
-      <c r="DY3" s="49"/>
-      <c r="DZ3" s="49"/>
-      <c r="EA3" s="49"/>
-      <c r="EB3" s="49"/>
-      <c r="EC3" s="46" t="s">
+      <c r="CX3" s="53"/>
+      <c r="CY3" s="53"/>
+      <c r="CZ3" s="53"/>
+      <c r="DA3" s="53"/>
+      <c r="DB3" s="53"/>
+      <c r="DC3" s="53"/>
+      <c r="DD3" s="53"/>
+      <c r="DE3" s="53"/>
+      <c r="DF3" s="53"/>
+      <c r="DG3" s="53"/>
+      <c r="DH3" s="53"/>
+      <c r="DI3" s="53"/>
+      <c r="DJ3" s="53"/>
+      <c r="DK3" s="53"/>
+      <c r="DL3" s="53"/>
+      <c r="DM3" s="53"/>
+      <c r="DN3" s="53"/>
+      <c r="DO3" s="53"/>
+      <c r="DP3" s="53"/>
+      <c r="DQ3" s="53"/>
+      <c r="DR3" s="53"/>
+      <c r="DS3" s="53"/>
+      <c r="DT3" s="53"/>
+      <c r="DU3" s="53"/>
+      <c r="DV3" s="53"/>
+      <c r="DW3" s="53"/>
+      <c r="DX3" s="53"/>
+      <c r="DY3" s="53"/>
+      <c r="DZ3" s="53"/>
+      <c r="EA3" s="53"/>
+      <c r="EB3" s="53"/>
+      <c r="EC3" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="ED3" s="46"/>
-      <c r="EE3" s="46"/>
-      <c r="EF3" s="46"/>
-      <c r="EG3" s="46"/>
-      <c r="EH3" s="46"/>
-      <c r="EI3" s="46"/>
-      <c r="EJ3" s="46"/>
-      <c r="EK3" s="46"/>
-      <c r="EL3" s="46"/>
-      <c r="EM3" s="46"/>
-      <c r="EN3" s="46"/>
-      <c r="EO3" s="46"/>
-      <c r="EP3" s="46"/>
-      <c r="EQ3" s="46"/>
-      <c r="ER3" s="46"/>
-      <c r="ES3" s="46"/>
-      <c r="ET3" s="46"/>
-      <c r="EU3" s="46"/>
-      <c r="EV3" s="46"/>
-      <c r="EW3" s="46"/>
-      <c r="EX3" s="46"/>
-      <c r="EY3" s="46"/>
-      <c r="EZ3" s="46"/>
-      <c r="FA3" s="46"/>
-      <c r="FB3" s="46"/>
-      <c r="FC3" s="46"/>
-      <c r="FD3" s="46"/>
-      <c r="FE3" s="46"/>
-      <c r="FF3" s="46"/>
-      <c r="FG3" s="46"/>
-      <c r="FH3" s="46"/>
-      <c r="FI3" s="49" t="s">
+      <c r="ED3" s="54"/>
+      <c r="EE3" s="54"/>
+      <c r="EF3" s="54"/>
+      <c r="EG3" s="54"/>
+      <c r="EH3" s="54"/>
+      <c r="EI3" s="54"/>
+      <c r="EJ3" s="54"/>
+      <c r="EK3" s="54"/>
+      <c r="EL3" s="54"/>
+      <c r="EM3" s="54"/>
+      <c r="EN3" s="54"/>
+      <c r="EO3" s="54"/>
+      <c r="EP3" s="54"/>
+      <c r="EQ3" s="54"/>
+      <c r="ER3" s="54"/>
+      <c r="ES3" s="54"/>
+      <c r="ET3" s="54"/>
+      <c r="EU3" s="54"/>
+      <c r="EV3" s="54"/>
+      <c r="EW3" s="54"/>
+      <c r="EX3" s="54"/>
+      <c r="EY3" s="54"/>
+      <c r="EZ3" s="54"/>
+      <c r="FA3" s="54"/>
+      <c r="FB3" s="54"/>
+      <c r="FC3" s="54"/>
+      <c r="FD3" s="54"/>
+      <c r="FE3" s="54"/>
+      <c r="FF3" s="54"/>
+      <c r="FG3" s="54"/>
+      <c r="FH3" s="54"/>
+      <c r="FI3" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="FJ3" s="49"/>
-      <c r="FK3" s="49"/>
-      <c r="FL3" s="49"/>
-      <c r="FM3" s="49"/>
-      <c r="FN3" s="49"/>
-      <c r="FO3" s="49"/>
-      <c r="FP3" s="49"/>
-      <c r="FQ3" s="49"/>
-      <c r="FR3" s="49"/>
-      <c r="FS3" s="49"/>
-      <c r="FT3" s="49"/>
-      <c r="FU3" s="49"/>
-      <c r="FV3" s="49"/>
-      <c r="FW3" s="49"/>
-      <c r="FX3" s="49"/>
-      <c r="FY3" s="49"/>
-      <c r="FZ3" s="49"/>
-      <c r="GA3" s="49"/>
-      <c r="GB3" s="49"/>
-      <c r="GC3" s="49"/>
-      <c r="GD3" s="49"/>
-      <c r="GE3" s="49"/>
-      <c r="GF3" s="49"/>
-      <c r="GG3" s="49"/>
-      <c r="GH3" s="49"/>
-      <c r="GI3" s="49"/>
-      <c r="GJ3" s="49"/>
-      <c r="GK3" s="49"/>
-      <c r="GL3" s="49"/>
-      <c r="GM3" s="49"/>
-      <c r="GN3" s="49"/>
-      <c r="GO3" s="49" t="s">
+      <c r="FJ3" s="53"/>
+      <c r="FK3" s="53"/>
+      <c r="FL3" s="53"/>
+      <c r="FM3" s="53"/>
+      <c r="FN3" s="53"/>
+      <c r="FO3" s="53"/>
+      <c r="FP3" s="53"/>
+      <c r="FQ3" s="53"/>
+      <c r="FR3" s="53"/>
+      <c r="FS3" s="53"/>
+      <c r="FT3" s="53"/>
+      <c r="FU3" s="53"/>
+      <c r="FV3" s="53"/>
+      <c r="FW3" s="53"/>
+      <c r="FX3" s="53"/>
+      <c r="FY3" s="53"/>
+      <c r="FZ3" s="53"/>
+      <c r="GA3" s="53"/>
+      <c r="GB3" s="53"/>
+      <c r="GC3" s="53"/>
+      <c r="GD3" s="53"/>
+      <c r="GE3" s="53"/>
+      <c r="GF3" s="53"/>
+      <c r="GG3" s="53"/>
+      <c r="GH3" s="53"/>
+      <c r="GI3" s="53"/>
+      <c r="GJ3" s="53"/>
+      <c r="GK3" s="53"/>
+      <c r="GL3" s="53"/>
+      <c r="GM3" s="53"/>
+      <c r="GN3" s="53"/>
+      <c r="GO3" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="GP3" s="49"/>
-      <c r="GQ3" s="49"/>
-      <c r="GR3" s="49"/>
-      <c r="GS3" s="49"/>
-      <c r="GT3" s="49"/>
-      <c r="GU3" s="49"/>
-      <c r="GV3" s="49"/>
-      <c r="GW3" s="49"/>
-      <c r="GX3" s="49"/>
-      <c r="GY3" s="49"/>
-      <c r="GZ3" s="49"/>
-      <c r="HA3" s="49"/>
-      <c r="HB3" s="49"/>
-      <c r="HC3" s="49"/>
-      <c r="HD3" s="49"/>
-      <c r="HE3" s="49"/>
-      <c r="HF3" s="49"/>
-      <c r="HG3" s="49"/>
-      <c r="HH3" s="49"/>
-      <c r="HI3" s="49"/>
-      <c r="HJ3" s="49"/>
-      <c r="HK3" s="49"/>
-      <c r="HL3" s="49"/>
-      <c r="HM3" s="49"/>
-      <c r="HN3" s="49"/>
-      <c r="HO3" s="49"/>
-      <c r="HP3" s="49"/>
-      <c r="HQ3" s="49"/>
-      <c r="HR3" s="49"/>
-      <c r="HS3" s="49"/>
-      <c r="HT3" s="49"/>
-      <c r="HU3" s="49" t="s">
+      <c r="GP3" s="53"/>
+      <c r="GQ3" s="53"/>
+      <c r="GR3" s="53"/>
+      <c r="GS3" s="53"/>
+      <c r="GT3" s="53"/>
+      <c r="GU3" s="53"/>
+      <c r="GV3" s="53"/>
+      <c r="GW3" s="53"/>
+      <c r="GX3" s="53"/>
+      <c r="GY3" s="53"/>
+      <c r="GZ3" s="53"/>
+      <c r="HA3" s="53"/>
+      <c r="HB3" s="53"/>
+      <c r="HC3" s="53"/>
+      <c r="HD3" s="53"/>
+      <c r="HE3" s="53"/>
+      <c r="HF3" s="53"/>
+      <c r="HG3" s="53"/>
+      <c r="HH3" s="53"/>
+      <c r="HI3" s="53"/>
+      <c r="HJ3" s="53"/>
+      <c r="HK3" s="53"/>
+      <c r="HL3" s="53"/>
+      <c r="HM3" s="53"/>
+      <c r="HN3" s="53"/>
+      <c r="HO3" s="53"/>
+      <c r="HP3" s="53"/>
+      <c r="HQ3" s="53"/>
+      <c r="HR3" s="53"/>
+      <c r="HS3" s="53"/>
+      <c r="HT3" s="53"/>
+      <c r="HU3" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="HV3" s="49"/>
-      <c r="HW3" s="49"/>
-      <c r="HX3" s="49"/>
-      <c r="HY3" s="49"/>
-      <c r="HZ3" s="49"/>
-      <c r="IA3" s="49"/>
-      <c r="IB3" s="49"/>
-      <c r="IC3" s="49"/>
-      <c r="ID3" s="49"/>
-      <c r="IE3" s="49"/>
-      <c r="IF3" s="49"/>
-      <c r="IG3" s="49"/>
-      <c r="IH3" s="49"/>
-      <c r="II3" s="49"/>
-      <c r="IJ3" s="49"/>
-      <c r="IK3" s="49"/>
-      <c r="IL3" s="49"/>
-      <c r="IM3" s="49"/>
-      <c r="IN3" s="49"/>
-      <c r="IO3" s="49"/>
-      <c r="IP3" s="49"/>
-      <c r="IQ3" s="49"/>
-      <c r="IR3" s="49"/>
-      <c r="IS3" s="49"/>
-      <c r="IT3" s="49"/>
-      <c r="IU3" s="49"/>
-      <c r="IV3" s="49"/>
-      <c r="IW3" s="49"/>
-      <c r="IX3" s="49"/>
-      <c r="IY3" s="49"/>
-      <c r="IZ3" s="49"/>
-      <c r="JA3" s="49" t="s">
+      <c r="HV3" s="53"/>
+      <c r="HW3" s="53"/>
+      <c r="HX3" s="53"/>
+      <c r="HY3" s="53"/>
+      <c r="HZ3" s="53"/>
+      <c r="IA3" s="53"/>
+      <c r="IB3" s="53"/>
+      <c r="IC3" s="53"/>
+      <c r="ID3" s="53"/>
+      <c r="IE3" s="53"/>
+      <c r="IF3" s="53"/>
+      <c r="IG3" s="53"/>
+      <c r="IH3" s="53"/>
+      <c r="II3" s="53"/>
+      <c r="IJ3" s="53"/>
+      <c r="IK3" s="53"/>
+      <c r="IL3" s="53"/>
+      <c r="IM3" s="53"/>
+      <c r="IN3" s="53"/>
+      <c r="IO3" s="53"/>
+      <c r="IP3" s="53"/>
+      <c r="IQ3" s="53"/>
+      <c r="IR3" s="53"/>
+      <c r="IS3" s="53"/>
+      <c r="IT3" s="53"/>
+      <c r="IU3" s="53"/>
+      <c r="IV3" s="53"/>
+      <c r="IW3" s="53"/>
+      <c r="IX3" s="53"/>
+      <c r="IY3" s="53"/>
+      <c r="IZ3" s="53"/>
+      <c r="JA3" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="JB3" s="49"/>
-      <c r="JC3" s="49"/>
-      <c r="JD3" s="49"/>
-      <c r="JE3" s="49"/>
-      <c r="JF3" s="49"/>
-      <c r="JG3" s="49"/>
-      <c r="JH3" s="49"/>
-      <c r="JI3" s="49"/>
-      <c r="JJ3" s="49"/>
-      <c r="JK3" s="49"/>
-      <c r="JL3" s="49"/>
-      <c r="JM3" s="49"/>
-      <c r="JN3" s="49"/>
-      <c r="JO3" s="49"/>
-      <c r="JP3" s="49"/>
-      <c r="JQ3" s="49"/>
-      <c r="JR3" s="49"/>
-      <c r="JS3" s="49"/>
-      <c r="JT3" s="49"/>
-      <c r="JU3" s="49"/>
-      <c r="JV3" s="49"/>
-      <c r="JW3" s="49"/>
-      <c r="JX3" s="49"/>
-      <c r="JY3" s="49"/>
-      <c r="JZ3" s="49"/>
-      <c r="KA3" s="49"/>
-      <c r="KB3" s="49"/>
-      <c r="KC3" s="49"/>
-      <c r="KD3" s="49"/>
-      <c r="KE3" s="49"/>
-      <c r="KF3" s="49"/>
-      <c r="KG3" s="46" t="s">
+      <c r="JB3" s="53"/>
+      <c r="JC3" s="53"/>
+      <c r="JD3" s="53"/>
+      <c r="JE3" s="53"/>
+      <c r="JF3" s="53"/>
+      <c r="JG3" s="53"/>
+      <c r="JH3" s="53"/>
+      <c r="JI3" s="53"/>
+      <c r="JJ3" s="53"/>
+      <c r="JK3" s="53"/>
+      <c r="JL3" s="53"/>
+      <c r="JM3" s="53"/>
+      <c r="JN3" s="53"/>
+      <c r="JO3" s="53"/>
+      <c r="JP3" s="53"/>
+      <c r="JQ3" s="53"/>
+      <c r="JR3" s="53"/>
+      <c r="JS3" s="53"/>
+      <c r="JT3" s="53"/>
+      <c r="JU3" s="53"/>
+      <c r="JV3" s="53"/>
+      <c r="JW3" s="53"/>
+      <c r="JX3" s="53"/>
+      <c r="JY3" s="53"/>
+      <c r="JZ3" s="53"/>
+      <c r="KA3" s="53"/>
+      <c r="KB3" s="53"/>
+      <c r="KC3" s="53"/>
+      <c r="KD3" s="53"/>
+      <c r="KE3" s="53"/>
+      <c r="KF3" s="53"/>
+      <c r="KG3" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="KH3" s="46"/>
-      <c r="KI3" s="46"/>
-      <c r="KJ3" s="46"/>
-      <c r="KK3" s="46"/>
-      <c r="KL3" s="46"/>
-      <c r="KM3" s="46"/>
-      <c r="KN3" s="46"/>
-      <c r="KO3" s="46"/>
-      <c r="KP3" s="46"/>
-      <c r="KQ3" s="46"/>
-      <c r="KR3" s="46"/>
-      <c r="KS3" s="46"/>
-      <c r="KT3" s="46"/>
-      <c r="KU3" s="46"/>
-      <c r="KV3" s="46"/>
-      <c r="KW3" s="46"/>
-      <c r="KX3" s="46"/>
-      <c r="KY3" s="46"/>
-      <c r="KZ3" s="46"/>
-      <c r="LA3" s="46"/>
-      <c r="LB3" s="46"/>
-      <c r="LC3" s="46"/>
-      <c r="LD3" s="46"/>
-      <c r="LE3" s="46"/>
-      <c r="LF3" s="46"/>
-      <c r="LG3" s="46"/>
-      <c r="LH3" s="46"/>
-      <c r="LI3" s="46"/>
-      <c r="LJ3" s="46"/>
-      <c r="LK3" s="46"/>
-      <c r="LL3" s="46"/>
-      <c r="LM3" s="49" t="s">
+      <c r="KH3" s="54"/>
+      <c r="KI3" s="54"/>
+      <c r="KJ3" s="54"/>
+      <c r="KK3" s="54"/>
+      <c r="KL3" s="54"/>
+      <c r="KM3" s="54"/>
+      <c r="KN3" s="54"/>
+      <c r="KO3" s="54"/>
+      <c r="KP3" s="54"/>
+      <c r="KQ3" s="54"/>
+      <c r="KR3" s="54"/>
+      <c r="KS3" s="54"/>
+      <c r="KT3" s="54"/>
+      <c r="KU3" s="54"/>
+      <c r="KV3" s="54"/>
+      <c r="KW3" s="54"/>
+      <c r="KX3" s="54"/>
+      <c r="KY3" s="54"/>
+      <c r="KZ3" s="54"/>
+      <c r="LA3" s="54"/>
+      <c r="LB3" s="54"/>
+      <c r="LC3" s="54"/>
+      <c r="LD3" s="54"/>
+      <c r="LE3" s="54"/>
+      <c r="LF3" s="54"/>
+      <c r="LG3" s="54"/>
+      <c r="LH3" s="54"/>
+      <c r="LI3" s="54"/>
+      <c r="LJ3" s="54"/>
+      <c r="LK3" s="54"/>
+      <c r="LL3" s="54"/>
+      <c r="LM3" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="LN3" s="49"/>
-      <c r="LO3" s="49"/>
-      <c r="LP3" s="49"/>
-      <c r="LQ3" s="49"/>
-      <c r="LR3" s="49"/>
-      <c r="LS3" s="49"/>
-      <c r="LT3" s="49"/>
-      <c r="LU3" s="49"/>
-      <c r="LV3" s="49"/>
-      <c r="LW3" s="49"/>
-      <c r="LX3" s="49"/>
-      <c r="LY3" s="49"/>
-      <c r="LZ3" s="49"/>
-      <c r="MA3" s="49"/>
-      <c r="MB3" s="49"/>
-      <c r="MC3" s="49"/>
-      <c r="MD3" s="49"/>
-      <c r="ME3" s="49"/>
-      <c r="MF3" s="49"/>
-      <c r="MG3" s="49"/>
-      <c r="MH3" s="49"/>
-      <c r="MI3" s="49"/>
-      <c r="MJ3" s="49"/>
-      <c r="MK3" s="49"/>
-      <c r="ML3" s="49"/>
-      <c r="MM3" s="49"/>
-      <c r="MN3" s="49"/>
-      <c r="MO3" s="49"/>
-      <c r="MP3" s="49"/>
-      <c r="MQ3" s="49"/>
-      <c r="MR3" s="49"/>
-      <c r="MS3" s="49" t="s">
+      <c r="LN3" s="53"/>
+      <c r="LO3" s="53"/>
+      <c r="LP3" s="53"/>
+      <c r="LQ3" s="53"/>
+      <c r="LR3" s="53"/>
+      <c r="LS3" s="53"/>
+      <c r="LT3" s="53"/>
+      <c r="LU3" s="53"/>
+      <c r="LV3" s="53"/>
+      <c r="LW3" s="53"/>
+      <c r="LX3" s="53"/>
+      <c r="LY3" s="53"/>
+      <c r="LZ3" s="53"/>
+      <c r="MA3" s="53"/>
+      <c r="MB3" s="53"/>
+      <c r="MC3" s="53"/>
+      <c r="MD3" s="53"/>
+      <c r="ME3" s="53"/>
+      <c r="MF3" s="53"/>
+      <c r="MG3" s="53"/>
+      <c r="MH3" s="53"/>
+      <c r="MI3" s="53"/>
+      <c r="MJ3" s="53"/>
+      <c r="MK3" s="53"/>
+      <c r="ML3" s="53"/>
+      <c r="MM3" s="53"/>
+      <c r="MN3" s="53"/>
+      <c r="MO3" s="53"/>
+      <c r="MP3" s="53"/>
+      <c r="MQ3" s="53"/>
+      <c r="MR3" s="53"/>
+      <c r="MS3" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="MT3" s="49"/>
-      <c r="MU3" s="49"/>
-      <c r="MV3" s="49"/>
-      <c r="MW3" s="49"/>
-      <c r="MX3" s="49"/>
-      <c r="MY3" s="49"/>
-      <c r="MZ3" s="49"/>
-      <c r="NA3" s="49"/>
-      <c r="NB3" s="49"/>
-      <c r="NC3" s="49"/>
-      <c r="ND3" s="49"/>
-      <c r="NE3" s="49"/>
-      <c r="NF3" s="49"/>
-      <c r="NG3" s="49"/>
-      <c r="NH3" s="49"/>
-      <c r="NI3" s="49"/>
-      <c r="NJ3" s="49"/>
-      <c r="NK3" s="49"/>
-      <c r="NL3" s="49"/>
-      <c r="NM3" s="49"/>
-      <c r="NN3" s="49"/>
-      <c r="NO3" s="49"/>
-      <c r="NP3" s="49"/>
-      <c r="NQ3" s="49"/>
-      <c r="NR3" s="49"/>
-      <c r="NS3" s="49"/>
-      <c r="NT3" s="49"/>
-      <c r="NU3" s="49"/>
-      <c r="NV3" s="49"/>
-      <c r="NW3" s="49"/>
-      <c r="NX3" s="49"/>
-      <c r="NY3" s="49" t="s">
+      <c r="MT3" s="53"/>
+      <c r="MU3" s="53"/>
+      <c r="MV3" s="53"/>
+      <c r="MW3" s="53"/>
+      <c r="MX3" s="53"/>
+      <c r="MY3" s="53"/>
+      <c r="MZ3" s="53"/>
+      <c r="NA3" s="53"/>
+      <c r="NB3" s="53"/>
+      <c r="NC3" s="53"/>
+      <c r="ND3" s="53"/>
+      <c r="NE3" s="53"/>
+      <c r="NF3" s="53"/>
+      <c r="NG3" s="53"/>
+      <c r="NH3" s="53"/>
+      <c r="NI3" s="53"/>
+      <c r="NJ3" s="53"/>
+      <c r="NK3" s="53"/>
+      <c r="NL3" s="53"/>
+      <c r="NM3" s="53"/>
+      <c r="NN3" s="53"/>
+      <c r="NO3" s="53"/>
+      <c r="NP3" s="53"/>
+      <c r="NQ3" s="53"/>
+      <c r="NR3" s="53"/>
+      <c r="NS3" s="53"/>
+      <c r="NT3" s="53"/>
+      <c r="NU3" s="53"/>
+      <c r="NV3" s="53"/>
+      <c r="NW3" s="53"/>
+      <c r="NX3" s="53"/>
+      <c r="NY3" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="NZ3" s="49"/>
-      <c r="OA3" s="49"/>
-      <c r="OB3" s="49"/>
-      <c r="OC3" s="49"/>
-      <c r="OD3" s="49"/>
-      <c r="OE3" s="49"/>
-      <c r="OF3" s="49"/>
-      <c r="OG3" s="49"/>
-      <c r="OH3" s="49"/>
-      <c r="OI3" s="49"/>
-      <c r="OJ3" s="49"/>
-      <c r="OK3" s="49"/>
-      <c r="OL3" s="49"/>
-      <c r="OM3" s="49"/>
-      <c r="ON3" s="49"/>
-      <c r="OO3" s="49"/>
-      <c r="OP3" s="49"/>
-      <c r="OQ3" s="49"/>
-      <c r="OR3" s="49"/>
-      <c r="OS3" s="49"/>
-      <c r="OT3" s="49"/>
-      <c r="OU3" s="49"/>
-      <c r="OV3" s="49"/>
-      <c r="OW3" s="49"/>
-      <c r="OX3" s="49"/>
-      <c r="OY3" s="49"/>
-      <c r="OZ3" s="49"/>
-      <c r="PA3" s="49"/>
-      <c r="PB3" s="49"/>
-      <c r="PC3" s="49"/>
-      <c r="PD3" s="49"/>
-      <c r="PE3" s="49" t="s">
+      <c r="NZ3" s="53"/>
+      <c r="OA3" s="53"/>
+      <c r="OB3" s="53"/>
+      <c r="OC3" s="53"/>
+      <c r="OD3" s="53"/>
+      <c r="OE3" s="53"/>
+      <c r="OF3" s="53"/>
+      <c r="OG3" s="53"/>
+      <c r="OH3" s="53"/>
+      <c r="OI3" s="53"/>
+      <c r="OJ3" s="53"/>
+      <c r="OK3" s="53"/>
+      <c r="OL3" s="53"/>
+      <c r="OM3" s="53"/>
+      <c r="ON3" s="53"/>
+      <c r="OO3" s="53"/>
+      <c r="OP3" s="53"/>
+      <c r="OQ3" s="53"/>
+      <c r="OR3" s="53"/>
+      <c r="OS3" s="53"/>
+      <c r="OT3" s="53"/>
+      <c r="OU3" s="53"/>
+      <c r="OV3" s="53"/>
+      <c r="OW3" s="53"/>
+      <c r="OX3" s="53"/>
+      <c r="OY3" s="53"/>
+      <c r="OZ3" s="53"/>
+      <c r="PA3" s="53"/>
+      <c r="PB3" s="53"/>
+      <c r="PC3" s="53"/>
+      <c r="PD3" s="53"/>
+      <c r="PE3" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="PF3" s="49"/>
-      <c r="PG3" s="49"/>
-      <c r="PH3" s="49"/>
-      <c r="PI3" s="49"/>
-      <c r="PJ3" s="49"/>
-      <c r="PK3" s="49"/>
-      <c r="PL3" s="49"/>
-      <c r="PM3" s="49"/>
-      <c r="PN3" s="49"/>
-      <c r="PO3" s="49"/>
-      <c r="PP3" s="49"/>
-      <c r="PQ3" s="49"/>
-      <c r="PR3" s="49"/>
-      <c r="PS3" s="49"/>
-      <c r="PT3" s="49"/>
-      <c r="PU3" s="49"/>
-      <c r="PV3" s="49"/>
-      <c r="PW3" s="49"/>
-      <c r="PX3" s="49"/>
-      <c r="PY3" s="49"/>
-      <c r="PZ3" s="49"/>
-      <c r="QA3" s="49"/>
-      <c r="QB3" s="49"/>
-      <c r="QC3" s="49"/>
-      <c r="QD3" s="49"/>
-      <c r="QE3" s="49"/>
-      <c r="QF3" s="49"/>
-      <c r="QG3" s="49"/>
-      <c r="QH3" s="49"/>
-      <c r="QI3" s="49"/>
-      <c r="QJ3" s="49"/>
-      <c r="QK3" s="46" t="s">
+      <c r="PF3" s="53"/>
+      <c r="PG3" s="53"/>
+      <c r="PH3" s="53"/>
+      <c r="PI3" s="53"/>
+      <c r="PJ3" s="53"/>
+      <c r="PK3" s="53"/>
+      <c r="PL3" s="53"/>
+      <c r="PM3" s="53"/>
+      <c r="PN3" s="53"/>
+      <c r="PO3" s="53"/>
+      <c r="PP3" s="53"/>
+      <c r="PQ3" s="53"/>
+      <c r="PR3" s="53"/>
+      <c r="PS3" s="53"/>
+      <c r="PT3" s="53"/>
+      <c r="PU3" s="53"/>
+      <c r="PV3" s="53"/>
+      <c r="PW3" s="53"/>
+      <c r="PX3" s="53"/>
+      <c r="PY3" s="53"/>
+      <c r="PZ3" s="53"/>
+      <c r="QA3" s="53"/>
+      <c r="QB3" s="53"/>
+      <c r="QC3" s="53"/>
+      <c r="QD3" s="53"/>
+      <c r="QE3" s="53"/>
+      <c r="QF3" s="53"/>
+      <c r="QG3" s="53"/>
+      <c r="QH3" s="53"/>
+      <c r="QI3" s="53"/>
+      <c r="QJ3" s="53"/>
+      <c r="QK3" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="QL3" s="46"/>
-      <c r="QM3" s="46"/>
-      <c r="QN3" s="46"/>
-      <c r="QO3" s="46"/>
-      <c r="QP3" s="46"/>
-      <c r="QQ3" s="46"/>
-      <c r="QR3" s="46"/>
-      <c r="QS3" s="46"/>
-      <c r="QT3" s="46"/>
-      <c r="QU3" s="46"/>
-      <c r="QV3" s="46"/>
-      <c r="QW3" s="46"/>
-      <c r="QX3" s="46"/>
-      <c r="QY3" s="46"/>
-      <c r="QZ3" s="46"/>
-      <c r="RA3" s="46"/>
-      <c r="RB3" s="46"/>
-      <c r="RC3" s="46"/>
-      <c r="RD3" s="46"/>
-      <c r="RE3" s="46"/>
-      <c r="RF3" s="46"/>
-      <c r="RG3" s="46"/>
-      <c r="RH3" s="46"/>
-      <c r="RI3" s="46"/>
-      <c r="RJ3" s="46"/>
-      <c r="RK3" s="46"/>
-      <c r="RL3" s="46"/>
-      <c r="RM3" s="46"/>
-      <c r="RN3" s="46"/>
-      <c r="RO3" s="46"/>
-      <c r="RP3" s="46"/>
-      <c r="RQ3" s="47" t="s">
+      <c r="QL3" s="54"/>
+      <c r="QM3" s="54"/>
+      <c r="QN3" s="54"/>
+      <c r="QO3" s="54"/>
+      <c r="QP3" s="54"/>
+      <c r="QQ3" s="54"/>
+      <c r="QR3" s="54"/>
+      <c r="QS3" s="54"/>
+      <c r="QT3" s="54"/>
+      <c r="QU3" s="54"/>
+      <c r="QV3" s="54"/>
+      <c r="QW3" s="54"/>
+      <c r="QX3" s="54"/>
+      <c r="QY3" s="54"/>
+      <c r="QZ3" s="54"/>
+      <c r="RA3" s="54"/>
+      <c r="RB3" s="54"/>
+      <c r="RC3" s="54"/>
+      <c r="RD3" s="54"/>
+      <c r="RE3" s="54"/>
+      <c r="RF3" s="54"/>
+      <c r="RG3" s="54"/>
+      <c r="RH3" s="54"/>
+      <c r="RI3" s="54"/>
+      <c r="RJ3" s="54"/>
+      <c r="RK3" s="54"/>
+      <c r="RL3" s="54"/>
+      <c r="RM3" s="54"/>
+      <c r="RN3" s="54"/>
+      <c r="RO3" s="54"/>
+      <c r="RP3" s="54"/>
+      <c r="RQ3" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="RR3" s="47"/>
-      <c r="RS3" s="47"/>
-      <c r="RT3" s="47"/>
-      <c r="RU3" s="47"/>
-      <c r="RV3" s="47"/>
-      <c r="RW3" s="47"/>
-      <c r="RX3" s="47"/>
-      <c r="RY3" s="47"/>
-      <c r="RZ3" s="47"/>
-      <c r="SA3" s="47"/>
-      <c r="SB3" s="47"/>
-      <c r="SC3" s="47"/>
-      <c r="SD3" s="47"/>
-      <c r="SE3" s="47"/>
-      <c r="SF3" s="47"/>
-      <c r="SG3" s="47"/>
-      <c r="SH3" s="47"/>
-      <c r="SI3" s="47"/>
-      <c r="SJ3" s="47"/>
-      <c r="SK3" s="47"/>
-      <c r="SL3" s="47"/>
-      <c r="SM3" s="47"/>
-      <c r="SN3" s="47"/>
-      <c r="SO3" s="47"/>
-      <c r="SP3" s="47"/>
-      <c r="SQ3" s="47"/>
-      <c r="SR3" s="47"/>
-      <c r="SS3" s="47"/>
-      <c r="ST3" s="47"/>
-      <c r="SU3" s="47"/>
-      <c r="SV3" s="47"/>
-      <c r="SW3" s="47" t="s">
+      <c r="RR3" s="52"/>
+      <c r="RS3" s="52"/>
+      <c r="RT3" s="52"/>
+      <c r="RU3" s="52"/>
+      <c r="RV3" s="52"/>
+      <c r="RW3" s="52"/>
+      <c r="RX3" s="52"/>
+      <c r="RY3" s="52"/>
+      <c r="RZ3" s="52"/>
+      <c r="SA3" s="52"/>
+      <c r="SB3" s="52"/>
+      <c r="SC3" s="52"/>
+      <c r="SD3" s="52"/>
+      <c r="SE3" s="52"/>
+      <c r="SF3" s="52"/>
+      <c r="SG3" s="52"/>
+      <c r="SH3" s="52"/>
+      <c r="SI3" s="52"/>
+      <c r="SJ3" s="52"/>
+      <c r="SK3" s="52"/>
+      <c r="SL3" s="52"/>
+      <c r="SM3" s="52"/>
+      <c r="SN3" s="52"/>
+      <c r="SO3" s="52"/>
+      <c r="SP3" s="52"/>
+      <c r="SQ3" s="52"/>
+      <c r="SR3" s="52"/>
+      <c r="SS3" s="52"/>
+      <c r="ST3" s="52"/>
+      <c r="SU3" s="52"/>
+      <c r="SV3" s="52"/>
+      <c r="SW3" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="SX3" s="47"/>
-      <c r="SY3" s="47"/>
-      <c r="SZ3" s="47"/>
-      <c r="TA3" s="47"/>
-      <c r="TB3" s="47"/>
-      <c r="TC3" s="47"/>
-      <c r="TD3" s="47"/>
-      <c r="TE3" s="47"/>
-      <c r="TF3" s="47"/>
-      <c r="TG3" s="47"/>
-      <c r="TH3" s="47"/>
-      <c r="TI3" s="47"/>
-      <c r="TJ3" s="47"/>
-      <c r="TK3" s="47"/>
-      <c r="TL3" s="47"/>
-      <c r="TM3" s="47"/>
-      <c r="TN3" s="47"/>
-      <c r="TO3" s="47"/>
-      <c r="TP3" s="47"/>
-      <c r="TQ3" s="47"/>
-      <c r="TR3" s="47"/>
-      <c r="TS3" s="47"/>
-      <c r="TT3" s="47"/>
-      <c r="TU3" s="47"/>
-      <c r="TV3" s="47"/>
-      <c r="TW3" s="47"/>
-      <c r="TX3" s="47"/>
-      <c r="TY3" s="47"/>
-      <c r="TZ3" s="47"/>
-      <c r="UA3" s="47"/>
-      <c r="UB3" s="47"/>
-      <c r="UC3" s="49" t="s">
+      <c r="SX3" s="52"/>
+      <c r="SY3" s="52"/>
+      <c r="SZ3" s="52"/>
+      <c r="TA3" s="52"/>
+      <c r="TB3" s="52"/>
+      <c r="TC3" s="52"/>
+      <c r="TD3" s="52"/>
+      <c r="TE3" s="52"/>
+      <c r="TF3" s="52"/>
+      <c r="TG3" s="52"/>
+      <c r="TH3" s="52"/>
+      <c r="TI3" s="52"/>
+      <c r="TJ3" s="52"/>
+      <c r="TK3" s="52"/>
+      <c r="TL3" s="52"/>
+      <c r="TM3" s="52"/>
+      <c r="TN3" s="52"/>
+      <c r="TO3" s="52"/>
+      <c r="TP3" s="52"/>
+      <c r="TQ3" s="52"/>
+      <c r="TR3" s="52"/>
+      <c r="TS3" s="52"/>
+      <c r="TT3" s="52"/>
+      <c r="TU3" s="52"/>
+      <c r="TV3" s="52"/>
+      <c r="TW3" s="52"/>
+      <c r="TX3" s="52"/>
+      <c r="TY3" s="52"/>
+      <c r="TZ3" s="52"/>
+      <c r="UA3" s="52"/>
+      <c r="UB3" s="52"/>
+      <c r="UC3" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="UD3" s="49"/>
-      <c r="UE3" s="49"/>
-      <c r="UF3" s="49"/>
-      <c r="UG3" s="49"/>
-      <c r="UH3" s="49"/>
-      <c r="UI3" s="49"/>
-      <c r="UJ3" s="49"/>
-      <c r="UK3" s="49"/>
-      <c r="UL3" s="49"/>
-      <c r="UM3" s="49"/>
-      <c r="UN3" s="49"/>
-      <c r="UO3" s="49"/>
-      <c r="UP3" s="49"/>
-      <c r="UQ3" s="49"/>
-      <c r="UR3" s="49"/>
-      <c r="US3" s="49"/>
-      <c r="UT3" s="49"/>
-      <c r="UU3" s="49"/>
-      <c r="UV3" s="49"/>
-      <c r="UW3" s="49"/>
-      <c r="UX3" s="49"/>
-      <c r="UY3" s="49"/>
-      <c r="UZ3" s="49"/>
-      <c r="VA3" s="49"/>
-      <c r="VB3" s="49"/>
-      <c r="VC3" s="49"/>
-      <c r="VD3" s="49"/>
-      <c r="VE3" s="49"/>
-      <c r="VF3" s="49"/>
-      <c r="VG3" s="49"/>
-      <c r="VH3" s="49"/>
-      <c r="VI3" s="49" t="s">
+      <c r="UD3" s="53"/>
+      <c r="UE3" s="53"/>
+      <c r="UF3" s="53"/>
+      <c r="UG3" s="53"/>
+      <c r="UH3" s="53"/>
+      <c r="UI3" s="53"/>
+      <c r="UJ3" s="53"/>
+      <c r="UK3" s="53"/>
+      <c r="UL3" s="53"/>
+      <c r="UM3" s="53"/>
+      <c r="UN3" s="53"/>
+      <c r="UO3" s="53"/>
+      <c r="UP3" s="53"/>
+      <c r="UQ3" s="53"/>
+      <c r="UR3" s="53"/>
+      <c r="US3" s="53"/>
+      <c r="UT3" s="53"/>
+      <c r="UU3" s="53"/>
+      <c r="UV3" s="53"/>
+      <c r="UW3" s="53"/>
+      <c r="UX3" s="53"/>
+      <c r="UY3" s="53"/>
+      <c r="UZ3" s="53"/>
+      <c r="VA3" s="53"/>
+      <c r="VB3" s="53"/>
+      <c r="VC3" s="53"/>
+      <c r="VD3" s="53"/>
+      <c r="VE3" s="53"/>
+      <c r="VF3" s="53"/>
+      <c r="VG3" s="53"/>
+      <c r="VH3" s="53"/>
+      <c r="VI3" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="VJ3" s="49"/>
-      <c r="VK3" s="49"/>
-      <c r="VL3" s="49"/>
-      <c r="VM3" s="49"/>
-      <c r="VN3" s="49"/>
-      <c r="VO3" s="49"/>
-      <c r="VP3" s="49"/>
-      <c r="VQ3" s="49"/>
-      <c r="VR3" s="49"/>
-      <c r="VS3" s="49"/>
-      <c r="VT3" s="49"/>
-      <c r="VU3" s="49"/>
-      <c r="VV3" s="49"/>
-      <c r="VW3" s="49"/>
-      <c r="VX3" s="49"/>
-      <c r="VY3" s="49"/>
-      <c r="VZ3" s="49"/>
-      <c r="WA3" s="49"/>
-      <c r="WB3" s="49"/>
-      <c r="WC3" s="49"/>
-      <c r="WD3" s="49"/>
-      <c r="WE3" s="49"/>
-      <c r="WF3" s="49"/>
-      <c r="WG3" s="49"/>
-      <c r="WH3" s="49"/>
-      <c r="WI3" s="49"/>
-      <c r="WJ3" s="49"/>
-      <c r="WK3" s="49"/>
-      <c r="WL3" s="49"/>
-      <c r="WM3" s="49"/>
-      <c r="WN3" s="49"/>
-      <c r="WO3" s="46" t="s">
+      <c r="VJ3" s="53"/>
+      <c r="VK3" s="53"/>
+      <c r="VL3" s="53"/>
+      <c r="VM3" s="53"/>
+      <c r="VN3" s="53"/>
+      <c r="VO3" s="53"/>
+      <c r="VP3" s="53"/>
+      <c r="VQ3" s="53"/>
+      <c r="VR3" s="53"/>
+      <c r="VS3" s="53"/>
+      <c r="VT3" s="53"/>
+      <c r="VU3" s="53"/>
+      <c r="VV3" s="53"/>
+      <c r="VW3" s="53"/>
+      <c r="VX3" s="53"/>
+      <c r="VY3" s="53"/>
+      <c r="VZ3" s="53"/>
+      <c r="WA3" s="53"/>
+      <c r="WB3" s="53"/>
+      <c r="WC3" s="53"/>
+      <c r="WD3" s="53"/>
+      <c r="WE3" s="53"/>
+      <c r="WF3" s="53"/>
+      <c r="WG3" s="53"/>
+      <c r="WH3" s="53"/>
+      <c r="WI3" s="53"/>
+      <c r="WJ3" s="53"/>
+      <c r="WK3" s="53"/>
+      <c r="WL3" s="53"/>
+      <c r="WM3" s="53"/>
+      <c r="WN3" s="53"/>
+      <c r="WO3" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="WP3" s="46"/>
-      <c r="WQ3" s="46"/>
-      <c r="WR3" s="46"/>
-      <c r="WS3" s="46"/>
-      <c r="WT3" s="46"/>
-      <c r="WU3" s="46"/>
-      <c r="WV3" s="46"/>
-      <c r="WW3" s="46"/>
-      <c r="WX3" s="46"/>
-      <c r="WY3" s="46"/>
-      <c r="WZ3" s="46"/>
-      <c r="XA3" s="46"/>
-      <c r="XB3" s="46"/>
-      <c r="XC3" s="46"/>
-      <c r="XD3" s="46"/>
-      <c r="XE3" s="46"/>
-      <c r="XF3" s="46"/>
-      <c r="XG3" s="46"/>
-      <c r="XH3" s="46"/>
-      <c r="XI3" s="46"/>
-      <c r="XJ3" s="46"/>
-      <c r="XK3" s="46"/>
-      <c r="XL3" s="46"/>
-      <c r="XM3" s="46"/>
-      <c r="XN3" s="46"/>
-      <c r="XO3" s="46"/>
-      <c r="XP3" s="46"/>
-      <c r="XQ3" s="46"/>
-      <c r="XR3" s="46"/>
-      <c r="XS3" s="46"/>
-      <c r="XT3" s="46"/>
-      <c r="XU3" s="49" t="s">
+      <c r="WP3" s="54"/>
+      <c r="WQ3" s="54"/>
+      <c r="WR3" s="54"/>
+      <c r="WS3" s="54"/>
+      <c r="WT3" s="54"/>
+      <c r="WU3" s="54"/>
+      <c r="WV3" s="54"/>
+      <c r="WW3" s="54"/>
+      <c r="WX3" s="54"/>
+      <c r="WY3" s="54"/>
+      <c r="WZ3" s="54"/>
+      <c r="XA3" s="54"/>
+      <c r="XB3" s="54"/>
+      <c r="XC3" s="54"/>
+      <c r="XD3" s="54"/>
+      <c r="XE3" s="54"/>
+      <c r="XF3" s="54"/>
+      <c r="XG3" s="54"/>
+      <c r="XH3" s="54"/>
+      <c r="XI3" s="54"/>
+      <c r="XJ3" s="54"/>
+      <c r="XK3" s="54"/>
+      <c r="XL3" s="54"/>
+      <c r="XM3" s="54"/>
+      <c r="XN3" s="54"/>
+      <c r="XO3" s="54"/>
+      <c r="XP3" s="54"/>
+      <c r="XQ3" s="54"/>
+      <c r="XR3" s="54"/>
+      <c r="XS3" s="54"/>
+      <c r="XT3" s="54"/>
+      <c r="XU3" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="XV3" s="49"/>
-      <c r="XW3" s="49"/>
-      <c r="XX3" s="49"/>
-      <c r="XY3" s="49"/>
-      <c r="XZ3" s="49"/>
-      <c r="YA3" s="49"/>
-      <c r="YB3" s="49"/>
-      <c r="YC3" s="49"/>
-      <c r="YD3" s="49"/>
-      <c r="YE3" s="49"/>
-      <c r="YF3" s="49"/>
-      <c r="YG3" s="49"/>
-      <c r="YH3" s="49"/>
-      <c r="YI3" s="49"/>
-      <c r="YJ3" s="49"/>
-      <c r="YK3" s="49"/>
-      <c r="YL3" s="49"/>
-      <c r="YM3" s="49"/>
-      <c r="YN3" s="49"/>
-      <c r="YO3" s="49"/>
-      <c r="YP3" s="49"/>
-      <c r="YQ3" s="49"/>
-      <c r="YR3" s="49"/>
-      <c r="YS3" s="49"/>
-      <c r="YT3" s="49"/>
-      <c r="YU3" s="49"/>
-      <c r="YV3" s="49"/>
-      <c r="YW3" s="49"/>
-      <c r="YX3" s="49"/>
-      <c r="YY3" s="49"/>
-      <c r="YZ3" s="49"/>
+      <c r="XV3" s="53"/>
+      <c r="XW3" s="53"/>
+      <c r="XX3" s="53"/>
+      <c r="XY3" s="53"/>
+      <c r="XZ3" s="53"/>
+      <c r="YA3" s="53"/>
+      <c r="YB3" s="53"/>
+      <c r="YC3" s="53"/>
+      <c r="YD3" s="53"/>
+      <c r="YE3" s="53"/>
+      <c r="YF3" s="53"/>
+      <c r="YG3" s="53"/>
+      <c r="YH3" s="53"/>
+      <c r="YI3" s="53"/>
+      <c r="YJ3" s="53"/>
+      <c r="YK3" s="53"/>
+      <c r="YL3" s="53"/>
+      <c r="YM3" s="53"/>
+      <c r="YN3" s="53"/>
+      <c r="YO3" s="53"/>
+      <c r="YP3" s="53"/>
+      <c r="YQ3" s="53"/>
+      <c r="YR3" s="53"/>
+      <c r="YS3" s="53"/>
+      <c r="YT3" s="53"/>
+      <c r="YU3" s="53"/>
+      <c r="YV3" s="53"/>
+      <c r="YW3" s="53"/>
+      <c r="YX3" s="53"/>
+      <c r="YY3" s="53"/>
+      <c r="YZ3" s="53"/>
     </row>
     <row r="4" spans="1:676" x14ac:dyDescent="0.25">
-      <c r="A4" s="51"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="48">
+      <c r="A4" s="57"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="47">
         <v>1</v>
       </c>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48">
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47">
         <v>2</v>
       </c>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
-      <c r="L4" s="48"/>
-      <c r="M4" s="48">
+      <c r="J4" s="47"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="47">
         <v>3</v>
       </c>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48">
+      <c r="N4" s="47"/>
+      <c r="O4" s="47"/>
+      <c r="P4" s="47"/>
+      <c r="Q4" s="47">
         <v>4</v>
       </c>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48">
+      <c r="R4" s="47"/>
+      <c r="S4" s="47"/>
+      <c r="T4" s="47"/>
+      <c r="U4" s="47">
         <v>5</v>
       </c>
-      <c r="V4" s="48"/>
-      <c r="W4" s="48"/>
-      <c r="X4" s="48"/>
-      <c r="Y4" s="48">
+      <c r="V4" s="47"/>
+      <c r="W4" s="47"/>
+      <c r="X4" s="47"/>
+      <c r="Y4" s="47">
         <v>6</v>
       </c>
-      <c r="Z4" s="48"/>
-      <c r="AA4" s="48"/>
-      <c r="AB4" s="48"/>
-      <c r="AC4" s="48">
+      <c r="Z4" s="47"/>
+      <c r="AA4" s="47"/>
+      <c r="AB4" s="47"/>
+      <c r="AC4" s="47">
         <v>7</v>
       </c>
-      <c r="AD4" s="48"/>
-      <c r="AE4" s="48"/>
-      <c r="AF4" s="48"/>
-      <c r="AG4" s="48">
+      <c r="AD4" s="47"/>
+      <c r="AE4" s="47"/>
+      <c r="AF4" s="47"/>
+      <c r="AG4" s="47">
         <v>8</v>
       </c>
-      <c r="AH4" s="52"/>
-      <c r="AI4" s="52"/>
-      <c r="AJ4" s="53"/>
-      <c r="AK4" s="48">
+      <c r="AH4" s="55"/>
+      <c r="AI4" s="55"/>
+      <c r="AJ4" s="56"/>
+      <c r="AK4" s="47">
         <v>1</v>
       </c>
-      <c r="AL4" s="48"/>
-      <c r="AM4" s="48"/>
-      <c r="AN4" s="48"/>
-      <c r="AO4" s="48">
+      <c r="AL4" s="47"/>
+      <c r="AM4" s="47"/>
+      <c r="AN4" s="47"/>
+      <c r="AO4" s="47">
         <v>2</v>
       </c>
-      <c r="AP4" s="48"/>
-      <c r="AQ4" s="48"/>
-      <c r="AR4" s="48"/>
-      <c r="AS4" s="48">
+      <c r="AP4" s="47"/>
+      <c r="AQ4" s="47"/>
+      <c r="AR4" s="47"/>
+      <c r="AS4" s="47">
         <v>3</v>
       </c>
-      <c r="AT4" s="48"/>
-      <c r="AU4" s="48"/>
-      <c r="AV4" s="48"/>
-      <c r="AW4" s="48">
+      <c r="AT4" s="47"/>
+      <c r="AU4" s="47"/>
+      <c r="AV4" s="47"/>
+      <c r="AW4" s="47">
         <v>4</v>
       </c>
-      <c r="AX4" s="48"/>
-      <c r="AY4" s="48"/>
-      <c r="AZ4" s="48"/>
-      <c r="BA4" s="50">
+      <c r="AX4" s="47"/>
+      <c r="AY4" s="47"/>
+      <c r="AZ4" s="47"/>
+      <c r="BA4" s="46">
         <v>5</v>
       </c>
-      <c r="BB4" s="50"/>
-      <c r="BC4" s="50"/>
-      <c r="BD4" s="50"/>
-      <c r="BE4" s="50">
+      <c r="BB4" s="46"/>
+      <c r="BC4" s="46"/>
+      <c r="BD4" s="46"/>
+      <c r="BE4" s="46">
         <v>6</v>
       </c>
-      <c r="BF4" s="50"/>
-      <c r="BG4" s="50"/>
-      <c r="BH4" s="50"/>
-      <c r="BI4" s="50">
+      <c r="BF4" s="46"/>
+      <c r="BG4" s="46"/>
+      <c r="BH4" s="46"/>
+      <c r="BI4" s="46">
         <v>7</v>
       </c>
-      <c r="BJ4" s="50"/>
-      <c r="BK4" s="50"/>
-      <c r="BL4" s="50"/>
-      <c r="BM4" s="50">
+      <c r="BJ4" s="46"/>
+      <c r="BK4" s="46"/>
+      <c r="BL4" s="46"/>
+      <c r="BM4" s="46">
         <v>8</v>
       </c>
-      <c r="BN4" s="50"/>
-      <c r="BO4" s="50"/>
-      <c r="BP4" s="50"/>
-      <c r="BQ4" s="48">
+      <c r="BN4" s="46"/>
+      <c r="BO4" s="46"/>
+      <c r="BP4" s="46"/>
+      <c r="BQ4" s="47">
         <v>1</v>
       </c>
-      <c r="BR4" s="48"/>
-      <c r="BS4" s="48"/>
-      <c r="BT4" s="48"/>
-      <c r="BU4" s="48">
+      <c r="BR4" s="47"/>
+      <c r="BS4" s="47"/>
+      <c r="BT4" s="47"/>
+      <c r="BU4" s="47">
         <v>2</v>
       </c>
-      <c r="BV4" s="48"/>
-      <c r="BW4" s="48"/>
-      <c r="BX4" s="48"/>
-      <c r="BY4" s="48">
+      <c r="BV4" s="47"/>
+      <c r="BW4" s="47"/>
+      <c r="BX4" s="47"/>
+      <c r="BY4" s="47">
         <v>3</v>
       </c>
-      <c r="BZ4" s="48"/>
-      <c r="CA4" s="48"/>
-      <c r="CB4" s="48"/>
-      <c r="CC4" s="48">
+      <c r="BZ4" s="47"/>
+      <c r="CA4" s="47"/>
+      <c r="CB4" s="47"/>
+      <c r="CC4" s="47">
         <v>4</v>
       </c>
-      <c r="CD4" s="48"/>
-      <c r="CE4" s="48"/>
-      <c r="CF4" s="48"/>
-      <c r="CG4" s="48">
+      <c r="CD4" s="47"/>
+      <c r="CE4" s="47"/>
+      <c r="CF4" s="47"/>
+      <c r="CG4" s="47">
         <v>5</v>
       </c>
-      <c r="CH4" s="48"/>
-      <c r="CI4" s="48"/>
-      <c r="CJ4" s="48"/>
-      <c r="CK4" s="48">
+      <c r="CH4" s="47"/>
+      <c r="CI4" s="47"/>
+      <c r="CJ4" s="47"/>
+      <c r="CK4" s="47">
         <v>6</v>
       </c>
-      <c r="CL4" s="48"/>
-      <c r="CM4" s="48"/>
-      <c r="CN4" s="48"/>
-      <c r="CO4" s="50">
+      <c r="CL4" s="47"/>
+      <c r="CM4" s="47"/>
+      <c r="CN4" s="47"/>
+      <c r="CO4" s="46">
         <v>7</v>
       </c>
-      <c r="CP4" s="50"/>
-      <c r="CQ4" s="50"/>
-      <c r="CR4" s="50"/>
-      <c r="CS4" s="50">
+      <c r="CP4" s="46"/>
+      <c r="CQ4" s="46"/>
+      <c r="CR4" s="46"/>
+      <c r="CS4" s="46">
         <v>8</v>
       </c>
-      <c r="CT4" s="50"/>
-      <c r="CU4" s="50"/>
-      <c r="CV4" s="50"/>
-      <c r="CW4" s="48">
+      <c r="CT4" s="46"/>
+      <c r="CU4" s="46"/>
+      <c r="CV4" s="46"/>
+      <c r="CW4" s="47">
         <v>1</v>
       </c>
-      <c r="CX4" s="48"/>
-      <c r="CY4" s="48"/>
-      <c r="CZ4" s="48"/>
-      <c r="DA4" s="48">
+      <c r="CX4" s="47"/>
+      <c r="CY4" s="47"/>
+      <c r="CZ4" s="47"/>
+      <c r="DA4" s="47">
         <v>2</v>
       </c>
-      <c r="DB4" s="48"/>
-      <c r="DC4" s="48"/>
-      <c r="DD4" s="48"/>
-      <c r="DE4" s="48">
+      <c r="DB4" s="47"/>
+      <c r="DC4" s="47"/>
+      <c r="DD4" s="47"/>
+      <c r="DE4" s="47">
         <v>3</v>
       </c>
-      <c r="DF4" s="48"/>
-      <c r="DG4" s="48"/>
-      <c r="DH4" s="48"/>
-      <c r="DI4" s="48">
+      <c r="DF4" s="47"/>
+      <c r="DG4" s="47"/>
+      <c r="DH4" s="47"/>
+      <c r="DI4" s="47">
         <v>4</v>
       </c>
-      <c r="DJ4" s="48"/>
-      <c r="DK4" s="48"/>
-      <c r="DL4" s="48"/>
-      <c r="DM4" s="48">
+      <c r="DJ4" s="47"/>
+      <c r="DK4" s="47"/>
+      <c r="DL4" s="47"/>
+      <c r="DM4" s="47">
         <v>5</v>
       </c>
-      <c r="DN4" s="48"/>
-      <c r="DO4" s="48"/>
-      <c r="DP4" s="48"/>
-      <c r="DQ4" s="48">
+      <c r="DN4" s="47"/>
+      <c r="DO4" s="47"/>
+      <c r="DP4" s="47"/>
+      <c r="DQ4" s="47">
         <v>6</v>
       </c>
-      <c r="DR4" s="48"/>
-      <c r="DS4" s="48"/>
-      <c r="DT4" s="48"/>
-      <c r="DU4" s="48">
+      <c r="DR4" s="47"/>
+      <c r="DS4" s="47"/>
+      <c r="DT4" s="47"/>
+      <c r="DU4" s="47">
         <v>7</v>
       </c>
-      <c r="DV4" s="48"/>
-      <c r="DW4" s="48"/>
-      <c r="DX4" s="48"/>
-      <c r="DY4" s="48">
+      <c r="DV4" s="47"/>
+      <c r="DW4" s="47"/>
+      <c r="DX4" s="47"/>
+      <c r="DY4" s="47">
         <v>8</v>
       </c>
-      <c r="DZ4" s="48"/>
-      <c r="EA4" s="48"/>
-      <c r="EB4" s="48"/>
-      <c r="EC4" s="50">
+      <c r="DZ4" s="47"/>
+      <c r="EA4" s="47"/>
+      <c r="EB4" s="47"/>
+      <c r="EC4" s="46">
         <v>1</v>
       </c>
-      <c r="ED4" s="50"/>
-      <c r="EE4" s="50"/>
-      <c r="EF4" s="50"/>
-      <c r="EG4" s="50">
+      <c r="ED4" s="46"/>
+      <c r="EE4" s="46"/>
+      <c r="EF4" s="46"/>
+      <c r="EG4" s="46">
         <v>2</v>
       </c>
-      <c r="EH4" s="50"/>
-      <c r="EI4" s="50"/>
-      <c r="EJ4" s="50"/>
-      <c r="EK4" s="50">
+      <c r="EH4" s="46"/>
+      <c r="EI4" s="46"/>
+      <c r="EJ4" s="46"/>
+      <c r="EK4" s="46">
         <v>3</v>
       </c>
-      <c r="EL4" s="50"/>
-      <c r="EM4" s="50"/>
-      <c r="EN4" s="50"/>
-      <c r="EO4" s="50">
+      <c r="EL4" s="46"/>
+      <c r="EM4" s="46"/>
+      <c r="EN4" s="46"/>
+      <c r="EO4" s="46">
         <v>4</v>
       </c>
-      <c r="EP4" s="50"/>
-      <c r="EQ4" s="50"/>
-      <c r="ER4" s="50"/>
-      <c r="ES4" s="50">
+      <c r="EP4" s="46"/>
+      <c r="EQ4" s="46"/>
+      <c r="ER4" s="46"/>
+      <c r="ES4" s="46">
         <v>5</v>
       </c>
-      <c r="ET4" s="50"/>
-      <c r="EU4" s="50"/>
-      <c r="EV4" s="50"/>
-      <c r="EW4" s="50">
+      <c r="ET4" s="46"/>
+      <c r="EU4" s="46"/>
+      <c r="EV4" s="46"/>
+      <c r="EW4" s="46">
         <v>6</v>
       </c>
-      <c r="EX4" s="50"/>
-      <c r="EY4" s="50"/>
-      <c r="EZ4" s="50"/>
-      <c r="FA4" s="50">
+      <c r="EX4" s="46"/>
+      <c r="EY4" s="46"/>
+      <c r="EZ4" s="46"/>
+      <c r="FA4" s="46">
         <v>7</v>
       </c>
-      <c r="FB4" s="50"/>
-      <c r="FC4" s="50"/>
-      <c r="FD4" s="50"/>
-      <c r="FE4" s="50">
+      <c r="FB4" s="46"/>
+      <c r="FC4" s="46"/>
+      <c r="FD4" s="46"/>
+      <c r="FE4" s="46">
         <v>8</v>
       </c>
-      <c r="FF4" s="50"/>
-      <c r="FG4" s="50"/>
-      <c r="FH4" s="50"/>
-      <c r="FI4" s="48">
+      <c r="FF4" s="46"/>
+      <c r="FG4" s="46"/>
+      <c r="FH4" s="46"/>
+      <c r="FI4" s="47">
         <v>1</v>
       </c>
-      <c r="FJ4" s="48"/>
-      <c r="FK4" s="48"/>
-      <c r="FL4" s="48"/>
-      <c r="FM4" s="48">
+      <c r="FJ4" s="47"/>
+      <c r="FK4" s="47"/>
+      <c r="FL4" s="47"/>
+      <c r="FM4" s="47">
         <v>2</v>
       </c>
-      <c r="FN4" s="48"/>
-      <c r="FO4" s="48"/>
-      <c r="FP4" s="48"/>
-      <c r="FQ4" s="48">
+      <c r="FN4" s="47"/>
+      <c r="FO4" s="47"/>
+      <c r="FP4" s="47"/>
+      <c r="FQ4" s="47">
         <v>3</v>
       </c>
-      <c r="FR4" s="48"/>
-      <c r="FS4" s="48"/>
-      <c r="FT4" s="48"/>
-      <c r="FU4" s="48">
+      <c r="FR4" s="47"/>
+      <c r="FS4" s="47"/>
+      <c r="FT4" s="47"/>
+      <c r="FU4" s="47">
         <v>4</v>
       </c>
-      <c r="FV4" s="48"/>
-      <c r="FW4" s="48"/>
-      <c r="FX4" s="48"/>
-      <c r="FY4" s="48">
+      <c r="FV4" s="47"/>
+      <c r="FW4" s="47"/>
+      <c r="FX4" s="47"/>
+      <c r="FY4" s="47">
         <v>5</v>
       </c>
-      <c r="FZ4" s="48"/>
-      <c r="GA4" s="48"/>
-      <c r="GB4" s="48"/>
-      <c r="GC4" s="48">
+      <c r="FZ4" s="47"/>
+      <c r="GA4" s="47"/>
+      <c r="GB4" s="47"/>
+      <c r="GC4" s="47">
         <v>6</v>
       </c>
-      <c r="GD4" s="48"/>
-      <c r="GE4" s="48"/>
-      <c r="GF4" s="48"/>
-      <c r="GG4" s="48">
+      <c r="GD4" s="47"/>
+      <c r="GE4" s="47"/>
+      <c r="GF4" s="47"/>
+      <c r="GG4" s="47">
         <v>7</v>
       </c>
-      <c r="GH4" s="48"/>
-      <c r="GI4" s="48"/>
-      <c r="GJ4" s="48"/>
-      <c r="GK4" s="48">
+      <c r="GH4" s="47"/>
+      <c r="GI4" s="47"/>
+      <c r="GJ4" s="47"/>
+      <c r="GK4" s="47">
         <v>8</v>
       </c>
-      <c r="GL4" s="48"/>
-      <c r="GM4" s="48"/>
-      <c r="GN4" s="48"/>
-      <c r="GO4" s="48">
+      <c r="GL4" s="47"/>
+      <c r="GM4" s="47"/>
+      <c r="GN4" s="47"/>
+      <c r="GO4" s="47">
         <v>1</v>
       </c>
-      <c r="GP4" s="48"/>
-      <c r="GQ4" s="48"/>
-      <c r="GR4" s="48"/>
-      <c r="GS4" s="48">
+      <c r="GP4" s="47"/>
+      <c r="GQ4" s="47"/>
+      <c r="GR4" s="47"/>
+      <c r="GS4" s="47">
         <v>2</v>
       </c>
-      <c r="GT4" s="48"/>
-      <c r="GU4" s="48"/>
-      <c r="GV4" s="48"/>
-      <c r="GW4" s="48">
+      <c r="GT4" s="47"/>
+      <c r="GU4" s="47"/>
+      <c r="GV4" s="47"/>
+      <c r="GW4" s="47">
         <v>3</v>
       </c>
-      <c r="GX4" s="48"/>
-      <c r="GY4" s="48"/>
-      <c r="GZ4" s="48"/>
-      <c r="HA4" s="48">
+      <c r="GX4" s="47"/>
+      <c r="GY4" s="47"/>
+      <c r="GZ4" s="47"/>
+      <c r="HA4" s="47">
         <v>4</v>
       </c>
-      <c r="HB4" s="48"/>
-      <c r="HC4" s="48"/>
-      <c r="HD4" s="48"/>
-      <c r="HE4" s="50">
+      <c r="HB4" s="47"/>
+      <c r="HC4" s="47"/>
+      <c r="HD4" s="47"/>
+      <c r="HE4" s="46">
         <v>5</v>
       </c>
-      <c r="HF4" s="50"/>
-      <c r="HG4" s="50"/>
-      <c r="HH4" s="50"/>
-      <c r="HI4" s="50">
+      <c r="HF4" s="46"/>
+      <c r="HG4" s="46"/>
+      <c r="HH4" s="46"/>
+      <c r="HI4" s="46">
         <v>6</v>
       </c>
-      <c r="HJ4" s="50"/>
-      <c r="HK4" s="50"/>
-      <c r="HL4" s="50"/>
-      <c r="HM4" s="50">
+      <c r="HJ4" s="46"/>
+      <c r="HK4" s="46"/>
+      <c r="HL4" s="46"/>
+      <c r="HM4" s="46">
         <v>7</v>
       </c>
-      <c r="HN4" s="50"/>
-      <c r="HO4" s="50"/>
-      <c r="HP4" s="50"/>
-      <c r="HQ4" s="50">
+      <c r="HN4" s="46"/>
+      <c r="HO4" s="46"/>
+      <c r="HP4" s="46"/>
+      <c r="HQ4" s="46">
         <v>8</v>
       </c>
-      <c r="HR4" s="50"/>
-      <c r="HS4" s="50"/>
-      <c r="HT4" s="50"/>
-      <c r="HU4" s="48">
+      <c r="HR4" s="46"/>
+      <c r="HS4" s="46"/>
+      <c r="HT4" s="46"/>
+      <c r="HU4" s="47">
         <v>1</v>
       </c>
-      <c r="HV4" s="48"/>
-      <c r="HW4" s="48"/>
-      <c r="HX4" s="48"/>
-      <c r="HY4" s="48">
+      <c r="HV4" s="47"/>
+      <c r="HW4" s="47"/>
+      <c r="HX4" s="47"/>
+      <c r="HY4" s="47">
         <v>2</v>
       </c>
-      <c r="HZ4" s="48"/>
-      <c r="IA4" s="48"/>
-      <c r="IB4" s="48"/>
-      <c r="IC4" s="48">
+      <c r="HZ4" s="47"/>
+      <c r="IA4" s="47"/>
+      <c r="IB4" s="47"/>
+      <c r="IC4" s="47">
         <v>3</v>
       </c>
-      <c r="ID4" s="48"/>
-      <c r="IE4" s="48"/>
-      <c r="IF4" s="48"/>
-      <c r="IG4" s="48">
+      <c r="ID4" s="47"/>
+      <c r="IE4" s="47"/>
+      <c r="IF4" s="47"/>
+      <c r="IG4" s="47">
         <v>4</v>
       </c>
-      <c r="IH4" s="48"/>
-      <c r="II4" s="48"/>
-      <c r="IJ4" s="48"/>
-      <c r="IK4" s="48">
+      <c r="IH4" s="47"/>
+      <c r="II4" s="47"/>
+      <c r="IJ4" s="47"/>
+      <c r="IK4" s="47">
         <v>5</v>
       </c>
-      <c r="IL4" s="48"/>
-      <c r="IM4" s="48"/>
-      <c r="IN4" s="48"/>
-      <c r="IO4" s="48">
+      <c r="IL4" s="47"/>
+      <c r="IM4" s="47"/>
+      <c r="IN4" s="47"/>
+      <c r="IO4" s="47">
         <v>6</v>
       </c>
-      <c r="IP4" s="48"/>
-      <c r="IQ4" s="48"/>
-      <c r="IR4" s="48"/>
-      <c r="IS4" s="50">
+      <c r="IP4" s="47"/>
+      <c r="IQ4" s="47"/>
+      <c r="IR4" s="47"/>
+      <c r="IS4" s="46">
         <v>7</v>
       </c>
-      <c r="IT4" s="50"/>
-      <c r="IU4" s="50"/>
-      <c r="IV4" s="50"/>
-      <c r="IW4" s="50">
+      <c r="IT4" s="46"/>
+      <c r="IU4" s="46"/>
+      <c r="IV4" s="46"/>
+      <c r="IW4" s="46">
         <v>8</v>
       </c>
-      <c r="IX4" s="50"/>
-      <c r="IY4" s="50"/>
-      <c r="IZ4" s="50"/>
-      <c r="JA4" s="48">
+      <c r="IX4" s="46"/>
+      <c r="IY4" s="46"/>
+      <c r="IZ4" s="46"/>
+      <c r="JA4" s="47">
         <v>1</v>
       </c>
-      <c r="JB4" s="48"/>
-      <c r="JC4" s="48"/>
-      <c r="JD4" s="48"/>
-      <c r="JE4" s="48">
+      <c r="JB4" s="47"/>
+      <c r="JC4" s="47"/>
+      <c r="JD4" s="47"/>
+      <c r="JE4" s="47">
         <v>2</v>
       </c>
-      <c r="JF4" s="48"/>
-      <c r="JG4" s="48"/>
-      <c r="JH4" s="48"/>
-      <c r="JI4" s="48">
+      <c r="JF4" s="47"/>
+      <c r="JG4" s="47"/>
+      <c r="JH4" s="47"/>
+      <c r="JI4" s="47">
         <v>3</v>
       </c>
-      <c r="JJ4" s="48"/>
-      <c r="JK4" s="48"/>
-      <c r="JL4" s="48"/>
-      <c r="JM4" s="48">
+      <c r="JJ4" s="47"/>
+      <c r="JK4" s="47"/>
+      <c r="JL4" s="47"/>
+      <c r="JM4" s="47">
         <v>4</v>
       </c>
-      <c r="JN4" s="48"/>
-      <c r="JO4" s="48"/>
-      <c r="JP4" s="48"/>
-      <c r="JQ4" s="48">
+      <c r="JN4" s="47"/>
+      <c r="JO4" s="47"/>
+      <c r="JP4" s="47"/>
+      <c r="JQ4" s="47">
         <v>5</v>
       </c>
-      <c r="JR4" s="48"/>
-      <c r="JS4" s="48"/>
-      <c r="JT4" s="48"/>
-      <c r="JU4" s="48">
+      <c r="JR4" s="47"/>
+      <c r="JS4" s="47"/>
+      <c r="JT4" s="47"/>
+      <c r="JU4" s="47">
         <v>6</v>
       </c>
-      <c r="JV4" s="48"/>
-      <c r="JW4" s="48"/>
-      <c r="JX4" s="48"/>
-      <c r="JY4" s="48">
+      <c r="JV4" s="47"/>
+      <c r="JW4" s="47"/>
+      <c r="JX4" s="47"/>
+      <c r="JY4" s="47">
         <v>7</v>
       </c>
-      <c r="JZ4" s="48"/>
-      <c r="KA4" s="48"/>
-      <c r="KB4" s="48"/>
-      <c r="KC4" s="48">
+      <c r="JZ4" s="47"/>
+      <c r="KA4" s="47"/>
+      <c r="KB4" s="47"/>
+      <c r="KC4" s="47">
         <v>8</v>
       </c>
-      <c r="KD4" s="48"/>
-      <c r="KE4" s="48"/>
-      <c r="KF4" s="48"/>
-      <c r="KG4" s="50">
+      <c r="KD4" s="47"/>
+      <c r="KE4" s="47"/>
+      <c r="KF4" s="47"/>
+      <c r="KG4" s="46">
         <v>1</v>
       </c>
-      <c r="KH4" s="50"/>
-      <c r="KI4" s="50"/>
-      <c r="KJ4" s="50"/>
-      <c r="KK4" s="50">
+      <c r="KH4" s="46"/>
+      <c r="KI4" s="46"/>
+      <c r="KJ4" s="46"/>
+      <c r="KK4" s="46">
         <v>2</v>
       </c>
-      <c r="KL4" s="50"/>
-      <c r="KM4" s="50"/>
-      <c r="KN4" s="50"/>
-      <c r="KO4" s="50">
+      <c r="KL4" s="46"/>
+      <c r="KM4" s="46"/>
+      <c r="KN4" s="46"/>
+      <c r="KO4" s="46">
         <v>3</v>
       </c>
-      <c r="KP4" s="50"/>
-      <c r="KQ4" s="50"/>
-      <c r="KR4" s="50"/>
-      <c r="KS4" s="50">
+      <c r="KP4" s="46"/>
+      <c r="KQ4" s="46"/>
+      <c r="KR4" s="46"/>
+      <c r="KS4" s="46">
         <v>4</v>
       </c>
-      <c r="KT4" s="50"/>
-      <c r="KU4" s="50"/>
-      <c r="KV4" s="50"/>
-      <c r="KW4" s="50">
+      <c r="KT4" s="46"/>
+      <c r="KU4" s="46"/>
+      <c r="KV4" s="46"/>
+      <c r="KW4" s="46">
         <v>5</v>
       </c>
-      <c r="KX4" s="50"/>
-      <c r="KY4" s="50"/>
-      <c r="KZ4" s="50"/>
-      <c r="LA4" s="50">
+      <c r="KX4" s="46"/>
+      <c r="KY4" s="46"/>
+      <c r="KZ4" s="46"/>
+      <c r="LA4" s="46">
         <v>6</v>
       </c>
-      <c r="LB4" s="50"/>
-      <c r="LC4" s="50"/>
-      <c r="LD4" s="50"/>
-      <c r="LE4" s="50">
+      <c r="LB4" s="46"/>
+      <c r="LC4" s="46"/>
+      <c r="LD4" s="46"/>
+      <c r="LE4" s="46">
         <v>7</v>
       </c>
-      <c r="LF4" s="50"/>
-      <c r="LG4" s="50"/>
-      <c r="LH4" s="50"/>
-      <c r="LI4" s="50">
+      <c r="LF4" s="46"/>
+      <c r="LG4" s="46"/>
+      <c r="LH4" s="46"/>
+      <c r="LI4" s="46">
         <v>8</v>
       </c>
-      <c r="LJ4" s="50"/>
-      <c r="LK4" s="50"/>
-      <c r="LL4" s="50"/>
-      <c r="LM4" s="48">
+      <c r="LJ4" s="46"/>
+      <c r="LK4" s="46"/>
+      <c r="LL4" s="46"/>
+      <c r="LM4" s="47">
         <v>1</v>
       </c>
-      <c r="LN4" s="48"/>
-      <c r="LO4" s="48"/>
-      <c r="LP4" s="48"/>
-      <c r="LQ4" s="48">
+      <c r="LN4" s="47"/>
+      <c r="LO4" s="47"/>
+      <c r="LP4" s="47"/>
+      <c r="LQ4" s="47">
         <v>2</v>
       </c>
-      <c r="LR4" s="48"/>
-      <c r="LS4" s="48"/>
-      <c r="LT4" s="48"/>
-      <c r="LU4" s="48">
+      <c r="LR4" s="47"/>
+      <c r="LS4" s="47"/>
+      <c r="LT4" s="47"/>
+      <c r="LU4" s="47">
         <v>3</v>
       </c>
-      <c r="LV4" s="48"/>
-      <c r="LW4" s="48"/>
-      <c r="LX4" s="48"/>
-      <c r="LY4" s="48">
+      <c r="LV4" s="47"/>
+      <c r="LW4" s="47"/>
+      <c r="LX4" s="47"/>
+      <c r="LY4" s="47">
         <v>4</v>
       </c>
-      <c r="LZ4" s="48"/>
-      <c r="MA4" s="48"/>
-      <c r="MB4" s="48"/>
-      <c r="MC4" s="48">
+      <c r="LZ4" s="47"/>
+      <c r="MA4" s="47"/>
+      <c r="MB4" s="47"/>
+      <c r="MC4" s="47">
         <v>5</v>
       </c>
-      <c r="MD4" s="48"/>
-      <c r="ME4" s="48"/>
-      <c r="MF4" s="48"/>
-      <c r="MG4" s="48">
+      <c r="MD4" s="47"/>
+      <c r="ME4" s="47"/>
+      <c r="MF4" s="47"/>
+      <c r="MG4" s="47">
         <v>6</v>
       </c>
-      <c r="MH4" s="48"/>
-      <c r="MI4" s="48"/>
-      <c r="MJ4" s="48"/>
-      <c r="MK4" s="48">
+      <c r="MH4" s="47"/>
+      <c r="MI4" s="47"/>
+      <c r="MJ4" s="47"/>
+      <c r="MK4" s="47">
         <v>7</v>
       </c>
-      <c r="ML4" s="48"/>
-      <c r="MM4" s="48"/>
-      <c r="MN4" s="48"/>
-      <c r="MO4" s="48">
+      <c r="ML4" s="47"/>
+      <c r="MM4" s="47"/>
+      <c r="MN4" s="47"/>
+      <c r="MO4" s="47">
         <v>8</v>
       </c>
-      <c r="MP4" s="48"/>
-      <c r="MQ4" s="48"/>
-      <c r="MR4" s="48"/>
-      <c r="MS4" s="48">
+      <c r="MP4" s="47"/>
+      <c r="MQ4" s="47"/>
+      <c r="MR4" s="47"/>
+      <c r="MS4" s="47">
         <v>1</v>
       </c>
-      <c r="MT4" s="48"/>
-      <c r="MU4" s="48"/>
-      <c r="MV4" s="48"/>
-      <c r="MW4" s="48">
+      <c r="MT4" s="47"/>
+      <c r="MU4" s="47"/>
+      <c r="MV4" s="47"/>
+      <c r="MW4" s="47">
         <v>2</v>
       </c>
-      <c r="MX4" s="48"/>
-      <c r="MY4" s="48"/>
-      <c r="MZ4" s="48"/>
-      <c r="NA4" s="48">
+      <c r="MX4" s="47"/>
+      <c r="MY4" s="47"/>
+      <c r="MZ4" s="47"/>
+      <c r="NA4" s="47">
         <v>3</v>
       </c>
-      <c r="NB4" s="48"/>
-      <c r="NC4" s="48"/>
-      <c r="ND4" s="48"/>
-      <c r="NE4" s="48">
+      <c r="NB4" s="47"/>
+      <c r="NC4" s="47"/>
+      <c r="ND4" s="47"/>
+      <c r="NE4" s="47">
         <v>4</v>
       </c>
-      <c r="NF4" s="48"/>
-      <c r="NG4" s="48"/>
-      <c r="NH4" s="48"/>
-      <c r="NI4" s="50">
+      <c r="NF4" s="47"/>
+      <c r="NG4" s="47"/>
+      <c r="NH4" s="47"/>
+      <c r="NI4" s="46">
         <v>5</v>
       </c>
-      <c r="NJ4" s="50"/>
-      <c r="NK4" s="50"/>
-      <c r="NL4" s="50"/>
-      <c r="NM4" s="50">
+      <c r="NJ4" s="46"/>
+      <c r="NK4" s="46"/>
+      <c r="NL4" s="46"/>
+      <c r="NM4" s="46">
         <v>6</v>
       </c>
-      <c r="NN4" s="50"/>
-      <c r="NO4" s="50"/>
-      <c r="NP4" s="50"/>
-      <c r="NQ4" s="50">
+      <c r="NN4" s="46"/>
+      <c r="NO4" s="46"/>
+      <c r="NP4" s="46"/>
+      <c r="NQ4" s="46">
         <v>7</v>
       </c>
-      <c r="NR4" s="50"/>
-      <c r="NS4" s="50"/>
-      <c r="NT4" s="50"/>
-      <c r="NU4" s="50">
+      <c r="NR4" s="46"/>
+      <c r="NS4" s="46"/>
+      <c r="NT4" s="46"/>
+      <c r="NU4" s="46">
         <v>8</v>
       </c>
-      <c r="NV4" s="50"/>
-      <c r="NW4" s="50"/>
-      <c r="NX4" s="50"/>
-      <c r="NY4" s="48">
+      <c r="NV4" s="46"/>
+      <c r="NW4" s="46"/>
+      <c r="NX4" s="46"/>
+      <c r="NY4" s="47">
         <v>1</v>
       </c>
-      <c r="NZ4" s="48"/>
-      <c r="OA4" s="48"/>
-      <c r="OB4" s="48"/>
-      <c r="OC4" s="48">
+      <c r="NZ4" s="47"/>
+      <c r="OA4" s="47"/>
+      <c r="OB4" s="47"/>
+      <c r="OC4" s="47">
         <v>2</v>
       </c>
-      <c r="OD4" s="48"/>
-      <c r="OE4" s="48"/>
-      <c r="OF4" s="48"/>
-      <c r="OG4" s="48">
+      <c r="OD4" s="47"/>
+      <c r="OE4" s="47"/>
+      <c r="OF4" s="47"/>
+      <c r="OG4" s="47">
         <v>3</v>
       </c>
-      <c r="OH4" s="48"/>
-      <c r="OI4" s="48"/>
-      <c r="OJ4" s="48"/>
-      <c r="OK4" s="48">
+      <c r="OH4" s="47"/>
+      <c r="OI4" s="47"/>
+      <c r="OJ4" s="47"/>
+      <c r="OK4" s="47">
         <v>4</v>
       </c>
-      <c r="OL4" s="48"/>
-      <c r="OM4" s="48"/>
-      <c r="ON4" s="48"/>
-      <c r="OO4" s="48">
+      <c r="OL4" s="47"/>
+      <c r="OM4" s="47"/>
+      <c r="ON4" s="47"/>
+      <c r="OO4" s="47">
         <v>5</v>
       </c>
-      <c r="OP4" s="48"/>
-      <c r="OQ4" s="48"/>
-      <c r="OR4" s="48"/>
-      <c r="OS4" s="48">
+      <c r="OP4" s="47"/>
+      <c r="OQ4" s="47"/>
+      <c r="OR4" s="47"/>
+      <c r="OS4" s="47">
         <v>6</v>
       </c>
-      <c r="OT4" s="48"/>
-      <c r="OU4" s="48"/>
-      <c r="OV4" s="48"/>
-      <c r="OW4" s="50">
+      <c r="OT4" s="47"/>
+      <c r="OU4" s="47"/>
+      <c r="OV4" s="47"/>
+      <c r="OW4" s="46">
         <v>7</v>
       </c>
-      <c r="OX4" s="50"/>
-      <c r="OY4" s="50"/>
-      <c r="OZ4" s="50"/>
-      <c r="PA4" s="50">
+      <c r="OX4" s="46"/>
+      <c r="OY4" s="46"/>
+      <c r="OZ4" s="46"/>
+      <c r="PA4" s="46">
         <v>8</v>
       </c>
-      <c r="PB4" s="50"/>
-      <c r="PC4" s="50"/>
-      <c r="PD4" s="50"/>
-      <c r="PE4" s="48">
+      <c r="PB4" s="46"/>
+      <c r="PC4" s="46"/>
+      <c r="PD4" s="46"/>
+      <c r="PE4" s="47">
         <v>1</v>
       </c>
-      <c r="PF4" s="48"/>
-      <c r="PG4" s="48"/>
-      <c r="PH4" s="48"/>
-      <c r="PI4" s="48">
+      <c r="PF4" s="47"/>
+      <c r="PG4" s="47"/>
+      <c r="PH4" s="47"/>
+      <c r="PI4" s="47">
         <v>2</v>
       </c>
-      <c r="PJ4" s="48"/>
-      <c r="PK4" s="48"/>
-      <c r="PL4" s="48"/>
-      <c r="PM4" s="48">
+      <c r="PJ4" s="47"/>
+      <c r="PK4" s="47"/>
+      <c r="PL4" s="47"/>
+      <c r="PM4" s="47">
         <v>3</v>
       </c>
-      <c r="PN4" s="48"/>
-      <c r="PO4" s="48"/>
-      <c r="PP4" s="48"/>
-      <c r="PQ4" s="48">
+      <c r="PN4" s="47"/>
+      <c r="PO4" s="47"/>
+      <c r="PP4" s="47"/>
+      <c r="PQ4" s="47">
         <v>4</v>
       </c>
-      <c r="PR4" s="48"/>
-      <c r="PS4" s="48"/>
-      <c r="PT4" s="48"/>
-      <c r="PU4" s="48">
+      <c r="PR4" s="47"/>
+      <c r="PS4" s="47"/>
+      <c r="PT4" s="47"/>
+      <c r="PU4" s="47">
         <v>5</v>
       </c>
-      <c r="PV4" s="48"/>
-      <c r="PW4" s="48"/>
-      <c r="PX4" s="48"/>
-      <c r="PY4" s="48">
+      <c r="PV4" s="47"/>
+      <c r="PW4" s="47"/>
+      <c r="PX4" s="47"/>
+      <c r="PY4" s="47">
         <v>6</v>
       </c>
-      <c r="PZ4" s="48"/>
-      <c r="QA4" s="48"/>
-      <c r="QB4" s="48"/>
-      <c r="QC4" s="48">
+      <c r="PZ4" s="47"/>
+      <c r="QA4" s="47"/>
+      <c r="QB4" s="47"/>
+      <c r="QC4" s="47">
         <v>7</v>
       </c>
-      <c r="QD4" s="48"/>
-      <c r="QE4" s="48"/>
-      <c r="QF4" s="48"/>
-      <c r="QG4" s="48">
+      <c r="QD4" s="47"/>
+      <c r="QE4" s="47"/>
+      <c r="QF4" s="47"/>
+      <c r="QG4" s="47">
         <v>8</v>
       </c>
-      <c r="QH4" s="48"/>
-      <c r="QI4" s="48"/>
-      <c r="QJ4" s="48"/>
-      <c r="QK4" s="50">
+      <c r="QH4" s="47"/>
+      <c r="QI4" s="47"/>
+      <c r="QJ4" s="47"/>
+      <c r="QK4" s="46">
         <v>1</v>
       </c>
-      <c r="QL4" s="50"/>
-      <c r="QM4" s="50"/>
-      <c r="QN4" s="50"/>
-      <c r="QO4" s="50">
+      <c r="QL4" s="46"/>
+      <c r="QM4" s="46"/>
+      <c r="QN4" s="46"/>
+      <c r="QO4" s="46">
         <v>2</v>
       </c>
-      <c r="QP4" s="50"/>
-      <c r="QQ4" s="50"/>
-      <c r="QR4" s="50"/>
-      <c r="QS4" s="50">
+      <c r="QP4" s="46"/>
+      <c r="QQ4" s="46"/>
+      <c r="QR4" s="46"/>
+      <c r="QS4" s="46">
         <v>3</v>
       </c>
-      <c r="QT4" s="50"/>
-      <c r="QU4" s="50"/>
-      <c r="QV4" s="50"/>
-      <c r="QW4" s="50">
+      <c r="QT4" s="46"/>
+      <c r="QU4" s="46"/>
+      <c r="QV4" s="46"/>
+      <c r="QW4" s="46">
         <v>4</v>
       </c>
-      <c r="QX4" s="50"/>
-      <c r="QY4" s="50"/>
-      <c r="QZ4" s="50"/>
-      <c r="RA4" s="50">
+      <c r="QX4" s="46"/>
+      <c r="QY4" s="46"/>
+      <c r="QZ4" s="46"/>
+      <c r="RA4" s="46">
         <v>5</v>
       </c>
-      <c r="RB4" s="50"/>
-      <c r="RC4" s="50"/>
-      <c r="RD4" s="50"/>
-      <c r="RE4" s="50">
+      <c r="RB4" s="46"/>
+      <c r="RC4" s="46"/>
+      <c r="RD4" s="46"/>
+      <c r="RE4" s="46">
         <v>6</v>
       </c>
-      <c r="RF4" s="50"/>
-      <c r="RG4" s="50"/>
-      <c r="RH4" s="50"/>
-      <c r="RI4" s="50">
+      <c r="RF4" s="46"/>
+      <c r="RG4" s="46"/>
+      <c r="RH4" s="46"/>
+      <c r="RI4" s="46">
         <v>7</v>
       </c>
-      <c r="RJ4" s="50"/>
-      <c r="RK4" s="50"/>
-      <c r="RL4" s="50"/>
-      <c r="RM4" s="50">
+      <c r="RJ4" s="46"/>
+      <c r="RK4" s="46"/>
+      <c r="RL4" s="46"/>
+      <c r="RM4" s="46">
         <v>8</v>
       </c>
-      <c r="RN4" s="50"/>
-      <c r="RO4" s="50"/>
-      <c r="RP4" s="50"/>
-      <c r="RQ4" s="54">
+      <c r="RN4" s="46"/>
+      <c r="RO4" s="46"/>
+      <c r="RP4" s="46"/>
+      <c r="RQ4" s="51">
         <v>1</v>
       </c>
-      <c r="RR4" s="54"/>
-      <c r="RS4" s="54"/>
-      <c r="RT4" s="54"/>
-      <c r="RU4" s="54">
+      <c r="RR4" s="51"/>
+      <c r="RS4" s="51"/>
+      <c r="RT4" s="51"/>
+      <c r="RU4" s="51">
         <v>2</v>
       </c>
-      <c r="RV4" s="54"/>
-      <c r="RW4" s="54"/>
-      <c r="RX4" s="54"/>
-      <c r="RY4" s="54">
+      <c r="RV4" s="51"/>
+      <c r="RW4" s="51"/>
+      <c r="RX4" s="51"/>
+      <c r="RY4" s="51">
         <v>3</v>
       </c>
-      <c r="RZ4" s="54"/>
-      <c r="SA4" s="54"/>
-      <c r="SB4" s="54"/>
-      <c r="SC4" s="54">
+      <c r="RZ4" s="51"/>
+      <c r="SA4" s="51"/>
+      <c r="SB4" s="51"/>
+      <c r="SC4" s="51">
         <v>4</v>
       </c>
-      <c r="SD4" s="54"/>
-      <c r="SE4" s="54"/>
-      <c r="SF4" s="54"/>
-      <c r="SG4" s="54">
+      <c r="SD4" s="51"/>
+      <c r="SE4" s="51"/>
+      <c r="SF4" s="51"/>
+      <c r="SG4" s="51">
         <v>5</v>
       </c>
-      <c r="SH4" s="54"/>
-      <c r="SI4" s="54"/>
-      <c r="SJ4" s="54"/>
-      <c r="SK4" s="54">
+      <c r="SH4" s="51"/>
+      <c r="SI4" s="51"/>
+      <c r="SJ4" s="51"/>
+      <c r="SK4" s="51">
         <v>6</v>
       </c>
-      <c r="SL4" s="54"/>
-      <c r="SM4" s="54"/>
-      <c r="SN4" s="54"/>
-      <c r="SO4" s="54">
+      <c r="SL4" s="51"/>
+      <c r="SM4" s="51"/>
+      <c r="SN4" s="51"/>
+      <c r="SO4" s="51">
         <v>7</v>
       </c>
-      <c r="SP4" s="54"/>
-      <c r="SQ4" s="54"/>
-      <c r="SR4" s="54"/>
-      <c r="SS4" s="54">
+      <c r="SP4" s="51"/>
+      <c r="SQ4" s="51"/>
+      <c r="SR4" s="51"/>
+      <c r="SS4" s="51">
         <v>8</v>
       </c>
-      <c r="ST4" s="54"/>
-      <c r="SU4" s="54"/>
-      <c r="SV4" s="54"/>
-      <c r="SW4" s="54">
+      <c r="ST4" s="51"/>
+      <c r="SU4" s="51"/>
+      <c r="SV4" s="51"/>
+      <c r="SW4" s="51">
         <v>1</v>
       </c>
-      <c r="SX4" s="54"/>
-      <c r="SY4" s="54"/>
-      <c r="SZ4" s="54"/>
-      <c r="TA4" s="54">
+      <c r="SX4" s="51"/>
+      <c r="SY4" s="51"/>
+      <c r="SZ4" s="51"/>
+      <c r="TA4" s="51">
         <v>2</v>
       </c>
-      <c r="TB4" s="54"/>
-      <c r="TC4" s="54"/>
-      <c r="TD4" s="54"/>
-      <c r="TE4" s="54">
+      <c r="TB4" s="51"/>
+      <c r="TC4" s="51"/>
+      <c r="TD4" s="51"/>
+      <c r="TE4" s="51">
         <v>3</v>
       </c>
-      <c r="TF4" s="54"/>
-      <c r="TG4" s="54"/>
-      <c r="TH4" s="54"/>
-      <c r="TI4" s="54">
+      <c r="TF4" s="51"/>
+      <c r="TG4" s="51"/>
+      <c r="TH4" s="51"/>
+      <c r="TI4" s="51">
         <v>4</v>
       </c>
-      <c r="TJ4" s="54"/>
-      <c r="TK4" s="54"/>
-      <c r="TL4" s="54"/>
-      <c r="TM4" s="54">
+      <c r="TJ4" s="51"/>
+      <c r="TK4" s="51"/>
+      <c r="TL4" s="51"/>
+      <c r="TM4" s="51">
         <v>5</v>
       </c>
-      <c r="TN4" s="54"/>
-      <c r="TO4" s="54"/>
-      <c r="TP4" s="54"/>
-      <c r="TQ4" s="54">
+      <c r="TN4" s="51"/>
+      <c r="TO4" s="51"/>
+      <c r="TP4" s="51"/>
+      <c r="TQ4" s="51">
         <v>6</v>
       </c>
-      <c r="TR4" s="54"/>
-      <c r="TS4" s="54"/>
-      <c r="TT4" s="54"/>
-      <c r="TU4" s="54">
+      <c r="TR4" s="51"/>
+      <c r="TS4" s="51"/>
+      <c r="TT4" s="51"/>
+      <c r="TU4" s="51">
         <v>7</v>
       </c>
-      <c r="TV4" s="54"/>
-      <c r="TW4" s="54"/>
-      <c r="TX4" s="54"/>
-      <c r="TY4" s="54">
+      <c r="TV4" s="51"/>
+      <c r="TW4" s="51"/>
+      <c r="TX4" s="51"/>
+      <c r="TY4" s="51">
         <v>8</v>
       </c>
-      <c r="TZ4" s="54"/>
-      <c r="UA4" s="54"/>
-      <c r="UB4" s="54"/>
-      <c r="UC4" s="48">
+      <c r="TZ4" s="51"/>
+      <c r="UA4" s="51"/>
+      <c r="UB4" s="51"/>
+      <c r="UC4" s="47">
         <v>1</v>
       </c>
-      <c r="UD4" s="48"/>
-      <c r="UE4" s="48"/>
-      <c r="UF4" s="48"/>
-      <c r="UG4" s="48">
+      <c r="UD4" s="47"/>
+      <c r="UE4" s="47"/>
+      <c r="UF4" s="47"/>
+      <c r="UG4" s="47">
         <v>2</v>
       </c>
-      <c r="UH4" s="48"/>
-      <c r="UI4" s="48"/>
-      <c r="UJ4" s="48"/>
-      <c r="UK4" s="48">
+      <c r="UH4" s="47"/>
+      <c r="UI4" s="47"/>
+      <c r="UJ4" s="47"/>
+      <c r="UK4" s="47">
         <v>3</v>
       </c>
-      <c r="UL4" s="48"/>
-      <c r="UM4" s="48"/>
-      <c r="UN4" s="48"/>
-      <c r="UO4" s="48">
+      <c r="UL4" s="47"/>
+      <c r="UM4" s="47"/>
+      <c r="UN4" s="47"/>
+      <c r="UO4" s="47">
         <v>4</v>
       </c>
-      <c r="UP4" s="48"/>
-      <c r="UQ4" s="48"/>
-      <c r="UR4" s="48"/>
-      <c r="US4" s="48">
+      <c r="UP4" s="47"/>
+      <c r="UQ4" s="47"/>
+      <c r="UR4" s="47"/>
+      <c r="US4" s="47">
         <v>5</v>
       </c>
-      <c r="UT4" s="48"/>
-      <c r="UU4" s="48"/>
-      <c r="UV4" s="48"/>
-      <c r="UW4" s="48">
+      <c r="UT4" s="47"/>
+      <c r="UU4" s="47"/>
+      <c r="UV4" s="47"/>
+      <c r="UW4" s="47">
         <v>6</v>
       </c>
-      <c r="UX4" s="48"/>
-      <c r="UY4" s="48"/>
-      <c r="UZ4" s="48"/>
-      <c r="VA4" s="50">
+      <c r="UX4" s="47"/>
+      <c r="UY4" s="47"/>
+      <c r="UZ4" s="47"/>
+      <c r="VA4" s="46">
         <v>7</v>
       </c>
-      <c r="VB4" s="50"/>
-      <c r="VC4" s="50"/>
-      <c r="VD4" s="50"/>
-      <c r="VE4" s="50">
+      <c r="VB4" s="46"/>
+      <c r="VC4" s="46"/>
+      <c r="VD4" s="46"/>
+      <c r="VE4" s="46">
         <v>8</v>
       </c>
-      <c r="VF4" s="50"/>
-      <c r="VG4" s="50"/>
-      <c r="VH4" s="50"/>
-      <c r="VI4" s="48">
+      <c r="VF4" s="46"/>
+      <c r="VG4" s="46"/>
+      <c r="VH4" s="46"/>
+      <c r="VI4" s="47">
         <v>1</v>
       </c>
-      <c r="VJ4" s="48"/>
-      <c r="VK4" s="48"/>
-      <c r="VL4" s="48"/>
-      <c r="VM4" s="48">
+      <c r="VJ4" s="47"/>
+      <c r="VK4" s="47"/>
+      <c r="VL4" s="47"/>
+      <c r="VM4" s="47">
         <v>2</v>
       </c>
-      <c r="VN4" s="48"/>
-      <c r="VO4" s="48"/>
-      <c r="VP4" s="48"/>
-      <c r="VQ4" s="48">
+      <c r="VN4" s="47"/>
+      <c r="VO4" s="47"/>
+      <c r="VP4" s="47"/>
+      <c r="VQ4" s="47">
         <v>3</v>
       </c>
-      <c r="VR4" s="48"/>
-      <c r="VS4" s="48"/>
-      <c r="VT4" s="48"/>
-      <c r="VU4" s="48">
+      <c r="VR4" s="47"/>
+      <c r="VS4" s="47"/>
+      <c r="VT4" s="47"/>
+      <c r="VU4" s="47">
         <v>4</v>
       </c>
-      <c r="VV4" s="48"/>
-      <c r="VW4" s="48"/>
-      <c r="VX4" s="48"/>
-      <c r="VY4" s="48">
+      <c r="VV4" s="47"/>
+      <c r="VW4" s="47"/>
+      <c r="VX4" s="47"/>
+      <c r="VY4" s="47">
         <v>5</v>
       </c>
-      <c r="VZ4" s="48"/>
-      <c r="WA4" s="48"/>
-      <c r="WB4" s="48"/>
-      <c r="WC4" s="48">
+      <c r="VZ4" s="47"/>
+      <c r="WA4" s="47"/>
+      <c r="WB4" s="47"/>
+      <c r="WC4" s="47">
         <v>6</v>
       </c>
-      <c r="WD4" s="48"/>
-      <c r="WE4" s="48"/>
-      <c r="WF4" s="48"/>
-      <c r="WG4" s="48">
+      <c r="WD4" s="47"/>
+      <c r="WE4" s="47"/>
+      <c r="WF4" s="47"/>
+      <c r="WG4" s="47">
         <v>7</v>
       </c>
-      <c r="WH4" s="48"/>
-      <c r="WI4" s="48"/>
-      <c r="WJ4" s="48"/>
-      <c r="WK4" s="48">
+      <c r="WH4" s="47"/>
+      <c r="WI4" s="47"/>
+      <c r="WJ4" s="47"/>
+      <c r="WK4" s="47">
         <v>8</v>
       </c>
-      <c r="WL4" s="48"/>
-      <c r="WM4" s="48"/>
-      <c r="WN4" s="48"/>
-      <c r="WO4" s="50">
+      <c r="WL4" s="47"/>
+      <c r="WM4" s="47"/>
+      <c r="WN4" s="47"/>
+      <c r="WO4" s="46">
         <v>1</v>
       </c>
-      <c r="WP4" s="50"/>
-      <c r="WQ4" s="50"/>
-      <c r="WR4" s="50"/>
-      <c r="WS4" s="50">
+      <c r="WP4" s="46"/>
+      <c r="WQ4" s="46"/>
+      <c r="WR4" s="46"/>
+      <c r="WS4" s="46">
         <v>2</v>
       </c>
-      <c r="WT4" s="50"/>
-      <c r="WU4" s="50"/>
-      <c r="WV4" s="50"/>
-      <c r="WW4" s="50">
+      <c r="WT4" s="46"/>
+      <c r="WU4" s="46"/>
+      <c r="WV4" s="46"/>
+      <c r="WW4" s="46">
         <v>3</v>
       </c>
-      <c r="WX4" s="50"/>
-      <c r="WY4" s="50"/>
-      <c r="WZ4" s="50"/>
-      <c r="XA4" s="50">
+      <c r="WX4" s="46"/>
+      <c r="WY4" s="46"/>
+      <c r="WZ4" s="46"/>
+      <c r="XA4" s="46">
         <v>4</v>
       </c>
-      <c r="XB4" s="50"/>
-      <c r="XC4" s="50"/>
-      <c r="XD4" s="50"/>
-      <c r="XE4" s="50">
+      <c r="XB4" s="46"/>
+      <c r="XC4" s="46"/>
+      <c r="XD4" s="46"/>
+      <c r="XE4" s="46">
         <v>5</v>
       </c>
-      <c r="XF4" s="50"/>
-      <c r="XG4" s="50"/>
-      <c r="XH4" s="50"/>
-      <c r="XI4" s="50">
+      <c r="XF4" s="46"/>
+      <c r="XG4" s="46"/>
+      <c r="XH4" s="46"/>
+      <c r="XI4" s="46">
         <v>6</v>
       </c>
-      <c r="XJ4" s="50"/>
-      <c r="XK4" s="50"/>
-      <c r="XL4" s="50"/>
-      <c r="XM4" s="50">
+      <c r="XJ4" s="46"/>
+      <c r="XK4" s="46"/>
+      <c r="XL4" s="46"/>
+      <c r="XM4" s="46">
         <v>7</v>
       </c>
-      <c r="XN4" s="50"/>
-      <c r="XO4" s="50"/>
-      <c r="XP4" s="50"/>
-      <c r="XQ4" s="50">
+      <c r="XN4" s="46"/>
+      <c r="XO4" s="46"/>
+      <c r="XP4" s="46"/>
+      <c r="XQ4" s="46">
         <v>8</v>
       </c>
-      <c r="XR4" s="50"/>
-      <c r="XS4" s="50"/>
-      <c r="XT4" s="50"/>
-      <c r="XU4" s="48">
+      <c r="XR4" s="46"/>
+      <c r="XS4" s="46"/>
+      <c r="XT4" s="46"/>
+      <c r="XU4" s="47">
         <v>1</v>
       </c>
-      <c r="XV4" s="48"/>
-      <c r="XW4" s="48"/>
-      <c r="XX4" s="48"/>
-      <c r="XY4" s="48">
+      <c r="XV4" s="47"/>
+      <c r="XW4" s="47"/>
+      <c r="XX4" s="47"/>
+      <c r="XY4" s="47">
         <v>2</v>
       </c>
-      <c r="XZ4" s="48"/>
-      <c r="YA4" s="48"/>
-      <c r="YB4" s="48"/>
-      <c r="YC4" s="48">
+      <c r="XZ4" s="47"/>
+      <c r="YA4" s="47"/>
+      <c r="YB4" s="47"/>
+      <c r="YC4" s="47">
         <v>3</v>
       </c>
-      <c r="YD4" s="48"/>
-      <c r="YE4" s="48"/>
-      <c r="YF4" s="48"/>
-      <c r="YG4" s="48">
+      <c r="YD4" s="47"/>
+      <c r="YE4" s="47"/>
+      <c r="YF4" s="47"/>
+      <c r="YG4" s="47">
         <v>4</v>
       </c>
-      <c r="YH4" s="48"/>
-      <c r="YI4" s="48"/>
-      <c r="YJ4" s="48"/>
-      <c r="YK4" s="48">
+      <c r="YH4" s="47"/>
+      <c r="YI4" s="47"/>
+      <c r="YJ4" s="47"/>
+      <c r="YK4" s="47">
         <v>5</v>
       </c>
-      <c r="YL4" s="48"/>
-      <c r="YM4" s="48"/>
-      <c r="YN4" s="48"/>
-      <c r="YO4" s="48">
+      <c r="YL4" s="47"/>
+      <c r="YM4" s="47"/>
+      <c r="YN4" s="47"/>
+      <c r="YO4" s="47">
         <v>6</v>
       </c>
-      <c r="YP4" s="48"/>
-      <c r="YQ4" s="48"/>
-      <c r="YR4" s="48"/>
-      <c r="YS4" s="48">
+      <c r="YP4" s="47"/>
+      <c r="YQ4" s="47"/>
+      <c r="YR4" s="47"/>
+      <c r="YS4" s="47">
         <v>7</v>
       </c>
-      <c r="YT4" s="48"/>
-      <c r="YU4" s="48"/>
-      <c r="YV4" s="48"/>
-      <c r="YW4" s="50">
+      <c r="YT4" s="47"/>
+      <c r="YU4" s="47"/>
+      <c r="YV4" s="47"/>
+      <c r="YW4" s="46">
         <v>8</v>
       </c>
-      <c r="YX4" s="50"/>
-      <c r="YY4" s="50"/>
-      <c r="YZ4" s="50"/>
+      <c r="YX4" s="46"/>
+      <c r="YY4" s="46"/>
+      <c r="YZ4" s="46"/>
     </row>
     <row r="5" spans="1:676" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="51"/>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
+      <c r="A5" s="57"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
       <c r="E5" s="1" t="s">
         <v>26</v>
       </c>
@@ -27591,7 +27591,7 @@
         <v>2</v>
       </c>
       <c r="D37" s="41">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E37" s="14"/>
       <c r="F37" s="15"/>
@@ -28276,7 +28276,9 @@
       <c r="C38" s="41">
         <v>0.25</v>
       </c>
-      <c r="D38" s="11"/>
+      <c r="D38" s="41">
+        <v>0.25</v>
+      </c>
       <c r="E38" s="14"/>
       <c r="F38" s="15"/>
       <c r="G38" s="15"/>
@@ -28960,7 +28962,9 @@
       <c r="C39" s="41">
         <v>0.25</v>
       </c>
-      <c r="D39" s="11"/>
+      <c r="D39" s="41">
+        <v>0.25</v>
+      </c>
       <c r="E39" s="14"/>
       <c r="F39" s="15"/>
       <c r="G39" s="15"/>
@@ -29644,7 +29648,9 @@
       <c r="C40" s="41">
         <v>0.25</v>
       </c>
-      <c r="D40" s="11"/>
+      <c r="D40" s="41">
+        <v>0.25</v>
+      </c>
       <c r="E40" s="14"/>
       <c r="F40" s="15"/>
       <c r="G40" s="15"/>
@@ -30327,7 +30333,9 @@
       <c r="C41" s="41">
         <v>0.25</v>
       </c>
-      <c r="D41" s="11"/>
+      <c r="D41" s="41">
+        <v>0.25</v>
+      </c>
       <c r="E41" s="14"/>
       <c r="F41" s="15"/>
       <c r="G41" s="15"/>
@@ -31011,7 +31019,9 @@
       <c r="C42" s="41">
         <v>0.25</v>
       </c>
-      <c r="D42" s="11"/>
+      <c r="D42" s="41">
+        <v>0.25</v>
+      </c>
       <c r="E42" s="14"/>
       <c r="F42" s="15"/>
       <c r="G42" s="15"/>
@@ -53561,6 +53571,178 @@
     </row>
   </sheetData>
   <mergeCells count="196">
+    <mergeCell ref="QK3:RP3"/>
+    <mergeCell ref="RQ3:SV3"/>
+    <mergeCell ref="CC4:CF4"/>
+    <mergeCell ref="CG4:CJ4"/>
+    <mergeCell ref="FI3:GN3"/>
+    <mergeCell ref="GO3:HT3"/>
+    <mergeCell ref="HU3:IZ3"/>
+    <mergeCell ref="JA3:KF3"/>
+    <mergeCell ref="KG3:LL3"/>
+    <mergeCell ref="LM3:MR3"/>
+    <mergeCell ref="MS3:NX3"/>
+    <mergeCell ref="NY3:PD3"/>
+    <mergeCell ref="PE3:QJ3"/>
+    <mergeCell ref="ES4:EV4"/>
+    <mergeCell ref="EW4:EZ4"/>
+    <mergeCell ref="FA4:FD4"/>
+    <mergeCell ref="FE4:FH4"/>
+    <mergeCell ref="FI4:FL4"/>
+    <mergeCell ref="FM4:FP4"/>
+    <mergeCell ref="FQ4:FT4"/>
+    <mergeCell ref="FU4:FX4"/>
+    <mergeCell ref="FY4:GB4"/>
+    <mergeCell ref="GC4:GF4"/>
+    <mergeCell ref="GG4:GJ4"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:AJ3"/>
+    <mergeCell ref="AK3:BP3"/>
+    <mergeCell ref="BQ3:CV3"/>
+    <mergeCell ref="CW3:EB3"/>
+    <mergeCell ref="EC3:FH3"/>
+    <mergeCell ref="CK4:CN4"/>
+    <mergeCell ref="CO4:CR4"/>
+    <mergeCell ref="CS4:CV4"/>
+    <mergeCell ref="CW4:CZ4"/>
+    <mergeCell ref="DA4:DD4"/>
+    <mergeCell ref="DE4:DH4"/>
+    <mergeCell ref="DI4:DL4"/>
+    <mergeCell ref="DM4:DP4"/>
+    <mergeCell ref="DQ4:DT4"/>
+    <mergeCell ref="DU4:DX4"/>
+    <mergeCell ref="DY4:EB4"/>
+    <mergeCell ref="EC4:EF4"/>
+    <mergeCell ref="EG4:EJ4"/>
+    <mergeCell ref="EK4:EN4"/>
+    <mergeCell ref="EO4:ER4"/>
+    <mergeCell ref="SW3:UB3"/>
+    <mergeCell ref="UC3:VH3"/>
+    <mergeCell ref="VI3:WN3"/>
+    <mergeCell ref="WO3:XT3"/>
+    <mergeCell ref="XU3:YZ3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:L4"/>
+    <mergeCell ref="M4:P4"/>
+    <mergeCell ref="Q4:T4"/>
+    <mergeCell ref="U4:X4"/>
+    <mergeCell ref="Y4:AB4"/>
+    <mergeCell ref="AC4:AF4"/>
+    <mergeCell ref="AG4:AJ4"/>
+    <mergeCell ref="AK4:AN4"/>
+    <mergeCell ref="AO4:AR4"/>
+    <mergeCell ref="AS4:AV4"/>
+    <mergeCell ref="AW4:AZ4"/>
+    <mergeCell ref="BA4:BD4"/>
+    <mergeCell ref="BE4:BH4"/>
+    <mergeCell ref="BI4:BL4"/>
+    <mergeCell ref="BM4:BP4"/>
+    <mergeCell ref="BQ4:BT4"/>
+    <mergeCell ref="BU4:BX4"/>
+    <mergeCell ref="BY4:CB4"/>
+    <mergeCell ref="GK4:GN4"/>
+    <mergeCell ref="GO4:GR4"/>
+    <mergeCell ref="GS4:GV4"/>
+    <mergeCell ref="GW4:GZ4"/>
+    <mergeCell ref="HA4:HD4"/>
+    <mergeCell ref="HE4:HH4"/>
+    <mergeCell ref="HI4:HL4"/>
+    <mergeCell ref="HM4:HP4"/>
+    <mergeCell ref="HQ4:HT4"/>
+    <mergeCell ref="HU4:HX4"/>
+    <mergeCell ref="HY4:IB4"/>
+    <mergeCell ref="IC4:IF4"/>
+    <mergeCell ref="IG4:IJ4"/>
+    <mergeCell ref="IK4:IN4"/>
+    <mergeCell ref="IO4:IR4"/>
+    <mergeCell ref="IS4:IV4"/>
+    <mergeCell ref="IW4:IZ4"/>
+    <mergeCell ref="JA4:JD4"/>
+    <mergeCell ref="JE4:JH4"/>
+    <mergeCell ref="JI4:JL4"/>
+    <mergeCell ref="JM4:JP4"/>
+    <mergeCell ref="JQ4:JT4"/>
+    <mergeCell ref="JU4:JX4"/>
+    <mergeCell ref="JY4:KB4"/>
+    <mergeCell ref="KC4:KF4"/>
+    <mergeCell ref="KG4:KJ4"/>
+    <mergeCell ref="KK4:KN4"/>
+    <mergeCell ref="KO4:KR4"/>
+    <mergeCell ref="KS4:KV4"/>
+    <mergeCell ref="KW4:KZ4"/>
+    <mergeCell ref="LA4:LD4"/>
+    <mergeCell ref="LE4:LH4"/>
+    <mergeCell ref="LI4:LL4"/>
+    <mergeCell ref="LM4:LP4"/>
+    <mergeCell ref="LQ4:LT4"/>
+    <mergeCell ref="LU4:LX4"/>
+    <mergeCell ref="LY4:MB4"/>
+    <mergeCell ref="MC4:MF4"/>
+    <mergeCell ref="MG4:MJ4"/>
+    <mergeCell ref="MK4:MN4"/>
+    <mergeCell ref="MO4:MR4"/>
+    <mergeCell ref="MS4:MV4"/>
+    <mergeCell ref="MW4:MZ4"/>
+    <mergeCell ref="NA4:ND4"/>
+    <mergeCell ref="NE4:NH4"/>
+    <mergeCell ref="NI4:NL4"/>
+    <mergeCell ref="NM4:NP4"/>
+    <mergeCell ref="NQ4:NT4"/>
+    <mergeCell ref="NU4:NX4"/>
+    <mergeCell ref="NY4:OB4"/>
+    <mergeCell ref="OC4:OF4"/>
+    <mergeCell ref="OG4:OJ4"/>
+    <mergeCell ref="OK4:ON4"/>
+    <mergeCell ref="OO4:OR4"/>
+    <mergeCell ref="OS4:OV4"/>
+    <mergeCell ref="OW4:OZ4"/>
+    <mergeCell ref="PA4:PD4"/>
+    <mergeCell ref="PE4:PH4"/>
+    <mergeCell ref="PI4:PL4"/>
+    <mergeCell ref="PM4:PP4"/>
+    <mergeCell ref="PQ4:PT4"/>
+    <mergeCell ref="PU4:PX4"/>
+    <mergeCell ref="PY4:QB4"/>
+    <mergeCell ref="QC4:QF4"/>
+    <mergeCell ref="QG4:QJ4"/>
+    <mergeCell ref="QK4:QN4"/>
+    <mergeCell ref="QO4:QR4"/>
+    <mergeCell ref="QS4:QV4"/>
+    <mergeCell ref="QW4:QZ4"/>
+    <mergeCell ref="RA4:RD4"/>
+    <mergeCell ref="RE4:RH4"/>
+    <mergeCell ref="RI4:RL4"/>
+    <mergeCell ref="RM4:RP4"/>
+    <mergeCell ref="RQ4:RT4"/>
+    <mergeCell ref="RU4:RX4"/>
+    <mergeCell ref="RY4:SB4"/>
+    <mergeCell ref="SC4:SF4"/>
+    <mergeCell ref="SG4:SJ4"/>
+    <mergeCell ref="SK4:SN4"/>
+    <mergeCell ref="SO4:SR4"/>
+    <mergeCell ref="SS4:SV4"/>
+    <mergeCell ref="SW4:SZ4"/>
+    <mergeCell ref="TA4:TD4"/>
+    <mergeCell ref="TE4:TH4"/>
+    <mergeCell ref="TI4:TL4"/>
+    <mergeCell ref="TM4:TP4"/>
+    <mergeCell ref="TQ4:TT4"/>
+    <mergeCell ref="TU4:TX4"/>
+    <mergeCell ref="TY4:UB4"/>
+    <mergeCell ref="UC4:UF4"/>
+    <mergeCell ref="WW4:WZ4"/>
+    <mergeCell ref="UG4:UJ4"/>
+    <mergeCell ref="UK4:UN4"/>
+    <mergeCell ref="UO4:UR4"/>
+    <mergeCell ref="US4:UV4"/>
+    <mergeCell ref="UW4:UZ4"/>
+    <mergeCell ref="VA4:VD4"/>
+    <mergeCell ref="VE4:VH4"/>
+    <mergeCell ref="VI4:VL4"/>
+    <mergeCell ref="VM4:VP4"/>
     <mergeCell ref="XA4:XD4"/>
     <mergeCell ref="VQ4:VT4"/>
     <mergeCell ref="YO4:YR4"/>
@@ -53585,178 +53767,6 @@
     <mergeCell ref="WK4:WN4"/>
     <mergeCell ref="WO4:WR4"/>
     <mergeCell ref="WS4:WV4"/>
-    <mergeCell ref="WW4:WZ4"/>
-    <mergeCell ref="UG4:UJ4"/>
-    <mergeCell ref="UK4:UN4"/>
-    <mergeCell ref="UO4:UR4"/>
-    <mergeCell ref="US4:UV4"/>
-    <mergeCell ref="UW4:UZ4"/>
-    <mergeCell ref="VA4:VD4"/>
-    <mergeCell ref="VE4:VH4"/>
-    <mergeCell ref="VI4:VL4"/>
-    <mergeCell ref="VM4:VP4"/>
-    <mergeCell ref="SW4:SZ4"/>
-    <mergeCell ref="TA4:TD4"/>
-    <mergeCell ref="TE4:TH4"/>
-    <mergeCell ref="TI4:TL4"/>
-    <mergeCell ref="TM4:TP4"/>
-    <mergeCell ref="TQ4:TT4"/>
-    <mergeCell ref="TU4:TX4"/>
-    <mergeCell ref="TY4:UB4"/>
-    <mergeCell ref="UC4:UF4"/>
-    <mergeCell ref="RM4:RP4"/>
-    <mergeCell ref="RQ4:RT4"/>
-    <mergeCell ref="RU4:RX4"/>
-    <mergeCell ref="RY4:SB4"/>
-    <mergeCell ref="SC4:SF4"/>
-    <mergeCell ref="SG4:SJ4"/>
-    <mergeCell ref="SK4:SN4"/>
-    <mergeCell ref="SO4:SR4"/>
-    <mergeCell ref="SS4:SV4"/>
-    <mergeCell ref="QC4:QF4"/>
-    <mergeCell ref="QG4:QJ4"/>
-    <mergeCell ref="QK4:QN4"/>
-    <mergeCell ref="QO4:QR4"/>
-    <mergeCell ref="QS4:QV4"/>
-    <mergeCell ref="QW4:QZ4"/>
-    <mergeCell ref="RA4:RD4"/>
-    <mergeCell ref="RE4:RH4"/>
-    <mergeCell ref="RI4:RL4"/>
-    <mergeCell ref="OS4:OV4"/>
-    <mergeCell ref="OW4:OZ4"/>
-    <mergeCell ref="PA4:PD4"/>
-    <mergeCell ref="PE4:PH4"/>
-    <mergeCell ref="PI4:PL4"/>
-    <mergeCell ref="PM4:PP4"/>
-    <mergeCell ref="PQ4:PT4"/>
-    <mergeCell ref="PU4:PX4"/>
-    <mergeCell ref="PY4:QB4"/>
-    <mergeCell ref="NI4:NL4"/>
-    <mergeCell ref="NM4:NP4"/>
-    <mergeCell ref="NQ4:NT4"/>
-    <mergeCell ref="NU4:NX4"/>
-    <mergeCell ref="NY4:OB4"/>
-    <mergeCell ref="OC4:OF4"/>
-    <mergeCell ref="OG4:OJ4"/>
-    <mergeCell ref="OK4:ON4"/>
-    <mergeCell ref="OO4:OR4"/>
-    <mergeCell ref="LY4:MB4"/>
-    <mergeCell ref="MC4:MF4"/>
-    <mergeCell ref="MG4:MJ4"/>
-    <mergeCell ref="MK4:MN4"/>
-    <mergeCell ref="MO4:MR4"/>
-    <mergeCell ref="MS4:MV4"/>
-    <mergeCell ref="MW4:MZ4"/>
-    <mergeCell ref="NA4:ND4"/>
-    <mergeCell ref="NE4:NH4"/>
-    <mergeCell ref="KO4:KR4"/>
-    <mergeCell ref="KS4:KV4"/>
-    <mergeCell ref="KW4:KZ4"/>
-    <mergeCell ref="LA4:LD4"/>
-    <mergeCell ref="LE4:LH4"/>
-    <mergeCell ref="LI4:LL4"/>
-    <mergeCell ref="LM4:LP4"/>
-    <mergeCell ref="LQ4:LT4"/>
-    <mergeCell ref="LU4:LX4"/>
-    <mergeCell ref="JE4:JH4"/>
-    <mergeCell ref="JI4:JL4"/>
-    <mergeCell ref="JM4:JP4"/>
-    <mergeCell ref="JQ4:JT4"/>
-    <mergeCell ref="JU4:JX4"/>
-    <mergeCell ref="JY4:KB4"/>
-    <mergeCell ref="KC4:KF4"/>
-    <mergeCell ref="KG4:KJ4"/>
-    <mergeCell ref="KK4:KN4"/>
-    <mergeCell ref="HU4:HX4"/>
-    <mergeCell ref="HY4:IB4"/>
-    <mergeCell ref="IC4:IF4"/>
-    <mergeCell ref="IG4:IJ4"/>
-    <mergeCell ref="IK4:IN4"/>
-    <mergeCell ref="IO4:IR4"/>
-    <mergeCell ref="IS4:IV4"/>
-    <mergeCell ref="IW4:IZ4"/>
-    <mergeCell ref="JA4:JD4"/>
-    <mergeCell ref="GK4:GN4"/>
-    <mergeCell ref="GO4:GR4"/>
-    <mergeCell ref="GS4:GV4"/>
-    <mergeCell ref="GW4:GZ4"/>
-    <mergeCell ref="HA4:HD4"/>
-    <mergeCell ref="HE4:HH4"/>
-    <mergeCell ref="HI4:HL4"/>
-    <mergeCell ref="HM4:HP4"/>
-    <mergeCell ref="HQ4:HT4"/>
-    <mergeCell ref="SW3:UB3"/>
-    <mergeCell ref="UC3:VH3"/>
-    <mergeCell ref="VI3:WN3"/>
-    <mergeCell ref="WO3:XT3"/>
-    <mergeCell ref="XU3:YZ3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:L4"/>
-    <mergeCell ref="M4:P4"/>
-    <mergeCell ref="Q4:T4"/>
-    <mergeCell ref="U4:X4"/>
-    <mergeCell ref="Y4:AB4"/>
-    <mergeCell ref="AC4:AF4"/>
-    <mergeCell ref="AG4:AJ4"/>
-    <mergeCell ref="AK4:AN4"/>
-    <mergeCell ref="AO4:AR4"/>
-    <mergeCell ref="AS4:AV4"/>
-    <mergeCell ref="AW4:AZ4"/>
-    <mergeCell ref="BA4:BD4"/>
-    <mergeCell ref="BE4:BH4"/>
-    <mergeCell ref="BI4:BL4"/>
-    <mergeCell ref="BM4:BP4"/>
-    <mergeCell ref="BQ4:BT4"/>
-    <mergeCell ref="BU4:BX4"/>
-    <mergeCell ref="BY4:CB4"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:AJ3"/>
-    <mergeCell ref="AK3:BP3"/>
-    <mergeCell ref="BQ3:CV3"/>
-    <mergeCell ref="CW3:EB3"/>
-    <mergeCell ref="EC3:FH3"/>
-    <mergeCell ref="CK4:CN4"/>
-    <mergeCell ref="CO4:CR4"/>
-    <mergeCell ref="CS4:CV4"/>
-    <mergeCell ref="CW4:CZ4"/>
-    <mergeCell ref="DA4:DD4"/>
-    <mergeCell ref="DE4:DH4"/>
-    <mergeCell ref="DI4:DL4"/>
-    <mergeCell ref="DM4:DP4"/>
-    <mergeCell ref="DQ4:DT4"/>
-    <mergeCell ref="DU4:DX4"/>
-    <mergeCell ref="DY4:EB4"/>
-    <mergeCell ref="EC4:EF4"/>
-    <mergeCell ref="EG4:EJ4"/>
-    <mergeCell ref="EK4:EN4"/>
-    <mergeCell ref="EO4:ER4"/>
-    <mergeCell ref="QK3:RP3"/>
-    <mergeCell ref="RQ3:SV3"/>
-    <mergeCell ref="CC4:CF4"/>
-    <mergeCell ref="CG4:CJ4"/>
-    <mergeCell ref="FI3:GN3"/>
-    <mergeCell ref="GO3:HT3"/>
-    <mergeCell ref="HU3:IZ3"/>
-    <mergeCell ref="JA3:KF3"/>
-    <mergeCell ref="KG3:LL3"/>
-    <mergeCell ref="LM3:MR3"/>
-    <mergeCell ref="MS3:NX3"/>
-    <mergeCell ref="NY3:PD3"/>
-    <mergeCell ref="PE3:QJ3"/>
-    <mergeCell ref="ES4:EV4"/>
-    <mergeCell ref="EW4:EZ4"/>
-    <mergeCell ref="FA4:FD4"/>
-    <mergeCell ref="FE4:FH4"/>
-    <mergeCell ref="FI4:FL4"/>
-    <mergeCell ref="FM4:FP4"/>
-    <mergeCell ref="FQ4:FT4"/>
-    <mergeCell ref="FU4:FX4"/>
-    <mergeCell ref="FY4:GB4"/>
-    <mergeCell ref="GC4:GF4"/>
-    <mergeCell ref="GG4:GJ4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="41" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
